--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>1012885</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>29.3600006103516</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>27.4699993133545</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>29.1200008392334</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>28.1700000762939</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>517518</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>28.6299991607666</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>28.2000007629395</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>28.3999996185303</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>491177</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>28.9500007629395</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>27.9500007629395</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>28.5100002288818</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>476011</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>29.2199993133545</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>28.7299995422363</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>28.7000007629395</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>645479</v>
+        <v>573811</v>
       </c>
       <c r="C2715" t="n">
-        <v>29.6399993896484</v>
+        <v>29.0400009155273</v>
       </c>
       <c r="D2715" t="n">
-        <v>28.1599998474121</v>
+        <v>28.3199996948242</v>
       </c>
       <c r="E2715" t="n">
-        <v>28.9099998474121</v>
+        <v>28.3199996948242</v>
       </c>
       <c r="F2715" t="n">
-        <v>29.5200004577637</v>
+        <v>29</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>636291</v>
+        <v>645479</v>
       </c>
       <c r="C2716" t="n">
-        <v>29.2600002288818</v>
+        <v>29.6399993896484</v>
       </c>
       <c r="D2716" t="n">
-        <v>28.5799999237061</v>
+        <v>28.1599998474121</v>
       </c>
       <c r="E2716" t="n">
-        <v>29.0599994659424</v>
+        <v>28.9099998474121</v>
       </c>
       <c r="F2716" t="n">
-        <v>28.7999992370605</v>
+        <v>29.5200004577637</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>879989</v>
+        <v>636291</v>
       </c>
       <c r="C2717" t="n">
-        <v>29.0400009155273</v>
+        <v>29.2600002288818</v>
       </c>
       <c r="D2717" t="n">
-        <v>26.0400009155273</v>
+        <v>28.5799999237061</v>
       </c>
       <c r="E2717" t="n">
-        <v>29.0400009155273</v>
+        <v>29.0599994659424</v>
       </c>
       <c r="F2717" t="n">
-        <v>28.0100002288818</v>
+        <v>28.7999992370605</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>1489825</v>
+        <v>879989</v>
       </c>
       <c r="C2718" t="n">
-        <v>30.3299999237061</v>
+        <v>29.0400009155273</v>
       </c>
       <c r="D2718" t="n">
-        <v>28.5799999237061</v>
+        <v>26.0400009155273</v>
       </c>
       <c r="E2718" t="n">
-        <v>28.6000003814697</v>
+        <v>29.0400009155273</v>
       </c>
       <c r="F2718" t="n">
-        <v>29.1000003814697</v>
+        <v>28.0100002288818</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>1012885</v>
+        <v>1489825</v>
       </c>
       <c r="C2719" t="n">
-        <v>29.3600006103516</v>
+        <v>30.3299999237061</v>
       </c>
       <c r="D2719" t="n">
-        <v>27.4699993133545</v>
+        <v>28.5799999237061</v>
       </c>
       <c r="E2719" t="n">
-        <v>29.1200008392334</v>
+        <v>28.6000003814697</v>
       </c>
       <c r="F2719" t="n">
-        <v>28.1700000762939</v>
+        <v>29.1000003814697</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>517518</v>
+        <v>1012885</v>
       </c>
       <c r="C2720" t="n">
-        <v>28.6299991607666</v>
+        <v>29.3600006103516</v>
       </c>
       <c r="D2720" t="n">
-        <v>28</v>
+        <v>27.4699993133545</v>
       </c>
       <c r="E2720" t="n">
-        <v>28.2000007629395</v>
+        <v>29.1200008392334</v>
       </c>
       <c r="F2720" t="n">
-        <v>28.3999996185303</v>
+        <v>28.1700000762939</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>491177</v>
+        <v>517518</v>
       </c>
       <c r="C2721" t="n">
-        <v>28.9500007629395</v>
+        <v>28.6299991607666</v>
       </c>
       <c r="D2721" t="n">
-        <v>27.9500007629395</v>
+        <v>28</v>
       </c>
       <c r="E2721" t="n">
-        <v>28.5100002288818</v>
+        <v>28.2000007629395</v>
       </c>
       <c r="F2721" t="n">
-        <v>28.5</v>
+        <v>28.3999996185303</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>476011</v>
+        <v>491177</v>
       </c>
       <c r="C2722" t="n">
-        <v>29.2199993133545</v>
+        <v>28.9500007629395</v>
       </c>
       <c r="D2722" t="n">
+        <v>27.9500007629395</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>28.5100002288818</v>
+      </c>
+      <c r="F2722" t="n">
         <v>28.5</v>
       </c>
-      <c r="E2722" t="n">
-        <v>28.7299995422363</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>28.7000007629395</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>721460</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>29.2700004577637</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>28.5300006866455</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>29.1399993896484</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>28.8099994659424</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.75</v>
       </c>
       <c r="G2" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>9.75</v>
       </c>
       <c r="G3" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>9.75</v>
       </c>
       <c r="G4" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G6" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G7" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G8" t="n">
-        <v>8.9108772277832</v>
+        <v>8.91087627410889</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.9108772277832</v>
+        <v>8.91087627410889</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.75</v>
       </c>
       <c r="G10" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G11" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>9.75</v>
       </c>
       <c r="G12" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>9.75</v>
       </c>
       <c r="G13" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>9.75</v>
       </c>
       <c r="G15" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.75</v>
       </c>
       <c r="G16" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G17" t="n">
-        <v>8.64958572387695</v>
+        <v>8.64958667755127</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G19" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.86582565307617</v>
+        <v>8.86582660675049</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G21" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G24" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.75</v>
       </c>
       <c r="G26" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G27" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G29" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G30" t="n">
-        <v>8.65859603881836</v>
+        <v>8.65859508514404</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G31" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G32" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G35" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.91988468170166</v>
+        <v>8.91988563537598</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G43" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G44" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G45" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G49" t="n">
-        <v>8.91988468170166</v>
+        <v>8.91988563537598</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G50" t="n">
-        <v>8.91988468170166</v>
+        <v>8.91988563537598</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G51" t="n">
-        <v>8.91988468170166</v>
+        <v>8.91988563537598</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G52" t="n">
-        <v>8.91988468170166</v>
+        <v>8.91988563537598</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.75</v>
       </c>
       <c r="G53" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G54" t="n">
-        <v>8.86582565307617</v>
+        <v>8.86582660675049</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G64" t="n">
-        <v>8.65859603881836</v>
+        <v>8.65859508514404</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G66" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G71" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G77" t="n">
-        <v>8.8387975692749</v>
+        <v>8.83879852294922</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.75</v>
       </c>
       <c r="G79" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.75</v>
       </c>
       <c r="G81" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.75</v>
       </c>
       <c r="G82" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G84" t="n">
-        <v>8.91988468170166</v>
+        <v>8.91988563537598</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G85" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G88" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G90" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>8.87483787536621</v>
+        <v>8.87483596801758</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>8.91988468170166</v>
+        <v>8.91988563537598</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>8.86582565307617</v>
+        <v>8.86582660675049</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.75</v>
       </c>
       <c r="G100" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G102" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G105" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G106" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G107" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G108" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.75</v>
       </c>
       <c r="G109" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.75</v>
       </c>
       <c r="G110" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.75</v>
       </c>
       <c r="G111" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.75</v>
       </c>
       <c r="G112" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.75</v>
       </c>
       <c r="G113" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G115" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>8.71716213226318</v>
+        <v>8.71716117858887</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>8.71716213226318</v>
+        <v>8.71716117858887</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.75</v>
       </c>
       <c r="G123" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.75</v>
       </c>
       <c r="G124" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.75</v>
       </c>
       <c r="G125" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.75</v>
       </c>
       <c r="G126" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.75</v>
       </c>
       <c r="G127" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.75</v>
       </c>
       <c r="G128" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.75</v>
       </c>
       <c r="G129" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G130" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G132" t="n">
-        <v>8.76671504974365</v>
+        <v>8.76671600341797</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.75</v>
       </c>
       <c r="G133" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.75</v>
       </c>
       <c r="G134" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.75</v>
       </c>
       <c r="G135" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.75</v>
       </c>
       <c r="G136" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.75</v>
       </c>
       <c r="G137" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.75</v>
       </c>
       <c r="G138" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G139" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G140" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G142" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.75</v>
       </c>
       <c r="G143" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.75</v>
       </c>
       <c r="G144" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.75</v>
       </c>
       <c r="G145" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.75</v>
       </c>
       <c r="G146" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G149" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G150" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>8.82077789306641</v>
+        <v>8.82077693939209</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>8.82077789306641</v>
+        <v>8.82077693939209</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>8.64958572387695</v>
+        <v>8.64958667755127</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G160" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G163" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.75</v>
       </c>
       <c r="G165" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G166" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G173" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G175" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.75</v>
       </c>
       <c r="G177" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.75</v>
       </c>
       <c r="G178" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.75</v>
       </c>
       <c r="G186" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G191" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.75</v>
       </c>
       <c r="G194" t="n">
-        <v>8.78473567962646</v>
+        <v>8.78473472595215</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>8.8297872543335</v>
+        <v>8.82978630065918</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.90499973297119</v>
       </c>
       <c r="G196" t="n">
-        <v>8.924391746521</v>
+        <v>8.92439079284668</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G197" t="n">
-        <v>8.8387975692749</v>
+        <v>8.83879852294922</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G198" t="n">
-        <v>8.8387975692749</v>
+        <v>8.83879852294922</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G199" t="n">
-        <v>8.8387975692749</v>
+        <v>8.83879852294922</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>9.05503559112549</v>
+        <v>9.0550365447998</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.05503559112549</v>
+        <v>9.0550365447998</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.85499954223633</v>
       </c>
       <c r="G203" t="n">
-        <v>8.87934017181396</v>
+        <v>8.87934112548828</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>9.190185546875</v>
+        <v>9.19018459320068</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>9.1451358795166</v>
+        <v>9.14513492584229</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G210" t="n">
-        <v>9.190185546875</v>
+        <v>9.19018459320068</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>9.1451358795166</v>
+        <v>9.14513492584229</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G212" t="n">
-        <v>9.22622489929199</v>
+        <v>9.22622585296631</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>9.32533550262451</v>
+        <v>9.3253345489502</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G215" t="n">
-        <v>9.36137580871582</v>
+        <v>9.36137676239014</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G216" t="n">
-        <v>9.36137580871582</v>
+        <v>9.36137676239014</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.25</v>
       </c>
       <c r="G217" t="n">
-        <v>9.2352352142334</v>
+        <v>9.23523426055908</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G219" t="n">
-        <v>9.22622489929199</v>
+        <v>9.22622585296631</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>9.190185546875</v>
+        <v>9.19018459320068</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>9.190185546875</v>
+        <v>9.19018459320068</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>9.37038516998291</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G224" t="n">
-        <v>9.44246482849121</v>
+        <v>9.44246387481689</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.5</v>
       </c>
       <c r="G225" t="n">
-        <v>9.46048450469971</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G227" t="n">
-        <v>9.38840579986572</v>
+        <v>9.38840675354004</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.46048450469971</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.5</v>
       </c>
       <c r="G229" t="n">
-        <v>9.46048450469971</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>9.44246482849121</v>
+        <v>9.44246387481689</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G231" t="n">
-        <v>9.44246482849121</v>
+        <v>9.44246387481689</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.5</v>
       </c>
       <c r="G232" t="n">
-        <v>9.46048450469971</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>9.37038516998291</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>9.37038516998291</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>9.37038516998291</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>9.37038516998291</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.5</v>
       </c>
       <c r="G237" t="n">
-        <v>9.46048450469971</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>9.37038516998291</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>9.37038516998291</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>9.37038516998291</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>9.37038516998291</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.5</v>
       </c>
       <c r="G242" t="n">
-        <v>9.46048450469971</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G243" t="n">
-        <v>9.29830455780029</v>
+        <v>9.29830551147461</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G244" t="n">
-        <v>9.29830455780029</v>
+        <v>9.29830551147461</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.5</v>
       </c>
       <c r="G245" t="n">
-        <v>9.46048450469971</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.5</v>
       </c>
       <c r="G246" t="n">
-        <v>9.46048450469971</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G250" t="n">
-        <v>9.57761383056641</v>
+        <v>9.57761478424072</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>9.73078441619873</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>9.52355480194092</v>
+        <v>9.52355575561523</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G260" t="n">
-        <v>9.62266445159912</v>
+        <v>9.62266635894775</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.75</v>
       </c>
       <c r="G261" t="n">
-        <v>9.68573570251465</v>
+        <v>9.68573474884033</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.75</v>
       </c>
       <c r="G262" t="n">
-        <v>9.68573570251465</v>
+        <v>9.68573474884033</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>9.55959510803223</v>
+        <v>9.55959415435791</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G264" t="n">
-        <v>9.51454639434814</v>
+        <v>9.51454544067383</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G265" t="n">
-        <v>9.62266445159912</v>
+        <v>9.62266635894775</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.75</v>
       </c>
       <c r="G267" t="n">
-        <v>9.68573570251465</v>
+        <v>9.68573474884033</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G270" t="n">
-        <v>9.73078441619873</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G272" t="n">
-        <v>9.73078441619873</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G273" t="n">
-        <v>9.69474411010742</v>
+        <v>9.69474601745605</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G274" t="n">
-        <v>9.79385471343994</v>
+        <v>9.79385375976562</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G283" t="n">
-        <v>9.73078441619873</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G284" t="n">
-        <v>9.71276473999023</v>
+        <v>9.71276378631592</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.75</v>
       </c>
       <c r="G285" t="n">
-        <v>9.68573570251465</v>
+        <v>9.68573474884033</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11</v>
       </c>
       <c r="G292" t="n">
-        <v>9.91098499298096</v>
+        <v>9.91098403930664</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11</v>
       </c>
       <c r="G293" t="n">
-        <v>9.91098499298096</v>
+        <v>9.91098403930664</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G294" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>9.86593341827393</v>
+        <v>9.86593437194824</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G300" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G303" t="n">
-        <v>9.79385471343994</v>
+        <v>9.79385375976562</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G304" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>11</v>
       </c>
       <c r="G306" t="n">
-        <v>9.91098499298096</v>
+        <v>9.91098403930664</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G307" t="n">
-        <v>9.73078441619873</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G308" t="n">
-        <v>9.80286312103271</v>
+        <v>9.80286502838135</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G309" t="n">
-        <v>9.79385471343994</v>
+        <v>9.79385375976562</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G313" t="n">
-        <v>9.82989501953125</v>
+        <v>9.82989406585693</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G314" t="n">
-        <v>9.80286312103271</v>
+        <v>9.80286502838135</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G316" t="n">
-        <v>9.80286312103271</v>
+        <v>9.80286502838135</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G317" t="n">
-        <v>9.86593341827393</v>
+        <v>9.86593437194824</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>9.86593341827393</v>
+        <v>9.86593437194824</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G319" t="n">
-        <v>9.93801403045654</v>
+        <v>9.93801498413086</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>10.0010862350464</v>
+        <v>10.0010843276978</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>10.2803936004639</v>
+        <v>10.2803926467896</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G324" t="n">
-        <v>10.5146541595459</v>
+        <v>10.5146532058716</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G326" t="n">
-        <v>11.6589212417603</v>
+        <v>11.6589202880859</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G330" t="n">
-        <v>12.1724901199341</v>
+        <v>12.1724910736084</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>11.9202108383179</v>
+        <v>11.9202098846436</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>12.0283317565918</v>
+        <v>12.0283327102661</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G333" t="n">
-        <v>12.0553607940674</v>
+        <v>12.0553617477417</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G337" t="n">
-        <v>11.7219915390015</v>
+        <v>11.7219924926758</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G339" t="n">
-        <v>11.6769418716431</v>
+        <v>11.6769409179688</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>11.6769418716431</v>
+        <v>11.6769409179688</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G341" t="n">
-        <v>11.667932510376</v>
+        <v>11.6679306030273</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G342" t="n">
-        <v>11.6589212417603</v>
+        <v>11.6589202880859</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>11.8481311798096</v>
+        <v>11.8481302261353</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>12.2986297607422</v>
+        <v>12.2986307144165</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>12.2986297607422</v>
+        <v>12.2986307144165</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G348" t="n">
-        <v>12.4157600402832</v>
+        <v>12.4157609939575</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G349" t="n">
-        <v>12.5689296722412</v>
+        <v>12.5689306259155</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>12.2085304260254</v>
+        <v>12.2085313796997</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G352" t="n">
-        <v>12.1364507675171</v>
+        <v>12.1364517211914</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G355" t="n">
-        <v>12.316650390625</v>
+        <v>12.3166513442993</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G356" t="n">
-        <v>12.0823917388916</v>
+        <v>12.0823907852173</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>12.2085304260254</v>
+        <v>12.2085313796997</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G359" t="n">
-        <v>12.1724901199341</v>
+        <v>12.1724910736084</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>11.893180847168</v>
+        <v>11.8931798934937</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>11.7940711975098</v>
+        <v>11.7940721511841</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G369" t="n">
-        <v>11.6318922042847</v>
+        <v>11.631893157959</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G370" t="n">
-        <v>11.6048622131348</v>
+        <v>11.6048631668091</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5688219070435</v>
+        <v>11.5688228607178</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G375" t="n">
-        <v>11.9742698669434</v>
+        <v>11.9742708206177</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G378" t="n">
-        <v>11.8661518096924</v>
+        <v>11.8661527633667</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>11.8481311798096</v>
+        <v>11.8481302261353</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>11.893180847168</v>
+        <v>11.8931798934937</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G384" t="n">
-        <v>11.893180847168</v>
+        <v>11.8931798934937</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G385" t="n">
-        <v>11.8120908737183</v>
+        <v>11.8120899200439</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G387" t="n">
-        <v>11.6859521865845</v>
+        <v>11.6859512329102</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G388" t="n">
-        <v>11.6589212417603</v>
+        <v>11.6589202880859</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G389" t="n">
-        <v>11.5147609710693</v>
+        <v>11.5147619247437</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>11.5778331756592</v>
+        <v>11.5778322219849</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G391" t="n">
-        <v>11.5598115921021</v>
+        <v>11.5598125457764</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G393" t="n">
-        <v>11.6138725280762</v>
+        <v>11.6138715744019</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>11.5778331756592</v>
+        <v>11.5778322219849</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G395" t="n">
-        <v>11.6048622131348</v>
+        <v>11.6048631668091</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G396" t="n">
-        <v>11.6138725280762</v>
+        <v>11.6138715744019</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G397" t="n">
-        <v>11.4787216186523</v>
+        <v>11.478720664978</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.4787216186523</v>
+        <v>11.478720664978</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G399" t="n">
-        <v>11.4066400527954</v>
+        <v>11.406641960144</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G402" t="n">
-        <v>11.217432975769</v>
+        <v>11.2174320220947</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G403" t="n">
-        <v>11.1453523635864</v>
+        <v>11.1453514099121</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>11.217432975769</v>
+        <v>11.2174320220947</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G406" t="n">
-        <v>11.2444610595703</v>
+        <v>11.2444620132446</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>11.5327825546265</v>
+        <v>11.5327835083008</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>11.5778331756592</v>
+        <v>11.5778322219849</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G409" t="n">
-        <v>11.5688219070435</v>
+        <v>11.5688228607178</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>11.5327825546265</v>
+        <v>11.5327835083008</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>11.5778331756592</v>
+        <v>11.5778322219849</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G412" t="n">
-        <v>11.6769418716431</v>
+        <v>11.6769409179688</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G415" t="n">
-        <v>11.3615922927856</v>
+        <v>11.3615913391113</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>11.5778331756592</v>
+        <v>11.5778322219849</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>11.3976316452026</v>
+        <v>11.397632598877</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G420" t="n">
-        <v>11.4516925811768</v>
+        <v>11.4516906738281</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>11.5778331756592</v>
+        <v>11.5778322219849</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>11.550802230835</v>
+        <v>11.5508003234863</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G423" t="n">
-        <v>11.550802230835</v>
+        <v>11.5508003234863</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G427" t="n">
-        <v>11.4697122573853</v>
+        <v>11.4697113037109</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>12.75</v>
       </c>
       <c r="G429" t="n">
-        <v>11.4877319335938</v>
+        <v>11.4877328872681</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G431" t="n">
-        <v>11.4246625900269</v>
+        <v>11.4246616363525</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>11.5778331756592</v>
+        <v>11.5778322219849</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G434" t="n">
-        <v>11.8120908737183</v>
+        <v>11.8120899200439</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G436" t="n">
-        <v>12.2085304260254</v>
+        <v>12.2085313796997</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>12.0283317565918</v>
+        <v>12.0283327102661</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G441" t="n">
-        <v>11.9562501907349</v>
+        <v>11.9562520980835</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G442" t="n">
-        <v>12.2896213531494</v>
+        <v>12.2896203994751</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G443" t="n">
-        <v>12.1364507675171</v>
+        <v>12.1364517211914</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>13.5</v>
       </c>
       <c r="G445" t="n">
-        <v>12.163480758667</v>
+        <v>12.1634817123413</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G446" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G449" t="n">
-        <v>12.2445697784424</v>
+        <v>12.2445707321167</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>12.2085304260254</v>
+        <v>12.2085313796997</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>12.2085304260254</v>
+        <v>12.2085313796997</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G453" t="n">
-        <v>12.1724901199341</v>
+        <v>12.1724910736084</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>13.75</v>
       </c>
       <c r="G454" t="n">
-        <v>12.3887300491333</v>
+        <v>12.3887310028076</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>13.75</v>
       </c>
       <c r="G456" t="n">
-        <v>12.3887300491333</v>
+        <v>12.3887310028076</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>14</v>
       </c>
       <c r="G458" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139793395996</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G459" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G460" t="n">
-        <v>12.5599193572998</v>
+        <v>12.5599203109741</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>14</v>
       </c>
       <c r="G461" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139793395996</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>13.75</v>
       </c>
       <c r="G463" t="n">
-        <v>12.3887300491333</v>
+        <v>12.3887310028076</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G464" t="n">
-        <v>12.4968490600586</v>
+        <v>12.4968500137329</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>14</v>
       </c>
       <c r="G469" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139793395996</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>14</v>
       </c>
       <c r="G476" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139793395996</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G477" t="n">
-        <v>12.6410093307495</v>
+        <v>12.6410102844238</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G480" t="n">
-        <v>12.5689296722412</v>
+        <v>12.5689306259155</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G481" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G483" t="n">
-        <v>12.5959606170654</v>
+        <v>12.5959596633911</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>12.5689296722412</v>
+        <v>12.5689306259155</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>12.5689296722412</v>
+        <v>12.5689306259155</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>12.3977403640747</v>
+        <v>12.397741317749</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G496" t="n">
-        <v>12.3977403640747</v>
+        <v>12.397741317749</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G497" t="n">
-        <v>12.2085304260254</v>
+        <v>12.2085313796997</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G498" t="n">
-        <v>12.3256597518921</v>
+        <v>12.3256607055664</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>12.3346691131592</v>
+        <v>12.3346700668335</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G501" t="n">
-        <v>12.3076419830322</v>
+        <v>12.3076400756836</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G502" t="n">
-        <v>12.1004114151001</v>
+        <v>12.1004123687744</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G508" t="n">
-        <v>12.1364507675171</v>
+        <v>12.1364517211914</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>13.5</v>
       </c>
       <c r="G509" t="n">
-        <v>12.163480758667</v>
+        <v>12.1634817123413</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G510" t="n">
-        <v>12.3076419830322</v>
+        <v>12.3076400756836</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G513" t="n">
-        <v>12.3076419830322</v>
+        <v>12.3076400756836</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G517" t="n">
-        <v>12.5058603286743</v>
+        <v>12.5058612823486</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G518" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G519" t="n">
-        <v>12.5779399871826</v>
+        <v>12.5779409408569</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G520" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G522" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>14</v>
       </c>
       <c r="G525" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139793395996</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G528" t="n">
-        <v>12.5779399871826</v>
+        <v>12.5779409408569</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>14</v>
       </c>
       <c r="G529" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139793395996</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G530" t="n">
-        <v>12.5959606170654</v>
+        <v>12.5959596633911</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G531" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G533" t="n">
-        <v>12.3256597518921</v>
+        <v>12.3256607055664</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G534" t="n">
-        <v>12.3076419830322</v>
+        <v>12.3076400756836</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G538" t="n">
-        <v>11.929220199585</v>
+        <v>11.9292211532593</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G539" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G541" t="n">
-        <v>11.7490205764771</v>
+        <v>11.7490215301514</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G545" t="n">
-        <v>11.7670412063599</v>
+        <v>11.7670421600342</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G546" t="n">
-        <v>11.7490205764771</v>
+        <v>11.7490215301514</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G548" t="n">
-        <v>11.6949615478516</v>
+        <v>11.6949625015259</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G549" t="n">
-        <v>11.7490205764771</v>
+        <v>11.7490215301514</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G551" t="n">
-        <v>11.6949615478516</v>
+        <v>11.6949625015259</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>11.7670412063599</v>
+        <v>11.7670421600342</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G555" t="n">
-        <v>10.8660430908203</v>
+        <v>10.8660449981689</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>11.172381401062</v>
+        <v>11.1723833084106</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G558" t="n">
-        <v>11.028223991394</v>
+        <v>11.0282230377197</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>11.172381401062</v>
+        <v>11.1723833084106</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G561" t="n">
-        <v>11.2805013656616</v>
+        <v>11.2805023193359</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G563" t="n">
-        <v>11.1543636322021</v>
+        <v>11.1543626785278</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G566" t="n">
-        <v>11.929220199585</v>
+        <v>11.9292211532593</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G570" t="n">
-        <v>12.2175407409668</v>
+        <v>12.2175397872925</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G572" t="n">
-        <v>12.4878387451172</v>
+        <v>12.4878396987915</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G575" t="n">
-        <v>12.5779399871826</v>
+        <v>12.5779409408569</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>14</v>
       </c>
       <c r="G579" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139793395996</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G580" t="n">
-        <v>12.5779399871826</v>
+        <v>12.5779409408569</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>14</v>
       </c>
       <c r="G581" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139793395996</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G585" t="n">
-        <v>12.7761602401733</v>
+        <v>12.776159286499</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G586" t="n">
-        <v>13.2807197570801</v>
+        <v>13.2807188034058</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>13.1185417175293</v>
+        <v>13.1185398101807</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G588" t="n">
-        <v>13.046459197998</v>
+        <v>13.0464582443237</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G591" t="n">
-        <v>13.4969577789307</v>
+        <v>13.496958732605</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G594" t="n">
-        <v>13.2626991271973</v>
+        <v>13.2627000808716</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G595" t="n">
-        <v>13.4789390563965</v>
+        <v>13.4789381027222</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G596" t="n">
-        <v>13.4428997039795</v>
+        <v>13.4428977966309</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>13.5870580673218</v>
+        <v>13.5870590209961</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G598" t="n">
-        <v>13.8213186264038</v>
+        <v>13.8213195800781</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G599" t="n">
-        <v>14.2177581787109</v>
+        <v>14.2177572250366</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G600" t="n">
-        <v>14.3979568481445</v>
+        <v>14.3979578018188</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G602" t="n">
-        <v>14.3619174957275</v>
+        <v>14.3619165420532</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G605" t="n">
-        <v>14.1097507476807</v>
+        <v>14.1097497940063</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G606" t="n">
-        <v>14.3302154541016</v>
+        <v>14.3302164077759</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G608" t="n">
-        <v>14.1648683547974</v>
+        <v>14.164867401123</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>14.3302154541016</v>
+        <v>14.3302164077759</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G611" t="n">
-        <v>14.2934722900391</v>
+        <v>14.2934713363647</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G612" t="n">
-        <v>14.2750997543335</v>
+        <v>14.2750978469849</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G617" t="n">
-        <v>14.1281232833862</v>
+        <v>14.1281223297119</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G621" t="n">
-        <v>13.9995174407959</v>
+        <v>13.9995183944702</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>14.3302154541016</v>
+        <v>14.3302164077759</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>14.4220752716064</v>
+        <v>14.4220743179321</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G626" t="n">
-        <v>14.311842918396</v>
+        <v>14.3118438720703</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G627" t="n">
-        <v>14.311842918396</v>
+        <v>14.3118438720703</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G628" t="n">
-        <v>14.2750997543335</v>
+        <v>14.2750978469849</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G629" t="n">
-        <v>14.2016115188599</v>
+        <v>14.2016105651855</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G632" t="n">
-        <v>13.3564958572388</v>
+        <v>13.3564968109131</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G634" t="n">
-        <v>13.3564958572388</v>
+        <v>13.3564968109131</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>14.5</v>
       </c>
       <c r="G635" t="n">
-        <v>13.319751739502</v>
+        <v>13.3197507858276</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G637" t="n">
-        <v>13.3564958572388</v>
+        <v>13.3564968109131</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G645" t="n">
-        <v>13.0074262619019</v>
+        <v>13.0074253082275</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G648" t="n">
-        <v>12.970682144165</v>
+        <v>12.9706811904907</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G649" t="n">
-        <v>13.0992870330811</v>
+        <v>13.0992860794067</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>13.0074262619019</v>
+        <v>13.0074253082275</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G651" t="n">
-        <v>13.0992870330811</v>
+        <v>13.0992860794067</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G652" t="n">
-        <v>12.8053321838379</v>
+        <v>12.8053331375122</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G653" t="n">
-        <v>12.7502174377441</v>
+        <v>12.7502183914185</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G654" t="n">
-        <v>12.7502174377441</v>
+        <v>12.7502183914185</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="G655" t="n">
-        <v>12.8604497909546</v>
+        <v>12.8604488372803</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G658" t="n">
-        <v>13.0074262619019</v>
+        <v>13.0074253082275</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G662" t="n">
-        <v>12.7318439483643</v>
+        <v>12.7318449020386</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>12.5848684310913</v>
+        <v>12.5848693847656</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.4930086135864</v>
+        <v>12.4930076599121</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G668" t="n">
-        <v>12.0520792007446</v>
+        <v>12.0520782470703</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G669" t="n">
-        <v>11.9602184295654</v>
+        <v>11.9602193832397</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>13</v>
       </c>
       <c r="G671" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418468475342</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G672" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051008224487</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G673" t="n">
-        <v>11.9602184295654</v>
+        <v>11.9602193832397</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G674" t="n">
-        <v>12.0520792007446</v>
+        <v>12.0520782470703</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G675" t="n">
-        <v>11.9969615936279</v>
+        <v>11.9969625473022</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G677" t="n">
-        <v>12.6216125488281</v>
+        <v>12.6216135025024</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G678" t="n">
-        <v>12.8053321838379</v>
+        <v>12.8053331375122</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>12.5848684310913</v>
+        <v>12.5848693847656</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>12.309287071228</v>
+        <v>12.3092861175537</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G681" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051008224487</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G682" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051008224487</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G684" t="n">
-        <v>11.6111488342285</v>
+        <v>11.6111497879028</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G685" t="n">
-        <v>11.849986076355</v>
+        <v>11.8499851226807</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G686" t="n">
-        <v>11.6295194625854</v>
+        <v>11.6295204162598</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G687" t="n">
-        <v>11.9969615936279</v>
+        <v>11.9969625473022</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G688" t="n">
-        <v>12.1990556716919</v>
+        <v>12.1990547180176</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G689" t="n">
-        <v>11.9969615936279</v>
+        <v>11.9969625473022</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>12.309287071228</v>
+        <v>12.3092861175537</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G692" t="n">
-        <v>12.3644027709961</v>
+        <v>12.3644037246704</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G697" t="n">
-        <v>11.9969615936279</v>
+        <v>11.9969625473022</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G702" t="n">
-        <v>11.776496887207</v>
+        <v>11.7764959335327</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>11.6662645339966</v>
+        <v>11.6662654876709</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G704" t="n">
-        <v>11.776496887207</v>
+        <v>11.7764959335327</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G705" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051008224487</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G707" t="n">
-        <v>11.5376596450806</v>
+        <v>11.5376605987549</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G712" t="n">
-        <v>10.9681253433228</v>
+        <v>10.9681262969971</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12</v>
       </c>
       <c r="G714" t="n">
-        <v>11.0232429504395</v>
+        <v>11.0232419967651</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>10.7476615905762</v>
+        <v>10.7476625442505</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G717" t="n">
-        <v>10.6374282836914</v>
+        <v>10.6374292373657</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G718" t="n">
-        <v>10.5823125839233</v>
+        <v>10.582311630249</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G719" t="n">
-        <v>10.2332439422607</v>
+        <v>10.2332448959351</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G720" t="n">
-        <v>10.2883596420288</v>
+        <v>10.2883605957031</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G721" t="n">
-        <v>10.0127782821655</v>
+        <v>10.0127792358398</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5271978378296</v>
+        <v>10.527195930481</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G724" t="n">
-        <v>10.5455684661865</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G725" t="n">
-        <v>10.5455684661865</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G728" t="n">
-        <v>10.5455684661865</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G730" t="n">
-        <v>10.6374282836914</v>
+        <v>10.6374292373657</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G731" t="n">
-        <v>10.5455684661865</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>10.1965007781982</v>
+        <v>10.1964998245239</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G733" t="n">
-        <v>10.4353370666504</v>
+        <v>10.4353361129761</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G735" t="n">
-        <v>10.2699880599976</v>
+        <v>10.2699890136719</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G737" t="n">
-        <v>10.2332439422607</v>
+        <v>10.2332448959351</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G739" t="n">
-        <v>10.0127782821655</v>
+        <v>10.0127792358398</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G740" t="n">
-        <v>10.0127782821655</v>
+        <v>10.0127792358398</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G742" t="n">
-        <v>10.2699880599976</v>
+        <v>10.2699890136719</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G746" t="n">
-        <v>10.1413822174072</v>
+        <v>10.1413831710815</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>10.3434743881226</v>
+        <v>10.3434762954712</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G750" t="n">
-        <v>9.7739429473877</v>
+        <v>9.77394199371338</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>9.82905769348145</v>
+        <v>9.82905673980713</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G754" t="n">
-        <v>10.1413822174072</v>
+        <v>10.1413831710815</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G755" t="n">
-        <v>10.2699880599976</v>
+        <v>10.2699890136719</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G756" t="n">
-        <v>10.0678949356079</v>
+        <v>10.0678939819336</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G763" t="n">
-        <v>10.251615524292</v>
+        <v>10.2516164779663</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G764" t="n">
-        <v>10.3618469238281</v>
+        <v>10.3618478775024</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>10.2883596420288</v>
+        <v>10.2883605957031</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G766" t="n">
-        <v>10.2883596420288</v>
+        <v>10.2883605957031</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G768" t="n">
-        <v>10.8762664794922</v>
+        <v>10.8762655258179</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>10.7476615905762</v>
+        <v>10.7476625442505</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>10.8395214080811</v>
+        <v>10.8395223617554</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G771" t="n">
-        <v>10.9681253433228</v>
+        <v>10.9681262969971</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G773" t="n">
-        <v>10.8395214080811</v>
+        <v>10.8395223617554</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G774" t="n">
-        <v>10.8395214080811</v>
+        <v>10.8395223617554</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G775" t="n">
-        <v>10.8762664794922</v>
+        <v>10.8762655258179</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G781" t="n">
-        <v>10.7476615905762</v>
+        <v>10.7476625442505</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G782" t="n">
-        <v>10.710916519165</v>
+        <v>10.7109184265137</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G784" t="n">
-        <v>10.6374282836914</v>
+        <v>10.6374292373657</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>10.7476615905762</v>
+        <v>10.7476625442505</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G788" t="n">
-        <v>10.5823125839233</v>
+        <v>10.582311630249</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G789" t="n">
-        <v>10.5271978378296</v>
+        <v>10.527195930481</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G792" t="n">
-        <v>10.2332439422607</v>
+        <v>10.2332448959351</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G793" t="n">
-        <v>10.3434743881226</v>
+        <v>10.3434762954712</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G794" t="n">
-        <v>10.4904527664185</v>
+        <v>10.4904537200928</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G797" t="n">
-        <v>10.6741724014282</v>
+        <v>10.6741733551025</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G800" t="n">
-        <v>10.5455684661865</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G803" t="n">
-        <v>10.5455684661865</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G804" t="n">
-        <v>10.5271978378296</v>
+        <v>10.527195930481</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G805" t="n">
-        <v>10.5823125839233</v>
+        <v>10.582311630249</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G806" t="n">
-        <v>10.6374282836914</v>
+        <v>10.6374292373657</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G807" t="n">
-        <v>10.8395214080811</v>
+        <v>10.8395223617554</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>12</v>
       </c>
       <c r="G809" t="n">
-        <v>11.0232429504395</v>
+        <v>11.0232419967651</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>10.7476615905762</v>
+        <v>10.7476625442505</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G811" t="n">
-        <v>10.4904527664185</v>
+        <v>10.4904537200928</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5823125839233</v>
+        <v>10.582311630249</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9130096435547</v>
+        <v>10.913010597229</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G816" t="n">
-        <v>11.2437086105347</v>
+        <v>11.243706703186</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G818" t="n">
-        <v>11.4641714096069</v>
+        <v>11.4641733169556</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G822" t="n">
-        <v>11.5376596450806</v>
+        <v>11.5376605987549</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>11.6295194625854</v>
+        <v>11.6295204162598</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G824" t="n">
-        <v>11.5560321807861</v>
+        <v>11.5560331344604</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G826" t="n">
-        <v>11.5376596450806</v>
+        <v>11.5376605987549</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G827" t="n">
-        <v>11.6478939056396</v>
+        <v>11.647891998291</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G829" t="n">
-        <v>11.6295194625854</v>
+        <v>11.6295204162598</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>11.6662645339966</v>
+        <v>11.6662654876709</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>11.6478939056396</v>
+        <v>11.647891998291</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G832" t="n">
-        <v>11.4641714096069</v>
+        <v>11.4641733169556</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>11.3906831741333</v>
+        <v>11.3906841278076</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G836" t="n">
-        <v>11.6295194625854</v>
+        <v>11.6295204162598</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5927772521973</v>
+        <v>11.5927762985229</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>11.6662645339966</v>
+        <v>11.6662654876709</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G841" t="n">
-        <v>11.6111488342285</v>
+        <v>11.6111497879028</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G842" t="n">
-        <v>11.5927772521973</v>
+        <v>11.5927762985229</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G843" t="n">
-        <v>11.6478939056396</v>
+        <v>11.647891998291</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G844" t="n">
-        <v>11.5560321807861</v>
+        <v>11.5560331344604</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G846" t="n">
-        <v>11.6295194625854</v>
+        <v>11.6295204162598</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G847" t="n">
-        <v>11.776496887207</v>
+        <v>11.7764959335327</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>13</v>
       </c>
       <c r="G848" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418468475342</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G850" t="n">
-        <v>12.1990556716919</v>
+        <v>12.1990547180176</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G851" t="n">
-        <v>12.1990556716919</v>
+        <v>12.1990547180176</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G853" t="n">
-        <v>12.1439399719238</v>
+        <v>12.1439390182495</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>13</v>
       </c>
       <c r="G855" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418468475342</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G856" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051008224487</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>13</v>
       </c>
       <c r="G857" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418468475342</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G858" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051008224487</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G864" t="n">
-        <v>12.182487487793</v>
+        <v>12.1824884414673</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G865" t="n">
-        <v>12.1069383621216</v>
+        <v>12.1069374084473</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>12.3713645935059</v>
+        <v>12.3713655471802</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G877" t="n">
-        <v>13.1835298538208</v>
+        <v>13.1835308074951</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G880" t="n">
-        <v>13.429069519043</v>
+        <v>13.4290685653687</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G884" t="n">
-        <v>13.5801687240601</v>
+        <v>13.5801696777344</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G885" t="n">
-        <v>13.7312698364258</v>
+        <v>13.7312707901001</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G887" t="n">
-        <v>13.636830329895</v>
+        <v>13.6368322372437</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G891" t="n">
-        <v>13.636830329895</v>
+        <v>13.6368322372437</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G893" t="n">
-        <v>13.429069519043</v>
+        <v>13.4290685653687</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G894" t="n">
-        <v>13.3724069595337</v>
+        <v>13.3724060058594</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>13.5046195983887</v>
+        <v>13.5046186447144</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>12.0880517959595</v>
+        <v>12.0880508422852</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G904" t="n">
-        <v>11.7858486175537</v>
+        <v>11.785849571228</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>11.7291870117188</v>
+        <v>11.7291860580444</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>12.5</v>
       </c>
       <c r="G906" t="n">
-        <v>11.8047370910645</v>
+        <v>11.8047361373901</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>12.5</v>
       </c>
       <c r="G907" t="n">
-        <v>11.8047370910645</v>
+        <v>11.8047361373901</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>11.710298538208</v>
+        <v>11.7102994918823</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G911" t="n">
-        <v>11.445873260498</v>
+        <v>11.4458723068237</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G914" t="n">
-        <v>11.1247844696045</v>
+        <v>11.1247835159302</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G915" t="n">
-        <v>11.087007522583</v>
+        <v>11.0870084762573</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>11.5403089523315</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G919" t="n">
-        <v>11.3892107009888</v>
+        <v>11.3892116546631</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>11.710298538208</v>
+        <v>11.7102994918823</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G927" t="n">
-        <v>11.4269857406616</v>
+        <v>11.4269847869873</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>11.4269857406616</v>
+        <v>11.4269847869873</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G931" t="n">
-        <v>11.578085899353</v>
+        <v>11.5780849456787</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>11.4269857406616</v>
+        <v>11.4269847869873</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G937" t="n">
-        <v>11.1247844696045</v>
+        <v>11.1247835159302</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G938" t="n">
-        <v>11.445873260498</v>
+        <v>11.4458723068237</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G940" t="n">
-        <v>11.3514356613159</v>
+        <v>11.3514347076416</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G941" t="n">
-        <v>11.5403089523315</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G942" t="n">
-        <v>11.5403089523315</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G946" t="n">
-        <v>11.2003345489502</v>
+        <v>11.2003335952759</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G947" t="n">
-        <v>11.3892107009888</v>
+        <v>11.3892116546631</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G950" t="n">
-        <v>11.2003345489502</v>
+        <v>11.2003335952759</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>11.2003345489502</v>
+        <v>11.2003335952759</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G952" t="n">
-        <v>11.1247844696045</v>
+        <v>11.1247835159302</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G955" t="n">
-        <v>10.7470321655273</v>
+        <v>10.747031211853</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G957" t="n">
-        <v>10.8981342315674</v>
+        <v>10.8981332778931</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G958" t="n">
-        <v>11.0492334365845</v>
+        <v>11.0492343902588</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>11.0114574432373</v>
+        <v>11.0114593505859</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G960" t="n">
-        <v>10.9925699234009</v>
+        <v>10.9925708770752</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>11.1436719894409</v>
+        <v>11.1436729431152</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G963" t="n">
-        <v>11.1436719894409</v>
+        <v>11.1436729431152</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G964" t="n">
-        <v>11.0492334365845</v>
+        <v>11.0492343902588</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G965" t="n">
-        <v>11.1436719894409</v>
+        <v>11.1436729431152</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>11.4269857406616</v>
+        <v>11.4269847869873</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G968" t="n">
-        <v>11.6347484588623</v>
+        <v>11.6347503662109</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>12.5</v>
       </c>
       <c r="G971" t="n">
-        <v>11.8047370910645</v>
+        <v>11.8047361373901</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>12.5</v>
       </c>
       <c r="G974" t="n">
-        <v>11.8047370910645</v>
+        <v>11.8047361373901</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G975" t="n">
-        <v>11.6347484588623</v>
+        <v>11.6347503662109</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G978" t="n">
-        <v>11.8613996505737</v>
+        <v>11.861400604248</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>12.5</v>
       </c>
       <c r="G980" t="n">
-        <v>11.8047370910645</v>
+        <v>11.8047361373901</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G981" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>11.710298538208</v>
+        <v>11.7102994918823</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G984" t="n">
-        <v>11.7858486175537</v>
+        <v>11.785849571228</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G985" t="n">
-        <v>11.7291870117188</v>
+        <v>11.7291860580444</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G991" t="n">
-        <v>11.3892107009888</v>
+        <v>11.3892116546631</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>11.710298538208</v>
+        <v>11.7102994918823</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>12.6546783447266</v>
+        <v>12.6546773910522</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>13.5</v>
       </c>
       <c r="G996" t="n">
-        <v>12.7491149902344</v>
+        <v>12.7491159439087</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>13.5</v>
       </c>
       <c r="G998" t="n">
-        <v>12.7491149902344</v>
+        <v>12.7491159439087</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>13.5</v>
       </c>
       <c r="G999" t="n">
-        <v>12.7491149902344</v>
+        <v>12.7491159439087</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>12.9002170562744</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.0135412216187</v>
+        <v>13.0135431289673</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.4668445587158</v>
+        <v>13.4668436050415</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.2024173736572</v>
+        <v>13.2024164199829</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.1646413803101</v>
+        <v>13.1646423339844</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.2779684066772</v>
+        <v>13.2779674530029</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>13.2779684066772</v>
+        <v>13.2779674530029</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>14</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.221305847168</v>
+        <v>13.2213048934937</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.2779684066772</v>
+        <v>13.2779674530029</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.0890913009644</v>
+        <v>13.0890922546387</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.9946546554565</v>
+        <v>12.9946556091309</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1020" t="n">
-        <v>13.0135412216187</v>
+        <v>13.0135431289673</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1022" t="n">
-        <v>13.2779684066772</v>
+        <v>13.2779674530029</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.4479570388794</v>
+        <v>13.4479551315308</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1029" t="n">
-        <v>14.67564868927</v>
+        <v>14.6756477355957</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1032" t="n">
-        <v>14.67564868927</v>
+        <v>14.6756477355957</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>14.2601222991943</v>
+        <v>14.2601232528687</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.0901346206665</v>
+        <v>14.0901336669922</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>13.8445959091187</v>
+        <v>13.8445949554443</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.1467971801758</v>
+        <v>14.1467962265015</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.2601222991943</v>
+        <v>14.2601232528687</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>14.2601222991943</v>
+        <v>14.2601232528687</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.1467971801758</v>
+        <v>14.1467962265015</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.5046195983887</v>
+        <v>13.5046186447144</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.5801687240601</v>
+        <v>13.5801696777344</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.0702037811279</v>
+        <v>13.0702047348022</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9002170562744</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1062" t="n">
-        <v>12.0502758026123</v>
+        <v>12.050274848938</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1063" t="n">
-        <v>11.4269857406616</v>
+        <v>11.4269847869873</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>11.3703231811523</v>
+        <v>11.370322227478</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1076" t="n">
-        <v>10.5581569671631</v>
+        <v>10.5581579208374</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1078" t="n">
-        <v>10.5392684936523</v>
+        <v>10.5392694473267</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.8225831985474</v>
+        <v>10.822582244873</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.8036956787109</v>
+        <v>10.8036947250366</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>11.4269857406616</v>
+        <v>11.4269847869873</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1083" t="n">
-        <v>11.445873260498</v>
+        <v>11.4458723068237</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1084" t="n">
-        <v>11.0681209564209</v>
+        <v>11.0681219100952</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.4269857406616</v>
+        <v>11.4269847869873</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1088" t="n">
-        <v>11.2003345489502</v>
+        <v>11.2003335952759</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1091" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>13</v>
       </c>
       <c r="G1093" t="n">
-        <v>12.2769260406494</v>
+        <v>12.2769269943237</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1095" t="n">
-        <v>12.6169023513794</v>
+        <v>12.6169033050537</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.6169023513794</v>
+        <v>12.6169033050537</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.8057794570923</v>
+        <v>12.8057775497437</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>14</v>
       </c>
       <c r="G1103" t="n">
-        <v>13.221305847168</v>
+        <v>13.2213048934937</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>13.5990562438965</v>
+        <v>13.5990581512451</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>14</v>
       </c>
       <c r="G1106" t="n">
-        <v>13.221305847168</v>
+        <v>13.2213048934937</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>13.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>12.7491149902344</v>
+        <v>12.7491159439087</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1108" t="n">
-        <v>12.8057794570923</v>
+        <v>12.8057775497437</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>12.8435544967651</v>
+        <v>12.8435535430908</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>14.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>13.6934957504272</v>
+        <v>13.6934947967529</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>14.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>13.6934957504272</v>
+        <v>13.6934947967529</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>13.8823699951172</v>
+        <v>13.8823709487915</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1116" t="n">
-        <v>14.5056610107422</v>
+        <v>14.5056600570679</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1118" t="n">
-        <v>14.2412347793579</v>
+        <v>14.2412357330322</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1127" t="n">
-        <v>14.1279096603394</v>
+        <v>14.127908706665</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1128" t="n">
-        <v>13.5801687240601</v>
+        <v>13.5801696777344</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>15.0533990859985</v>
+        <v>15.0534000396729</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>14.9211883544922</v>
+        <v>14.9211874008179</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1137" t="n">
-        <v>14.5056610107422</v>
+        <v>14.5056600570679</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1139" t="n">
-        <v>14.5812101364136</v>
+        <v>14.5812110900879</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1140" t="n">
-        <v>14.5812101364136</v>
+        <v>14.5812110900879</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.2601222991943</v>
+        <v>14.2601232528687</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1149" t="n">
-        <v>14.1467971801758</v>
+        <v>14.1467962265015</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1152" t="n">
-        <v>14.1279096603394</v>
+        <v>14.127908706665</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1156" t="n">
-        <v>13.5990562438965</v>
+        <v>13.5990581512451</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1157" t="n">
-        <v>13.636830329895</v>
+        <v>13.6368322372437</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1160" t="n">
-        <v>13.1646413803101</v>
+        <v>13.1646423339844</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1163" t="n">
-        <v>12.8813304901123</v>
+        <v>12.8813285827637</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1168" t="n">
-        <v>14.1279096603394</v>
+        <v>14.127908706665</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>14.2601222991943</v>
+        <v>14.2601232528687</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1170" t="n">
-        <v>14.5056610107422</v>
+        <v>14.5056600570679</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1178" t="n">
-        <v>13.5046195983887</v>
+        <v>13.5046186447144</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>14.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>13.6934957504272</v>
+        <v>13.6934947967529</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1184" t="n">
-        <v>13.7312698364258</v>
+        <v>13.7312707901001</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1185" t="n">
-        <v>13.8257093429565</v>
+        <v>13.8257083892822</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1186" t="n">
-        <v>13.7690458297729</v>
+        <v>13.7690448760986</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1187" t="n">
-        <v>13.7312698364258</v>
+        <v>13.7312707901001</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1188" t="n">
-        <v>14.67564868927</v>
+        <v>14.6756477355957</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1189" t="n">
-        <v>14.33567237854</v>
+        <v>14.3356733322144</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1192" t="n">
-        <v>14.5056610107422</v>
+        <v>14.5056600570679</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>14.2601222991943</v>
+        <v>14.2601232528687</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1195" t="n">
-        <v>14.467885017395</v>
+        <v>14.4678859710693</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.7312698364258</v>
+        <v>13.7312707901001</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1200" t="n">
-        <v>12.8246660232544</v>
+        <v>12.8246650695801</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.6546783447266</v>
+        <v>12.6546773910522</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.9002170562744</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1203" t="n">
-        <v>12.9002170562744</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.6169023513794</v>
+        <v>12.6169033050537</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1208" t="n">
-        <v>12.5035762786865</v>
+        <v>12.5035772323608</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>12.6546783447266</v>
+        <v>12.6546773910522</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.8246660232544</v>
+        <v>12.8246650695801</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.9946546554565</v>
+        <v>12.9946556091309</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1213" t="n">
-        <v>13.0135412216187</v>
+        <v>13.0135431289673</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1214" t="n">
-        <v>12.8813304901123</v>
+        <v>12.8813285827637</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.2580375671387</v>
+        <v>12.2580394744873</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.2391510009766</v>
+        <v>12.2391500473022</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1221" t="n">
-        <v>12.1069383621216</v>
+        <v>12.1069374084473</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>11.8613996505737</v>
+        <v>11.861400604248</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1226" t="n">
-        <v>11.1247844696045</v>
+        <v>11.1247835159302</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1227" t="n">
-        <v>11.5403089523315</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1228" t="n">
-        <v>11.2003345489502</v>
+        <v>11.2003335952759</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.710298538208</v>
+        <v>11.7102994918823</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.6347484588623</v>
+        <v>11.6347503662109</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1235" t="n">
-        <v>12.182487487793</v>
+        <v>12.1824884414673</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1237" t="n">
-        <v>12.2391510009766</v>
+        <v>12.2391500473022</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.2580375671387</v>
+        <v>12.2580394744873</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1240" t="n">
-        <v>12.4846906661987</v>
+        <v>12.4846897125244</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1242" t="n">
-        <v>10.5581569671631</v>
+        <v>10.5581579208374</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1243" t="n">
-        <v>10.8981342315674</v>
+        <v>10.8981332778931</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.8414707183838</v>
+        <v>10.8414697647095</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1246" t="n">
-        <v>10.5581569671631</v>
+        <v>10.5581579208374</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1248" t="n">
-        <v>10.5581569671631</v>
+        <v>10.5581579208374</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>11.5</v>
       </c>
       <c r="G1251" t="n">
-        <v>10.8603582382202</v>
+        <v>10.8603572845459</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>11.5</v>
       </c>
       <c r="G1252" t="n">
-        <v>10.8603582382202</v>
+        <v>10.8603572845459</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1253" t="n">
-        <v>10.7470321655273</v>
+        <v>10.747031211853</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1254" t="n">
-        <v>10.6903686523438</v>
+        <v>10.6903696060181</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1260" t="n">
-        <v>10.6714811325073</v>
+        <v>10.6714820861816</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.8414707183838</v>
+        <v>10.8414697647095</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.8981342315674</v>
+        <v>10.8981332778931</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.6714811325073</v>
+        <v>10.6714820861816</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1266" t="n">
-        <v>10.879246711731</v>
+        <v>10.8792448043823</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1267" t="n">
-        <v>10.8036956787109</v>
+        <v>10.8036947250366</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.8981342315674</v>
+        <v>10.8981332778931</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1269" t="n">
-        <v>10.8414707183838</v>
+        <v>10.8414697647095</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>11.5</v>
       </c>
       <c r="G1271" t="n">
-        <v>10.8603582382202</v>
+        <v>10.8603572845459</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>10.879246711731</v>
+        <v>10.8792448043823</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>11.030345916748</v>
+        <v>11.0303468704224</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1277" t="n">
-        <v>10.9925699234009</v>
+        <v>10.9925708770752</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>11.5</v>
       </c>
       <c r="G1278" t="n">
-        <v>10.8603582382202</v>
+        <v>10.8603572845459</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>11.4269857406616</v>
+        <v>11.4269847869873</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.3703231811523</v>
+        <v>11.370322227478</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1288" t="n">
-        <v>11.3703231811523</v>
+        <v>11.370322227478</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1289" t="n">
-        <v>11.3703231811523</v>
+        <v>11.370322227478</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1293" t="n">
-        <v>11.3703231811523</v>
+        <v>11.370322227478</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>12.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.8047370910645</v>
+        <v>11.8047361373901</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>12.3713645935059</v>
+        <v>12.3713655471802</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1306" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.4269857406616</v>
+        <v>11.4269847869873</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.7858486175537</v>
+        <v>11.785849571228</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>12.5</v>
       </c>
       <c r="G1314" t="n">
-        <v>11.8047370910645</v>
+        <v>11.8047361373901</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>12.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>11.8047370910645</v>
+        <v>11.8047361373901</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1322" t="n">
-        <v>11.9747257232666</v>
+        <v>11.9747247695923</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1328" t="n">
-        <v>11.6347484588623</v>
+        <v>11.6347503662109</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1331" t="n">
-        <v>11.5403089523315</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1334" t="n">
-        <v>11.710298538208</v>
+        <v>11.7102994918823</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1338" t="n">
-        <v>14.1467971801758</v>
+        <v>14.1467962265015</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1340" t="n">
-        <v>13.2024173736572</v>
+        <v>13.2024164199829</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1341" t="n">
-        <v>12.9002170562744</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>13.5</v>
       </c>
       <c r="G1342" t="n">
-        <v>12.7491149902344</v>
+        <v>12.7491159439087</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1348" t="n">
-        <v>12.9002170562744</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1349" t="n">
-        <v>12.9002170562744</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0702037811279</v>
+        <v>13.0702047348022</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1353" t="n">
-        <v>13.0890913009644</v>
+        <v>13.0890922546387</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1354" t="n">
-        <v>13.3724069595337</v>
+        <v>13.3724060058594</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1355" t="n">
-        <v>13.0702037811279</v>
+        <v>13.0702047348022</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1356" t="n">
-        <v>13.1835298538208</v>
+        <v>13.1835308074951</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>14</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.221305847168</v>
+        <v>13.2213048934937</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1359" t="n">
-        <v>13.1718292236328</v>
+        <v>13.1718282699585</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1361" t="n">
-        <v>12.6918058395386</v>
+        <v>12.6918048858643</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1362" t="n">
-        <v>12.5958023071289</v>
+        <v>12.5958003997803</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1363" t="n">
-        <v>12.5573987960815</v>
+        <v>12.5573997497559</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1364" t="n">
-        <v>12.8070106506348</v>
+        <v>12.8070116043091</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1366" t="n">
-        <v>12.5958023071289</v>
+        <v>12.5958003997803</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1367" t="n">
-        <v>12.5189971923828</v>
+        <v>12.5189981460571</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1369" t="n">
-        <v>12.5573987960815</v>
+        <v>12.5573997497559</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1371" t="n">
-        <v>12.2501840591431</v>
+        <v>12.2501850128174</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1374" t="n">
-        <v>12.6534042358398</v>
+        <v>12.6534032821655</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>12.5573987960815</v>
+        <v>12.5573997497559</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1376" t="n">
-        <v>12.5381984710693</v>
+        <v>12.5381994247437</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1377" t="n">
-        <v>12.5381984710693</v>
+        <v>12.5381994247437</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1378" t="n">
-        <v>12.5573987960815</v>
+        <v>12.5573997497559</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1379" t="n">
-        <v>12.5381984710693</v>
+        <v>12.5381994247437</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1380" t="n">
-        <v>12.6534042358398</v>
+        <v>12.6534032821655</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1381" t="n">
-        <v>12.5189971923828</v>
+        <v>12.5189981460571</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1383" t="n">
-        <v>12.6150026321411</v>
+        <v>12.6150016784668</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.826210975647</v>
+        <v>12.8262119293213</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1385" t="n">
-        <v>12.8454122543335</v>
+        <v>12.8454132080078</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1388" t="n">
-        <v>12.1733808517456</v>
+        <v>12.1733798980713</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1389" t="n">
-        <v>12.5958023071289</v>
+        <v>12.5958003997803</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1391" t="n">
-        <v>12.3077869415283</v>
+        <v>12.307785987854</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1397" t="n">
-        <v>11.9237689971924</v>
+        <v>11.9237680435181</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1401" t="n">
-        <v>11.9621706008911</v>
+        <v>11.9621715545654</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1402" t="n">
-        <v>11.6357555389404</v>
+        <v>11.6357545852661</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1406" t="n">
-        <v>11.7125577926636</v>
+        <v>11.7125587463379</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1407" t="n">
-        <v>11.6933574676514</v>
+        <v>11.6933584213257</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1408" t="n">
-        <v>11.6933574676514</v>
+        <v>11.6933584213257</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.2517356872559</v>
+        <v>11.2517366409302</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.2901382446289</v>
+        <v>11.2901391983032</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>11.4245452880859</v>
+        <v>11.4245443344116</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1417" t="n">
-        <v>11.4245452880859</v>
+        <v>11.4245443344116</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1420" t="n">
-        <v>11.2517356872559</v>
+        <v>11.2517366409302</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1421" t="n">
-        <v>11.2133350372314</v>
+        <v>11.2133359909058</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1422" t="n">
-        <v>11.2325353622437</v>
+        <v>11.232536315918</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1423" t="n">
-        <v>11.3477411270142</v>
+        <v>11.3477401733398</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1424" t="n">
-        <v>11.2133350372314</v>
+        <v>11.2133359909058</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1429" t="n">
-        <v>10.9253215789795</v>
+        <v>10.9253206253052</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1430" t="n">
-        <v>10.906120300293</v>
+        <v>10.9061193466187</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.8101148605347</v>
+        <v>10.810115814209</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1436" t="n">
-        <v>11.328540802002</v>
+        <v>11.3285398483276</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>11.6165552139282</v>
+        <v>11.6165542602539</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>11.6165552139282</v>
+        <v>11.6165542602539</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1441" t="n">
-        <v>11.6933574676514</v>
+        <v>11.6933584213257</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1442" t="n">
-        <v>11.7125577926636</v>
+        <v>11.7125587463379</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>11.4245452880859</v>
+        <v>11.4245443344116</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1444" t="n">
-        <v>11.2517356872559</v>
+        <v>11.2517366409302</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1445" t="n">
-        <v>11.2133350372314</v>
+        <v>11.2133359909058</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>11</v>
       </c>
       <c r="G1452" t="n">
-        <v>10.5605049133301</v>
+        <v>10.5605039596558</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1453" t="n">
-        <v>10.4068956375122</v>
+        <v>10.4068965911865</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>10.4837007522583</v>
+        <v>10.483699798584</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>10.714111328125</v>
+        <v>10.7141122817993</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>11.1365327835083</v>
+        <v>11.136531829834</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1470" t="n">
-        <v>11.2517356872559</v>
+        <v>11.2517366409302</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>11.328540802002</v>
+        <v>11.3285398483276</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1476" t="n">
-        <v>11.7125577926636</v>
+        <v>11.7125587463379</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1479" t="n">
-        <v>11.328540802002</v>
+        <v>11.3285398483276</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1480" t="n">
-        <v>11.3477411270142</v>
+        <v>11.3477401733398</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>11.5</v>
       </c>
       <c r="G1483" t="n">
-        <v>11.04052734375</v>
+        <v>11.0405263900757</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>11.5</v>
       </c>
       <c r="G1486" t="n">
-        <v>11.04052734375</v>
+        <v>11.0405263900757</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>11.1365327835083</v>
+        <v>11.136531829834</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1490" t="n">
-        <v>11.2133350372314</v>
+        <v>11.2133359909058</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1495" t="n">
-        <v>11.2901382446289</v>
+        <v>11.2901391983032</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1497" t="n">
-        <v>10.8869199752808</v>
+        <v>10.8869190216064</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1498" t="n">
-        <v>10.7909135818481</v>
+        <v>10.7909145355225</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1500" t="n">
-        <v>10.7333126068115</v>
+        <v>10.7333135604858</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>10.8869199752808</v>
+        <v>10.8869190216064</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1503" t="n">
-        <v>10.714111328125</v>
+        <v>10.7141122817993</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1505" t="n">
-        <v>10.6181077957153</v>
+        <v>10.618106842041</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1508" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1511" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1513" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>11.5</v>
       </c>
       <c r="G1516" t="n">
-        <v>11.04052734375</v>
+        <v>11.0405263900757</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>11.5</v>
       </c>
       <c r="G1519" t="n">
-        <v>11.04052734375</v>
+        <v>11.0405263900757</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1523" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1524" t="n">
-        <v>11.1365327835083</v>
+        <v>11.136531829834</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1525" t="n">
-        <v>10.9253215789795</v>
+        <v>10.9253206253052</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>11.2325353622437</v>
+        <v>11.232536315918</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1527" t="n">
-        <v>11.2325353622437</v>
+        <v>11.232536315918</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1528" t="n">
-        <v>11.2133350372314</v>
+        <v>11.2133359909058</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1530" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>11.5</v>
       </c>
       <c r="G1531" t="n">
-        <v>11.04052734375</v>
+        <v>11.0405263900757</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1532" t="n">
-        <v>10.8869199752808</v>
+        <v>10.8869190216064</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1533" t="n">
-        <v>10.9253215789795</v>
+        <v>10.9253206253052</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>11.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>11.04052734375</v>
+        <v>11.0405263900757</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>11.2133350372314</v>
+        <v>11.2133359909058</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>11.1365327835083</v>
+        <v>11.136531829834</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>11.5</v>
       </c>
       <c r="G1539" t="n">
-        <v>11.04052734375</v>
+        <v>11.0405263900757</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1540" t="n">
-        <v>11.2901382446289</v>
+        <v>11.2901391983032</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>10.4837007522583</v>
+        <v>10.483699798584</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1543" t="n">
-        <v>10.1764860153198</v>
+        <v>10.1764850616455</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1544" t="n">
-        <v>10.2532892227173</v>
+        <v>10.2532901763916</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1546" t="n">
-        <v>10.195686340332</v>
+        <v>10.1956853866577</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1548" t="n">
-        <v>10.3108921051025</v>
+        <v>10.3108930587769</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1552" t="n">
-        <v>10.0612802505493</v>
+        <v>10.061279296875</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1553" t="n">
-        <v>10.0612802505493</v>
+        <v>10.061279296875</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>10.5</v>
       </c>
       <c r="G1554" t="n">
-        <v>10.0804815292358</v>
+        <v>10.0804805755615</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1555" t="n">
-        <v>10.2148876190186</v>
+        <v>10.2148885726929</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>10.5</v>
       </c>
       <c r="G1557" t="n">
-        <v>10.0804815292358</v>
+        <v>10.0804805755615</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1558" t="n">
-        <v>10.1188821792603</v>
+        <v>10.1188831329346</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1559" t="n">
-        <v>10.2148876190186</v>
+        <v>10.2148885726929</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1560" t="n">
-        <v>10.2532892227173</v>
+        <v>10.2532901763916</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1561" t="n">
-        <v>10.195686340332</v>
+        <v>10.1956853866577</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1562" t="n">
-        <v>9.88847160339355</v>
+        <v>9.88847064971924</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1565" t="n">
-        <v>10.1188821792603</v>
+        <v>10.1188831329346</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1568" t="n">
-        <v>10.5989065170288</v>
+        <v>10.5989055633545</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>11</v>
       </c>
       <c r="G1569" t="n">
-        <v>10.5605049133301</v>
+        <v>10.5605039596558</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1571" t="n">
-        <v>10.195686340332</v>
+        <v>10.1956853866577</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1573" t="n">
-        <v>10.3108921051025</v>
+        <v>10.3108930587769</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>10.1764860153198</v>
+        <v>10.1764850616455</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>9.07243251800537</v>
+        <v>9.07243347167969</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1579" t="n">
-        <v>9.40844917297363</v>
+        <v>9.40844821929932</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1586" t="n">
-        <v>9.96527481079102</v>
+        <v>9.96527576446533</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1587" t="n">
-        <v>9.96527481079102</v>
+        <v>9.96527576446533</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1590" t="n">
-        <v>10.2148876190186</v>
+        <v>10.2148885726929</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1592" t="n">
-        <v>10.1764860153198</v>
+        <v>10.1764850616455</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1593" t="n">
-        <v>10.0420799255371</v>
+        <v>10.0420789718628</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1595" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>11.4245452880859</v>
+        <v>11.4245443344116</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1600" t="n">
-        <v>11.2901382446289</v>
+        <v>11.2901391983032</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1602" t="n">
-        <v>10.7333126068115</v>
+        <v>10.7333135604858</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1604" t="n">
-        <v>10.4837007522583</v>
+        <v>10.483699798584</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1606" t="n">
-        <v>10.4068956375122</v>
+        <v>10.4068965911865</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1608" t="n">
-        <v>10.714111328125</v>
+        <v>10.7141122817993</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>11.5</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.04052734375</v>
+        <v>11.0405263900757</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1617" t="n">
-        <v>10.7324523925781</v>
+        <v>10.7324533462524</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1636" t="n">
-        <v>11.3546237945557</v>
+        <v>11.35462474823</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1639" t="n">
-        <v>10.8491096496582</v>
+        <v>10.8491106033325</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1644" t="n">
-        <v>10.1491661071777</v>
+        <v>10.1491670608521</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1645" t="n">
-        <v>10.1491661071777</v>
+        <v>10.1491670608521</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1647" t="n">
-        <v>9.95473766326904</v>
+        <v>9.95473861694336</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1649" t="n">
-        <v>10.2463808059692</v>
+        <v>10.2463817596436</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1652" t="n">
-        <v>10.4991397857666</v>
+        <v>10.4991388320923</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1658" t="n">
-        <v>11.0046529769897</v>
+        <v>11.0046520233154</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1659" t="n">
-        <v>10.8685522079468</v>
+        <v>10.8685531616211</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1663" t="n">
-        <v>10.8491096496582</v>
+        <v>10.8491106033325</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1668" t="n">
-        <v>10.8491096496582</v>
+        <v>10.8491106033325</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>11.7823667526245</v>
+        <v>11.7823657989502</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1686" t="n">
-        <v>12.8517236709595</v>
+        <v>12.8517227172852</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1687" t="n">
-        <v>12.8711671829224</v>
+        <v>12.871166229248</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1689" t="n">
-        <v>13.0267095565796</v>
+        <v>13.0267086029053</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1690" t="n">
-        <v>13.3961219787598</v>
+        <v>13.3961229324341</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1691" t="n">
-        <v>13.6683235168457</v>
+        <v>13.66832447052</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1698" t="n">
-        <v>13.2016935348511</v>
+        <v>13.2016944885254</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1699" t="n">
-        <v>12.8322811126709</v>
+        <v>12.8322801589966</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1701" t="n">
-        <v>12.3656520843506</v>
+        <v>12.3656511306763</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1704" t="n">
-        <v>10.3241529464722</v>
+        <v>10.3241519927979</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>10</v>
       </c>
       <c r="G1708" t="n">
-        <v>9.72142505645752</v>
+        <v>9.7214241027832</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1711" t="n">
-        <v>9.85752487182617</v>
+        <v>9.85752582550049</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1714" t="n">
-        <v>8.96315383911133</v>
+        <v>8.96315288543701</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1716" t="n">
-        <v>8.93398857116699</v>
+        <v>8.93398952484131</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1717" t="n">
-        <v>8.87566184997559</v>
+        <v>8.87566089630127</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1718" t="n">
-        <v>8.93398857116699</v>
+        <v>8.93398952484131</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1721" t="n">
-        <v>9.25479698181152</v>
+        <v>9.25479602813721</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1722" t="n">
-        <v>9.22563171386719</v>
+        <v>9.2256326675415</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1724" t="n">
-        <v>8.89510345458984</v>
+        <v>8.89510250091553</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1725" t="n">
-        <v>8.94371128082275</v>
+        <v>8.94371032714844</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1733" t="n">
-        <v>10.3047113418579</v>
+        <v>10.3047103881836</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1734" t="n">
-        <v>10.4991397857666</v>
+        <v>10.4991388320923</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1738" t="n">
-        <v>10.7907819747925</v>
+        <v>10.7907810211182</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>10.9852104187012</v>
+        <v>10.9852094650269</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1740" t="n">
-        <v>10.7907819747925</v>
+        <v>10.7907810211182</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1743" t="n">
-        <v>10.4408092498779</v>
+        <v>10.4408102035522</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1747" t="n">
-        <v>10.3241529464722</v>
+        <v>10.3241519927979</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1750" t="n">
-        <v>10.090838432312</v>
+        <v>10.0908393859863</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1751" t="n">
-        <v>10.1491661071777</v>
+        <v>10.1491670608521</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1752" t="n">
-        <v>10.0130681991577</v>
+        <v>10.0130672454834</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1753" t="n">
-        <v>10.1491661071777</v>
+        <v>10.1491670608521</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1754" t="n">
-        <v>10.3047113418579</v>
+        <v>10.3047103881836</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1755" t="n">
-        <v>10.3435964584351</v>
+        <v>10.3435974121094</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>10.5</v>
       </c>
       <c r="G1756" t="n">
-        <v>10.2074966430664</v>
+        <v>10.2074956893921</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1761" t="n">
-        <v>10.8685522079468</v>
+        <v>10.8685531616211</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1763" t="n">
-        <v>11.0824241638184</v>
+        <v>11.082423210144</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1766" t="n">
-        <v>10.4991397857666</v>
+        <v>10.4991388320923</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1768" t="n">
-        <v>10.6352376937866</v>
+        <v>10.6352386474609</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1771" t="n">
-        <v>10.6352376937866</v>
+        <v>10.6352386474609</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1772" t="n">
-        <v>10.5185813903809</v>
+        <v>10.5185804367065</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1773" t="n">
-        <v>10.3047113418579</v>
+        <v>10.3047103881836</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1774" t="n">
-        <v>10.3435964584351</v>
+        <v>10.3435974121094</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1776" t="n">
-        <v>9.30340385437012</v>
+        <v>9.3034029006958</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1780" t="n">
-        <v>9.25479698181152</v>
+        <v>9.25479602813721</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1781" t="n">
-        <v>9.42978286743164</v>
+        <v>9.42978191375732</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1782" t="n">
-        <v>9.30340385437012</v>
+        <v>9.3034029006958</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1787" t="n">
-        <v>10.3824815750122</v>
+        <v>10.3824825286865</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1788" t="n">
-        <v>10.090838432312</v>
+        <v>10.0908393859863</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>10</v>
       </c>
       <c r="G1790" t="n">
-        <v>9.72142505645752</v>
+        <v>9.7214241027832</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G1791" t="n">
-        <v>9.71170330047607</v>
+        <v>9.71170425415039</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1792" t="n">
-        <v>9.74086856842041</v>
+        <v>9.74086761474609</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>10</v>
       </c>
       <c r="G1793" t="n">
-        <v>9.72142505645752</v>
+        <v>9.7214241027832</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1795" t="n">
-        <v>9.65337562561035</v>
+        <v>9.65337467193604</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1796" t="n">
-        <v>9.52699661254883</v>
+        <v>9.52699565887451</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>10</v>
       </c>
       <c r="G1799" t="n">
-        <v>9.72142505645752</v>
+        <v>9.7214241027832</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1801" t="n">
-        <v>9.74086856842041</v>
+        <v>9.74086761474609</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1803" t="n">
-        <v>9.65337562561035</v>
+        <v>9.65337467193604</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1804" t="n">
-        <v>9.66309547424316</v>
+        <v>9.66309642791748</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>9.74086856842041</v>
+        <v>9.74086761474609</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>10</v>
       </c>
       <c r="G1808" t="n">
-        <v>9.72142505645752</v>
+        <v>9.7214241027832</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G1810" t="n">
-        <v>9.71170330047607</v>
+        <v>9.71170425415039</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1813" t="n">
-        <v>9.85752487182617</v>
+        <v>9.85752582550049</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1814" t="n">
-        <v>9.76030921936035</v>
+        <v>9.76031017303467</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1818" t="n">
-        <v>9.85752487182617</v>
+        <v>9.85752582550049</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1819" t="n">
-        <v>9.74086856842041</v>
+        <v>9.74086761474609</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1823" t="n">
-        <v>10.0130681991577</v>
+        <v>10.0130672454834</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1826" t="n">
-        <v>9.95473766326904</v>
+        <v>9.95473861694336</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1827" t="n">
-        <v>9.85752487182617</v>
+        <v>9.85752582550049</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1830" t="n">
-        <v>9.76030921936035</v>
+        <v>9.76031017303467</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1831" t="n">
-        <v>9.74086856842041</v>
+        <v>9.74086761474609</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>10</v>
       </c>
       <c r="G1832" t="n">
-        <v>9.72142505645752</v>
+        <v>9.7214241027832</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1833" t="n">
-        <v>9.56588172912598</v>
+        <v>9.56588268280029</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1834" t="n">
-        <v>9.76030921936035</v>
+        <v>9.76031017303467</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1842" t="n">
-        <v>8.96315383911133</v>
+        <v>8.96315288543701</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1843" t="n">
-        <v>8.98259544372559</v>
+        <v>8.9825963973999</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1844" t="n">
-        <v>9.07981109619141</v>
+        <v>9.07981204986572</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1845" t="n">
-        <v>9.16730403900146</v>
+        <v>9.16730308532715</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1848" t="n">
-        <v>9.16730403900146</v>
+        <v>9.16730308532715</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1850" t="n">
-        <v>8.94371128082275</v>
+        <v>8.94371032714844</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.94371128082275</v>
+        <v>8.94371032714844</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1857" t="n">
-        <v>8.93398857116699</v>
+        <v>8.93398952484131</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1865" t="n">
-        <v>8.93398857116699</v>
+        <v>8.93398952484131</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1870" t="n">
-        <v>9.16730403900146</v>
+        <v>9.16730308532715</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1872" t="n">
-        <v>9.43950271606445</v>
+        <v>9.43950366973877</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1873" t="n">
-        <v>9.37145328521729</v>
+        <v>9.3714542388916</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1875" t="n">
-        <v>9.43950271606445</v>
+        <v>9.43950366973877</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G1877" t="n">
-        <v>9.71170330047607</v>
+        <v>9.71170425415039</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1878" t="n">
-        <v>9.66309547424316</v>
+        <v>9.66309642791748</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1880" t="n">
-        <v>9.85752487182617</v>
+        <v>9.85752582550049</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1881" t="n">
-        <v>9.95473766326904</v>
+        <v>9.95473861694336</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1884" t="n">
-        <v>9.56588172912598</v>
+        <v>9.56588268280029</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1885" t="n">
-        <v>9.37145328521729</v>
+        <v>9.3714542388916</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1890" t="n">
-        <v>9.30340385437012</v>
+        <v>9.3034029006958</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1891" t="n">
-        <v>9.30340385437012</v>
+        <v>9.3034029006958</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1893" t="n">
-        <v>9.37145328521729</v>
+        <v>9.3714542388916</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1897" t="n">
-        <v>9.30340385437012</v>
+        <v>9.3034029006958</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1898" t="n">
-        <v>9.24507427215576</v>
+        <v>9.24507522583008</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>9.5</v>
       </c>
       <c r="G1901" t="n">
-        <v>9.23535442352295</v>
+        <v>9.23535346984863</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1904" t="n">
-        <v>9.25479698181152</v>
+        <v>9.25479602813721</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1905" t="n">
-        <v>9.07981109619141</v>
+        <v>9.07981204986572</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1907" t="n">
-        <v>8.87566184997559</v>
+        <v>8.87566089630127</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1911" t="n">
-        <v>8.98259544372559</v>
+        <v>8.9825963973999</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1919" t="n">
-        <v>8.8853816986084</v>
+        <v>8.88538265228271</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1929" t="n">
-        <v>8.76872539520264</v>
+        <v>8.76872444152832</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1941" t="n">
-        <v>8.8853816986084</v>
+        <v>8.88538265228271</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1947" t="n">
-        <v>8.98259544372559</v>
+        <v>8.9825963973999</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1948" t="n">
-        <v>8.89510345458984</v>
+        <v>8.89510250091553</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1950" t="n">
-        <v>9.07981109619141</v>
+        <v>9.07981204986572</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1955" t="n">
-        <v>8.58401870727539</v>
+        <v>8.58401775360107</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1956" t="n">
-        <v>8.59373950958252</v>
+        <v>8.59374046325684</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1958" t="n">
-        <v>8.44791698455811</v>
+        <v>8.44791793823242</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1959" t="n">
-        <v>8.59373950958252</v>
+        <v>8.59374046325684</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1961" t="n">
-        <v>8.94371128082275</v>
+        <v>8.94371032714844</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1962" t="n">
-        <v>8.95343208312988</v>
+        <v>8.9534330368042</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1963" t="n">
-        <v>8.75900363922119</v>
+        <v>8.75900459289551</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1964" t="n">
-        <v>8.58401870727539</v>
+        <v>8.58401775360107</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1965" t="n">
-        <v>8.59373950958252</v>
+        <v>8.59374046325684</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1966" t="n">
-        <v>8.58401870727539</v>
+        <v>8.58401775360107</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1969" t="n">
-        <v>7.97156858444214</v>
+        <v>7.97156763076782</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1970" t="n">
-        <v>7.8549108505249</v>
+        <v>7.85491132736206</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1971" t="n">
-        <v>7.78686094284058</v>
+        <v>7.78686141967773</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G1975" t="n">
-        <v>7.61187505722046</v>
+        <v>7.61187553405762</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1979" t="n">
-        <v>7.42716884613037</v>
+        <v>7.42716836929321</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1983" t="n">
-        <v>7.22301816940308</v>
+        <v>7.22301864624023</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1984" t="n">
-        <v>7.19385433197021</v>
+        <v>7.19385385513306</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1986" t="n">
-        <v>7.10636138916016</v>
+        <v>7.10636186599731</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1988" t="n">
-        <v>6.96053981781006</v>
+        <v>6.96054029464722</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1989" t="n">
-        <v>6.98970413208008</v>
+        <v>6.98970460891724</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1999" t="n">
-        <v>7.43689012527466</v>
+        <v>7.4368896484375</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2000" t="n">
-        <v>7.32995414733887</v>
+        <v>7.32995367050171</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>7.5</v>
       </c>
       <c r="G2001" t="n">
-        <v>7.29106855392456</v>
+        <v>7.2910680770874</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2002" t="n">
-        <v>7.30078983306885</v>
+        <v>7.30079030990601</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2003" t="n">
-        <v>7.30078983306885</v>
+        <v>7.30079030990601</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2010" t="n">
-        <v>7.52438306808472</v>
+        <v>7.52438259124756</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52655,7 +52655,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2011" t="n">
-        <v>7.57298994064331</v>
+        <v>7.57298946380615</v>
       </c>
       <c r="H2011" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G2018" t="n">
-        <v>7.28134727478027</v>
+        <v>7.28134679794312</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G2019" t="n">
-        <v>7.28134727478027</v>
+        <v>7.28134679794312</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G2021" t="n">
-        <v>7.49521827697754</v>
+        <v>7.4952187538147</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2024" t="n">
-        <v>7.46605396270752</v>
+        <v>7.46605443954468</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G2025" t="n">
-        <v>7.49521827697754</v>
+        <v>7.4952187538147</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2026" t="n">
-        <v>7.52438306808472</v>
+        <v>7.52438259124756</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G2029" t="n">
-        <v>7.67020416259766</v>
+        <v>7.6702036857605</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2030" t="n">
-        <v>7.6799259185791</v>
+        <v>7.67992544174194</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G2038" t="n">
-        <v>8.1757173538208</v>
+        <v>8.17571830749512</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2039" t="n">
-        <v>8.44791698455811</v>
+        <v>8.44791793823242</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2044" t="n">
-        <v>8.45763969421387</v>
+        <v>8.45763874053955</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G2045" t="n">
-        <v>8.467360496521</v>
+        <v>8.46736145019531</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2047" t="n">
-        <v>8.3895902633667</v>
+        <v>8.38958930969238</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2050" t="n">
-        <v>8.30209636688232</v>
+        <v>8.30209732055664</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G2055" t="n">
-        <v>8.1757173538208</v>
+        <v>8.17571830749512</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2056" t="n">
-        <v>8.02989768981934</v>
+        <v>8.02989673614502</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2060" t="n">
-        <v>8.28265476226807</v>
+        <v>8.28265380859375</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2066" t="n">
-        <v>8.2729320526123</v>
+        <v>8.27293300628662</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2068" t="n">
-        <v>8.40903186798096</v>
+        <v>8.40903091430664</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2070" t="n">
-        <v>8.58401870727539</v>
+        <v>8.58401775360107</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2076" t="n">
-        <v>8.58401870727539</v>
+        <v>8.58401775360107</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>9.5</v>
       </c>
       <c r="G2080" t="n">
-        <v>9.23535442352295</v>
+        <v>9.23535346984863</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>9</v>
       </c>
       <c r="G2086" t="n">
-        <v>8.74928283691406</v>
+        <v>8.74928188323975</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G2087" t="n">
-        <v>8.87566184997559</v>
+        <v>8.87566089630127</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>9.5</v>
       </c>
       <c r="G2095" t="n">
-        <v>9.23535442352295</v>
+        <v>9.23535346984863</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2105" t="n">
-        <v>9.74086856842041</v>
+        <v>9.74086761474609</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2110" t="n">
-        <v>10.090838432312</v>
+        <v>10.0908393859863</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2112" t="n">
-        <v>10.9852104187012</v>
+        <v>10.9852094650269</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2113" t="n">
-        <v>10.5185813903809</v>
+        <v>10.5185804367065</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2116" t="n">
-        <v>10.7324523925781</v>
+        <v>10.7324533462524</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2117" t="n">
-        <v>10.5185813903809</v>
+        <v>10.5185804367065</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>29.2099990844727</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>502775</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>29.2099990844727</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>28.2399997711182</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>29.0499992370605</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>28.3299999237061</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>28.3299999237061</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>29.0499992370605</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>30.1399993896484</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>1078478</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>30.4099998474121</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>29.1200008392334</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>30.1399993896484</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>30.1399993896484</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>29.3600006103516</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>550162</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>29.3999996185303</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>28.6900005340576</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>29.1200008392334</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>29.1200008392334</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>28.75</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>578508</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>29.4799995422363</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>28.2999992370605</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>28.5</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>29</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>521633</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>29.1700000762939</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>28.3899993896484</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>29.0400009155273</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>691596</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>29.6299991607666</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>28.6900005340576</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>28.7099990844727</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>29.1700000762939</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -514,7 +514,7 @@
         <v>9.5</v>
       </c>
       <c r="G5" t="n">
-        <v>8.55948543548584</v>
+        <v>8.55948638916016</v>
       </c>
       <c r="H5" t="n">
         <v>367</v>
@@ -572,7 +572,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G7" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H7" t="n">
         <v>2000</v>
@@ -601,7 +601,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G8" t="n">
-        <v>8.91087627410889</v>
+        <v>8.9108772277832</v>
       </c>
       <c r="H8" t="n">
         <v>55700</v>
@@ -630,7 +630,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.91087627410889</v>
+        <v>8.9108772277832</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>9.5</v>
       </c>
       <c r="G14" t="n">
-        <v>8.55948543548584</v>
+        <v>8.55948638916016</v>
       </c>
       <c r="H14" t="n">
         <v>156</v>
@@ -862,7 +862,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G17" t="n">
-        <v>8.64958763122559</v>
+        <v>8.6495885848999</v>
       </c>
       <c r="H17" t="n">
         <v>1566</v>
@@ -949,7 +949,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.86582565307617</v>
+        <v>8.86582660675049</v>
       </c>
       <c r="H20" t="n">
         <v>828</v>
@@ -978,7 +978,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G21" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H21" t="n">
         <v>25250</v>
@@ -1036,7 +1036,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G23" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H23" t="n">
         <v>1197</v>
@@ -1094,7 +1094,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H25" t="n">
         <v>241</v>
@@ -1152,7 +1152,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G27" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H27" t="n">
         <v>104</v>
@@ -1181,7 +1181,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H28" t="n">
         <v>60304</v>
@@ -1210,7 +1210,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G29" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H29" t="n">
         <v>30000</v>
@@ -1268,7 +1268,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G31" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H31" t="n">
         <v>250</v>
@@ -1297,7 +1297,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G32" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H32" t="n">
         <v>1305</v>
@@ -1326,7 +1326,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H34" t="n">
         <v>2500</v>
@@ -1384,7 +1384,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G35" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H35" t="n">
         <v>7500</v>
@@ -1471,7 +1471,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.91988563537598</v>
+        <v>8.91988658905029</v>
       </c>
       <c r="H38" t="n">
         <v>10735</v>
@@ -1500,7 +1500,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H39" t="n">
         <v>116</v>
@@ -1529,7 +1529,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G43" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H43" t="n">
         <v>6210</v>
@@ -1645,7 +1645,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G44" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G45" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H45" t="n">
         <v>2651</v>
@@ -1703,7 +1703,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H46" t="n">
         <v>1336</v>
@@ -1732,7 +1732,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H47" t="n">
         <v>243</v>
@@ -1761,7 +1761,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H48" t="n">
         <v>289</v>
@@ -1790,7 +1790,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G49" t="n">
-        <v>8.91988563537598</v>
+        <v>8.91988658905029</v>
       </c>
       <c r="H49" t="n">
         <v>1886</v>
@@ -1819,7 +1819,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G50" t="n">
-        <v>8.91988563537598</v>
+        <v>8.91988658905029</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G51" t="n">
-        <v>8.91988563537598</v>
+        <v>8.91988658905029</v>
       </c>
       <c r="H51" t="n">
         <v>748</v>
@@ -1877,7 +1877,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G52" t="n">
-        <v>8.91988563537598</v>
+        <v>8.91988658905029</v>
       </c>
       <c r="H52" t="n">
         <v>1864</v>
@@ -1935,7 +1935,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G54" t="n">
-        <v>8.86582565307617</v>
+        <v>8.86582660675049</v>
       </c>
       <c r="H54" t="n">
         <v>1111</v>
@@ -2254,7 +2254,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H65" t="n">
         <v>148</v>
@@ -2283,7 +2283,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G66" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H74" t="n">
         <v>12985</v>
@@ -2544,7 +2544,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G75" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H75" t="n">
         <v>3495</v>
@@ -2573,7 +2573,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G77" t="n">
-        <v>8.8387975692749</v>
+        <v>8.83879661560059</v>
       </c>
       <c r="H77" t="n">
         <v>48906</v>
@@ -2805,7 +2805,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G84" t="n">
-        <v>8.91988563537598</v>
+        <v>8.91988658905029</v>
       </c>
       <c r="H84" t="n">
         <v>6138</v>
@@ -2834,7 +2834,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G85" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H85" t="n">
         <v>8000</v>
@@ -2921,7 +2921,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G88" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H88" t="n">
         <v>10082</v>
@@ -2950,7 +2950,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H89" t="n">
         <v>57790</v>
@@ -2979,7 +2979,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G90" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H90" t="n">
         <v>3936</v>
@@ -3037,7 +3037,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H92" t="n">
         <v>9500</v>
@@ -3095,7 +3095,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H94" t="n">
         <v>14704</v>
@@ -3124,7 +3124,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>8.87483596801758</v>
+        <v>8.87483692169189</v>
       </c>
       <c r="H95" t="n">
         <v>10000</v>
@@ -3153,7 +3153,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>8.91988563537598</v>
+        <v>8.91988658905029</v>
       </c>
       <c r="H96" t="n">
         <v>10000</v>
@@ -3211,7 +3211,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>8.86582565307617</v>
+        <v>8.86582660675049</v>
       </c>
       <c r="H98" t="n">
         <v>10772</v>
@@ -3298,7 +3298,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H101" t="n">
         <v>5914</v>
@@ -3327,7 +3327,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G102" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H102" t="n">
         <v>14771</v>
@@ -3356,7 +3356,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H103" t="n">
         <v>64</v>
@@ -3704,7 +3704,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G115" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H115" t="n">
         <v>52</v>
@@ -3733,7 +3733,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>8.71716213226318</v>
+        <v>8.71716022491455</v>
       </c>
       <c r="H121" t="n">
         <v>435</v>
@@ -3907,7 +3907,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>8.71716213226318</v>
+        <v>8.71716022491455</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>8.82077789306641</v>
+        <v>8.82077693939209</v>
       </c>
       <c r="H156" t="n">
         <v>442</v>
@@ -4951,7 +4951,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>8.82077789306641</v>
+        <v>8.82077693939209</v>
       </c>
       <c r="H158" t="n">
         <v>1120</v>
@@ -4980,7 +4980,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>8.64958763122559</v>
+        <v>8.6495885848999</v>
       </c>
       <c r="H159" t="n">
         <v>1862</v>
@@ -5183,7 +5183,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G166" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H166" t="n">
         <v>478</v>
@@ -5560,7 +5560,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>8.73968505859375</v>
+        <v>8.73968696594238</v>
       </c>
       <c r="H179" t="n">
         <v>1155</v>
@@ -6082,7 +6082,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G197" t="n">
-        <v>8.8387975692749</v>
+        <v>8.83879661560059</v>
       </c>
       <c r="H197" t="n">
         <v>664</v>
@@ -6111,7 +6111,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G198" t="n">
-        <v>8.8387975692749</v>
+        <v>8.83879661560059</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G199" t="n">
-        <v>8.8387975692749</v>
+        <v>8.83879661560059</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>9.0550365447998</v>
+        <v>9.05503559112549</v>
       </c>
       <c r="H200" t="n">
         <v>7102</v>
@@ -6198,7 +6198,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.0550365447998</v>
+        <v>9.05503559112549</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>9.10008525848389</v>
+        <v>9.1000862121582</v>
       </c>
       <c r="H207" t="n">
         <v>9160</v>
@@ -6401,7 +6401,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>9.190185546875</v>
+        <v>9.19018459320068</v>
       </c>
       <c r="H208" t="n">
         <v>10641</v>
@@ -6459,7 +6459,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G210" t="n">
-        <v>9.190185546875</v>
+        <v>9.19018459320068</v>
       </c>
       <c r="H210" t="n">
         <v>5170</v>
@@ -6604,7 +6604,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G215" t="n">
-        <v>9.36137580871582</v>
+        <v>9.3613748550415</v>
       </c>
       <c r="H215" t="n">
         <v>105</v>
@@ -6633,7 +6633,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G216" t="n">
-        <v>9.36137580871582</v>
+        <v>9.3613748550415</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>10.25</v>
       </c>
       <c r="G217" t="n">
-        <v>9.2352352142334</v>
+        <v>9.23523616790771</v>
       </c>
       <c r="H217" t="n">
         <v>2068</v>
@@ -6691,7 +6691,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G218" t="n">
-        <v>9.27127456665039</v>
+        <v>9.27127552032471</v>
       </c>
       <c r="H218" t="n">
         <v>12432</v>
@@ -6749,7 +6749,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>9.190185546875</v>
+        <v>9.19018459320068</v>
       </c>
       <c r="H220" t="n">
         <v>2000</v>
@@ -6778,7 +6778,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>9.190185546875</v>
+        <v>9.19018459320068</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038516998291</v>
       </c>
       <c r="H222" t="n">
         <v>45127</v>
@@ -6894,7 +6894,7 @@
         <v>10.5</v>
       </c>
       <c r="G225" t="n">
-        <v>9.46048545837402</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H225" t="n">
         <v>3628</v>
@@ -6952,7 +6952,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G227" t="n">
-        <v>9.38840579986572</v>
+        <v>9.38840675354004</v>
       </c>
       <c r="H227" t="n">
         <v>38098</v>
@@ -6981,7 +6981,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.46048545837402</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H228" t="n">
         <v>50010</v>
@@ -7010,7 +7010,7 @@
         <v>10.5</v>
       </c>
       <c r="G229" t="n">
-        <v>9.46048545837402</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>10.5</v>
       </c>
       <c r="G232" t="n">
-        <v>9.46048545837402</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H232" t="n">
         <v>8750</v>
@@ -7126,7 +7126,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038516998291</v>
       </c>
       <c r="H233" t="n">
         <v>947</v>
@@ -7155,7 +7155,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038516998291</v>
       </c>
       <c r="H234" t="n">
         <v>3210</v>
@@ -7184,7 +7184,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038516998291</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038516998291</v>
       </c>
       <c r="H236" t="n">
         <v>10000</v>
@@ -7242,7 +7242,7 @@
         <v>10.5</v>
       </c>
       <c r="G237" t="n">
-        <v>9.46048545837402</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H237" t="n">
         <v>2518</v>
@@ -7271,7 +7271,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038516998291</v>
       </c>
       <c r="H238" t="n">
         <v>20501</v>
@@ -7300,7 +7300,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038516998291</v>
       </c>
       <c r="H239" t="n">
         <v>11746</v>
@@ -7329,7 +7329,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038516998291</v>
       </c>
       <c r="H240" t="n">
         <v>9589</v>
@@ -7358,7 +7358,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038516998291</v>
       </c>
       <c r="H241" t="n">
         <v>458</v>
@@ -7387,7 +7387,7 @@
         <v>10.5</v>
       </c>
       <c r="G242" t="n">
-        <v>9.46048545837402</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H242" t="n">
         <v>427</v>
@@ -7416,7 +7416,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G243" t="n">
-        <v>9.29830455780029</v>
+        <v>9.29830551147461</v>
       </c>
       <c r="H243" t="n">
         <v>1059</v>
@@ -7445,7 +7445,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G244" t="n">
-        <v>9.29830455780029</v>
+        <v>9.29830551147461</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>10.5</v>
       </c>
       <c r="G245" t="n">
-        <v>9.46048545837402</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H245" t="n">
         <v>57006</v>
@@ -7503,7 +7503,7 @@
         <v>10.5</v>
       </c>
       <c r="G246" t="n">
-        <v>9.46048545837402</v>
+        <v>9.46048641204834</v>
       </c>
       <c r="H246" t="n">
         <v>3079</v>
@@ -7532,7 +7532,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>9.55058479309082</v>
+        <v>9.55058670043945</v>
       </c>
       <c r="H247" t="n">
         <v>33200</v>
@@ -7561,7 +7561,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>9.55058479309082</v>
+        <v>9.55058670043945</v>
       </c>
       <c r="H248" t="n">
         <v>19179</v>
@@ -7590,7 +7590,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>9.55058479309082</v>
+        <v>9.55058670043945</v>
       </c>
       <c r="H249" t="n">
         <v>53993</v>
@@ -7619,7 +7619,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G250" t="n">
-        <v>9.57761478424072</v>
+        <v>9.57761383056641</v>
       </c>
       <c r="H250" t="n">
         <v>3589</v>
@@ -7648,7 +7648,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H251" t="n">
         <v>3150</v>
@@ -7706,7 +7706,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G253" t="n">
-        <v>9.81187534332275</v>
+        <v>9.81187438964844</v>
       </c>
       <c r="H253" t="n">
         <v>4959</v>
@@ -7822,7 +7822,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>9.56860446929932</v>
+        <v>9.56860542297363</v>
       </c>
       <c r="H257" t="n">
         <v>1638</v>
@@ -7851,7 +7851,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>9.52355575561523</v>
+        <v>9.52355480194092</v>
       </c>
       <c r="H258" t="n">
         <v>559</v>
@@ -7880,7 +7880,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>9.55058479309082</v>
+        <v>9.55058670043945</v>
       </c>
       <c r="H259" t="n">
         <v>11700</v>
@@ -7909,7 +7909,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G260" t="n">
-        <v>9.62266540527344</v>
+        <v>9.62266445159912</v>
       </c>
       <c r="H260" t="n">
         <v>22172</v>
@@ -7996,7 +7996,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G263" t="n">
-        <v>9.55959510803223</v>
+        <v>9.55959606170654</v>
       </c>
       <c r="H263" t="n">
         <v>100</v>
@@ -8025,7 +8025,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G264" t="n">
-        <v>9.51454448699951</v>
+        <v>9.51454544067383</v>
       </c>
       <c r="H264" t="n">
         <v>3200</v>
@@ -8054,7 +8054,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G265" t="n">
-        <v>9.62266540527344</v>
+        <v>9.62266445159912</v>
       </c>
       <c r="H265" t="n">
         <v>2029</v>
@@ -8083,7 +8083,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G266" t="n">
-        <v>9.66771411895752</v>
+        <v>9.66771507263184</v>
       </c>
       <c r="H266" t="n">
         <v>34440</v>
@@ -8170,7 +8170,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>9.81187534332275</v>
+        <v>9.81187438964844</v>
       </c>
       <c r="H269" t="n">
         <v>11400</v>
@@ -8199,7 +8199,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G270" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H270" t="n">
         <v>10518</v>
@@ -8257,7 +8257,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G272" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H272" t="n">
         <v>69700</v>
@@ -8286,7 +8286,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G273" t="n">
-        <v>9.69474506378174</v>
+        <v>9.69474411010742</v>
       </c>
       <c r="H273" t="n">
         <v>4575</v>
@@ -8315,7 +8315,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G274" t="n">
-        <v>9.79385566711426</v>
+        <v>9.79385471343994</v>
       </c>
       <c r="H274" t="n">
         <v>45166</v>
@@ -8373,7 +8373,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>9.77583599090576</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H276" t="n">
         <v>7940</v>
@@ -8431,7 +8431,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>9.77583599090576</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H278" t="n">
         <v>43120</v>
@@ -8460,7 +8460,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>9.77583599090576</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H279" t="n">
         <v>21400</v>
@@ -8489,7 +8489,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>9.77583599090576</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H280" t="n">
         <v>2300</v>
@@ -8518,7 +8518,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>9.77583599090576</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H281" t="n">
         <v>8191</v>
@@ -8547,7 +8547,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>9.77583599090576</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H282" t="n">
         <v>5760</v>
@@ -8576,7 +8576,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G283" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H283" t="n">
         <v>2106</v>
@@ -8605,7 +8605,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G284" t="n">
-        <v>9.71276378631592</v>
+        <v>9.71276569366455</v>
       </c>
       <c r="H284" t="n">
         <v>23450</v>
@@ -8663,7 +8663,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G286" t="n">
-        <v>9.77583599090576</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H286" t="n">
         <v>2280</v>
@@ -8895,7 +8895,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G294" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H294" t="n">
         <v>13559</v>
@@ -8924,7 +8924,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>9.86593437194824</v>
+        <v>9.86593341827393</v>
       </c>
       <c r="H295" t="n">
         <v>1250</v>
@@ -9011,7 +9011,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H298" t="n">
         <v>3700</v>
@@ -9040,7 +9040,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H299" t="n">
         <v>20194</v>
@@ -9069,7 +9069,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G300" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H300" t="n">
         <v>2643</v>
@@ -9127,7 +9127,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G302" t="n">
-        <v>9.77583599090576</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H302" t="n">
         <v>10894</v>
@@ -9156,7 +9156,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G303" t="n">
-        <v>9.79385566711426</v>
+        <v>9.79385471343994</v>
       </c>
       <c r="H303" t="n">
         <v>9398</v>
@@ -9185,7 +9185,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G304" t="n">
-        <v>9.89296340942383</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H304" t="n">
         <v>11725</v>
@@ -9272,7 +9272,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G307" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H307" t="n">
         <v>7373</v>
@@ -9301,7 +9301,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G308" t="n">
-        <v>9.80286407470703</v>
+        <v>9.80286502838135</v>
       </c>
       <c r="H308" t="n">
         <v>10783</v>
@@ -9330,7 +9330,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G309" t="n">
-        <v>9.79385566711426</v>
+        <v>9.79385471343994</v>
       </c>
       <c r="H309" t="n">
         <v>1849</v>
@@ -9417,7 +9417,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G312" t="n">
-        <v>9.81187534332275</v>
+        <v>9.81187438964844</v>
       </c>
       <c r="H312" t="n">
         <v>3646</v>
@@ -9446,7 +9446,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G313" t="n">
-        <v>9.82989406585693</v>
+        <v>9.82989311218262</v>
       </c>
       <c r="H313" t="n">
         <v>1080</v>
@@ -9475,7 +9475,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G314" t="n">
-        <v>9.80286407470703</v>
+        <v>9.80286502838135</v>
       </c>
       <c r="H314" t="n">
         <v>2812</v>
@@ -9504,7 +9504,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>9.81187534332275</v>
+        <v>9.81187438964844</v>
       </c>
       <c r="H315" t="n">
         <v>22937</v>
@@ -9533,7 +9533,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G316" t="n">
-        <v>9.80286407470703</v>
+        <v>9.80286502838135</v>
       </c>
       <c r="H316" t="n">
         <v>38581</v>
@@ -9562,7 +9562,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G317" t="n">
-        <v>9.86593437194824</v>
+        <v>9.86593341827393</v>
       </c>
       <c r="H317" t="n">
         <v>21076</v>
@@ -9591,7 +9591,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>9.86593437194824</v>
+        <v>9.86593341827393</v>
       </c>
       <c r="H318" t="n">
         <v>33718</v>
@@ -9620,7 +9620,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G319" t="n">
-        <v>9.93801212310791</v>
+        <v>9.93801403045654</v>
       </c>
       <c r="H319" t="n">
         <v>78688</v>
@@ -9649,7 +9649,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>10.0010843276978</v>
+        <v>10.0010833740234</v>
       </c>
       <c r="H320" t="n">
         <v>55938</v>
@@ -9707,7 +9707,7 @@
         <v>11.25</v>
       </c>
       <c r="G322" t="n">
-        <v>10.1362352371216</v>
+        <v>10.1362342834473</v>
       </c>
       <c r="H322" t="n">
         <v>12281</v>
@@ -9736,7 +9736,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>10.2803945541382</v>
+        <v>10.2803936004639</v>
       </c>
       <c r="H323" t="n">
         <v>70878</v>
@@ -9765,7 +9765,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G324" t="n">
-        <v>10.5146541595459</v>
+        <v>10.5146532058716</v>
       </c>
       <c r="H324" t="n">
         <v>43038</v>
@@ -9794,7 +9794,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G325" t="n">
-        <v>11.3075313568115</v>
+        <v>11.3075323104858</v>
       </c>
       <c r="H325" t="n">
         <v>351489</v>
@@ -9823,7 +9823,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G326" t="n">
-        <v>11.6589212417603</v>
+        <v>11.6589202880859</v>
       </c>
       <c r="H326" t="n">
         <v>51959</v>
@@ -9852,7 +9852,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G327" t="n">
-        <v>12.0013008117676</v>
+        <v>12.0013017654419</v>
       </c>
       <c r="H327" t="n">
         <v>163719</v>
@@ -9881,7 +9881,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>12.0733814239502</v>
+        <v>12.0733804702759</v>
       </c>
       <c r="H328" t="n">
         <v>986804</v>
@@ -10026,7 +10026,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G333" t="n">
-        <v>12.0553617477417</v>
+        <v>12.0553607940674</v>
       </c>
       <c r="H333" t="n">
         <v>95115</v>
@@ -10084,7 +10084,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>12.0733814239502</v>
+        <v>12.0733804702759</v>
       </c>
       <c r="H335" t="n">
         <v>71696</v>
@@ -10113,7 +10113,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>11.8030824661255</v>
+        <v>11.8030815124512</v>
       </c>
       <c r="H336" t="n">
         <v>172168</v>
@@ -10142,7 +10142,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G337" t="n">
-        <v>11.7219915390015</v>
+        <v>11.7219924926758</v>
       </c>
       <c r="H337" t="n">
         <v>91150</v>
@@ -10200,7 +10200,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G339" t="n">
-        <v>11.6769409179688</v>
+        <v>11.6769428253174</v>
       </c>
       <c r="H339" t="n">
         <v>148255</v>
@@ -10229,7 +10229,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>11.6769409179688</v>
+        <v>11.6769428253174</v>
       </c>
       <c r="H340" t="n">
         <v>206230</v>
@@ -10287,7 +10287,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G342" t="n">
-        <v>11.6589212417603</v>
+        <v>11.6589202880859</v>
       </c>
       <c r="H342" t="n">
         <v>73637</v>
@@ -10316,7 +10316,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>11.8481311798096</v>
+        <v>11.8481321334839</v>
       </c>
       <c r="H343" t="n">
         <v>319564</v>
@@ -10374,7 +10374,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>12.2986307144165</v>
+        <v>12.2986297607422</v>
       </c>
       <c r="H345" t="n">
         <v>222706</v>
@@ -10403,7 +10403,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>12.2986307144165</v>
+        <v>12.2986297607422</v>
       </c>
       <c r="H346" t="n">
         <v>270020</v>
@@ -10461,7 +10461,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G348" t="n">
-        <v>12.4157600402832</v>
+        <v>12.4157609939575</v>
       </c>
       <c r="H348" t="n">
         <v>204010</v>
@@ -10490,7 +10490,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G349" t="n">
-        <v>12.5689296722412</v>
+        <v>12.5689306259155</v>
       </c>
       <c r="H349" t="n">
         <v>154343</v>
@@ -10519,7 +10519,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>12.4337797164917</v>
+        <v>12.433780670166</v>
       </c>
       <c r="H350" t="n">
         <v>70343</v>
@@ -10606,7 +10606,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G353" t="n">
-        <v>12.0013008117676</v>
+        <v>12.0013017654419</v>
       </c>
       <c r="H353" t="n">
         <v>90767</v>
@@ -10635,7 +10635,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>12.0733814239502</v>
+        <v>12.0733804702759</v>
       </c>
       <c r="H354" t="n">
         <v>82730</v>
@@ -10693,7 +10693,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G356" t="n">
-        <v>12.0823907852173</v>
+        <v>12.082389831543</v>
       </c>
       <c r="H356" t="n">
         <v>100444</v>
@@ -10751,7 +10751,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>12.2535810470581</v>
+        <v>12.2535800933838</v>
       </c>
       <c r="H358" t="n">
         <v>17581</v>
@@ -10809,7 +10809,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>12.0733814239502</v>
+        <v>12.0733804702759</v>
       </c>
       <c r="H360" t="n">
         <v>16894</v>
@@ -10838,7 +10838,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>11.8931798934937</v>
+        <v>11.893180847168</v>
       </c>
       <c r="H361" t="n">
         <v>254063</v>
@@ -10925,7 +10925,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>12.0733814239502</v>
+        <v>12.0733804702759</v>
       </c>
       <c r="H364" t="n">
         <v>16925</v>
@@ -11012,7 +11012,7 @@
         <v>13</v>
       </c>
       <c r="G367" t="n">
-        <v>11.7129802703857</v>
+        <v>11.7129812240601</v>
       </c>
       <c r="H367" t="n">
         <v>31507</v>
@@ -11041,7 +11041,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8030824661255</v>
+        <v>11.8030815124512</v>
       </c>
       <c r="H368" t="n">
         <v>57690</v>
@@ -11070,7 +11070,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G369" t="n">
-        <v>11.6318922042847</v>
+        <v>11.6318912506104</v>
       </c>
       <c r="H369" t="n">
         <v>20084</v>
@@ -11099,7 +11099,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G370" t="n">
-        <v>11.6048612594604</v>
+        <v>11.6048631668091</v>
       </c>
       <c r="H370" t="n">
         <v>54129</v>
@@ -11128,7 +11128,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5688228607178</v>
+        <v>11.5688219070435</v>
       </c>
       <c r="H371" t="n">
         <v>41864</v>
@@ -11273,7 +11273,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G376" t="n">
-        <v>11.9472398757935</v>
+        <v>11.9472417831421</v>
       </c>
       <c r="H376" t="n">
         <v>97992</v>
@@ -11331,7 +11331,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G378" t="n">
-        <v>11.8661527633667</v>
+        <v>11.8661518096924</v>
       </c>
       <c r="H378" t="n">
         <v>26303</v>
@@ -11360,7 +11360,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>11.8481311798096</v>
+        <v>11.8481321334839</v>
       </c>
       <c r="H379" t="n">
         <v>26402</v>
@@ -11389,7 +11389,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>11.8931798934937</v>
+        <v>11.893180847168</v>
       </c>
       <c r="H380" t="n">
         <v>72914</v>
@@ -11476,7 +11476,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>11.8030824661255</v>
+        <v>11.8030815124512</v>
       </c>
       <c r="H383" t="n">
         <v>36087</v>
@@ -11505,7 +11505,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G384" t="n">
-        <v>11.8931798934937</v>
+        <v>11.893180847168</v>
       </c>
       <c r="H384" t="n">
         <v>85810</v>
@@ -11563,7 +11563,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G386" t="n">
-        <v>11.74001121521</v>
+        <v>11.7400121688843</v>
       </c>
       <c r="H386" t="n">
         <v>24726</v>
@@ -11592,7 +11592,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G387" t="n">
-        <v>11.6859512329102</v>
+        <v>11.6859521865845</v>
       </c>
       <c r="H387" t="n">
         <v>30586</v>
@@ -11621,7 +11621,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G388" t="n">
-        <v>11.6589212417603</v>
+        <v>11.6589202880859</v>
       </c>
       <c r="H388" t="n">
         <v>24585</v>
@@ -11650,7 +11650,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G389" t="n">
-        <v>11.5147609710693</v>
+        <v>11.5147619247437</v>
       </c>
       <c r="H389" t="n">
         <v>39594</v>
@@ -11679,7 +11679,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>11.5778322219849</v>
+        <v>11.5778312683105</v>
       </c>
       <c r="H390" t="n">
         <v>33186</v>
@@ -11708,7 +11708,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G391" t="n">
-        <v>11.5598106384277</v>
+        <v>11.5598115921021</v>
       </c>
       <c r="H391" t="n">
         <v>13985</v>
@@ -11766,7 +11766,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G393" t="n">
-        <v>11.6138734817505</v>
+        <v>11.6138715744019</v>
       </c>
       <c r="H393" t="n">
         <v>28134</v>
@@ -11795,7 +11795,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>11.5778322219849</v>
+        <v>11.5778312683105</v>
       </c>
       <c r="H394" t="n">
         <v>7456</v>
@@ -11824,7 +11824,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G395" t="n">
-        <v>11.6048612594604</v>
+        <v>11.6048631668091</v>
       </c>
       <c r="H395" t="n">
         <v>21078</v>
@@ -11853,7 +11853,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G396" t="n">
-        <v>11.6138734817505</v>
+        <v>11.6138715744019</v>
       </c>
       <c r="H396" t="n">
         <v>16840</v>
@@ -11969,7 +11969,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>11.3525810241699</v>
+        <v>11.3525819778442</v>
       </c>
       <c r="H400" t="n">
         <v>40741</v>
@@ -11998,7 +11998,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G401" t="n">
-        <v>11.0912923812866</v>
+        <v>11.0912933349609</v>
       </c>
       <c r="H401" t="n">
         <v>33453</v>
@@ -12027,7 +12027,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G402" t="n">
-        <v>11.2174320220947</v>
+        <v>11.217432975769</v>
       </c>
       <c r="H402" t="n">
         <v>45075</v>
@@ -12056,7 +12056,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G403" t="n">
-        <v>11.1453523635864</v>
+        <v>11.1453504562378</v>
       </c>
       <c r="H403" t="n">
         <v>17065</v>
@@ -12085,7 +12085,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>11.2174320220947</v>
+        <v>11.217432975769</v>
       </c>
       <c r="H404" t="n">
         <v>43054</v>
@@ -12143,7 +12143,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G406" t="n">
-        <v>11.2444610595703</v>
+        <v>11.2444620132446</v>
       </c>
       <c r="H406" t="n">
         <v>68026</v>
@@ -12172,7 +12172,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>11.5327816009521</v>
+        <v>11.5327825546265</v>
       </c>
       <c r="H407" t="n">
         <v>77258</v>
@@ -12201,7 +12201,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>11.5778322219849</v>
+        <v>11.5778312683105</v>
       </c>
       <c r="H408" t="n">
         <v>218833</v>
@@ -12230,7 +12230,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G409" t="n">
-        <v>11.5688228607178</v>
+        <v>11.5688219070435</v>
       </c>
       <c r="H409" t="n">
         <v>17980</v>
@@ -12259,7 +12259,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>11.5327816009521</v>
+        <v>11.5327825546265</v>
       </c>
       <c r="H410" t="n">
         <v>12688</v>
@@ -12288,7 +12288,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>11.5778322219849</v>
+        <v>11.5778312683105</v>
       </c>
       <c r="H411" t="n">
         <v>50166</v>
@@ -12317,7 +12317,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G412" t="n">
-        <v>11.6769409179688</v>
+        <v>11.6769428253174</v>
       </c>
       <c r="H412" t="n">
         <v>54821</v>
@@ -12375,7 +12375,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G414" t="n">
-        <v>11.5417909622192</v>
+        <v>11.5417919158936</v>
       </c>
       <c r="H414" t="n">
         <v>121306</v>
@@ -12404,7 +12404,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G415" t="n">
-        <v>11.36159324646</v>
+        <v>11.3615922927856</v>
       </c>
       <c r="H415" t="n">
         <v>16324</v>
@@ -12433,7 +12433,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>11.5778322219849</v>
+        <v>11.5778312683105</v>
       </c>
       <c r="H416" t="n">
         <v>28774</v>
@@ -12462,7 +12462,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>11.397632598877</v>
+        <v>11.3976316452026</v>
       </c>
       <c r="H417" t="n">
         <v>56834</v>
@@ -12549,7 +12549,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G420" t="n">
-        <v>11.4516916275024</v>
+        <v>11.4516925811768</v>
       </c>
       <c r="H420" t="n">
         <v>5117</v>
@@ -12578,7 +12578,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>11.5778322219849</v>
+        <v>11.5778312683105</v>
       </c>
       <c r="H421" t="n">
         <v>229727</v>
@@ -12607,7 +12607,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>11.5508012771606</v>
+        <v>11.5508031845093</v>
       </c>
       <c r="H422" t="n">
         <v>36471</v>
@@ -12636,7 +12636,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G423" t="n">
-        <v>11.5508012771606</v>
+        <v>11.5508031845093</v>
       </c>
       <c r="H423" t="n">
         <v>10199</v>
@@ -12752,7 +12752,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G427" t="n">
-        <v>11.4697103500366</v>
+        <v>11.4697113037109</v>
       </c>
       <c r="H427" t="n">
         <v>43133</v>
@@ -12781,7 +12781,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G428" t="n">
-        <v>11.4607009887695</v>
+        <v>11.4607019424438</v>
       </c>
       <c r="H428" t="n">
         <v>43415</v>
@@ -12810,7 +12810,7 @@
         <v>12.75</v>
       </c>
       <c r="G429" t="n">
-        <v>11.4877319335938</v>
+        <v>11.4877309799194</v>
       </c>
       <c r="H429" t="n">
         <v>25791</v>
@@ -12926,7 +12926,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>11.5778322219849</v>
+        <v>11.5778312683105</v>
       </c>
       <c r="H433" t="n">
         <v>66860</v>
@@ -12984,7 +12984,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>12.1184301376343</v>
+        <v>12.11842918396</v>
       </c>
       <c r="H435" t="n">
         <v>101466</v>
@@ -13100,7 +13100,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>11.8030824661255</v>
+        <v>11.8030815124512</v>
       </c>
       <c r="H439" t="n">
         <v>64563</v>
@@ -13129,7 +13129,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>12.0733814239502</v>
+        <v>12.0733804702759</v>
       </c>
       <c r="H440" t="n">
         <v>64801</v>
@@ -13158,7 +13158,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G441" t="n">
-        <v>11.9562511444092</v>
+        <v>11.9562501907349</v>
       </c>
       <c r="H441" t="n">
         <v>24522</v>
@@ -13187,7 +13187,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G442" t="n">
-        <v>12.2896223068237</v>
+        <v>12.2896203994751</v>
       </c>
       <c r="H442" t="n">
         <v>198527</v>
@@ -13245,7 +13245,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>12.0733814239502</v>
+        <v>12.0733804702759</v>
       </c>
       <c r="H444" t="n">
         <v>26069</v>
@@ -13274,7 +13274,7 @@
         <v>13.5</v>
       </c>
       <c r="G445" t="n">
-        <v>12.163480758667</v>
+        <v>12.1634798049927</v>
       </c>
       <c r="H445" t="n">
         <v>75349</v>
@@ -13303,7 +13303,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G446" t="n">
-        <v>12.2535810470581</v>
+        <v>12.2535800933838</v>
       </c>
       <c r="H446" t="n">
         <v>54923</v>
@@ -13332,7 +13332,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>12.2535810470581</v>
+        <v>12.2535800933838</v>
       </c>
       <c r="H447" t="n">
         <v>61161</v>
@@ -13361,7 +13361,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>12.2535810470581</v>
+        <v>12.2535800933838</v>
       </c>
       <c r="H448" t="n">
         <v>80711</v>
@@ -13390,7 +13390,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G449" t="n">
-        <v>12.2445707321167</v>
+        <v>12.244571685791</v>
       </c>
       <c r="H449" t="n">
         <v>58522</v>
@@ -13477,7 +13477,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G452" t="n">
-        <v>12.4337797164917</v>
+        <v>12.433780670166</v>
       </c>
       <c r="H452" t="n">
         <v>140534</v>
@@ -13564,7 +13564,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G455" t="n">
-        <v>12.3436803817749</v>
+        <v>12.3436813354492</v>
       </c>
       <c r="H455" t="n">
         <v>45994</v>
@@ -13622,7 +13622,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>12.3436803817749</v>
+        <v>12.3436813354492</v>
       </c>
       <c r="H457" t="n">
         <v>69003</v>
@@ -13651,7 +13651,7 @@
         <v>14</v>
       </c>
       <c r="G458" t="n">
-        <v>12.6139812469482</v>
+        <v>12.6139802932739</v>
       </c>
       <c r="H458" t="n">
         <v>94927</v>
@@ -13709,7 +13709,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G460" t="n">
-        <v>12.5599193572998</v>
+        <v>12.5599184036255</v>
       </c>
       <c r="H460" t="n">
         <v>83879</v>
@@ -13738,7 +13738,7 @@
         <v>14</v>
       </c>
       <c r="G461" t="n">
-        <v>12.6139812469482</v>
+        <v>12.6139802932739</v>
       </c>
       <c r="H461" t="n">
         <v>57363</v>
@@ -13825,7 +13825,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G464" t="n">
-        <v>12.4968509674072</v>
+        <v>12.4968500137329</v>
       </c>
       <c r="H464" t="n">
         <v>20139</v>
@@ -13854,7 +13854,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>12.4788312911987</v>
+        <v>12.4788303375244</v>
       </c>
       <c r="H465" t="n">
         <v>21815</v>
@@ -13941,7 +13941,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G468" t="n">
-        <v>12.6320018768311</v>
+        <v>12.6319999694824</v>
       </c>
       <c r="H468" t="n">
         <v>66196</v>
@@ -13970,7 +13970,7 @@
         <v>14</v>
       </c>
       <c r="G469" t="n">
-        <v>12.6139812469482</v>
+        <v>12.6139802932739</v>
       </c>
       <c r="H469" t="n">
         <v>42342</v>
@@ -13999,7 +13999,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>12.6590299606323</v>
+        <v>12.6590309143066</v>
       </c>
       <c r="H470" t="n">
         <v>43109</v>
@@ -14057,7 +14057,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G472" t="n">
-        <v>12.7040796279907</v>
+        <v>12.704080581665</v>
       </c>
       <c r="H472" t="n">
         <v>37727</v>
@@ -14115,7 +14115,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G474" t="n">
-        <v>12.6590299606323</v>
+        <v>12.6590309143066</v>
       </c>
       <c r="H474" t="n">
         <v>36011</v>
@@ -14173,7 +14173,7 @@
         <v>14</v>
       </c>
       <c r="G476" t="n">
-        <v>12.6139812469482</v>
+        <v>12.6139802932739</v>
       </c>
       <c r="H476" t="n">
         <v>220806</v>
@@ -14231,7 +14231,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>12.6590299606323</v>
+        <v>12.6590309143066</v>
       </c>
       <c r="H478" t="n">
         <v>374971</v>
@@ -14289,7 +14289,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G480" t="n">
-        <v>12.5689296722412</v>
+        <v>12.5689306259155</v>
       </c>
       <c r="H480" t="n">
         <v>27713</v>
@@ -14376,7 +14376,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G483" t="n">
-        <v>12.5959596633911</v>
+        <v>12.5959587097168</v>
       </c>
       <c r="H483" t="n">
         <v>20343</v>
@@ -14434,7 +14434,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>12.5689296722412</v>
+        <v>12.5689306259155</v>
       </c>
       <c r="H485" t="n">
         <v>45644</v>
@@ -14492,7 +14492,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G487" t="n">
-        <v>12.6590299606323</v>
+        <v>12.6590309143066</v>
       </c>
       <c r="H487" t="n">
         <v>37231</v>
@@ -14521,7 +14521,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6590299606323</v>
+        <v>12.6590309143066</v>
       </c>
       <c r="H488" t="n">
         <v>12949</v>
@@ -14550,7 +14550,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>12.5689296722412</v>
+        <v>12.5689306259155</v>
       </c>
       <c r="H489" t="n">
         <v>25212</v>
@@ -14579,7 +14579,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G490" t="n">
-        <v>12.6590299606323</v>
+        <v>12.6590309143066</v>
       </c>
       <c r="H490" t="n">
         <v>56385</v>
@@ -14666,7 +14666,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G493" t="n">
-        <v>12.4337797164917</v>
+        <v>12.433780670166</v>
       </c>
       <c r="H493" t="n">
         <v>74288</v>
@@ -14724,7 +14724,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>12.3977403640747</v>
+        <v>12.397741317749</v>
       </c>
       <c r="H495" t="n">
         <v>21443</v>
@@ -14753,7 +14753,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G496" t="n">
-        <v>12.3977403640747</v>
+        <v>12.397741317749</v>
       </c>
       <c r="H496" t="n">
         <v>16190</v>
@@ -14811,7 +14811,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G498" t="n">
-        <v>12.3256607055664</v>
+        <v>12.3256616592407</v>
       </c>
       <c r="H498" t="n">
         <v>16531</v>
@@ -14840,7 +14840,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>12.3346700668335</v>
+        <v>12.3346710205078</v>
       </c>
       <c r="H499" t="n">
         <v>72968</v>
@@ -14898,7 +14898,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G501" t="n">
-        <v>12.3076410293579</v>
+        <v>12.3076391220093</v>
       </c>
       <c r="H501" t="n">
         <v>37502</v>
@@ -14956,7 +14956,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G503" t="n">
-        <v>12.2625904083252</v>
+        <v>12.2625894546509</v>
       </c>
       <c r="H503" t="n">
         <v>27217</v>
@@ -15043,7 +15043,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>12.2535810470581</v>
+        <v>12.2535800933838</v>
       </c>
       <c r="H506" t="n">
         <v>30148</v>
@@ -15072,7 +15072,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>12.0733814239502</v>
+        <v>12.0733804702759</v>
       </c>
       <c r="H507" t="n">
         <v>28410</v>
@@ -15130,7 +15130,7 @@
         <v>13.5</v>
       </c>
       <c r="G509" t="n">
-        <v>12.163480758667</v>
+        <v>12.1634798049927</v>
       </c>
       <c r="H509" t="n">
         <v>17475</v>
@@ -15159,7 +15159,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G510" t="n">
-        <v>12.3076410293579</v>
+        <v>12.3076391220093</v>
       </c>
       <c r="H510" t="n">
         <v>22660</v>
@@ -15246,7 +15246,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G513" t="n">
-        <v>12.3076410293579</v>
+        <v>12.3076391220093</v>
       </c>
       <c r="H513" t="n">
         <v>6295</v>
@@ -15333,7 +15333,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>12.3436803817749</v>
+        <v>12.3436813354492</v>
       </c>
       <c r="H516" t="n">
         <v>16296</v>
@@ -15362,7 +15362,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G517" t="n">
-        <v>12.5058622360229</v>
+        <v>12.5058612823486</v>
       </c>
       <c r="H517" t="n">
         <v>56631</v>
@@ -15420,7 +15420,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G519" t="n">
-        <v>12.5779399871826</v>
+        <v>12.5779390335083</v>
       </c>
       <c r="H519" t="n">
         <v>400862</v>
@@ -15565,7 +15565,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>12.7040796279907</v>
+        <v>12.704080581665</v>
       </c>
       <c r="H524" t="n">
         <v>18162</v>
@@ -15594,7 +15594,7 @@
         <v>14</v>
       </c>
       <c r="G525" t="n">
-        <v>12.6139812469482</v>
+        <v>12.6139802932739</v>
       </c>
       <c r="H525" t="n">
         <v>28810</v>
@@ -15681,7 +15681,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G528" t="n">
-        <v>12.5779399871826</v>
+        <v>12.5779390335083</v>
       </c>
       <c r="H528" t="n">
         <v>17748</v>
@@ -15710,7 +15710,7 @@
         <v>14</v>
       </c>
       <c r="G529" t="n">
-        <v>12.6139812469482</v>
+        <v>12.6139802932739</v>
       </c>
       <c r="H529" t="n">
         <v>23448</v>
@@ -15739,7 +15739,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G530" t="n">
-        <v>12.5959596633911</v>
+        <v>12.5959587097168</v>
       </c>
       <c r="H530" t="n">
         <v>74663</v>
@@ -15797,7 +15797,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>12.4337797164917</v>
+        <v>12.433780670166</v>
       </c>
       <c r="H532" t="n">
         <v>36369</v>
@@ -15826,7 +15826,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G533" t="n">
-        <v>12.3256607055664</v>
+        <v>12.3256616592407</v>
       </c>
       <c r="H533" t="n">
         <v>54195</v>
@@ -15855,7 +15855,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G534" t="n">
-        <v>12.3076410293579</v>
+        <v>12.3076391220093</v>
       </c>
       <c r="H534" t="n">
         <v>16295</v>
@@ -15884,7 +15884,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>12.2535810470581</v>
+        <v>12.2535800933838</v>
       </c>
       <c r="H535" t="n">
         <v>20589</v>
@@ -15942,7 +15942,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G537" t="n">
-        <v>11.9472398757935</v>
+        <v>11.9472417831421</v>
       </c>
       <c r="H537" t="n">
         <v>63390</v>
@@ -15971,7 +15971,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G538" t="n">
-        <v>11.929220199585</v>
+        <v>11.9292211532593</v>
       </c>
       <c r="H538" t="n">
         <v>24240</v>
@@ -16000,7 +16000,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G539" t="n">
-        <v>11.8030824661255</v>
+        <v>11.8030815124512</v>
       </c>
       <c r="H539" t="n">
         <v>19499</v>
@@ -16087,7 +16087,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>11.8030824661255</v>
+        <v>11.8030815124512</v>
       </c>
       <c r="H542" t="n">
         <v>17412</v>
@@ -16261,7 +16261,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G548" t="n">
-        <v>11.6949596405029</v>
+        <v>11.6949615478516</v>
       </c>
       <c r="H548" t="n">
         <v>26349</v>
@@ -16319,7 +16319,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G550" t="n">
-        <v>11.6409015655518</v>
+        <v>11.6409025192261</v>
       </c>
       <c r="H550" t="n">
         <v>25649</v>
@@ -16348,7 +16348,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G551" t="n">
-        <v>11.6949596405029</v>
+        <v>11.6949615478516</v>
       </c>
       <c r="H551" t="n">
         <v>20983</v>
@@ -16377,7 +16377,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G552" t="n">
-        <v>11.7310018539429</v>
+        <v>11.7310028076172</v>
       </c>
       <c r="H552" t="n">
         <v>582671</v>
@@ -16435,7 +16435,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G554" t="n">
-        <v>11.3525810241699</v>
+        <v>11.3525819778442</v>
       </c>
       <c r="H554" t="n">
         <v>54581</v>
@@ -16464,7 +16464,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G555" t="n">
-        <v>10.866042137146</v>
+        <v>10.8660430908203</v>
       </c>
       <c r="H555" t="n">
         <v>55289</v>
@@ -16493,7 +16493,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G556" t="n">
-        <v>10.8480205535889</v>
+        <v>10.8480224609375</v>
       </c>
       <c r="H556" t="n">
         <v>19437</v>
@@ -16551,7 +16551,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G558" t="n">
-        <v>11.0282220840454</v>
+        <v>11.0282230377197</v>
       </c>
       <c r="H558" t="n">
         <v>17257</v>
@@ -16580,7 +16580,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G559" t="n">
-        <v>11.0462427139282</v>
+        <v>11.0462446212769</v>
       </c>
       <c r="H559" t="n">
         <v>32128</v>
@@ -16667,7 +16667,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G562" t="n">
-        <v>11.2264413833618</v>
+        <v>11.2264423370361</v>
       </c>
       <c r="H562" t="n">
         <v>19439</v>
@@ -16754,7 +16754,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G565" t="n">
-        <v>11.7310018539429</v>
+        <v>11.7310028076172</v>
       </c>
       <c r="H565" t="n">
         <v>207603</v>
@@ -16783,7 +16783,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G566" t="n">
-        <v>11.929220199585</v>
+        <v>11.9292211532593</v>
       </c>
       <c r="H566" t="n">
         <v>185128</v>
@@ -16841,7 +16841,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G568" t="n">
-        <v>12.1454601287842</v>
+        <v>12.1454610824585</v>
       </c>
       <c r="H568" t="n">
         <v>43144</v>
@@ -16870,7 +16870,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G569" t="n">
-        <v>12.0733814239502</v>
+        <v>12.0733804702759</v>
       </c>
       <c r="H569" t="n">
         <v>55878</v>
@@ -16899,7 +16899,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G570" t="n">
-        <v>12.2175397872925</v>
+        <v>12.2175407409668</v>
       </c>
       <c r="H570" t="n">
         <v>65134</v>
@@ -16928,7 +16928,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>12.2535810470581</v>
+        <v>12.2535800933838</v>
       </c>
       <c r="H571" t="n">
         <v>76093</v>
@@ -16957,7 +16957,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G572" t="n">
-        <v>12.4878416061401</v>
+        <v>12.4878406524658</v>
       </c>
       <c r="H572" t="n">
         <v>49845</v>
@@ -17044,7 +17044,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G575" t="n">
-        <v>12.5779399871826</v>
+        <v>12.5779390335083</v>
       </c>
       <c r="H575" t="n">
         <v>38369</v>
@@ -17160,7 +17160,7 @@
         <v>14</v>
       </c>
       <c r="G579" t="n">
-        <v>12.6139812469482</v>
+        <v>12.6139802932739</v>
       </c>
       <c r="H579" t="n">
         <v>47634</v>
@@ -17189,7 +17189,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G580" t="n">
-        <v>12.5779399871826</v>
+        <v>12.5779390335083</v>
       </c>
       <c r="H580" t="n">
         <v>65852</v>
@@ -17218,7 +17218,7 @@
         <v>14</v>
       </c>
       <c r="G581" t="n">
-        <v>12.6139812469482</v>
+        <v>12.6139802932739</v>
       </c>
       <c r="H581" t="n">
         <v>46907</v>
@@ -17334,7 +17334,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G585" t="n">
-        <v>12.7761611938477</v>
+        <v>12.7761602401733</v>
       </c>
       <c r="H585" t="n">
         <v>63012</v>
@@ -17363,7 +17363,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G586" t="n">
-        <v>13.2807188034058</v>
+        <v>13.2807178497314</v>
       </c>
       <c r="H586" t="n">
         <v>100885</v>
@@ -17392,7 +17392,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>13.118540763855</v>
+        <v>13.1185398101807</v>
       </c>
       <c r="H587" t="n">
         <v>91238</v>
@@ -17421,7 +17421,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G588" t="n">
-        <v>13.046459197998</v>
+        <v>13.0464582443237</v>
       </c>
       <c r="H588" t="n">
         <v>77148</v>
@@ -17450,7 +17450,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G589" t="n">
-        <v>13.3528003692627</v>
+        <v>13.3527994155884</v>
       </c>
       <c r="H589" t="n">
         <v>136346</v>
@@ -17537,7 +17537,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>13.154580116272</v>
+        <v>13.1545791625977</v>
       </c>
       <c r="H592" t="n">
         <v>67211</v>
@@ -17653,7 +17653,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G596" t="n">
-        <v>13.4428987503052</v>
+        <v>13.4428977966309</v>
       </c>
       <c r="H596" t="n">
         <v>68738</v>
@@ -17769,7 +17769,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G600" t="n">
-        <v>14.3979578018188</v>
+        <v>14.3979568481445</v>
       </c>
       <c r="H600" t="n">
         <v>122086</v>
@@ -17798,7 +17798,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G601" t="n">
-        <v>14.0375576019287</v>
+        <v>14.0375566482544</v>
       </c>
       <c r="H601" t="n">
         <v>114031</v>
@@ -17827,7 +17827,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G602" t="n">
-        <v>14.3619174957275</v>
+        <v>14.3619165420532</v>
       </c>
       <c r="H602" t="n">
         <v>54712</v>
@@ -17856,7 +17856,7 @@
         <v>15.5</v>
       </c>
       <c r="G603" t="n">
-        <v>14.2383556365967</v>
+        <v>14.2383546829224</v>
       </c>
       <c r="H603" t="n">
         <v>176624</v>
@@ -17972,7 +17972,7 @@
         <v>15.5</v>
       </c>
       <c r="G607" t="n">
-        <v>14.2383556365967</v>
+        <v>14.2383546829224</v>
       </c>
       <c r="H607" t="n">
         <v>50628</v>
@@ -18001,7 +18001,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G608" t="n">
-        <v>14.164867401123</v>
+        <v>14.1648654937744</v>
       </c>
       <c r="H608" t="n">
         <v>34955</v>
@@ -18175,7 +18175,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G614" t="n">
-        <v>13.5218448638916</v>
+        <v>13.5218458175659</v>
       </c>
       <c r="H614" t="n">
         <v>135707</v>
@@ -18262,7 +18262,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G617" t="n">
-        <v>14.1281232833862</v>
+        <v>14.1281242370605</v>
       </c>
       <c r="H617" t="n">
         <v>55058</v>
@@ -18320,7 +18320,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G619" t="n">
-        <v>14.3853330612183</v>
+        <v>14.3853321075439</v>
       </c>
       <c r="H619" t="n">
         <v>61695</v>
@@ -18349,7 +18349,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G620" t="n">
-        <v>14.1464948654175</v>
+        <v>14.1464939117432</v>
       </c>
       <c r="H620" t="n">
         <v>47308</v>
@@ -18378,7 +18378,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G621" t="n">
-        <v>13.9995183944702</v>
+        <v>13.9995174407959</v>
       </c>
       <c r="H621" t="n">
         <v>51339</v>
@@ -18465,7 +18465,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>14.4220762252808</v>
+        <v>14.4220752716064</v>
       </c>
       <c r="H624" t="n">
         <v>125787</v>
@@ -18610,7 +18610,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G629" t="n">
-        <v>14.2016115188599</v>
+        <v>14.2016105651855</v>
       </c>
       <c r="H629" t="n">
         <v>39296</v>
@@ -18639,7 +18639,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G630" t="n">
-        <v>13.9260301589966</v>
+        <v>13.9260292053223</v>
       </c>
       <c r="H630" t="n">
         <v>39144</v>
@@ -18668,7 +18668,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G631" t="n">
-        <v>13.5402164459229</v>
+        <v>13.5402154922485</v>
       </c>
       <c r="H631" t="n">
         <v>36869</v>
@@ -18697,7 +18697,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G632" t="n">
-        <v>13.3564958572388</v>
+        <v>13.3564949035645</v>
       </c>
       <c r="H632" t="n">
         <v>71465</v>
@@ -18755,7 +18755,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G634" t="n">
-        <v>13.3564958572388</v>
+        <v>13.3564949035645</v>
       </c>
       <c r="H634" t="n">
         <v>51629</v>
@@ -18813,7 +18813,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G636" t="n">
-        <v>13.3381252288818</v>
+        <v>13.3381233215332</v>
       </c>
       <c r="H636" t="n">
         <v>33851</v>
@@ -18842,7 +18842,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G637" t="n">
-        <v>13.3564958572388</v>
+        <v>13.3564949035645</v>
       </c>
       <c r="H637" t="n">
         <v>12019</v>
@@ -18871,7 +18871,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G638" t="n">
-        <v>13.3381252288818</v>
+        <v>13.3381233215332</v>
       </c>
       <c r="H638" t="n">
         <v>15391</v>
@@ -18958,7 +18958,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G641" t="n">
-        <v>13.2646360397339</v>
+        <v>13.2646350860596</v>
       </c>
       <c r="H641" t="n">
         <v>19675</v>
@@ -18987,7 +18987,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G642" t="n">
-        <v>13.0625438690186</v>
+        <v>13.0625429153442</v>
       </c>
       <c r="H642" t="n">
         <v>8732</v>
@@ -19016,7 +19016,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G643" t="n">
-        <v>13.0625438690186</v>
+        <v>13.0625429153442</v>
       </c>
       <c r="H643" t="n">
         <v>23236</v>
@@ -19045,7 +19045,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G644" t="n">
-        <v>13.2095193862915</v>
+        <v>13.2095174789429</v>
       </c>
       <c r="H644" t="n">
         <v>11168</v>
@@ -19103,7 +19103,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G646" t="n">
-        <v>13.1360321044922</v>
+        <v>13.1360301971436</v>
       </c>
       <c r="H646" t="n">
         <v>10395</v>
@@ -19132,7 +19132,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G647" t="n">
-        <v>13.1360321044922</v>
+        <v>13.1360301971436</v>
       </c>
       <c r="H647" t="n">
         <v>17578</v>
@@ -19161,7 +19161,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G648" t="n">
-        <v>12.970682144165</v>
+        <v>12.9706811904907</v>
       </c>
       <c r="H648" t="n">
         <v>43570</v>
@@ -19277,7 +19277,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G652" t="n">
-        <v>12.8053331375122</v>
+        <v>12.8053321838379</v>
       </c>
       <c r="H652" t="n">
         <v>25195</v>
@@ -19306,7 +19306,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G653" t="n">
-        <v>12.7502183914185</v>
+        <v>12.7502174377441</v>
       </c>
       <c r="H653" t="n">
         <v>25003</v>
@@ -19335,7 +19335,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G654" t="n">
-        <v>12.7502183914185</v>
+        <v>12.7502174377441</v>
       </c>
       <c r="H654" t="n">
         <v>48943</v>
@@ -19422,7 +19422,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.2830076217651</v>
+        <v>13.2830066680908</v>
       </c>
       <c r="H657" t="n">
         <v>35610</v>
@@ -19567,7 +19567,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G662" t="n">
-        <v>12.7318458557129</v>
+        <v>12.7318449020386</v>
       </c>
       <c r="H662" t="n">
         <v>35571</v>
@@ -19654,7 +19654,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.4930076599121</v>
+        <v>12.4930086135864</v>
       </c>
       <c r="H665" t="n">
         <v>19345</v>
@@ -19712,7 +19712,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>12.1255655288696</v>
+        <v>12.1255664825439</v>
       </c>
       <c r="H667" t="n">
         <v>23253</v>
@@ -19741,7 +19741,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G668" t="n">
-        <v>12.0520782470703</v>
+        <v>12.0520792007446</v>
       </c>
       <c r="H668" t="n">
         <v>19347</v>
@@ -19799,7 +19799,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G670" t="n">
-        <v>12.0704507827759</v>
+        <v>12.0704498291016</v>
       </c>
       <c r="H670" t="n">
         <v>17409</v>
@@ -19828,7 +19828,7 @@
         <v>13</v>
       </c>
       <c r="G671" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418449401855</v>
       </c>
       <c r="H671" t="n">
         <v>11997</v>
@@ -19857,7 +19857,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G672" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051027297974</v>
       </c>
       <c r="H672" t="n">
         <v>23468</v>
@@ -19915,7 +19915,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G674" t="n">
-        <v>12.0520782470703</v>
+        <v>12.0520792007446</v>
       </c>
       <c r="H674" t="n">
         <v>12157</v>
@@ -19944,7 +19944,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G675" t="n">
-        <v>11.9969615936279</v>
+        <v>11.9969625473022</v>
       </c>
       <c r="H675" t="n">
         <v>20753</v>
@@ -20031,7 +20031,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G678" t="n">
-        <v>12.8053331375122</v>
+        <v>12.8053321838379</v>
       </c>
       <c r="H678" t="n">
         <v>77708</v>
@@ -20089,7 +20089,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>12.3092880249023</v>
+        <v>12.3092861175537</v>
       </c>
       <c r="H680" t="n">
         <v>34421</v>
@@ -20118,7 +20118,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G681" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051027297974</v>
       </c>
       <c r="H681" t="n">
         <v>66643</v>
@@ -20147,7 +20147,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G682" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051027297974</v>
       </c>
       <c r="H682" t="n">
         <v>19278</v>
@@ -20234,7 +20234,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G685" t="n">
-        <v>11.8499841690063</v>
+        <v>11.8499851226807</v>
       </c>
       <c r="H685" t="n">
         <v>24280</v>
@@ -20263,7 +20263,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G686" t="n">
-        <v>11.6295204162598</v>
+        <v>11.6295213699341</v>
       </c>
       <c r="H686" t="n">
         <v>17809</v>
@@ -20292,7 +20292,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G687" t="n">
-        <v>11.9969615936279</v>
+        <v>11.9969625473022</v>
       </c>
       <c r="H687" t="n">
         <v>27016</v>
@@ -20321,7 +20321,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G688" t="n">
-        <v>12.1990537643433</v>
+        <v>12.1990556716919</v>
       </c>
       <c r="H688" t="n">
         <v>23826</v>
@@ -20350,7 +20350,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G689" t="n">
-        <v>11.9969615936279</v>
+        <v>11.9969625473022</v>
       </c>
       <c r="H689" t="n">
         <v>26917</v>
@@ -20379,7 +20379,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G690" t="n">
-        <v>12.0704507827759</v>
+        <v>12.0704498291016</v>
       </c>
       <c r="H690" t="n">
         <v>22703</v>
@@ -20408,7 +20408,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>12.3092880249023</v>
+        <v>12.3092861175537</v>
       </c>
       <c r="H691" t="n">
         <v>51716</v>
@@ -20466,7 +20466,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G693" t="n">
-        <v>12.3827753067017</v>
+        <v>12.382776260376</v>
       </c>
       <c r="H693" t="n">
         <v>25062</v>
@@ -20524,7 +20524,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G695" t="n">
-        <v>12.1255655288696</v>
+        <v>12.1255664825439</v>
       </c>
       <c r="H695" t="n">
         <v>16112</v>
@@ -20553,7 +20553,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G696" t="n">
-        <v>12.1255655288696</v>
+        <v>12.1255664825439</v>
       </c>
       <c r="H696" t="n">
         <v>29302</v>
@@ -20582,7 +20582,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G697" t="n">
-        <v>11.9969615936279</v>
+        <v>11.9969625473022</v>
       </c>
       <c r="H697" t="n">
         <v>7540</v>
@@ -20640,7 +20640,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G699" t="n">
-        <v>12.1071949005127</v>
+        <v>12.107195854187</v>
       </c>
       <c r="H699" t="n">
         <v>23417</v>
@@ -20669,7 +20669,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G700" t="n">
-        <v>12.1071949005127</v>
+        <v>12.107195854187</v>
       </c>
       <c r="H700" t="n">
         <v>24980</v>
@@ -20727,7 +20727,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G702" t="n">
-        <v>11.776496887207</v>
+        <v>11.7764978408813</v>
       </c>
       <c r="H702" t="n">
         <v>42526</v>
@@ -20785,7 +20785,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G704" t="n">
-        <v>11.776496887207</v>
+        <v>11.7764978408813</v>
       </c>
       <c r="H704" t="n">
         <v>111386</v>
@@ -20814,7 +20814,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G705" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051027297974</v>
       </c>
       <c r="H705" t="n">
         <v>16833</v>
@@ -20901,7 +20901,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G708" t="n">
-        <v>11.2804517745972</v>
+        <v>11.2804508209229</v>
       </c>
       <c r="H708" t="n">
         <v>41975</v>
@@ -20930,7 +20930,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G709" t="n">
-        <v>11.2253351211548</v>
+        <v>11.2253341674805</v>
       </c>
       <c r="H709" t="n">
         <v>66928</v>
@@ -20988,7 +20988,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G711" t="n">
-        <v>11.2253351211548</v>
+        <v>11.2253341674805</v>
       </c>
       <c r="H711" t="n">
         <v>27214</v>
@@ -21017,7 +21017,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G712" t="n">
-        <v>10.9681253433228</v>
+        <v>10.9681262969971</v>
       </c>
       <c r="H712" t="n">
         <v>33615</v>
@@ -21046,7 +21046,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G713" t="n">
-        <v>11.0599851608276</v>
+        <v>11.059986114502</v>
       </c>
       <c r="H713" t="n">
         <v>18428</v>
@@ -21075,7 +21075,7 @@
         <v>12</v>
       </c>
       <c r="G714" t="n">
-        <v>11.0232419967651</v>
+        <v>11.0232429504395</v>
       </c>
       <c r="H714" t="n">
         <v>44154</v>
@@ -21162,7 +21162,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G717" t="n">
-        <v>10.6374292373657</v>
+        <v>10.6374282836914</v>
       </c>
       <c r="H717" t="n">
         <v>15352</v>
@@ -21191,7 +21191,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G718" t="n">
-        <v>10.5823125839233</v>
+        <v>10.5823135375977</v>
       </c>
       <c r="H718" t="n">
         <v>32772</v>
@@ -21336,7 +21336,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G723" t="n">
-        <v>10.527195930481</v>
+        <v>10.5271968841553</v>
       </c>
       <c r="H723" t="n">
         <v>141266</v>
@@ -21365,7 +21365,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G724" t="n">
-        <v>10.5455675125122</v>
+        <v>10.5455684661865</v>
       </c>
       <c r="H724" t="n">
         <v>81085</v>
@@ -21394,7 +21394,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G725" t="n">
-        <v>10.5455675125122</v>
+        <v>10.5455684661865</v>
       </c>
       <c r="H725" t="n">
         <v>11959</v>
@@ -21423,7 +21423,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G726" t="n">
-        <v>10.7844047546387</v>
+        <v>10.784405708313</v>
       </c>
       <c r="H726" t="n">
         <v>27360</v>
@@ -21452,7 +21452,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>10.6558017730713</v>
+        <v>10.6558027267456</v>
       </c>
       <c r="H727" t="n">
         <v>45564</v>
@@ -21481,7 +21481,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G728" t="n">
-        <v>10.5455675125122</v>
+        <v>10.5455684661865</v>
       </c>
       <c r="H728" t="n">
         <v>30621</v>
@@ -21539,7 +21539,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G730" t="n">
-        <v>10.6374292373657</v>
+        <v>10.6374282836914</v>
       </c>
       <c r="H730" t="n">
         <v>57080</v>
@@ -21568,7 +21568,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G731" t="n">
-        <v>10.5455675125122</v>
+        <v>10.5455684661865</v>
       </c>
       <c r="H731" t="n">
         <v>26969</v>
@@ -21655,7 +21655,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G734" t="n">
-        <v>10.2148714065552</v>
+        <v>10.2148704528809</v>
       </c>
       <c r="H734" t="n">
         <v>24046</v>
@@ -21684,7 +21684,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G735" t="n">
-        <v>10.2699871063232</v>
+        <v>10.2699880599976</v>
       </c>
       <c r="H735" t="n">
         <v>31073</v>
@@ -21713,7 +21713,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G736" t="n">
-        <v>10.3251028060913</v>
+        <v>10.3251037597656</v>
       </c>
       <c r="H736" t="n">
         <v>42397</v>
@@ -21858,7 +21858,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G741" t="n">
-        <v>10.1597566604614</v>
+        <v>10.1597557067871</v>
       </c>
       <c r="H741" t="n">
         <v>32046</v>
@@ -21887,7 +21887,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G742" t="n">
-        <v>10.2699871063232</v>
+        <v>10.2699880599976</v>
       </c>
       <c r="H742" t="n">
         <v>24494</v>
@@ -21916,7 +21916,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G743" t="n">
-        <v>10.3067321777344</v>
+        <v>10.3067331314087</v>
       </c>
       <c r="H743" t="n">
         <v>18813</v>
@@ -21945,7 +21945,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G744" t="n">
-        <v>10.123010635376</v>
+        <v>10.1230115890503</v>
       </c>
       <c r="H744" t="n">
         <v>26803</v>
@@ -22032,7 +22032,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>10.3434743881226</v>
+        <v>10.3434753417969</v>
       </c>
       <c r="H747" t="n">
         <v>31303</v>
@@ -22061,7 +22061,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G748" t="n">
-        <v>10.123010635376</v>
+        <v>10.1230115890503</v>
       </c>
       <c r="H748" t="n">
         <v>46409</v>
@@ -22090,7 +22090,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G749" t="n">
-        <v>10.1597566604614</v>
+        <v>10.1597557067871</v>
       </c>
       <c r="H749" t="n">
         <v>10525</v>
@@ -22119,7 +22119,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G750" t="n">
-        <v>9.77394199371338</v>
+        <v>9.7739429473877</v>
       </c>
       <c r="H750" t="n">
         <v>79581</v>
@@ -22177,7 +22177,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>9.82905673980713</v>
+        <v>9.82905769348145</v>
       </c>
       <c r="H752" t="n">
         <v>77372</v>
@@ -22206,7 +22206,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G753" t="n">
-        <v>10.1597566604614</v>
+        <v>10.1597557067871</v>
       </c>
       <c r="H753" t="n">
         <v>84270</v>
@@ -22264,7 +22264,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G755" t="n">
-        <v>10.2699871063232</v>
+        <v>10.2699880599976</v>
       </c>
       <c r="H755" t="n">
         <v>34506</v>
@@ -22293,7 +22293,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G756" t="n">
-        <v>10.0678930282593</v>
+        <v>10.0678949356079</v>
       </c>
       <c r="H756" t="n">
         <v>6571</v>
@@ -22322,7 +22322,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G757" t="n">
-        <v>9.97603321075439</v>
+        <v>9.97603416442871</v>
       </c>
       <c r="H757" t="n">
         <v>15326</v>
@@ -22351,7 +22351,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G758" t="n">
-        <v>9.95766258239746</v>
+        <v>9.95766162872314</v>
       </c>
       <c r="H758" t="n">
         <v>15039</v>
@@ -22438,7 +22438,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G761" t="n">
-        <v>10.2148714065552</v>
+        <v>10.2148704528809</v>
       </c>
       <c r="H761" t="n">
         <v>24337</v>
@@ -22496,7 +22496,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G763" t="n">
-        <v>10.2516145706177</v>
+        <v>10.251615524292</v>
       </c>
       <c r="H763" t="n">
         <v>15823</v>
@@ -22525,7 +22525,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G764" t="n">
-        <v>10.3618469238281</v>
+        <v>10.3618478775024</v>
       </c>
       <c r="H764" t="n">
         <v>13053</v>
@@ -22699,7 +22699,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>10.8395214080811</v>
+        <v>10.8395223617554</v>
       </c>
       <c r="H770" t="n">
         <v>13921</v>
@@ -22728,7 +22728,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G771" t="n">
-        <v>10.9681253433228</v>
+        <v>10.9681262969971</v>
       </c>
       <c r="H771" t="n">
         <v>32796</v>
@@ -22786,7 +22786,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G773" t="n">
-        <v>10.8395214080811</v>
+        <v>10.8395223617554</v>
       </c>
       <c r="H773" t="n">
         <v>29760</v>
@@ -22815,7 +22815,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G774" t="n">
-        <v>10.8395214080811</v>
+        <v>10.8395223617554</v>
       </c>
       <c r="H774" t="n">
         <v>26099</v>
@@ -22873,7 +22873,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G776" t="n">
-        <v>10.7292900085449</v>
+        <v>10.7292909622192</v>
       </c>
       <c r="H776" t="n">
         <v>29539</v>
@@ -22902,7 +22902,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G777" t="n">
-        <v>10.7844047546387</v>
+        <v>10.784405708313</v>
       </c>
       <c r="H777" t="n">
         <v>13471</v>
@@ -22931,7 +22931,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>10.6558017730713</v>
+        <v>10.6558027267456</v>
       </c>
       <c r="H778" t="n">
         <v>16149</v>
@@ -23047,7 +23047,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G782" t="n">
-        <v>10.7109174728394</v>
+        <v>10.710916519165</v>
       </c>
       <c r="H782" t="n">
         <v>5620</v>
@@ -23076,7 +23076,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G783" t="n">
-        <v>10.6006841659546</v>
+        <v>10.6006860733032</v>
       </c>
       <c r="H783" t="n">
         <v>24179</v>
@@ -23105,7 +23105,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G784" t="n">
-        <v>10.6374292373657</v>
+        <v>10.6374282836914</v>
       </c>
       <c r="H784" t="n">
         <v>22660</v>
@@ -23192,7 +23192,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G787" t="n">
-        <v>10.6006841659546</v>
+        <v>10.6006860733032</v>
       </c>
       <c r="H787" t="n">
         <v>7178</v>
@@ -23221,7 +23221,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G788" t="n">
-        <v>10.5823125839233</v>
+        <v>10.5823135375977</v>
       </c>
       <c r="H788" t="n">
         <v>12288</v>
@@ -23250,7 +23250,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G789" t="n">
-        <v>10.527195930481</v>
+        <v>10.5271968841553</v>
       </c>
       <c r="H789" t="n">
         <v>20045</v>
@@ -23308,7 +23308,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G791" t="n">
-        <v>10.2148714065552</v>
+        <v>10.2148704528809</v>
       </c>
       <c r="H791" t="n">
         <v>19180</v>
@@ -23366,7 +23366,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G793" t="n">
-        <v>10.3434743881226</v>
+        <v>10.3434753417969</v>
       </c>
       <c r="H793" t="n">
         <v>5226</v>
@@ -23395,7 +23395,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G794" t="n">
-        <v>10.4904527664185</v>
+        <v>10.4904518127441</v>
       </c>
       <c r="H794" t="n">
         <v>11946</v>
@@ -23453,7 +23453,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G796" t="n">
-        <v>10.5088233947754</v>
+        <v>10.5088243484497</v>
       </c>
       <c r="H796" t="n">
         <v>10323</v>
@@ -23511,7 +23511,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>10.6558017730713</v>
+        <v>10.6558027267456</v>
       </c>
       <c r="H798" t="n">
         <v>26328</v>
@@ -23540,7 +23540,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>10.6558017730713</v>
+        <v>10.6558027267456</v>
       </c>
       <c r="H799" t="n">
         <v>38463</v>
@@ -23569,7 +23569,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G800" t="n">
-        <v>10.5455675125122</v>
+        <v>10.5455684661865</v>
       </c>
       <c r="H800" t="n">
         <v>15103</v>
@@ -23627,7 +23627,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G802" t="n">
-        <v>10.6006841659546</v>
+        <v>10.6006860733032</v>
       </c>
       <c r="H802" t="n">
         <v>22188</v>
@@ -23656,7 +23656,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G803" t="n">
-        <v>10.5455675125122</v>
+        <v>10.5455684661865</v>
       </c>
       <c r="H803" t="n">
         <v>12960</v>
@@ -23685,7 +23685,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G804" t="n">
-        <v>10.527195930481</v>
+        <v>10.5271968841553</v>
       </c>
       <c r="H804" t="n">
         <v>43296</v>
@@ -23714,7 +23714,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G805" t="n">
-        <v>10.5823125839233</v>
+        <v>10.5823135375977</v>
       </c>
       <c r="H805" t="n">
         <v>8446</v>
@@ -23743,7 +23743,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G806" t="n">
-        <v>10.6374292373657</v>
+        <v>10.6374282836914</v>
       </c>
       <c r="H806" t="n">
         <v>22024</v>
@@ -23772,7 +23772,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G807" t="n">
-        <v>10.8395214080811</v>
+        <v>10.8395223617554</v>
       </c>
       <c r="H807" t="n">
         <v>27681</v>
@@ -23830,7 +23830,7 @@
         <v>12</v>
       </c>
       <c r="G809" t="n">
-        <v>11.0232419967651</v>
+        <v>11.0232429504395</v>
       </c>
       <c r="H809" t="n">
         <v>33705</v>
@@ -23888,7 +23888,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G811" t="n">
-        <v>10.4904527664185</v>
+        <v>10.4904518127441</v>
       </c>
       <c r="H811" t="n">
         <v>41004</v>
@@ -23917,7 +23917,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5823125839233</v>
+        <v>10.5823135375977</v>
       </c>
       <c r="H812" t="n">
         <v>8811</v>
@@ -23946,7 +23946,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G813" t="n">
-        <v>10.5088233947754</v>
+        <v>10.5088243484497</v>
       </c>
       <c r="H813" t="n">
         <v>6949</v>
@@ -24033,7 +24033,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G816" t="n">
-        <v>11.243706703186</v>
+        <v>11.2437076568604</v>
       </c>
       <c r="H816" t="n">
         <v>130139</v>
@@ -24062,7 +24062,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G817" t="n">
-        <v>11.2988224029541</v>
+        <v>11.2988233566284</v>
       </c>
       <c r="H817" t="n">
         <v>64392</v>
@@ -24120,7 +24120,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5009164810181</v>
+        <v>11.5009174346924</v>
       </c>
       <c r="H819" t="n">
         <v>30170</v>
@@ -24149,7 +24149,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>11.5744037628174</v>
+        <v>11.5744047164917</v>
       </c>
       <c r="H820" t="n">
         <v>52455</v>
@@ -24178,7 +24178,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>11.5744037628174</v>
+        <v>11.5744047164917</v>
       </c>
       <c r="H821" t="n">
         <v>37889</v>
@@ -24236,7 +24236,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>11.6295204162598</v>
+        <v>11.6295213699341</v>
       </c>
       <c r="H823" t="n">
         <v>32043</v>
@@ -24410,7 +24410,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G829" t="n">
-        <v>11.6295204162598</v>
+        <v>11.6295213699341</v>
       </c>
       <c r="H829" t="n">
         <v>33602</v>
@@ -24526,7 +24526,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G833" t="n">
-        <v>11.4090566635132</v>
+        <v>11.4090557098389</v>
       </c>
       <c r="H833" t="n">
         <v>62638</v>
@@ -24555,7 +24555,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G834" t="n">
-        <v>11.2804517745972</v>
+        <v>11.2804508209229</v>
       </c>
       <c r="H834" t="n">
         <v>21258</v>
@@ -24584,7 +24584,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>11.3906841278076</v>
+        <v>11.3906850814819</v>
       </c>
       <c r="H835" t="n">
         <v>18232</v>
@@ -24613,7 +24613,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G836" t="n">
-        <v>11.6295204162598</v>
+        <v>11.6295213699341</v>
       </c>
       <c r="H836" t="n">
         <v>19773</v>
@@ -24642,7 +24642,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G837" t="n">
-        <v>11.6846370697021</v>
+        <v>11.6846380233765</v>
       </c>
       <c r="H837" t="n">
         <v>37803</v>
@@ -24671,7 +24671,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5927753448486</v>
+        <v>11.5927762985229</v>
       </c>
       <c r="H838" t="n">
         <v>35190</v>
@@ -24700,7 +24700,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>11.5744037628174</v>
+        <v>11.5744047164917</v>
       </c>
       <c r="H839" t="n">
         <v>30833</v>
@@ -24787,7 +24787,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G842" t="n">
-        <v>11.5927753448486</v>
+        <v>11.5927762985229</v>
       </c>
       <c r="H842" t="n">
         <v>50833</v>
@@ -24874,7 +24874,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G845" t="n">
-        <v>11.4457988739014</v>
+        <v>11.4457998275757</v>
       </c>
       <c r="H845" t="n">
         <v>311672</v>
@@ -24903,7 +24903,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G846" t="n">
-        <v>11.6295204162598</v>
+        <v>11.6295213699341</v>
       </c>
       <c r="H846" t="n">
         <v>164445</v>
@@ -24932,7 +24932,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G847" t="n">
-        <v>11.776496887207</v>
+        <v>11.7764978408813</v>
       </c>
       <c r="H847" t="n">
         <v>88509</v>
@@ -24961,7 +24961,7 @@
         <v>13</v>
       </c>
       <c r="G848" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418449401855</v>
       </c>
       <c r="H848" t="n">
         <v>164023</v>
@@ -24990,7 +24990,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G849" t="n">
-        <v>12.0704507827759</v>
+        <v>12.0704498291016</v>
       </c>
       <c r="H849" t="n">
         <v>119148</v>
@@ -25019,7 +25019,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G850" t="n">
-        <v>12.1990537643433</v>
+        <v>12.1990556716919</v>
       </c>
       <c r="H850" t="n">
         <v>131994</v>
@@ -25048,7 +25048,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G851" t="n">
-        <v>12.1990537643433</v>
+        <v>12.1990556716919</v>
       </c>
       <c r="H851" t="n">
         <v>61746</v>
@@ -25106,7 +25106,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G853" t="n">
-        <v>12.1439380645752</v>
+        <v>12.1439390182495</v>
       </c>
       <c r="H853" t="n">
         <v>29379</v>
@@ -25135,7 +25135,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G854" t="n">
-        <v>11.6846370697021</v>
+        <v>11.6846380233765</v>
       </c>
       <c r="H854" t="n">
         <v>86975</v>
@@ -25164,7 +25164,7 @@
         <v>13</v>
       </c>
       <c r="G855" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418449401855</v>
       </c>
       <c r="H855" t="n">
         <v>50128</v>
@@ -25193,7 +25193,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G856" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051027297974</v>
       </c>
       <c r="H856" t="n">
         <v>63134</v>
@@ -25222,7 +25222,7 @@
         <v>13</v>
       </c>
       <c r="G857" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418449401855</v>
       </c>
       <c r="H857" t="n">
         <v>14044</v>
@@ -25251,7 +25251,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G858" t="n">
-        <v>11.905101776123</v>
+        <v>11.9051027297974</v>
       </c>
       <c r="H858" t="n">
         <v>32041</v>
@@ -25396,7 +25396,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G863" t="n">
-        <v>12.0125007629395</v>
+        <v>12.0124998092651</v>
       </c>
       <c r="H863" t="n">
         <v>37881</v>
@@ -25541,7 +25541,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>12.3524770736694</v>
+        <v>12.3524761199951</v>
       </c>
       <c r="H868" t="n">
         <v>57547</v>
@@ -25570,7 +25570,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G869" t="n">
-        <v>12.2958145141602</v>
+        <v>12.2958135604858</v>
       </c>
       <c r="H869" t="n">
         <v>16656</v>
@@ -25628,7 +25628,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G871" t="n">
-        <v>12.409140586853</v>
+        <v>12.4091396331787</v>
       </c>
       <c r="H871" t="n">
         <v>105396</v>
@@ -25773,7 +25773,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>13.1268682479858</v>
+        <v>13.1268672943115</v>
       </c>
       <c r="H876" t="n">
         <v>98043</v>
@@ -25802,7 +25802,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G877" t="n">
-        <v>13.1835298538208</v>
+        <v>13.1835289001465</v>
       </c>
       <c r="H877" t="n">
         <v>43371</v>
@@ -25831,7 +25831,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G878" t="n">
-        <v>13.2401943206787</v>
+        <v>13.2401933670044</v>
       </c>
       <c r="H878" t="n">
         <v>52129</v>
@@ -25860,7 +25860,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G879" t="n">
-        <v>13.3346309661865</v>
+        <v>13.3346300125122</v>
       </c>
       <c r="H879" t="n">
         <v>29336</v>
@@ -25889,7 +25889,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G880" t="n">
-        <v>13.4290685653687</v>
+        <v>13.4290676116943</v>
       </c>
       <c r="H880" t="n">
         <v>202506</v>
@@ -25918,7 +25918,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G881" t="n">
-        <v>13.6557197570801</v>
+        <v>13.6557188034058</v>
       </c>
       <c r="H881" t="n">
         <v>92427</v>
@@ -25947,7 +25947,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G882" t="n">
-        <v>13.9012594223022</v>
+        <v>13.9012584686279</v>
       </c>
       <c r="H882" t="n">
         <v>79221</v>
@@ -25976,7 +25976,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G883" t="n">
-        <v>13.6557197570801</v>
+        <v>13.6557188034058</v>
       </c>
       <c r="H883" t="n">
         <v>87772</v>
@@ -26034,7 +26034,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G885" t="n">
-        <v>13.7312698364258</v>
+        <v>13.7312707901001</v>
       </c>
       <c r="H885" t="n">
         <v>145087</v>
@@ -26063,7 +26063,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G886" t="n">
-        <v>13.7123832702637</v>
+        <v>13.7123823165894</v>
       </c>
       <c r="H886" t="n">
         <v>88031</v>
@@ -26121,7 +26121,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G888" t="n">
-        <v>13.7123832702637</v>
+        <v>13.7123823165894</v>
       </c>
       <c r="H888" t="n">
         <v>32639</v>
@@ -26150,7 +26150,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G889" t="n">
-        <v>13.4857301712036</v>
+        <v>13.4857311248779</v>
       </c>
       <c r="H889" t="n">
         <v>50920</v>
@@ -26179,7 +26179,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G890" t="n">
-        <v>13.4857301712036</v>
+        <v>13.4857311248779</v>
       </c>
       <c r="H890" t="n">
         <v>47034</v>
@@ -26237,7 +26237,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G892" t="n">
-        <v>13.6557197570801</v>
+        <v>13.6557188034058</v>
       </c>
       <c r="H892" t="n">
         <v>64487</v>
@@ -26266,7 +26266,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G893" t="n">
-        <v>13.4290685653687</v>
+        <v>13.4290676116943</v>
       </c>
       <c r="H893" t="n">
         <v>43307</v>
@@ -26295,7 +26295,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G894" t="n">
-        <v>13.3724060058594</v>
+        <v>13.3724069595337</v>
       </c>
       <c r="H894" t="n">
         <v>208586</v>
@@ -26324,7 +26324,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G895" t="n">
-        <v>13.3346309661865</v>
+        <v>13.3346300125122</v>
       </c>
       <c r="H895" t="n">
         <v>46504</v>
@@ -26382,7 +26382,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>11.5214223861694</v>
+        <v>11.5214233398438</v>
       </c>
       <c r="H897" t="n">
         <v>1099754</v>
@@ -26411,7 +26411,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G898" t="n">
-        <v>11.8425130844116</v>
+        <v>11.8425121307373</v>
       </c>
       <c r="H898" t="n">
         <v>542195</v>
@@ -26440,7 +26440,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>12.0880508422852</v>
+        <v>12.0880517959595</v>
       </c>
       <c r="H899" t="n">
         <v>384021</v>
@@ -26498,7 +26498,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G901" t="n">
-        <v>11.8425130844116</v>
+        <v>11.8425121307373</v>
       </c>
       <c r="H901" t="n">
         <v>104875</v>
@@ -26527,7 +26527,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G902" t="n">
-        <v>11.7480745315552</v>
+        <v>11.7480726242065</v>
       </c>
       <c r="H902" t="n">
         <v>73837</v>
@@ -26585,7 +26585,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G904" t="n">
-        <v>11.785849571228</v>
+        <v>11.7858486175537</v>
       </c>
       <c r="H904" t="n">
         <v>61947</v>
@@ -26614,7 +26614,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>11.7291870117188</v>
+        <v>11.7291879653931</v>
       </c>
       <c r="H905" t="n">
         <v>65960</v>
@@ -26701,7 +26701,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G908" t="n">
-        <v>11.8425130844116</v>
+        <v>11.8425121307373</v>
       </c>
       <c r="H908" t="n">
         <v>44842</v>
@@ -26759,7 +26759,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G910" t="n">
-        <v>11.5214223861694</v>
+        <v>11.5214233398438</v>
       </c>
       <c r="H910" t="n">
         <v>75713</v>
@@ -26875,7 +26875,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G914" t="n">
-        <v>11.1247835159302</v>
+        <v>11.1247825622559</v>
       </c>
       <c r="H914" t="n">
         <v>108643</v>
@@ -26933,7 +26933,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G916" t="n">
-        <v>11.3136587142944</v>
+        <v>11.3136596679688</v>
       </c>
       <c r="H916" t="n">
         <v>61548</v>
@@ -26991,7 +26991,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>11.5403118133545</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H918" t="n">
         <v>93570</v>
@@ -27020,7 +27020,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G919" t="n">
-        <v>11.3892107009888</v>
+        <v>11.3892097473145</v>
       </c>
       <c r="H919" t="n">
         <v>40951</v>
@@ -27165,7 +27165,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G924" t="n">
-        <v>11.6536359786987</v>
+        <v>11.653636932373</v>
       </c>
       <c r="H924" t="n">
         <v>19065</v>
@@ -27223,7 +27223,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G926" t="n">
-        <v>11.5025358200073</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H926" t="n">
         <v>16775</v>
@@ -27310,7 +27310,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G929" t="n">
-        <v>11.5214223861694</v>
+        <v>11.5214233398438</v>
       </c>
       <c r="H929" t="n">
         <v>14033</v>
@@ -27397,7 +27397,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G932" t="n">
-        <v>11.5025358200073</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H932" t="n">
         <v>33755</v>
@@ -27426,7 +27426,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G933" t="n">
-        <v>11.5214223861694</v>
+        <v>11.5214233398438</v>
       </c>
       <c r="H933" t="n">
         <v>33240</v>
@@ -27513,7 +27513,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G936" t="n">
-        <v>11.3136587142944</v>
+        <v>11.3136596679688</v>
       </c>
       <c r="H936" t="n">
         <v>79678</v>
@@ -27542,7 +27542,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G937" t="n">
-        <v>11.1247835159302</v>
+        <v>11.1247825622559</v>
       </c>
       <c r="H937" t="n">
         <v>85172</v>
@@ -27658,7 +27658,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G941" t="n">
-        <v>11.5403118133545</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H941" t="n">
         <v>131770</v>
@@ -27687,7 +27687,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G942" t="n">
-        <v>11.5403118133545</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H942" t="n">
         <v>92762</v>
@@ -27716,7 +27716,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G943" t="n">
-        <v>11.2758846282959</v>
+        <v>11.2758836746216</v>
       </c>
       <c r="H943" t="n">
         <v>68390</v>
@@ -27745,7 +27745,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G944" t="n">
-        <v>11.2758846282959</v>
+        <v>11.2758836746216</v>
       </c>
       <c r="H944" t="n">
         <v>70477</v>
@@ -27803,7 +27803,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G946" t="n">
-        <v>11.2003335952759</v>
+        <v>11.2003345489502</v>
       </c>
       <c r="H946" t="n">
         <v>107324</v>
@@ -27832,7 +27832,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G947" t="n">
-        <v>11.3892107009888</v>
+        <v>11.3892097473145</v>
       </c>
       <c r="H947" t="n">
         <v>98958</v>
@@ -27919,7 +27919,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G950" t="n">
-        <v>11.2003335952759</v>
+        <v>11.2003345489502</v>
       </c>
       <c r="H950" t="n">
         <v>32730</v>
@@ -27948,7 +27948,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G951" t="n">
-        <v>11.2003335952759</v>
+        <v>11.2003345489502</v>
       </c>
       <c r="H951" t="n">
         <v>24813</v>
@@ -27977,7 +27977,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G952" t="n">
-        <v>11.1247835159302</v>
+        <v>11.1247825622559</v>
       </c>
       <c r="H952" t="n">
         <v>47841</v>
@@ -28006,7 +28006,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>11.2381076812744</v>
+        <v>11.2381086349487</v>
       </c>
       <c r="H953" t="n">
         <v>57068</v>
@@ -28064,7 +28064,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G955" t="n">
-        <v>10.7470321655273</v>
+        <v>10.7470331192017</v>
       </c>
       <c r="H955" t="n">
         <v>118351</v>
@@ -28093,7 +28093,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G956" t="n">
-        <v>10.7848072052002</v>
+        <v>10.7848081588745</v>
       </c>
       <c r="H956" t="n">
         <v>84552</v>
@@ -28180,7 +28180,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>11.0114583969116</v>
+        <v>11.0114593505859</v>
       </c>
       <c r="H959" t="n">
         <v>91040</v>
@@ -28238,7 +28238,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G961" t="n">
-        <v>10.9359083175659</v>
+        <v>10.9359073638916</v>
       </c>
       <c r="H961" t="n">
         <v>54047</v>
@@ -28441,7 +28441,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G968" t="n">
-        <v>11.634747505188</v>
+        <v>11.6347484588623</v>
       </c>
       <c r="H968" t="n">
         <v>192096</v>
@@ -28557,7 +28557,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G972" t="n">
-        <v>11.8425130844116</v>
+        <v>11.8425121307373</v>
       </c>
       <c r="H972" t="n">
         <v>92839</v>
@@ -28644,7 +28644,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G975" t="n">
-        <v>11.634747505188</v>
+        <v>11.6347484588623</v>
       </c>
       <c r="H975" t="n">
         <v>50595</v>
@@ -28760,7 +28760,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G979" t="n">
-        <v>11.8425130844116</v>
+        <v>11.8425121307373</v>
       </c>
       <c r="H979" t="n">
         <v>93132</v>
@@ -28876,7 +28876,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G983" t="n">
-        <v>11.7480745315552</v>
+        <v>11.7480726242065</v>
       </c>
       <c r="H983" t="n">
         <v>81447</v>
@@ -28905,7 +28905,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G984" t="n">
-        <v>11.785849571228</v>
+        <v>11.7858486175537</v>
       </c>
       <c r="H984" t="n">
         <v>60579</v>
@@ -28934,7 +28934,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G985" t="n">
-        <v>11.7291870117188</v>
+        <v>11.7291879653931</v>
       </c>
       <c r="H985" t="n">
         <v>44297</v>
@@ -28963,7 +28963,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G986" t="n">
-        <v>11.6725244522095</v>
+        <v>11.6725234985352</v>
       </c>
       <c r="H986" t="n">
         <v>27172</v>
@@ -29021,7 +29021,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>11.6536359786987</v>
+        <v>11.653636932373</v>
       </c>
       <c r="H988" t="n">
         <v>45514</v>
@@ -29079,7 +29079,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G990" t="n">
-        <v>11.5214223861694</v>
+        <v>11.5214233398438</v>
       </c>
       <c r="H990" t="n">
         <v>14946</v>
@@ -29108,7 +29108,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G991" t="n">
-        <v>11.3892107009888</v>
+        <v>11.3892097473145</v>
       </c>
       <c r="H991" t="n">
         <v>38492</v>
@@ -29137,7 +29137,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>11.5025358200073</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H992" t="n">
         <v>29817</v>
@@ -29195,7 +29195,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G994" t="n">
-        <v>12.2958145141602</v>
+        <v>12.2958135604858</v>
       </c>
       <c r="H994" t="n">
         <v>345936</v>
@@ -29224,7 +29224,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>12.6546773910522</v>
+        <v>12.6546783447266</v>
       </c>
       <c r="H995" t="n">
         <v>364444</v>
@@ -29253,7 +29253,7 @@
         <v>13.5</v>
       </c>
       <c r="G996" t="n">
-        <v>12.7491159439087</v>
+        <v>12.749116897583</v>
       </c>
       <c r="H996" t="n">
         <v>146940</v>
@@ -29282,7 +29282,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>12.9191045761108</v>
+        <v>12.9191036224365</v>
       </c>
       <c r="H997" t="n">
         <v>105572</v>
@@ -29311,7 +29311,7 @@
         <v>13.5</v>
       </c>
       <c r="G998" t="n">
-        <v>12.7491159439087</v>
+        <v>12.749116897583</v>
       </c>
       <c r="H998" t="n">
         <v>127248</v>
@@ -29340,7 +29340,7 @@
         <v>13.5</v>
       </c>
       <c r="G999" t="n">
-        <v>12.7491159439087</v>
+        <v>12.749116897583</v>
       </c>
       <c r="H999" t="n">
         <v>116523</v>
@@ -29369,7 +29369,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>12.9002151489258</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1000" t="n">
         <v>171927</v>
@@ -29398,7 +29398,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.013542175293</v>
+        <v>13.0135431289673</v>
       </c>
       <c r="H1001" t="n">
         <v>82257</v>
@@ -29456,7 +29456,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.2024164199829</v>
+        <v>13.2024173736572</v>
       </c>
       <c r="H1003" t="n">
         <v>185914</v>
@@ -29659,7 +29659,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.6746063232422</v>
+        <v>13.6746072769165</v>
       </c>
       <c r="H1010" t="n">
         <v>1286825</v>
@@ -29746,7 +29746,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>13.3157434463501</v>
+        <v>13.3157444000244</v>
       </c>
       <c r="H1013" t="n">
         <v>51168</v>
@@ -29804,7 +29804,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.0890913009644</v>
+        <v>13.0890922546387</v>
       </c>
       <c r="H1015" t="n">
         <v>68241</v>
@@ -29833,7 +29833,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>13.1268682479858</v>
+        <v>13.1268672943115</v>
       </c>
       <c r="H1016" t="n">
         <v>62155</v>
@@ -29949,7 +29949,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1020" t="n">
-        <v>13.013542175293</v>
+        <v>13.0135431289673</v>
       </c>
       <c r="H1020" t="n">
         <v>61600</v>
@@ -29978,7 +29978,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>13.3157434463501</v>
+        <v>13.3157444000244</v>
       </c>
       <c r="H1021" t="n">
         <v>82988</v>
@@ -30065,7 +30065,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1024" t="n">
-        <v>13.4479570388794</v>
+        <v>13.4479560852051</v>
       </c>
       <c r="H1024" t="n">
         <v>78928</v>
@@ -30152,7 +30152,7 @@
         <v>15</v>
       </c>
       <c r="G1027" t="n">
-        <v>14.1656837463379</v>
+        <v>14.1656847000122</v>
       </c>
       <c r="H1027" t="n">
         <v>347744</v>
@@ -30181,7 +30181,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1028" t="n">
-        <v>14.3545598983765</v>
+        <v>14.3545589447021</v>
       </c>
       <c r="H1028" t="n">
         <v>136320</v>
@@ -30210,7 +30210,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1029" t="n">
-        <v>14.6756477355957</v>
+        <v>14.67564868927</v>
       </c>
       <c r="H1029" t="n">
         <v>157037</v>
@@ -30239,7 +30239,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1030" t="n">
-        <v>14.3545598983765</v>
+        <v>14.3545589447021</v>
       </c>
       <c r="H1030" t="n">
         <v>139669</v>
@@ -30268,7 +30268,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1031" t="n">
-        <v>14.6189861297607</v>
+        <v>14.6189851760864</v>
       </c>
       <c r="H1031" t="n">
         <v>170225</v>
@@ -30297,7 +30297,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1032" t="n">
-        <v>14.6756477355957</v>
+        <v>14.67564868927</v>
       </c>
       <c r="H1032" t="n">
         <v>116636</v>
@@ -30471,7 +30471,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.0145845413208</v>
+        <v>14.0145835876465</v>
       </c>
       <c r="H1038" t="n">
         <v>109922</v>
@@ -30587,7 +30587,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.0901336669922</v>
+        <v>14.0901346206665</v>
       </c>
       <c r="H1042" t="n">
         <v>80725</v>
@@ -30616,7 +30616,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1043" t="n">
-        <v>13.8445959091187</v>
+        <v>13.8445949554443</v>
       </c>
       <c r="H1043" t="n">
         <v>68294</v>
@@ -30645,7 +30645,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.1467962265015</v>
+        <v>14.1467971801758</v>
       </c>
       <c r="H1044" t="n">
         <v>95719</v>
@@ -30848,7 +30848,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.2978982925415</v>
+        <v>14.2978973388672</v>
       </c>
       <c r="H1051" t="n">
         <v>58228</v>
@@ -30877,7 +30877,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.1467962265015</v>
+        <v>14.1467971801758</v>
       </c>
       <c r="H1052" t="n">
         <v>69603</v>
@@ -30935,7 +30935,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.3157434463501</v>
+        <v>13.3157444000244</v>
       </c>
       <c r="H1054" t="n">
         <v>61297</v>
@@ -30993,7 +30993,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.4857301712036</v>
+        <v>13.4857311248779</v>
       </c>
       <c r="H1056" t="n">
         <v>127925</v>
@@ -31022,7 +31022,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.0702037811279</v>
+        <v>13.0702047348022</v>
       </c>
       <c r="H1057" t="n">
         <v>86420</v>
@@ -31051,7 +31051,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>13.1268682479858</v>
+        <v>13.1268672943115</v>
       </c>
       <c r="H1058" t="n">
         <v>173298</v>
@@ -31080,7 +31080,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1059" t="n">
-        <v>13.3157434463501</v>
+        <v>13.3157444000244</v>
       </c>
       <c r="H1059" t="n">
         <v>207965</v>
@@ -31109,7 +31109,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9002151489258</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1060" t="n">
         <v>89394</v>
@@ -31225,7 +31225,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1064" t="n">
         <v>172709</v>
@@ -31254,7 +31254,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1065" t="n">
-        <v>10.954797744751</v>
+        <v>10.9547967910767</v>
       </c>
       <c r="H1065" t="n">
         <v>69290</v>
@@ -31283,7 +31283,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1066" t="n">
-        <v>9.72710227966309</v>
+        <v>9.7271032333374</v>
       </c>
       <c r="H1066" t="n">
         <v>153655</v>
@@ -31341,7 +31341,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1068" t="n">
-        <v>9.50045394897461</v>
+        <v>9.50045204162598</v>
       </c>
       <c r="H1068" t="n">
         <v>132039</v>
@@ -31399,7 +31399,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.576003074646</v>
+        <v>9.57600402832031</v>
       </c>
       <c r="H1070" t="n">
         <v>43703</v>
@@ -31428,7 +31428,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1071" t="n">
-        <v>9.68932914733887</v>
+        <v>9.68932819366455</v>
       </c>
       <c r="H1071" t="n">
         <v>41718</v>
@@ -31486,7 +31486,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1073" t="n">
-        <v>10.1237421035767</v>
+        <v>10.123743057251</v>
       </c>
       <c r="H1073" t="n">
         <v>107636</v>
@@ -31602,7 +31602,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1077" t="n">
-        <v>10.4448308944702</v>
+        <v>10.4448328018188</v>
       </c>
       <c r="H1077" t="n">
         <v>177907</v>
@@ -31631,7 +31631,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1078" t="n">
-        <v>10.5392694473267</v>
+        <v>10.5392684936523</v>
       </c>
       <c r="H1078" t="n">
         <v>46038</v>
@@ -31660,7 +31660,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.8225831985474</v>
+        <v>10.822582244873</v>
       </c>
       <c r="H1079" t="n">
         <v>59396</v>
@@ -31689,7 +31689,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.8036947250366</v>
+        <v>10.8036956787109</v>
       </c>
       <c r="H1080" t="n">
         <v>22648</v>
@@ -31718,7 +31718,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1081" t="n">
-        <v>11.6725244522095</v>
+        <v>11.6725234985352</v>
       </c>
       <c r="H1081" t="n">
         <v>74957</v>
@@ -31921,7 +31921,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1088" t="n">
-        <v>11.2003335952759</v>
+        <v>11.2003345489502</v>
       </c>
       <c r="H1088" t="n">
         <v>28966</v>
@@ -31950,7 +31950,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1089" t="n">
-        <v>11.2192230224609</v>
+        <v>11.2192220687866</v>
       </c>
       <c r="H1089" t="n">
         <v>35118</v>
@@ -31979,7 +31979,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1090" t="n">
-        <v>11.4647617340088</v>
+        <v>11.4647607803345</v>
       </c>
       <c r="H1090" t="n">
         <v>36123</v>
@@ -32037,7 +32037,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1092" t="n">
-        <v>11.7480745315552</v>
+        <v>11.7480726242065</v>
       </c>
       <c r="H1092" t="n">
         <v>44824</v>
@@ -32182,7 +32182,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1097" t="n">
-        <v>12.541353225708</v>
+        <v>12.5413513183594</v>
       </c>
       <c r="H1097" t="n">
         <v>65229</v>
@@ -32269,7 +32269,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.8057775497437</v>
+        <v>12.8057804107666</v>
       </c>
       <c r="H1100" t="n">
         <v>83899</v>
@@ -32327,7 +32327,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>13.1268682479858</v>
+        <v>13.1268672943115</v>
       </c>
       <c r="H1102" t="n">
         <v>74814</v>
@@ -32385,7 +32385,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>13.3157434463501</v>
+        <v>13.3157444000244</v>
       </c>
       <c r="H1104" t="n">
         <v>55131</v>
@@ -32414,7 +32414,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>13.5990552902222</v>
+        <v>13.5990571975708</v>
       </c>
       <c r="H1105" t="n">
         <v>39976</v>
@@ -32472,7 +32472,7 @@
         <v>13.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>12.7491159439087</v>
+        <v>12.749116897583</v>
       </c>
       <c r="H1107" t="n">
         <v>131079</v>
@@ -32501,7 +32501,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1108" t="n">
-        <v>12.8057775497437</v>
+        <v>12.8057804107666</v>
       </c>
       <c r="H1108" t="n">
         <v>72306</v>
@@ -32559,7 +32559,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>13.7879333496094</v>
+        <v>13.7879323959351</v>
       </c>
       <c r="H1110" t="n">
         <v>99693</v>
@@ -32588,7 +32588,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1111" t="n">
-        <v>13.3346309661865</v>
+        <v>13.3346300125122</v>
       </c>
       <c r="H1111" t="n">
         <v>87072</v>
@@ -32617,7 +32617,7 @@
         <v>14.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>13.6934938430786</v>
+        <v>13.6934947967529</v>
       </c>
       <c r="H1112" t="n">
         <v>90451</v>
@@ -32646,7 +32646,7 @@
         <v>14.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>13.6934938430786</v>
+        <v>13.6934947967529</v>
       </c>
       <c r="H1113" t="n">
         <v>65227</v>
@@ -32675,7 +32675,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>13.8823699951172</v>
+        <v>13.8823719024658</v>
       </c>
       <c r="H1114" t="n">
         <v>86472</v>
@@ -32704,7 +32704,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1115" t="n">
-        <v>14.3545598983765</v>
+        <v>14.3545589447021</v>
       </c>
       <c r="H1115" t="n">
         <v>88034</v>
@@ -32936,7 +32936,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>14.3545598983765</v>
+        <v>14.3545589447021</v>
       </c>
       <c r="H1123" t="n">
         <v>81355</v>
@@ -32965,7 +32965,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1124" t="n">
-        <v>13.9390325546265</v>
+        <v>13.9390335083008</v>
       </c>
       <c r="H1124" t="n">
         <v>138092</v>
@@ -32994,7 +32994,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1125" t="n">
-        <v>14.3923349380493</v>
+        <v>14.3923358917236</v>
       </c>
       <c r="H1125" t="n">
         <v>182801</v>
@@ -33110,7 +33110,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1129" t="n">
-        <v>13.4857301712036</v>
+        <v>13.4857311248779</v>
       </c>
       <c r="H1129" t="n">
         <v>78088</v>
@@ -33197,7 +33197,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>15.0533990859985</v>
+        <v>15.0534009933472</v>
       </c>
       <c r="H1132" t="n">
         <v>290925</v>
@@ -33226,7 +33226,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>14.9211874008179</v>
+        <v>14.9211864471436</v>
       </c>
       <c r="H1133" t="n">
         <v>76809</v>
@@ -33255,7 +33255,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1134" t="n">
-        <v>14.9023008346558</v>
+        <v>14.9022998809814</v>
       </c>
       <c r="H1134" t="n">
         <v>204087</v>
@@ -33313,7 +33313,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1136" t="n">
-        <v>14.9023008346558</v>
+        <v>14.9022998809814</v>
       </c>
       <c r="H1136" t="n">
         <v>70158</v>
@@ -33371,7 +33371,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>14.6189861297607</v>
+        <v>14.6189851760864</v>
       </c>
       <c r="H1138" t="n">
         <v>51733</v>
@@ -33400,7 +33400,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1139" t="n">
-        <v>14.5812110900879</v>
+        <v>14.5812101364136</v>
       </c>
       <c r="H1139" t="n">
         <v>47039</v>
@@ -33429,7 +33429,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1140" t="n">
-        <v>14.5812110900879</v>
+        <v>14.5812101364136</v>
       </c>
       <c r="H1140" t="n">
         <v>13135</v>
@@ -33458,7 +33458,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1141" t="n">
-        <v>14.4112243652344</v>
+        <v>14.4112234115601</v>
       </c>
       <c r="H1141" t="n">
         <v>19363</v>
@@ -33516,7 +33516,7 @@
         <v>15.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>14.6378746032715</v>
+        <v>14.6378736495972</v>
       </c>
       <c r="H1143" t="n">
         <v>54376</v>
@@ -33574,7 +33574,7 @@
         <v>15.5</v>
       </c>
       <c r="G1145" t="n">
-        <v>14.6378746032715</v>
+        <v>14.6378736495972</v>
       </c>
       <c r="H1145" t="n">
         <v>37212</v>
@@ -33603,7 +33603,7 @@
         <v>15.5</v>
       </c>
       <c r="G1146" t="n">
-        <v>14.6378746032715</v>
+        <v>14.6378736495972</v>
       </c>
       <c r="H1146" t="n">
         <v>22508</v>
@@ -33690,7 +33690,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1149" t="n">
-        <v>14.1467962265015</v>
+        <v>14.1467971801758</v>
       </c>
       <c r="H1149" t="n">
         <v>23325</v>
@@ -33864,7 +33864,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1155" t="n">
-        <v>13.9012594223022</v>
+        <v>13.9012584686279</v>
       </c>
       <c r="H1155" t="n">
         <v>20658</v>
@@ -33893,7 +33893,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1156" t="n">
-        <v>13.5990552902222</v>
+        <v>13.5990571975708</v>
       </c>
       <c r="H1156" t="n">
         <v>49035</v>
@@ -33951,7 +33951,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1158" t="n">
-        <v>13.6746063232422</v>
+        <v>13.6746072769165</v>
       </c>
       <c r="H1158" t="n">
         <v>23816</v>
@@ -34154,7 +34154,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1165" t="n">
-        <v>13.6746063232422</v>
+        <v>13.6746072769165</v>
       </c>
       <c r="H1165" t="n">
         <v>80532</v>
@@ -34183,7 +34183,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1166" t="n">
-        <v>13.7123832702637</v>
+        <v>13.7123823165894</v>
       </c>
       <c r="H1166" t="n">
         <v>36014</v>
@@ -34212,7 +34212,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1167" t="n">
-        <v>13.7123832702637</v>
+        <v>13.7123823165894</v>
       </c>
       <c r="H1167" t="n">
         <v>45948</v>
@@ -34357,7 +34357,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1172" t="n">
-        <v>14.3545598983765</v>
+        <v>14.3545589447021</v>
       </c>
       <c r="H1172" t="n">
         <v>15906</v>
@@ -34473,7 +34473,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1176" t="n">
-        <v>13.7879333496094</v>
+        <v>13.7879323959351</v>
       </c>
       <c r="H1176" t="n">
         <v>40379</v>
@@ -34502,7 +34502,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1177" t="n">
-        <v>13.7879333496094</v>
+        <v>13.7879323959351</v>
       </c>
       <c r="H1177" t="n">
         <v>11112</v>
@@ -34560,7 +34560,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1179" t="n">
-        <v>13.3535184860229</v>
+        <v>13.3535194396973</v>
       </c>
       <c r="H1179" t="n">
         <v>29935</v>
@@ -34589,7 +34589,7 @@
         <v>14.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>13.6934938430786</v>
+        <v>13.6934947967529</v>
       </c>
       <c r="H1180" t="n">
         <v>47938</v>
@@ -34647,7 +34647,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1182" t="n">
-        <v>13.6746063232422</v>
+        <v>13.6746072769165</v>
       </c>
       <c r="H1182" t="n">
         <v>41126</v>
@@ -34676,7 +34676,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.6557197570801</v>
+        <v>13.6557188034058</v>
       </c>
       <c r="H1183" t="n">
         <v>53850</v>
@@ -34705,7 +34705,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1184" t="n">
-        <v>13.7312698364258</v>
+        <v>13.7312707901001</v>
       </c>
       <c r="H1184" t="n">
         <v>29968</v>
@@ -34763,7 +34763,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1186" t="n">
-        <v>13.7690448760986</v>
+        <v>13.7690458297729</v>
       </c>
       <c r="H1186" t="n">
         <v>41582</v>
@@ -34792,7 +34792,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1187" t="n">
-        <v>13.7312698364258</v>
+        <v>13.7312707901001</v>
       </c>
       <c r="H1187" t="n">
         <v>18458</v>
@@ -34821,7 +34821,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1188" t="n">
-        <v>14.6756477355957</v>
+        <v>14.67564868927</v>
       </c>
       <c r="H1188" t="n">
         <v>250989</v>
@@ -34879,7 +34879,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1190" t="n">
-        <v>14.3923349380493</v>
+        <v>14.3923358917236</v>
       </c>
       <c r="H1190" t="n">
         <v>27011</v>
@@ -34908,7 +34908,7 @@
         <v>15</v>
       </c>
       <c r="G1191" t="n">
-        <v>14.1656837463379</v>
+        <v>14.1656847000122</v>
       </c>
       <c r="H1191" t="n">
         <v>24435</v>
@@ -35053,7 +35053,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.7312698364258</v>
+        <v>13.7312707901001</v>
       </c>
       <c r="H1196" t="n">
         <v>176235</v>
@@ -35169,7 +35169,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1200" t="n">
-        <v>12.8246669769287</v>
+        <v>12.8246650695801</v>
       </c>
       <c r="H1200" t="n">
         <v>67411</v>
@@ -35198,7 +35198,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.6546773910522</v>
+        <v>12.6546783447266</v>
       </c>
       <c r="H1201" t="n">
         <v>81412</v>
@@ -35227,7 +35227,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.9002151489258</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1202" t="n">
         <v>65638</v>
@@ -35256,7 +35256,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1203" t="n">
-        <v>12.9002151489258</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1203" t="n">
         <v>93020</v>
@@ -35314,7 +35314,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.673565864563</v>
+        <v>12.6735649108887</v>
       </c>
       <c r="H1205" t="n">
         <v>44299</v>
@@ -35343,7 +35343,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.5791273117065</v>
+        <v>12.5791263580322</v>
       </c>
       <c r="H1206" t="n">
         <v>67933</v>
@@ -35372,7 +35372,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.673565864563</v>
+        <v>12.6735649108887</v>
       </c>
       <c r="H1207" t="n">
         <v>43151</v>
@@ -35401,7 +35401,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1208" t="n">
-        <v>12.5035772323608</v>
+        <v>12.5035781860352</v>
       </c>
       <c r="H1208" t="n">
         <v>80617</v>
@@ -35430,7 +35430,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>12.6546773910522</v>
+        <v>12.6546783447266</v>
       </c>
       <c r="H1209" t="n">
         <v>67989</v>
@@ -35459,7 +35459,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.8246669769287</v>
+        <v>12.8246650695801</v>
       </c>
       <c r="H1210" t="n">
         <v>45582</v>
@@ -35517,7 +35517,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.9191045761108</v>
+        <v>12.9191036224365</v>
       </c>
       <c r="H1212" t="n">
         <v>30848</v>
@@ -35546,7 +35546,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1213" t="n">
-        <v>13.013542175293</v>
+        <v>13.0135431289673</v>
       </c>
       <c r="H1213" t="n">
         <v>39451</v>
@@ -35633,7 +35633,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1216" t="n">
-        <v>12.5791273117065</v>
+        <v>12.5791263580322</v>
       </c>
       <c r="H1216" t="n">
         <v>40116</v>
@@ -35662,7 +35662,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1217" t="n">
-        <v>12.4469146728516</v>
+        <v>12.4469156265259</v>
       </c>
       <c r="H1217" t="n">
         <v>62227</v>
@@ -35691,7 +35691,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.258038520813</v>
+        <v>12.2580366134644</v>
       </c>
       <c r="H1218" t="n">
         <v>45412</v>
@@ -35749,7 +35749,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.2391519546509</v>
+        <v>12.2391529083252</v>
       </c>
       <c r="H1220" t="n">
         <v>27685</v>
@@ -35807,7 +35807,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1222" t="n">
-        <v>11.8425130844116</v>
+        <v>11.8425121307373</v>
       </c>
       <c r="H1222" t="n">
         <v>58032</v>
@@ -35894,7 +35894,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.3136587142944</v>
+        <v>11.3136596679688</v>
       </c>
       <c r="H1225" t="n">
         <v>79683</v>
@@ -35923,7 +35923,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1226" t="n">
-        <v>11.1247835159302</v>
+        <v>11.1247825622559</v>
       </c>
       <c r="H1226" t="n">
         <v>164368</v>
@@ -35952,7 +35952,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1227" t="n">
-        <v>11.5403118133545</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H1227" t="n">
         <v>75434</v>
@@ -35981,7 +35981,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1228" t="n">
-        <v>11.2003335952759</v>
+        <v>11.2003345489502</v>
       </c>
       <c r="H1228" t="n">
         <v>80587</v>
@@ -36010,7 +36010,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1229" t="n">
-        <v>11.5025358200073</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H1229" t="n">
         <v>129870</v>
@@ -36039,7 +36039,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1230" t="n">
-        <v>11.6536359786987</v>
+        <v>11.653636932373</v>
       </c>
       <c r="H1230" t="n">
         <v>158350</v>
@@ -36097,7 +36097,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.7480745315552</v>
+        <v>11.7480726242065</v>
       </c>
       <c r="H1232" t="n">
         <v>32850</v>
@@ -36126,7 +36126,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.634747505188</v>
+        <v>11.6347484588623</v>
       </c>
       <c r="H1233" t="n">
         <v>115719</v>
@@ -36155,7 +36155,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1234" t="n">
-        <v>12.4469146728516</v>
+        <v>12.4469156265259</v>
       </c>
       <c r="H1234" t="n">
         <v>94725</v>
@@ -36242,7 +36242,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1237" t="n">
-        <v>12.2391519546509</v>
+        <v>12.2391529083252</v>
       </c>
       <c r="H1237" t="n">
         <v>43185</v>
@@ -36271,7 +36271,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.258038520813</v>
+        <v>12.2580366134644</v>
       </c>
       <c r="H1238" t="n">
         <v>77755</v>
@@ -36329,7 +36329,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1240" t="n">
-        <v>12.4846897125244</v>
+        <v>12.4846906661987</v>
       </c>
       <c r="H1240" t="n">
         <v>49942</v>
@@ -36358,7 +36358,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1241" t="n">
-        <v>10.4070558547974</v>
+        <v>10.4070568084717</v>
       </c>
       <c r="H1241" t="n">
         <v>1787033</v>
@@ -36445,7 +36445,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.8414697647095</v>
+        <v>10.8414707183838</v>
       </c>
       <c r="H1244" t="n">
         <v>308303</v>
@@ -36532,7 +36532,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1247" t="n">
-        <v>10.5014944076538</v>
+        <v>10.5014934539795</v>
       </c>
       <c r="H1247" t="n">
         <v>214428</v>
@@ -36590,7 +36590,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1249" t="n">
-        <v>10.6525936126709</v>
+        <v>10.6525955200195</v>
       </c>
       <c r="H1249" t="n">
         <v>93452</v>
@@ -36619,7 +36619,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1250" t="n">
-        <v>10.6525936126709</v>
+        <v>10.6525955200195</v>
       </c>
       <c r="H1250" t="n">
         <v>135853</v>
@@ -36706,7 +36706,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1253" t="n">
-        <v>10.7470321655273</v>
+        <v>10.7470331192017</v>
       </c>
       <c r="H1253" t="n">
         <v>87227</v>
@@ -36735,7 +36735,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1254" t="n">
-        <v>10.6903696060181</v>
+        <v>10.6903705596924</v>
       </c>
       <c r="H1254" t="n">
         <v>134370</v>
@@ -36793,7 +36793,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1256" t="n">
-        <v>10.7848072052002</v>
+        <v>10.7848081588745</v>
       </c>
       <c r="H1256" t="n">
         <v>81826</v>
@@ -36851,7 +36851,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1258" t="n">
-        <v>10.7092580795288</v>
+        <v>10.7092571258545</v>
       </c>
       <c r="H1258" t="n">
         <v>159754</v>
@@ -36880,7 +36880,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1259" t="n">
-        <v>10.6525936126709</v>
+        <v>10.6525955200195</v>
       </c>
       <c r="H1259" t="n">
         <v>187456</v>
@@ -36909,7 +36909,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1260" t="n">
-        <v>10.671483039856</v>
+        <v>10.6714820861816</v>
       </c>
       <c r="H1260" t="n">
         <v>142399</v>
@@ -36938,7 +36938,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1261" t="n">
-        <v>10.5014944076538</v>
+        <v>10.5014934539795</v>
       </c>
       <c r="H1261" t="n">
         <v>94914</v>
@@ -36967,7 +36967,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.6337060928345</v>
+        <v>10.6337070465088</v>
       </c>
       <c r="H1262" t="n">
         <v>213214</v>
@@ -36996,7 +36996,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.8414697647095</v>
+        <v>10.8414707183838</v>
       </c>
       <c r="H1263" t="n">
         <v>276933</v>
@@ -37054,7 +37054,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.671483039856</v>
+        <v>10.6714820861816</v>
       </c>
       <c r="H1265" t="n">
         <v>145457</v>
@@ -37083,7 +37083,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1266" t="n">
-        <v>10.879246711731</v>
+        <v>10.8792457580566</v>
       </c>
       <c r="H1266" t="n">
         <v>95967</v>
@@ -37112,7 +37112,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1267" t="n">
-        <v>10.8036947250366</v>
+        <v>10.8036956787109</v>
       </c>
       <c r="H1267" t="n">
         <v>41933</v>
@@ -37170,7 +37170,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1269" t="n">
-        <v>10.8414697647095</v>
+        <v>10.8414707183838</v>
       </c>
       <c r="H1269" t="n">
         <v>36773</v>
@@ -37199,7 +37199,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1270" t="n">
-        <v>10.7092580795288</v>
+        <v>10.7092571258545</v>
       </c>
       <c r="H1270" t="n">
         <v>39658</v>
@@ -37257,7 +37257,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>10.879246711731</v>
+        <v>10.8792457580566</v>
       </c>
       <c r="H1272" t="n">
         <v>87618</v>
@@ -37286,7 +37286,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1273" t="n">
-        <v>10.9359083175659</v>
+        <v>10.9359073638916</v>
       </c>
       <c r="H1273" t="n">
         <v>97279</v>
@@ -37315,7 +37315,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1274" t="n">
-        <v>11.2947721481323</v>
+        <v>11.2947731018066</v>
       </c>
       <c r="H1274" t="n">
         <v>205711</v>
@@ -37344,7 +37344,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>11.0303449630737</v>
+        <v>11.030345916748</v>
       </c>
       <c r="H1275" t="n">
         <v>197728</v>
@@ -37373,7 +37373,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>11.2381076812744</v>
+        <v>11.2381086349487</v>
       </c>
       <c r="H1276" t="n">
         <v>162597</v>
@@ -37605,7 +37605,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>11.6536359786987</v>
+        <v>11.653636932373</v>
       </c>
       <c r="H1284" t="n">
         <v>101314</v>
@@ -37634,7 +37634,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1285" t="n">
         <v>111072</v>
@@ -37663,7 +37663,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1286" t="n">
-        <v>11.5025358200073</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H1286" t="n">
         <v>122588</v>
@@ -37721,7 +37721,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1288" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1288" t="n">
         <v>85640</v>
@@ -37750,7 +37750,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1289" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1289" t="n">
         <v>115871</v>
@@ -37808,7 +37808,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1291" t="n">
-        <v>11.2192230224609</v>
+        <v>11.2192220687866</v>
       </c>
       <c r="H1291" t="n">
         <v>74002</v>
@@ -37837,7 +37837,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1292" t="n">
-        <v>11.2947721481323</v>
+        <v>11.2947731018066</v>
       </c>
       <c r="H1292" t="n">
         <v>67505</v>
@@ -37866,7 +37866,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1293" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1293" t="n">
         <v>58479</v>
@@ -38011,7 +38011,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1298" t="n">
-        <v>12.0125007629395</v>
+        <v>12.0124998092651</v>
       </c>
       <c r="H1298" t="n">
         <v>139903</v>
@@ -38040,7 +38040,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1299" t="n">
-        <v>11.918062210083</v>
+        <v>11.9180631637573</v>
       </c>
       <c r="H1299" t="n">
         <v>65713</v>
@@ -38127,7 +38127,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1302" t="n">
-        <v>11.918062210083</v>
+        <v>11.9180631637573</v>
       </c>
       <c r="H1302" t="n">
         <v>119208</v>
@@ -38272,7 +38272,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1307" t="n">
-        <v>11.6536359786987</v>
+        <v>11.653636932373</v>
       </c>
       <c r="H1307" t="n">
         <v>51596</v>
@@ -38417,7 +38417,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.785849571228</v>
+        <v>11.7858486175537</v>
       </c>
       <c r="H1312" t="n">
         <v>74454</v>
@@ -38446,7 +38446,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.8425130844116</v>
+        <v>11.8425121307373</v>
       </c>
       <c r="H1313" t="n">
         <v>98684</v>
@@ -38591,7 +38591,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1318" t="n">
-        <v>11.918062210083</v>
+        <v>11.9180631637573</v>
       </c>
       <c r="H1318" t="n">
         <v>41971</v>
@@ -38620,7 +38620,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.993613243103</v>
+        <v>11.9936122894287</v>
       </c>
       <c r="H1319" t="n">
         <v>66770</v>
@@ -38649,7 +38649,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1320" t="n">
-        <v>11.918062210083</v>
+        <v>11.9180631637573</v>
       </c>
       <c r="H1320" t="n">
         <v>49228</v>
@@ -38678,7 +38678,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1321" t="n">
-        <v>11.8236236572266</v>
+        <v>11.8236255645752</v>
       </c>
       <c r="H1321" t="n">
         <v>110314</v>
@@ -38707,7 +38707,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1322" t="n">
-        <v>11.9747257232666</v>
+        <v>11.9747247695923</v>
       </c>
       <c r="H1322" t="n">
         <v>91116</v>
@@ -38794,7 +38794,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1325" t="n">
-        <v>11.6725244522095</v>
+        <v>11.6725234985352</v>
       </c>
       <c r="H1325" t="n">
         <v>147010</v>
@@ -38852,7 +38852,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1327" t="n">
-        <v>11.8425130844116</v>
+        <v>11.8425121307373</v>
       </c>
       <c r="H1327" t="n">
         <v>37857</v>
@@ -38881,7 +38881,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1328" t="n">
-        <v>11.634747505188</v>
+        <v>11.6347484588623</v>
       </c>
       <c r="H1328" t="n">
         <v>67972</v>
@@ -38968,7 +38968,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1331" t="n">
-        <v>11.5403118133545</v>
+        <v>11.5403108596802</v>
       </c>
       <c r="H1331" t="n">
         <v>116336</v>
@@ -38997,7 +38997,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1332" t="n">
-        <v>11.7669610977173</v>
+        <v>11.7669620513916</v>
       </c>
       <c r="H1332" t="n">
         <v>83161</v>
@@ -39113,7 +39113,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1336" t="n">
-        <v>12.0125007629395</v>
+        <v>12.0124998092651</v>
       </c>
       <c r="H1336" t="n">
         <v>112912</v>
@@ -39142,7 +39142,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1337" t="n">
-        <v>14.0145845413208</v>
+        <v>14.0145835876465</v>
       </c>
       <c r="H1337" t="n">
         <v>1066070</v>
@@ -39171,7 +39171,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1338" t="n">
-        <v>14.1467962265015</v>
+        <v>14.1467971801758</v>
       </c>
       <c r="H1338" t="n">
         <v>457633</v>
@@ -39229,7 +39229,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1340" t="n">
-        <v>13.2024164199829</v>
+        <v>13.2024173736572</v>
       </c>
       <c r="H1340" t="n">
         <v>214737</v>
@@ -39258,7 +39258,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1341" t="n">
-        <v>12.9002151489258</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1341" t="n">
         <v>192706</v>
@@ -39287,7 +39287,7 @@
         <v>13.5</v>
       </c>
       <c r="G1342" t="n">
-        <v>12.7491159439087</v>
+        <v>12.749116897583</v>
       </c>
       <c r="H1342" t="n">
         <v>110065</v>
@@ -39403,7 +39403,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1346" t="n">
-        <v>12.5791273117065</v>
+        <v>12.5791263580322</v>
       </c>
       <c r="H1346" t="n">
         <v>178511</v>
@@ -39461,7 +39461,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1348" t="n">
-        <v>12.9002151489258</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1348" t="n">
         <v>98043</v>
@@ -39490,7 +39490,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1349" t="n">
-        <v>12.9002151489258</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1349" t="n">
         <v>91612</v>
@@ -39548,7 +39548,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0702037811279</v>
+        <v>13.0702047348022</v>
       </c>
       <c r="H1351" t="n">
         <v>153049</v>
@@ -39606,7 +39606,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1353" t="n">
-        <v>13.0890913009644</v>
+        <v>13.0890922546387</v>
       </c>
       <c r="H1353" t="n">
         <v>119006</v>
@@ -39635,7 +39635,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1354" t="n">
-        <v>13.3724060058594</v>
+        <v>13.3724069595337</v>
       </c>
       <c r="H1354" t="n">
         <v>162621</v>
@@ -39664,7 +39664,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1355" t="n">
-        <v>13.0702037811279</v>
+        <v>13.0702047348022</v>
       </c>
       <c r="H1355" t="n">
         <v>156743</v>
@@ -39693,7 +39693,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1356" t="n">
-        <v>13.1835298538208</v>
+        <v>13.1835289001465</v>
       </c>
       <c r="H1356" t="n">
         <v>113672</v>
@@ -39780,7 +39780,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1359" t="n">
-        <v>13.1718282699585</v>
+        <v>13.1718292236328</v>
       </c>
       <c r="H1359" t="n">
         <v>112558</v>
@@ -39809,7 +39809,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1360" t="n">
-        <v>12.9222173690796</v>
+        <v>12.9222164154053</v>
       </c>
       <c r="H1360" t="n">
         <v>136286</v>
@@ -39838,7 +39838,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1361" t="n">
-        <v>12.6918058395386</v>
+        <v>12.6918067932129</v>
       </c>
       <c r="H1361" t="n">
         <v>79685</v>
@@ -39896,7 +39896,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1363" t="n">
-        <v>12.5573997497559</v>
+        <v>12.5573987960815</v>
       </c>
       <c r="H1363" t="n">
         <v>130670</v>
@@ -40041,7 +40041,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1368" t="n">
-        <v>12.4421939849854</v>
+        <v>12.4421949386597</v>
       </c>
       <c r="H1368" t="n">
         <v>50790</v>
@@ -40070,7 +40070,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1369" t="n">
-        <v>12.5573997497559</v>
+        <v>12.5573987960815</v>
       </c>
       <c r="H1369" t="n">
         <v>38990</v>
@@ -40099,7 +40099,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1370" t="n">
-        <v>12.4229936599731</v>
+        <v>12.4229927062988</v>
       </c>
       <c r="H1370" t="n">
         <v>48611</v>
@@ -40186,7 +40186,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1373" t="n">
-        <v>12.4229936599731</v>
+        <v>12.4229927062988</v>
       </c>
       <c r="H1373" t="n">
         <v>51920</v>
@@ -40244,7 +40244,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>12.5573997497559</v>
+        <v>12.5573987960815</v>
       </c>
       <c r="H1375" t="n">
         <v>80608</v>
@@ -40273,7 +40273,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1376" t="n">
-        <v>12.5381984710693</v>
+        <v>12.5381994247437</v>
       </c>
       <c r="H1376" t="n">
         <v>25990</v>
@@ -40302,7 +40302,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1377" t="n">
-        <v>12.5381984710693</v>
+        <v>12.5381994247437</v>
       </c>
       <c r="H1377" t="n">
         <v>66418</v>
@@ -40331,7 +40331,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1378" t="n">
-        <v>12.5573997497559</v>
+        <v>12.5573987960815</v>
       </c>
       <c r="H1378" t="n">
         <v>73905</v>
@@ -40360,7 +40360,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1379" t="n">
-        <v>12.5381984710693</v>
+        <v>12.5381994247437</v>
       </c>
       <c r="H1379" t="n">
         <v>49734</v>
@@ -40447,7 +40447,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1382" t="n">
-        <v>12.4997968673706</v>
+        <v>12.4997959136963</v>
       </c>
       <c r="H1382" t="n">
         <v>36731</v>
@@ -40476,7 +40476,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1383" t="n">
-        <v>12.6150016784668</v>
+        <v>12.6150026321411</v>
       </c>
       <c r="H1383" t="n">
         <v>152039</v>
@@ -40505,7 +40505,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.8262119293213</v>
+        <v>12.826210975647</v>
       </c>
       <c r="H1384" t="n">
         <v>135738</v>
@@ -40563,7 +40563,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1386" t="n">
-        <v>12.7878103256226</v>
+        <v>12.7878093719482</v>
       </c>
       <c r="H1386" t="n">
         <v>68715</v>
@@ -40708,7 +40708,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1391" t="n">
-        <v>12.3077878952026</v>
+        <v>12.3077869415283</v>
       </c>
       <c r="H1391" t="n">
         <v>55545</v>
@@ -40795,7 +40795,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1394" t="n">
-        <v>12.115777015686</v>
+        <v>12.1157779693604</v>
       </c>
       <c r="H1394" t="n">
         <v>55280</v>
@@ -40853,7 +40853,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1396" t="n">
-        <v>11.9429693222046</v>
+        <v>11.9429683685303</v>
       </c>
       <c r="H1396" t="n">
         <v>46883</v>
@@ -40911,7 +40911,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1398" t="n">
-        <v>11.8661661148071</v>
+        <v>11.8661651611328</v>
       </c>
       <c r="H1398" t="n">
         <v>56582</v>
@@ -40940,7 +40940,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1399" t="n">
-        <v>11.9429693222046</v>
+        <v>11.9429683685303</v>
       </c>
       <c r="H1399" t="n">
         <v>42590</v>
@@ -40969,7 +40969,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1400" t="n">
-        <v>11.8661661148071</v>
+        <v>11.8661651611328</v>
       </c>
       <c r="H1400" t="n">
         <v>85839</v>
@@ -41114,7 +41114,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1405" t="n">
-        <v>11.7509613037109</v>
+        <v>11.7509603500366</v>
       </c>
       <c r="H1405" t="n">
         <v>32782</v>
@@ -41172,7 +41172,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1407" t="n">
-        <v>11.6933584213257</v>
+        <v>11.6933574676514</v>
       </c>
       <c r="H1407" t="n">
         <v>41617</v>
@@ -41201,7 +41201,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1408" t="n">
-        <v>11.6933584213257</v>
+        <v>11.6933574676514</v>
       </c>
       <c r="H1408" t="n">
         <v>21978</v>
@@ -41230,7 +41230,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.2517366409302</v>
+        <v>11.2517375946045</v>
       </c>
       <c r="H1409" t="n">
         <v>97412</v>
@@ -41259,7 +41259,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.4053449630737</v>
+        <v>11.4053440093994</v>
       </c>
       <c r="H1410" t="n">
         <v>78201</v>
@@ -41317,7 +41317,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1412" t="n">
-        <v>11.4053449630737</v>
+        <v>11.4053440093994</v>
       </c>
       <c r="H1412" t="n">
         <v>45455</v>
@@ -41346,7 +41346,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1413" t="n">
-        <v>11.4053449630737</v>
+        <v>11.4053440093994</v>
       </c>
       <c r="H1413" t="n">
         <v>97108</v>
@@ -41404,7 +41404,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.2901401519775</v>
+        <v>11.2901382446289</v>
       </c>
       <c r="H1415" t="n">
         <v>38827</v>
@@ -41433,7 +41433,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>11.4245433807373</v>
+        <v>11.4245443344116</v>
       </c>
       <c r="H1416" t="n">
         <v>44295</v>
@@ -41462,7 +41462,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1417" t="n">
-        <v>11.4245433807373</v>
+        <v>11.4245443344116</v>
       </c>
       <c r="H1417" t="n">
         <v>50545</v>
@@ -41491,7 +41491,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1418" t="n">
-        <v>11.3861436843872</v>
+        <v>11.3861427307129</v>
       </c>
       <c r="H1418" t="n">
         <v>33627</v>
@@ -41520,7 +41520,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1419" t="n">
-        <v>11.4053449630737</v>
+        <v>11.4053440093994</v>
       </c>
       <c r="H1419" t="n">
         <v>83673</v>
@@ -41549,7 +41549,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1420" t="n">
-        <v>11.2517366409302</v>
+        <v>11.2517375946045</v>
       </c>
       <c r="H1420" t="n">
         <v>57286</v>
@@ -41694,7 +41694,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1425" t="n">
-        <v>11.0213260650635</v>
+        <v>11.0213251113892</v>
       </c>
       <c r="H1425" t="n">
         <v>127563</v>
@@ -41810,7 +41810,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1429" t="n">
-        <v>10.9253206253052</v>
+        <v>10.9253215789795</v>
       </c>
       <c r="H1429" t="n">
         <v>102974</v>
@@ -41839,7 +41839,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1430" t="n">
-        <v>10.906120300293</v>
+        <v>10.9061212539673</v>
       </c>
       <c r="H1430" t="n">
         <v>105267</v>
@@ -41955,7 +41955,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1434" t="n">
-        <v>10.9829235076904</v>
+        <v>10.9829244613647</v>
       </c>
       <c r="H1434" t="n">
         <v>135271</v>
@@ -41984,7 +41984,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1435" t="n">
-        <v>10.9829235076904</v>
+        <v>10.9829244613647</v>
       </c>
       <c r="H1435" t="n">
         <v>118624</v>
@@ -42013,7 +42013,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1436" t="n">
-        <v>11.328540802002</v>
+        <v>11.3285398483276</v>
       </c>
       <c r="H1436" t="n">
         <v>290421</v>
@@ -42100,7 +42100,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1439" t="n">
-        <v>11.5397510528564</v>
+        <v>11.5397520065308</v>
       </c>
       <c r="H1439" t="n">
         <v>103193</v>
@@ -42158,7 +42158,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1441" t="n">
-        <v>11.6933584213257</v>
+        <v>11.6933574676514</v>
       </c>
       <c r="H1441" t="n">
         <v>74226</v>
@@ -42216,7 +42216,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>11.4245433807373</v>
+        <v>11.4245443344116</v>
       </c>
       <c r="H1443" t="n">
         <v>105208</v>
@@ -42245,7 +42245,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1444" t="n">
-        <v>11.2517366409302</v>
+        <v>11.2517375946045</v>
       </c>
       <c r="H1444" t="n">
         <v>125746</v>
@@ -42535,7 +42535,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1454" t="n">
-        <v>10.4260969161987</v>
+        <v>10.4260959625244</v>
       </c>
       <c r="H1454" t="n">
         <v>116474</v>
@@ -42564,7 +42564,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1455" t="n">
-        <v>10.3684949874878</v>
+        <v>10.3684959411621</v>
       </c>
       <c r="H1455" t="n">
         <v>49899</v>
@@ -42622,7 +42622,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1457" t="n">
-        <v>10.6373071670532</v>
+        <v>10.6373081207275</v>
       </c>
       <c r="H1457" t="n">
         <v>74160</v>
@@ -42651,7 +42651,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>10.4837007522583</v>
+        <v>10.483699798584</v>
       </c>
       <c r="H1458" t="n">
         <v>95012</v>
@@ -42680,7 +42680,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>10.714111328125</v>
+        <v>10.7141103744507</v>
       </c>
       <c r="H1459" t="n">
         <v>105508</v>
@@ -42709,7 +42709,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1460" t="n">
-        <v>10.4260969161987</v>
+        <v>10.4260959625244</v>
       </c>
       <c r="H1460" t="n">
         <v>110593</v>
@@ -42738,7 +42738,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1461" t="n">
-        <v>10.4452991485596</v>
+        <v>10.4452981948853</v>
       </c>
       <c r="H1461" t="n">
         <v>73880</v>
@@ -42767,7 +42767,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1462" t="n">
-        <v>10.4452991485596</v>
+        <v>10.4452981948853</v>
       </c>
       <c r="H1462" t="n">
         <v>63600</v>
@@ -42796,7 +42796,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1463" t="n">
-        <v>10.4260969161987</v>
+        <v>10.4260959625244</v>
       </c>
       <c r="H1463" t="n">
         <v>34488</v>
@@ -42825,7 +42825,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1464" t="n">
-        <v>10.6373071670532</v>
+        <v>10.6373081207275</v>
       </c>
       <c r="H1464" t="n">
         <v>104012</v>
@@ -42912,7 +42912,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>11.1365308761597</v>
+        <v>11.136531829834</v>
       </c>
       <c r="H1467" t="n">
         <v>194373</v>
@@ -42970,7 +42970,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1469" t="n">
-        <v>11.0789289474487</v>
+        <v>11.0789279937744</v>
       </c>
       <c r="H1469" t="n">
         <v>115300</v>
@@ -42999,7 +42999,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1470" t="n">
-        <v>11.2517366409302</v>
+        <v>11.2517375946045</v>
       </c>
       <c r="H1470" t="n">
         <v>71816</v>
@@ -43028,7 +43028,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1471" t="n">
-        <v>11.1941328048706</v>
+        <v>11.1941347122192</v>
       </c>
       <c r="H1471" t="n">
         <v>82137</v>
@@ -43057,7 +43057,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>11.328540802002</v>
+        <v>11.3285398483276</v>
       </c>
       <c r="H1472" t="n">
         <v>84441</v>
@@ -43115,7 +43115,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1474" t="n">
-        <v>11.4821472167969</v>
+        <v>11.4821481704712</v>
       </c>
       <c r="H1474" t="n">
         <v>310751</v>
@@ -43144,7 +43144,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1475" t="n">
-        <v>11.5397510528564</v>
+        <v>11.5397520065308</v>
       </c>
       <c r="H1475" t="n">
         <v>135084</v>
@@ -43202,7 +43202,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1477" t="n">
-        <v>11.5781536102295</v>
+        <v>11.5781517028809</v>
       </c>
       <c r="H1477" t="n">
         <v>69164</v>
@@ -43231,7 +43231,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1478" t="n">
-        <v>11.3861436843872</v>
+        <v>11.3861427307129</v>
       </c>
       <c r="H1478" t="n">
         <v>67064</v>
@@ -43260,7 +43260,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1479" t="n">
-        <v>11.328540802002</v>
+        <v>11.3285398483276</v>
       </c>
       <c r="H1479" t="n">
         <v>56697</v>
@@ -43376,7 +43376,7 @@
         <v>11.5</v>
       </c>
       <c r="G1483" t="n">
-        <v>11.0405263900757</v>
+        <v>11.0405254364014</v>
       </c>
       <c r="H1483" t="n">
         <v>31160</v>
@@ -43463,7 +43463,7 @@
         <v>11.5</v>
       </c>
       <c r="G1486" t="n">
-        <v>11.0405263900757</v>
+        <v>11.0405254364014</v>
       </c>
       <c r="H1486" t="n">
         <v>57858</v>
@@ -43492,7 +43492,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>11.1365308761597</v>
+        <v>11.136531829834</v>
       </c>
       <c r="H1487" t="n">
         <v>75136</v>
@@ -43608,7 +43608,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1491" t="n">
-        <v>11.1941328048706</v>
+        <v>11.1941347122192</v>
       </c>
       <c r="H1491" t="n">
         <v>48441</v>
@@ -43637,7 +43637,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1492" t="n">
-        <v>11.0789289474487</v>
+        <v>11.0789279937744</v>
       </c>
       <c r="H1492" t="n">
         <v>89248</v>
@@ -43695,7 +43695,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1494" t="n">
-        <v>11.0789289474487</v>
+        <v>11.0789279937744</v>
       </c>
       <c r="H1494" t="n">
         <v>31852</v>
@@ -43724,7 +43724,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1495" t="n">
-        <v>11.2901401519775</v>
+        <v>11.2901382446289</v>
       </c>
       <c r="H1495" t="n">
         <v>53448</v>
@@ -43811,7 +43811,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1498" t="n">
-        <v>10.7909135818481</v>
+        <v>10.7909145355225</v>
       </c>
       <c r="H1498" t="n">
         <v>66770</v>
@@ -43869,7 +43869,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1500" t="n">
-        <v>10.7333135604858</v>
+        <v>10.7333126068115</v>
       </c>
       <c r="H1500" t="n">
         <v>55918</v>
@@ -43956,7 +43956,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1503" t="n">
-        <v>10.714111328125</v>
+        <v>10.7141103744507</v>
       </c>
       <c r="H1503" t="n">
         <v>69151</v>
@@ -43985,7 +43985,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1504" t="n">
-        <v>10.6373071670532</v>
+        <v>10.6373081207275</v>
       </c>
       <c r="H1504" t="n">
         <v>50745</v>
@@ -44130,7 +44130,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1509" t="n">
-        <v>11.0789289474487</v>
+        <v>11.0789279937744</v>
       </c>
       <c r="H1509" t="n">
         <v>73655</v>
@@ -44159,7 +44159,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1510" t="n">
-        <v>11.1173305511475</v>
+        <v>11.1173295974731</v>
       </c>
       <c r="H1510" t="n">
         <v>28154</v>
@@ -44217,7 +44217,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1512" t="n">
-        <v>10.9829235076904</v>
+        <v>10.9829244613647</v>
       </c>
       <c r="H1512" t="n">
         <v>16957</v>
@@ -44333,7 +44333,7 @@
         <v>11.5</v>
       </c>
       <c r="G1516" t="n">
-        <v>11.0405263900757</v>
+        <v>11.0405254364014</v>
       </c>
       <c r="H1516" t="n">
         <v>30653</v>
@@ -44420,7 +44420,7 @@
         <v>11.5</v>
       </c>
       <c r="G1519" t="n">
-        <v>11.0405263900757</v>
+        <v>11.0405254364014</v>
       </c>
       <c r="H1519" t="n">
         <v>125194</v>
@@ -44449,7 +44449,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1520" t="n">
-        <v>11.0213260650635</v>
+        <v>11.0213251113892</v>
       </c>
       <c r="H1520" t="n">
         <v>11721</v>
@@ -44478,7 +44478,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1521" t="n">
-        <v>11.1173305511475</v>
+        <v>11.1173295974731</v>
       </c>
       <c r="H1521" t="n">
         <v>34540</v>
@@ -44507,7 +44507,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1522" t="n">
-        <v>11.0213260650635</v>
+        <v>11.0213251113892</v>
       </c>
       <c r="H1522" t="n">
         <v>36743</v>
@@ -44565,7 +44565,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1524" t="n">
-        <v>11.1365308761597</v>
+        <v>11.136531829834</v>
       </c>
       <c r="H1524" t="n">
         <v>16811</v>
@@ -44594,7 +44594,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1525" t="n">
-        <v>10.9253206253052</v>
+        <v>10.9253215789795</v>
       </c>
       <c r="H1525" t="n">
         <v>38419</v>
@@ -44710,7 +44710,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1529" t="n">
-        <v>11.1173305511475</v>
+        <v>11.1173295974731</v>
       </c>
       <c r="H1529" t="n">
         <v>42275</v>
@@ -44768,7 +44768,7 @@
         <v>11.5</v>
       </c>
       <c r="G1531" t="n">
-        <v>11.0405263900757</v>
+        <v>11.0405254364014</v>
       </c>
       <c r="H1531" t="n">
         <v>55549</v>
@@ -44826,7 +44826,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1533" t="n">
-        <v>10.9253206253052</v>
+        <v>10.9253215789795</v>
       </c>
       <c r="H1533" t="n">
         <v>71087</v>
@@ -44855,7 +44855,7 @@
         <v>11.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>11.0405263900757</v>
+        <v>11.0405254364014</v>
       </c>
       <c r="H1534" t="n">
         <v>88807</v>
@@ -44913,7 +44913,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>11.1365308761597</v>
+        <v>11.136531829834</v>
       </c>
       <c r="H1536" t="n">
         <v>116843</v>
@@ -44942,7 +44942,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1537" t="n">
-        <v>11.4053449630737</v>
+        <v>11.4053440093994</v>
       </c>
       <c r="H1537" t="n">
         <v>129936</v>
@@ -45000,7 +45000,7 @@
         <v>11.5</v>
       </c>
       <c r="G1539" t="n">
-        <v>11.0405263900757</v>
+        <v>11.0405254364014</v>
       </c>
       <c r="H1539" t="n">
         <v>53700</v>
@@ -45029,7 +45029,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1540" t="n">
-        <v>11.2901401519775</v>
+        <v>11.2901382446289</v>
       </c>
       <c r="H1540" t="n">
         <v>240254</v>
@@ -45087,7 +45087,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>10.4837007522583</v>
+        <v>10.483699798584</v>
       </c>
       <c r="H1542" t="n">
         <v>186364</v>
@@ -45261,7 +45261,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1548" t="n">
-        <v>10.3108921051025</v>
+        <v>10.3108911514282</v>
       </c>
       <c r="H1548" t="n">
         <v>68405</v>
@@ -45435,7 +45435,7 @@
         <v>10.5</v>
       </c>
       <c r="G1554" t="n">
-        <v>10.0804805755615</v>
+        <v>10.0804815292358</v>
       </c>
       <c r="H1554" t="n">
         <v>58920</v>
@@ -45522,7 +45522,7 @@
         <v>10.5</v>
       </c>
       <c r="G1557" t="n">
-        <v>10.0804805755615</v>
+        <v>10.0804815292358</v>
       </c>
       <c r="H1557" t="n">
         <v>129375</v>
@@ -45783,7 +45783,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1566" t="n">
-        <v>10.291690826416</v>
+        <v>10.2916917800903</v>
       </c>
       <c r="H1566" t="n">
         <v>76613</v>
@@ -45812,7 +45812,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1567" t="n">
-        <v>10.7525129318237</v>
+        <v>10.7525119781494</v>
       </c>
       <c r="H1567" t="n">
         <v>210689</v>
@@ -45841,7 +45841,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1568" t="n">
-        <v>10.5989065170288</v>
+        <v>10.5989055633545</v>
       </c>
       <c r="H1568" t="n">
         <v>100520</v>
@@ -45957,7 +45957,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.0996828079224</v>
+        <v>10.0996837615967</v>
       </c>
       <c r="H1572" t="n">
         <v>137218</v>
@@ -45986,7 +45986,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1573" t="n">
-        <v>10.3108921051025</v>
+        <v>10.3108911514282</v>
       </c>
       <c r="H1573" t="n">
         <v>42895</v>
@@ -46131,7 +46131,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>9.07243347167969</v>
+        <v>9.07243251800537</v>
       </c>
       <c r="H1578" t="n">
         <v>636789</v>
@@ -46189,7 +46189,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1580" t="n">
-        <v>9.18763828277588</v>
+        <v>9.18763732910156</v>
       </c>
       <c r="H1580" t="n">
         <v>96581</v>
@@ -46218,7 +46218,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1581" t="n">
-        <v>9.31244468688965</v>
+        <v>9.31244373321533</v>
       </c>
       <c r="H1581" t="n">
         <v>71124</v>
@@ -46334,7 +46334,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.67726230621338</v>
+        <v>9.67726135253906</v>
       </c>
       <c r="H1585" t="n">
         <v>63603</v>
@@ -46450,7 +46450,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1589" t="n">
-        <v>10.4260969161987</v>
+        <v>10.4260959625244</v>
       </c>
       <c r="H1589" t="n">
         <v>127523</v>
@@ -46566,7 +46566,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1593" t="n">
-        <v>10.0420799255371</v>
+        <v>10.0420789718628</v>
       </c>
       <c r="H1593" t="n">
         <v>97917</v>
@@ -46595,7 +46595,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1594" t="n">
-        <v>11.4053449630737</v>
+        <v>11.4053440093994</v>
       </c>
       <c r="H1594" t="n">
         <v>876236</v>
@@ -46711,7 +46711,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>11.4245433807373</v>
+        <v>11.4245443344116</v>
       </c>
       <c r="H1598" t="n">
         <v>165793</v>
@@ -46769,7 +46769,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1600" t="n">
-        <v>11.2901401519775</v>
+        <v>11.2901382446289</v>
       </c>
       <c r="H1600" t="n">
         <v>118634</v>
@@ -46827,7 +46827,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1602" t="n">
-        <v>10.7333135604858</v>
+        <v>10.7333126068115</v>
       </c>
       <c r="H1602" t="n">
         <v>27587</v>
@@ -46885,7 +46885,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1604" t="n">
-        <v>10.4837007522583</v>
+        <v>10.483699798584</v>
       </c>
       <c r="H1604" t="n">
         <v>35975</v>
@@ -46914,7 +46914,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1605" t="n">
-        <v>10.291690826416</v>
+        <v>10.2916917800903</v>
       </c>
       <c r="H1605" t="n">
         <v>38880</v>
@@ -47001,7 +47001,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1608" t="n">
-        <v>10.714111328125</v>
+        <v>10.7141103744507</v>
       </c>
       <c r="H1608" t="n">
         <v>63066</v>
@@ -47146,7 +47146,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1613" t="n">
-        <v>10.9829235076904</v>
+        <v>10.9829244613647</v>
       </c>
       <c r="H1613" t="n">
         <v>31157</v>
@@ -47175,7 +47175,7 @@
         <v>11.5</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.0405263900757</v>
+        <v>11.0405254364014</v>
       </c>
       <c r="H1614" t="n">
         <v>65798</v>
@@ -80009,6 +80009,35 @@
         <v>410139</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>29.3799991607666</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>30.1700000762939</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>28.9599990844727</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>29.8700008392334</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>29.8700008392334</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>539807</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AVIO.MI.xlsx
+++ b/data/AVIO.MI.xlsx
@@ -514,7 +514,7 @@
         <v>9.5</v>
       </c>
       <c r="G5" t="n">
-        <v>8.55948638916016</v>
+        <v>8.55948734283447</v>
       </c>
       <c r="H5" t="n">
         <v>367</v>
@@ -543,7 +543,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G6" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H6" t="n">
         <v>407</v>
@@ -601,7 +601,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G8" t="n">
-        <v>8.91087532043457</v>
+        <v>8.91087627410889</v>
       </c>
       <c r="H8" t="n">
         <v>55700</v>
@@ -630,7 +630,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.91087532043457</v>
+        <v>8.91087627410889</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G11" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H11" t="n">
         <v>1392</v>
@@ -775,7 +775,7 @@
         <v>9.5</v>
       </c>
       <c r="G14" t="n">
-        <v>8.55948638916016</v>
+        <v>8.55948734283447</v>
       </c>
       <c r="H14" t="n">
         <v>156</v>
@@ -862,7 +862,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G17" t="n">
-        <v>8.64958763122559</v>
+        <v>8.64958572387695</v>
       </c>
       <c r="H17" t="n">
         <v>1566</v>
@@ -891,7 +891,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H18" t="n">
         <v>436</v>
@@ -920,7 +920,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G19" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H19" t="n">
         <v>204</v>
@@ -949,7 +949,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.86582565307617</v>
+        <v>8.86582660675049</v>
       </c>
       <c r="H20" t="n">
         <v>828</v>
@@ -1007,7 +1007,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G22" t="n">
-        <v>8.81176662445068</v>
+        <v>8.81176567077637</v>
       </c>
       <c r="H22" t="n">
         <v>3790</v>
@@ -1065,7 +1065,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G24" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H24" t="n">
         <v>8144</v>
@@ -1413,7 +1413,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H36" t="n">
         <v>2000</v>
@@ -1558,7 +1558,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H41" t="n">
         <v>120</v>
@@ -1587,7 +1587,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G42" t="n">
-        <v>8.75770664215088</v>
+        <v>8.75770473480225</v>
       </c>
       <c r="H42" t="n">
         <v>6892</v>
@@ -1935,7 +1935,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G54" t="n">
-        <v>8.86582565307617</v>
+        <v>8.86582660675049</v>
       </c>
       <c r="H54" t="n">
         <v>1111</v>
@@ -1964,7 +1964,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H55" t="n">
         <v>1767</v>
@@ -1993,7 +1993,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H58" t="n">
         <v>1127</v>
@@ -2080,7 +2080,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H59" t="n">
         <v>1517</v>
@@ -2109,7 +2109,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H61" t="n">
         <v>2000</v>
@@ -2167,7 +2167,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H62" t="n">
         <v>1888</v>
@@ -2196,7 +2196,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H63" t="n">
         <v>4000</v>
@@ -2370,7 +2370,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H69" t="n">
         <v>836</v>
@@ -2399,7 +2399,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G71" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H71" t="n">
         <v>64</v>
@@ -2457,7 +2457,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H72" t="n">
         <v>7935</v>
@@ -2486,7 +2486,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2602,7 +2602,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G77" t="n">
-        <v>8.83879661560059</v>
+        <v>8.83879566192627</v>
       </c>
       <c r="H77" t="n">
         <v>48906</v>
@@ -2631,7 +2631,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H78" t="n">
         <v>11483</v>
@@ -2689,7 +2689,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H80" t="n">
         <v>8000</v>
@@ -2776,7 +2776,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H83" t="n">
         <v>12000</v>
@@ -2863,7 +2863,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H86" t="n">
         <v>5000</v>
@@ -2892,7 +2892,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H87" t="n">
         <v>7922</v>
@@ -3008,7 +3008,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H91" t="n">
         <v>220</v>
@@ -3066,7 +3066,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H93" t="n">
         <v>8248</v>
@@ -3182,7 +3182,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>8.9018669128418</v>
+        <v>8.90186595916748</v>
       </c>
       <c r="H97" t="n">
         <v>4354</v>
@@ -3211,7 +3211,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>8.86582565307617</v>
+        <v>8.86582660675049</v>
       </c>
       <c r="H98" t="n">
         <v>10772</v>
@@ -3240,7 +3240,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H99" t="n">
         <v>48692</v>
@@ -3385,7 +3385,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H104" t="n">
         <v>2837</v>
@@ -3414,7 +3414,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G105" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H105" t="n">
         <v>2588</v>
@@ -3443,7 +3443,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G106" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H106" t="n">
         <v>601</v>
@@ -3472,7 +3472,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G107" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G108" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H114" t="n">
         <v>2563</v>
@@ -3820,7 +3820,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.69463634490967</v>
+        <v>8.69463539123535</v>
       </c>
       <c r="H119" t="n">
         <v>16379</v>
@@ -3849,7 +3849,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>8.9018669128418</v>
+        <v>8.90186595916748</v>
       </c>
       <c r="H120" t="n">
         <v>32081</v>
@@ -3878,7 +3878,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>8.71716213226318</v>
+        <v>8.71716117858887</v>
       </c>
       <c r="H121" t="n">
         <v>435</v>
@@ -3907,7 +3907,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>8.71716213226318</v>
+        <v>8.71716117858887</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G130" t="n">
-        <v>8.69914150238037</v>
+        <v>8.69913959503174</v>
       </c>
       <c r="H130" t="n">
         <v>52</v>
@@ -4168,7 +4168,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G131" t="n">
-        <v>8.81176662445068</v>
+        <v>8.81176567077637</v>
       </c>
       <c r="H131" t="n">
         <v>34000</v>
@@ -4400,7 +4400,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G139" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H139" t="n">
         <v>5000</v>
@@ -4429,7 +4429,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G140" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H140" t="n">
         <v>24071</v>
@@ -4458,7 +4458,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H141" t="n">
         <v>2337</v>
@@ -4487,7 +4487,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G142" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H142" t="n">
         <v>1531</v>
@@ -4632,7 +4632,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H147" t="n">
         <v>5000</v>
@@ -4661,7 +4661,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H148" t="n">
         <v>11255</v>
@@ -4690,7 +4690,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G149" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H149" t="n">
         <v>10000</v>
@@ -4719,7 +4719,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G150" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H150" t="n">
         <v>500</v>
@@ -4748,7 +4748,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H151" t="n">
         <v>5000</v>
@@ -4777,7 +4777,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G152" t="n">
-        <v>8.81176662445068</v>
+        <v>8.81176567077637</v>
       </c>
       <c r="H152" t="n">
         <v>2929</v>
@@ -4806,7 +4806,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G153" t="n">
-        <v>8.81176662445068</v>
+        <v>8.81176567077637</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G154" t="n">
-        <v>8.81176662445068</v>
+        <v>8.81176567077637</v>
       </c>
       <c r="H154" t="n">
         <v>1483</v>
@@ -4864,7 +4864,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G155" t="n">
-        <v>8.81176662445068</v>
+        <v>8.81176567077637</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>8.82077598571777</v>
+        <v>8.82077693939209</v>
       </c>
       <c r="H156" t="n">
         <v>442</v>
@@ -4922,7 +4922,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H157" t="n">
         <v>387</v>
@@ -4951,7 +4951,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>8.82077598571777</v>
+        <v>8.82077693939209</v>
       </c>
       <c r="H158" t="n">
         <v>1120</v>
@@ -4980,7 +4980,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>8.64958763122559</v>
+        <v>8.64958572387695</v>
       </c>
       <c r="H159" t="n">
         <v>1862</v>
@@ -5009,7 +5009,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G160" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H160" t="n">
         <v>458</v>
@@ -5038,7 +5038,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G163" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H169" t="n">
         <v>10692</v>
@@ -5299,7 +5299,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H170" t="n">
         <v>10000</v>
@@ -5328,7 +5328,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H171" t="n">
         <v>15758</v>
@@ -5357,7 +5357,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G173" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H174" t="n">
         <v>4436</v>
@@ -5444,7 +5444,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G175" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H176" t="n">
         <v>4687</v>
@@ -5589,7 +5589,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H180" t="n">
         <v>3500</v>
@@ -5618,7 +5618,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H181" t="n">
         <v>7576</v>
@@ -5647,7 +5647,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H182" t="n">
         <v>5572</v>
@@ -5676,7 +5676,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H183" t="n">
         <v>175</v>
@@ -5705,7 +5705,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H184" t="n">
         <v>25000</v>
@@ -5734,7 +5734,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H185" t="n">
         <v>15000</v>
@@ -5792,7 +5792,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H187" t="n">
         <v>10000</v>
@@ -5821,7 +5821,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H190" t="n">
         <v>5204</v>
@@ -5908,7 +5908,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G191" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H191" t="n">
         <v>8000</v>
@@ -5937,7 +5937,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H192" t="n">
         <v>5979</v>
@@ -5966,7 +5966,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H193" t="n">
         <v>10122</v>
@@ -6024,7 +6024,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>8.82978630065918</v>
+        <v>8.8297872543335</v>
       </c>
       <c r="H195" t="n">
         <v>10029</v>
@@ -6082,7 +6082,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G197" t="n">
-        <v>8.83879661560059</v>
+        <v>8.83879566192627</v>
       </c>
       <c r="H197" t="n">
         <v>664</v>
@@ -6111,7 +6111,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G198" t="n">
-        <v>8.83879661560059</v>
+        <v>8.83879566192627</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G199" t="n">
-        <v>8.83879661560059</v>
+        <v>8.83879566192627</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G202" t="n">
-        <v>9.09107685089111</v>
+        <v>9.0910758972168</v>
       </c>
       <c r="H202" t="n">
         <v>15277</v>
@@ -6285,7 +6285,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G204" t="n">
-        <v>9.12711620330811</v>
+        <v>9.12711524963379</v>
       </c>
       <c r="H204" t="n">
         <v>5000</v>
@@ -6372,7 +6372,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>9.1000862121582</v>
+        <v>9.10008716583252</v>
       </c>
       <c r="H207" t="n">
         <v>9160</v>
@@ -6401,7 +6401,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>9.19018650054932</v>
+        <v>9.190185546875</v>
       </c>
       <c r="H208" t="n">
         <v>10641</v>
@@ -6459,7 +6459,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G210" t="n">
-        <v>9.19018650054932</v>
+        <v>9.190185546875</v>
       </c>
       <c r="H210" t="n">
         <v>5170</v>
@@ -6517,7 +6517,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G212" t="n">
-        <v>9.22622585296631</v>
+        <v>9.22622394561768</v>
       </c>
       <c r="H212" t="n">
         <v>90</v>
@@ -6546,7 +6546,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>9.32533645629883</v>
+        <v>9.3253345489502</v>
       </c>
       <c r="H213" t="n">
         <v>54680</v>
@@ -6720,7 +6720,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G219" t="n">
-        <v>9.22622585296631</v>
+        <v>9.22622394561768</v>
       </c>
       <c r="H219" t="n">
         <v>5395</v>
@@ -6749,7 +6749,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>9.19018650054932</v>
+        <v>9.190185546875</v>
       </c>
       <c r="H220" t="n">
         <v>2000</v>
@@ -6778,7 +6778,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>9.19018650054932</v>
+        <v>9.190185546875</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H222" t="n">
         <v>45127</v>
@@ -6836,7 +6836,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>9.41543579101562</v>
+        <v>9.41543483734131</v>
       </c>
       <c r="H223" t="n">
         <v>25828</v>
@@ -6865,7 +6865,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G224" t="n">
-        <v>9.44246482849121</v>
+        <v>9.44246578216553</v>
       </c>
       <c r="H224" t="n">
         <v>5100</v>
@@ -6923,7 +6923,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>9.41543579101562</v>
+        <v>9.41543483734131</v>
       </c>
       <c r="H226" t="n">
         <v>2200</v>
@@ -6952,7 +6952,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G227" t="n">
-        <v>9.38840389251709</v>
+        <v>9.38840579986572</v>
       </c>
       <c r="H227" t="n">
         <v>38098</v>
@@ -7039,7 +7039,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>9.44246482849121</v>
+        <v>9.44246578216553</v>
       </c>
       <c r="H230" t="n">
         <v>25450</v>
@@ -7068,7 +7068,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G231" t="n">
-        <v>9.44246482849121</v>
+        <v>9.44246578216553</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H233" t="n">
         <v>947</v>
@@ -7155,7 +7155,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H234" t="n">
         <v>3210</v>
@@ -7184,7 +7184,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H236" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H238" t="n">
         <v>20501</v>
@@ -7300,7 +7300,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H239" t="n">
         <v>11746</v>
@@ -7329,7 +7329,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H240" t="n">
         <v>9589</v>
@@ -7358,7 +7358,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>9.37038421630859</v>
+        <v>9.37038612365723</v>
       </c>
       <c r="H241" t="n">
         <v>458</v>
@@ -7416,7 +7416,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G243" t="n">
-        <v>9.29830360412598</v>
+        <v>9.29830455780029</v>
       </c>
       <c r="H243" t="n">
         <v>1059</v>
@@ -7445,7 +7445,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G244" t="n">
-        <v>9.29830360412598</v>
+        <v>9.29830455780029</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>9.55058479309082</v>
+        <v>9.55058574676514</v>
       </c>
       <c r="H247" t="n">
         <v>33200</v>
@@ -7561,7 +7561,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>9.55058479309082</v>
+        <v>9.55058574676514</v>
       </c>
       <c r="H248" t="n">
         <v>19179</v>
@@ -7590,7 +7590,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G249" t="n">
-        <v>9.55058479309082</v>
+        <v>9.55058574676514</v>
       </c>
       <c r="H249" t="n">
         <v>53993</v>
@@ -7619,7 +7619,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G250" t="n">
-        <v>9.57761383056641</v>
+        <v>9.57761573791504</v>
       </c>
       <c r="H250" t="n">
         <v>3589</v>
@@ -7648,7 +7648,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H251" t="n">
         <v>3150</v>
@@ -7764,7 +7764,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>9.64068412780762</v>
+        <v>9.64068508148193</v>
       </c>
       <c r="H255" t="n">
         <v>7600</v>
@@ -7793,7 +7793,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>9.64068412780762</v>
+        <v>9.64068508148193</v>
       </c>
       <c r="H256" t="n">
         <v>4300</v>
@@ -7822,7 +7822,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>9.56860446929932</v>
+        <v>9.56860542297363</v>
       </c>
       <c r="H257" t="n">
         <v>1638</v>
@@ -7851,7 +7851,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>9.52355480194092</v>
+        <v>9.52355575561523</v>
       </c>
       <c r="H258" t="n">
         <v>559</v>
@@ -7880,7 +7880,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>9.55058479309082</v>
+        <v>9.55058574676514</v>
       </c>
       <c r="H259" t="n">
         <v>11700</v>
@@ -7909,7 +7909,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G260" t="n">
-        <v>9.62266540527344</v>
+        <v>9.62266445159912</v>
       </c>
       <c r="H260" t="n">
         <v>22172</v>
@@ -8054,7 +8054,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G265" t="n">
-        <v>9.62266540527344</v>
+        <v>9.62266445159912</v>
       </c>
       <c r="H265" t="n">
         <v>2029</v>
@@ -8083,7 +8083,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G266" t="n">
-        <v>9.66771411895752</v>
+        <v>9.66771507263184</v>
       </c>
       <c r="H266" t="n">
         <v>34440</v>
@@ -8199,7 +8199,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G270" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H270" t="n">
         <v>10518</v>
@@ -8228,7 +8228,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G271" t="n">
-        <v>9.70375537872314</v>
+        <v>9.70375442504883</v>
       </c>
       <c r="H271" t="n">
         <v>1828</v>
@@ -8257,7 +8257,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G272" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H272" t="n">
         <v>69700</v>
@@ -8286,7 +8286,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G273" t="n">
-        <v>9.69474411010742</v>
+        <v>9.69474506378174</v>
       </c>
       <c r="H273" t="n">
         <v>4575</v>
@@ -8344,7 +8344,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>9.70375537872314</v>
+        <v>9.70375442504883</v>
       </c>
       <c r="H275" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>9.77583408355713</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H276" t="n">
         <v>7940</v>
@@ -8431,7 +8431,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>9.77583408355713</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H278" t="n">
         <v>43120</v>
@@ -8460,7 +8460,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>9.77583408355713</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H279" t="n">
         <v>21400</v>
@@ -8489,7 +8489,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>9.77583408355713</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H280" t="n">
         <v>2300</v>
@@ -8518,7 +8518,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>9.77583408355713</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H281" t="n">
         <v>8191</v>
@@ -8547,7 +8547,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>9.77583408355713</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H282" t="n">
         <v>5760</v>
@@ -8576,7 +8576,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G283" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H283" t="n">
         <v>2106</v>
@@ -8663,7 +8663,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G286" t="n">
-        <v>9.77583408355713</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H286" t="n">
         <v>2280</v>
@@ -8779,7 +8779,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>9.84791660308838</v>
+        <v>9.84791374206543</v>
       </c>
       <c r="H290" t="n">
         <v>250</v>
@@ -8808,7 +8808,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G291" t="n">
-        <v>9.91999435424805</v>
+        <v>9.91999530792236</v>
       </c>
       <c r="H291" t="n">
         <v>6450</v>
@@ -8895,7 +8895,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G294" t="n">
-        <v>9.89296531677246</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H294" t="n">
         <v>13559</v>
@@ -9011,7 +9011,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>9.89296531677246</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H298" t="n">
         <v>3700</v>
@@ -9040,7 +9040,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>9.89296531677246</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H299" t="n">
         <v>20194</v>
@@ -9069,7 +9069,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G300" t="n">
-        <v>9.89296531677246</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H300" t="n">
         <v>2643</v>
@@ -9127,7 +9127,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G302" t="n">
-        <v>9.77583408355713</v>
+        <v>9.77583503723145</v>
       </c>
       <c r="H302" t="n">
         <v>10894</v>
@@ -9185,7 +9185,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G304" t="n">
-        <v>9.89296531677246</v>
+        <v>9.89296436309814</v>
       </c>
       <c r="H304" t="n">
         <v>11725</v>
@@ -9272,7 +9272,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G307" t="n">
-        <v>9.73078346252441</v>
+        <v>9.73078536987305</v>
       </c>
       <c r="H307" t="n">
         <v>7373</v>
@@ -9301,7 +9301,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G308" t="n">
-        <v>9.80286598205566</v>
+        <v>9.80286312103271</v>
       </c>
       <c r="H308" t="n">
         <v>10783</v>
@@ -9446,7 +9446,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G313" t="n">
-        <v>9.82989501953125</v>
+        <v>9.82989406585693</v>
       </c>
       <c r="H313" t="n">
         <v>1080</v>
@@ -9475,7 +9475,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G314" t="n">
-        <v>9.80286598205566</v>
+        <v>9.80286312103271</v>
       </c>
       <c r="H314" t="n">
         <v>2812</v>
@@ -9533,7 +9533,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G316" t="n">
-        <v>9.80286598205566</v>
+        <v>9.80286312103271</v>
       </c>
       <c r="H316" t="n">
         <v>38581</v>
@@ -9620,7 +9620,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G319" t="n">
-        <v>9.93801498413086</v>
+        <v>9.93801403045654</v>
       </c>
       <c r="H319" t="n">
         <v>78688</v>
@@ -9649,7 +9649,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>10.0010843276978</v>
+        <v>10.0010852813721</v>
       </c>
       <c r="H320" t="n">
         <v>55938</v>
@@ -9678,7 +9678,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G321" t="n">
-        <v>10.0911836624146</v>
+        <v>10.0911846160889</v>
       </c>
       <c r="H321" t="n">
         <v>82567</v>
@@ -9707,7 +9707,7 @@
         <v>11.25</v>
       </c>
       <c r="G322" t="n">
-        <v>10.1362342834473</v>
+        <v>10.1362333297729</v>
       </c>
       <c r="H322" t="n">
         <v>12281</v>
@@ -9736,7 +9736,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>10.2803945541382</v>
+        <v>10.2803936004639</v>
       </c>
       <c r="H323" t="n">
         <v>70878</v>
@@ -9765,7 +9765,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G324" t="n">
-        <v>10.5146541595459</v>
+        <v>10.5146532058716</v>
       </c>
       <c r="H324" t="n">
         <v>43038</v>
@@ -9852,7 +9852,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G327" t="n">
-        <v>12.0012998580933</v>
+        <v>12.0013008117676</v>
       </c>
       <c r="H327" t="n">
         <v>163719</v>
@@ -9881,7 +9881,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>12.0733804702759</v>
+        <v>12.0733814239502</v>
       </c>
       <c r="H328" t="n">
         <v>986804</v>
@@ -9910,7 +9910,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>12.5238800048828</v>
+        <v>12.5238790512085</v>
       </c>
       <c r="H329" t="n">
         <v>1186589</v>
@@ -9939,7 +9939,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G330" t="n">
-        <v>12.1724901199341</v>
+        <v>12.1724910736084</v>
       </c>
       <c r="H330" t="n">
         <v>368945</v>
@@ -9968,7 +9968,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>11.9202108383179</v>
+        <v>11.9202098846436</v>
       </c>
       <c r="H331" t="n">
         <v>181693</v>
@@ -9997,7 +9997,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>12.0283317565918</v>
+        <v>12.0283308029175</v>
       </c>
       <c r="H332" t="n">
         <v>230387</v>
@@ -10026,7 +10026,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G333" t="n">
-        <v>12.0553598403931</v>
+        <v>12.0553617477417</v>
       </c>
       <c r="H333" t="n">
         <v>95115</v>
@@ -10055,7 +10055,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G334" t="n">
-        <v>12.1544713973999</v>
+        <v>12.1544704437256</v>
       </c>
       <c r="H334" t="n">
         <v>104387</v>
@@ -10084,7 +10084,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>12.0733804702759</v>
+        <v>12.0733814239502</v>
       </c>
       <c r="H335" t="n">
         <v>71696</v>
@@ -10113,7 +10113,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H336" t="n">
         <v>172168</v>
@@ -10142,7 +10142,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G337" t="n">
-        <v>11.7219924926758</v>
+        <v>11.7219915390015</v>
       </c>
       <c r="H337" t="n">
         <v>91150</v>
@@ -10258,7 +10258,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G341" t="n">
-        <v>11.6679315567017</v>
+        <v>11.667932510376</v>
       </c>
       <c r="H341" t="n">
         <v>68371</v>
@@ -10316,7 +10316,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>11.8481302261353</v>
+        <v>11.8481311798096</v>
       </c>
       <c r="H343" t="n">
         <v>319564</v>
@@ -10374,7 +10374,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>12.2986307144165</v>
+        <v>12.2986288070679</v>
       </c>
       <c r="H345" t="n">
         <v>222706</v>
@@ -10403,7 +10403,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>12.2986307144165</v>
+        <v>12.2986288070679</v>
       </c>
       <c r="H346" t="n">
         <v>270020</v>
@@ -10432,7 +10432,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G347" t="n">
-        <v>12.4067516326904</v>
+        <v>12.4067506790161</v>
       </c>
       <c r="H347" t="n">
         <v>103074</v>
@@ -10519,7 +10519,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>12.433780670166</v>
+        <v>12.4337797164917</v>
       </c>
       <c r="H350" t="n">
         <v>70343</v>
@@ -10548,7 +10548,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>12.2085313796997</v>
+        <v>12.2085304260254</v>
       </c>
       <c r="H351" t="n">
         <v>72522</v>
@@ -10577,7 +10577,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G352" t="n">
-        <v>12.1364517211914</v>
+        <v>12.1364526748657</v>
       </c>
       <c r="H352" t="n">
         <v>108748</v>
@@ -10606,7 +10606,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G353" t="n">
-        <v>12.0012998580933</v>
+        <v>12.0013008117676</v>
       </c>
       <c r="H353" t="n">
         <v>90767</v>
@@ -10635,7 +10635,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>12.0733804702759</v>
+        <v>12.0733814239502</v>
       </c>
       <c r="H354" t="n">
         <v>82730</v>
@@ -10722,7 +10722,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>12.2085313796997</v>
+        <v>12.2085304260254</v>
       </c>
       <c r="H357" t="n">
         <v>83237</v>
@@ -10751,7 +10751,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H358" t="n">
         <v>17581</v>
@@ -10780,7 +10780,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G359" t="n">
-        <v>12.1724901199341</v>
+        <v>12.1724910736084</v>
       </c>
       <c r="H359" t="n">
         <v>27128</v>
@@ -10809,7 +10809,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>12.0733804702759</v>
+        <v>12.0733814239502</v>
       </c>
       <c r="H360" t="n">
         <v>16894</v>
@@ -10838,7 +10838,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>11.8931798934937</v>
+        <v>11.8931818008423</v>
       </c>
       <c r="H361" t="n">
         <v>254063</v>
@@ -10896,7 +10896,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>11.9832811355591</v>
+        <v>11.9832801818848</v>
       </c>
       <c r="H363" t="n">
         <v>41778</v>
@@ -10925,7 +10925,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>12.0733804702759</v>
+        <v>12.0733814239502</v>
       </c>
       <c r="H364" t="n">
         <v>16925</v>
@@ -11012,7 +11012,7 @@
         <v>13</v>
       </c>
       <c r="G367" t="n">
-        <v>11.7129812240601</v>
+        <v>11.7129821777344</v>
       </c>
       <c r="H367" t="n">
         <v>31507</v>
@@ -11041,7 +11041,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H368" t="n">
         <v>57690</v>
@@ -11070,7 +11070,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G369" t="n">
-        <v>11.6318922042847</v>
+        <v>11.631893157959</v>
       </c>
       <c r="H369" t="n">
         <v>20084</v>
@@ -11099,7 +11099,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G370" t="n">
-        <v>11.6048612594604</v>
+        <v>11.6048622131348</v>
       </c>
       <c r="H370" t="n">
         <v>54129</v>
@@ -11128,7 +11128,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G371" t="n">
-        <v>11.5688209533691</v>
+        <v>11.5688238143921</v>
       </c>
       <c r="H371" t="n">
         <v>41864</v>
@@ -11157,7 +11157,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G372" t="n">
-        <v>11.8391227722168</v>
+        <v>11.8391218185425</v>
       </c>
       <c r="H372" t="n">
         <v>57442</v>
@@ -11215,7 +11215,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G374" t="n">
-        <v>11.8301105499268</v>
+        <v>11.8301115036011</v>
       </c>
       <c r="H374" t="n">
         <v>77136</v>
@@ -11273,7 +11273,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G376" t="n">
-        <v>11.9472417831421</v>
+        <v>11.9472408294678</v>
       </c>
       <c r="H376" t="n">
         <v>97992</v>
@@ -11331,7 +11331,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G378" t="n">
-        <v>11.8661508560181</v>
+        <v>11.8661518096924</v>
       </c>
       <c r="H378" t="n">
         <v>26303</v>
@@ -11360,7 +11360,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>11.8481302261353</v>
+        <v>11.8481311798096</v>
       </c>
       <c r="H379" t="n">
         <v>26402</v>
@@ -11389,7 +11389,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>11.8931798934937</v>
+        <v>11.8931818008423</v>
       </c>
       <c r="H380" t="n">
         <v>72914</v>
@@ -11447,7 +11447,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G382" t="n">
-        <v>11.9832811355591</v>
+        <v>11.9832801818848</v>
       </c>
       <c r="H382" t="n">
         <v>53046</v>
@@ -11476,7 +11476,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H383" t="n">
         <v>36087</v>
@@ -11505,7 +11505,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G384" t="n">
-        <v>11.8931798934937</v>
+        <v>11.8931818008423</v>
       </c>
       <c r="H384" t="n">
         <v>85810</v>
@@ -11592,7 +11592,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G387" t="n">
-        <v>11.6859531402588</v>
+        <v>11.6859521865845</v>
       </c>
       <c r="H387" t="n">
         <v>30586</v>
@@ -11650,7 +11650,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G389" t="n">
-        <v>11.5147609710693</v>
+        <v>11.5147619247437</v>
       </c>
       <c r="H389" t="n">
         <v>39594</v>
@@ -11708,7 +11708,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G391" t="n">
-        <v>11.5598106384277</v>
+        <v>11.5598115921021</v>
       </c>
       <c r="H391" t="n">
         <v>13985</v>
@@ -11766,7 +11766,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G393" t="n">
-        <v>11.6138715744019</v>
+        <v>11.6138725280762</v>
       </c>
       <c r="H393" t="n">
         <v>28134</v>
@@ -11824,7 +11824,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G395" t="n">
-        <v>11.6048612594604</v>
+        <v>11.6048622131348</v>
       </c>
       <c r="H395" t="n">
         <v>21078</v>
@@ -11853,7 +11853,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G396" t="n">
-        <v>11.6138715744019</v>
+        <v>11.6138725280762</v>
       </c>
       <c r="H396" t="n">
         <v>16840</v>
@@ -11882,7 +11882,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G397" t="n">
-        <v>11.4787216186523</v>
+        <v>11.4787225723267</v>
       </c>
       <c r="H397" t="n">
         <v>24031</v>
@@ -11911,7 +11911,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.4787216186523</v>
+        <v>11.4787225723267</v>
       </c>
       <c r="H398" t="n">
         <v>14480</v>
@@ -11969,7 +11969,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>11.3525819778442</v>
+        <v>11.3525829315186</v>
       </c>
       <c r="H400" t="n">
         <v>40741</v>
@@ -11998,7 +11998,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G401" t="n">
-        <v>11.0912933349609</v>
+        <v>11.0912942886353</v>
       </c>
       <c r="H401" t="n">
         <v>33453</v>
@@ -12027,7 +12027,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G402" t="n">
-        <v>11.217432975769</v>
+        <v>11.2174320220947</v>
       </c>
       <c r="H402" t="n">
         <v>45075</v>
@@ -12085,7 +12085,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>11.217432975769</v>
+        <v>11.2174320220947</v>
       </c>
       <c r="H404" t="n">
         <v>43054</v>
@@ -12114,7 +12114,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G405" t="n">
-        <v>11.2985219955444</v>
+        <v>11.2985229492188</v>
       </c>
       <c r="H405" t="n">
         <v>63942</v>
@@ -12143,7 +12143,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G406" t="n">
-        <v>11.2444610595703</v>
+        <v>11.2444620132446</v>
       </c>
       <c r="H406" t="n">
         <v>68026</v>
@@ -12172,7 +12172,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>11.5327816009521</v>
+        <v>11.5327825546265</v>
       </c>
       <c r="H407" t="n">
         <v>77258</v>
@@ -12230,7 +12230,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G409" t="n">
-        <v>11.5688209533691</v>
+        <v>11.5688238143921</v>
       </c>
       <c r="H409" t="n">
         <v>17980</v>
@@ -12259,7 +12259,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>11.5327816009521</v>
+        <v>11.5327825546265</v>
       </c>
       <c r="H410" t="n">
         <v>12688</v>
@@ -12346,7 +12346,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G413" t="n">
-        <v>11.5237712860107</v>
+        <v>11.5237722396851</v>
       </c>
       <c r="H413" t="n">
         <v>204296</v>
@@ -12375,7 +12375,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G414" t="n">
-        <v>11.5417919158936</v>
+        <v>11.5417928695679</v>
       </c>
       <c r="H414" t="n">
         <v>121306</v>
@@ -12404,7 +12404,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G415" t="n">
-        <v>11.36159324646</v>
+        <v>11.3615913391113</v>
       </c>
       <c r="H415" t="n">
         <v>16324</v>
@@ -12462,7 +12462,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>11.3976306915283</v>
+        <v>11.3976316452026</v>
       </c>
       <c r="H417" t="n">
         <v>56834</v>
@@ -12549,7 +12549,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G420" t="n">
-        <v>11.4516925811768</v>
+        <v>11.4516906738281</v>
       </c>
       <c r="H420" t="n">
         <v>5117</v>
@@ -12607,7 +12607,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>11.550802230835</v>
+        <v>11.5508012771606</v>
       </c>
       <c r="H422" t="n">
         <v>36471</v>
@@ -12636,7 +12636,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G423" t="n">
-        <v>11.550802230835</v>
+        <v>11.5508012771606</v>
       </c>
       <c r="H423" t="n">
         <v>10199</v>
@@ -12694,7 +12694,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G425" t="n">
-        <v>11.2714939117432</v>
+        <v>11.2714920043945</v>
       </c>
       <c r="H425" t="n">
         <v>14522</v>
@@ -12723,7 +12723,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G426" t="n">
-        <v>11.3706007003784</v>
+        <v>11.3706016540527</v>
       </c>
       <c r="H426" t="n">
         <v>25040</v>
@@ -12752,7 +12752,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G427" t="n">
-        <v>11.4697103500366</v>
+        <v>11.4697122573853</v>
       </c>
       <c r="H427" t="n">
         <v>43133</v>
@@ -12868,7 +12868,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G431" t="n">
-        <v>11.4246625900269</v>
+        <v>11.4246616363525</v>
       </c>
       <c r="H431" t="n">
         <v>9646</v>
@@ -13013,7 +13013,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G436" t="n">
-        <v>12.2085313796997</v>
+        <v>12.2085304260254</v>
       </c>
       <c r="H436" t="n">
         <v>65196</v>
@@ -13042,7 +13042,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>12.0283317565918</v>
+        <v>12.0283308029175</v>
       </c>
       <c r="H437" t="n">
         <v>212837</v>
@@ -13100,7 +13100,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H439" t="n">
         <v>64563</v>
@@ -13129,7 +13129,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>12.0733804702759</v>
+        <v>12.0733814239502</v>
       </c>
       <c r="H440" t="n">
         <v>64801</v>
@@ -13158,7 +13158,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G441" t="n">
-        <v>11.9562501907349</v>
+        <v>11.9562520980835</v>
       </c>
       <c r="H441" t="n">
         <v>24522</v>
@@ -13187,7 +13187,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G442" t="n">
-        <v>12.2896223068237</v>
+        <v>12.2896213531494</v>
       </c>
       <c r="H442" t="n">
         <v>198527</v>
@@ -13216,7 +13216,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G443" t="n">
-        <v>12.1364517211914</v>
+        <v>12.1364526748657</v>
       </c>
       <c r="H443" t="n">
         <v>45951</v>
@@ -13245,7 +13245,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>12.0733804702759</v>
+        <v>12.0733814239502</v>
       </c>
       <c r="H444" t="n">
         <v>26069</v>
@@ -13303,7 +13303,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G446" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H446" t="n">
         <v>54923</v>
@@ -13332,7 +13332,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H447" t="n">
         <v>61161</v>
@@ -13361,7 +13361,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H448" t="n">
         <v>80711</v>
@@ -13390,7 +13390,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G449" t="n">
-        <v>12.2445726394653</v>
+        <v>12.2445707321167</v>
       </c>
       <c r="H449" t="n">
         <v>58522</v>
@@ -13419,7 +13419,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>12.2085313796997</v>
+        <v>12.2085304260254</v>
       </c>
       <c r="H450" t="n">
         <v>32576</v>
@@ -13448,7 +13448,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>12.2085313796997</v>
+        <v>12.2085304260254</v>
       </c>
       <c r="H451" t="n">
         <v>139654</v>
@@ -13477,7 +13477,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G452" t="n">
-        <v>12.433780670166</v>
+        <v>12.4337797164917</v>
       </c>
       <c r="H452" t="n">
         <v>140534</v>
@@ -13506,7 +13506,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G453" t="n">
-        <v>12.1724901199341</v>
+        <v>12.1724910736084</v>
       </c>
       <c r="H453" t="n">
         <v>99550</v>
@@ -13651,7 +13651,7 @@
         <v>14</v>
       </c>
       <c r="G458" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139812469482</v>
       </c>
       <c r="H458" t="n">
         <v>94927</v>
@@ -13680,7 +13680,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G459" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H459" t="n">
         <v>95869</v>
@@ -13709,7 +13709,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G460" t="n">
-        <v>12.5599193572998</v>
+        <v>12.5599203109741</v>
       </c>
       <c r="H460" t="n">
         <v>83879</v>
@@ -13738,7 +13738,7 @@
         <v>14</v>
       </c>
       <c r="G461" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139812469482</v>
       </c>
       <c r="H461" t="n">
         <v>57363</v>
@@ -13767,7 +13767,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G462" t="n">
-        <v>12.4427919387817</v>
+        <v>12.4427909851074</v>
       </c>
       <c r="H462" t="n">
         <v>52555</v>
@@ -13825,7 +13825,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G464" t="n">
-        <v>12.4968509674072</v>
+        <v>12.4968490600586</v>
       </c>
       <c r="H464" t="n">
         <v>20139</v>
@@ -13854,7 +13854,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>12.4788312911987</v>
+        <v>12.4788303375244</v>
       </c>
       <c r="H465" t="n">
         <v>21815</v>
@@ -13941,7 +13941,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G468" t="n">
-        <v>12.6320018768311</v>
+        <v>12.6319999694824</v>
       </c>
       <c r="H468" t="n">
         <v>66196</v>
@@ -13970,7 +13970,7 @@
         <v>14</v>
       </c>
       <c r="G469" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139812469482</v>
       </c>
       <c r="H469" t="n">
         <v>42342</v>
@@ -14086,7 +14086,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G473" t="n">
-        <v>12.6860599517822</v>
+        <v>12.6860589981079</v>
       </c>
       <c r="H473" t="n">
         <v>66022</v>
@@ -14144,7 +14144,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G475" t="n">
-        <v>12.4427919387817</v>
+        <v>12.4427909851074</v>
       </c>
       <c r="H475" t="n">
         <v>30801</v>
@@ -14173,7 +14173,7 @@
         <v>14</v>
       </c>
       <c r="G476" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139812469482</v>
       </c>
       <c r="H476" t="n">
         <v>220806</v>
@@ -14202,7 +14202,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G477" t="n">
-        <v>12.6410102844238</v>
+        <v>12.6410093307495</v>
       </c>
       <c r="H477" t="n">
         <v>71558</v>
@@ -14318,7 +14318,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G481" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H481" t="n">
         <v>40539</v>
@@ -14347,7 +14347,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G482" t="n">
-        <v>12.5869512557983</v>
+        <v>12.586950302124</v>
       </c>
       <c r="H482" t="n">
         <v>13719</v>
@@ -14376,7 +14376,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G483" t="n">
-        <v>12.5959596633911</v>
+        <v>12.5959587097168</v>
       </c>
       <c r="H483" t="n">
         <v>20343</v>
@@ -14405,7 +14405,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G484" t="n">
-        <v>12.5238800048828</v>
+        <v>12.5238790512085</v>
       </c>
       <c r="H484" t="n">
         <v>24244</v>
@@ -14463,7 +14463,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G486" t="n">
-        <v>12.5869512557983</v>
+        <v>12.586950302124</v>
       </c>
       <c r="H486" t="n">
         <v>14291</v>
@@ -14608,7 +14608,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>12.5238800048828</v>
+        <v>12.5238790512085</v>
       </c>
       <c r="H491" t="n">
         <v>66588</v>
@@ -14637,7 +14637,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G492" t="n">
-        <v>12.5869512557983</v>
+        <v>12.586950302124</v>
       </c>
       <c r="H492" t="n">
         <v>94783</v>
@@ -14666,7 +14666,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G493" t="n">
-        <v>12.433780670166</v>
+        <v>12.4337797164917</v>
       </c>
       <c r="H493" t="n">
         <v>74288</v>
@@ -14695,7 +14695,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>12.5238800048828</v>
+        <v>12.5238790512085</v>
       </c>
       <c r="H494" t="n">
         <v>76144</v>
@@ -14724,7 +14724,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>12.397741317749</v>
+        <v>12.3977394104004</v>
       </c>
       <c r="H495" t="n">
         <v>21443</v>
@@ -14753,7 +14753,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G496" t="n">
-        <v>12.397741317749</v>
+        <v>12.3977394104004</v>
       </c>
       <c r="H496" t="n">
         <v>16190</v>
@@ -14782,7 +14782,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G497" t="n">
-        <v>12.2085313796997</v>
+        <v>12.2085304260254</v>
       </c>
       <c r="H497" t="n">
         <v>21467</v>
@@ -14840,7 +14840,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G499" t="n">
-        <v>12.3346710205078</v>
+        <v>12.3346691131592</v>
       </c>
       <c r="H499" t="n">
         <v>72968</v>
@@ -14898,7 +14898,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G501" t="n">
-        <v>12.3076419830322</v>
+        <v>12.3076400756836</v>
       </c>
       <c r="H501" t="n">
         <v>37502</v>
@@ -14956,7 +14956,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G503" t="n">
-        <v>12.2625913619995</v>
+        <v>12.2625904083252</v>
       </c>
       <c r="H503" t="n">
         <v>27217</v>
@@ -14985,7 +14985,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G504" t="n">
-        <v>12.4067516326904</v>
+        <v>12.4067506790161</v>
       </c>
       <c r="H504" t="n">
         <v>30414</v>
@@ -15014,7 +15014,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G505" t="n">
-        <v>12.4067516326904</v>
+        <v>12.4067506790161</v>
       </c>
       <c r="H505" t="n">
         <v>11226</v>
@@ -15043,7 +15043,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H506" t="n">
         <v>30148</v>
@@ -15072,7 +15072,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>12.0733804702759</v>
+        <v>12.0733814239502</v>
       </c>
       <c r="H507" t="n">
         <v>28410</v>
@@ -15101,7 +15101,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G508" t="n">
-        <v>12.1364517211914</v>
+        <v>12.1364526748657</v>
       </c>
       <c r="H508" t="n">
         <v>33752</v>
@@ -15159,7 +15159,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G510" t="n">
-        <v>12.3076419830322</v>
+        <v>12.3076400756836</v>
       </c>
       <c r="H510" t="n">
         <v>22660</v>
@@ -15188,7 +15188,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G511" t="n">
-        <v>12.1544713973999</v>
+        <v>12.1544704437256</v>
       </c>
       <c r="H511" t="n">
         <v>13230</v>
@@ -15217,7 +15217,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G512" t="n">
-        <v>12.1544713973999</v>
+        <v>12.1544704437256</v>
       </c>
       <c r="H512" t="n">
         <v>12169</v>
@@ -15246,7 +15246,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G513" t="n">
-        <v>12.3076419830322</v>
+        <v>12.3076400756836</v>
       </c>
       <c r="H513" t="n">
         <v>6295</v>
@@ -15275,7 +15275,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G514" t="n">
-        <v>12.4698209762573</v>
+        <v>12.469820022583</v>
       </c>
       <c r="H514" t="n">
         <v>417306</v>
@@ -15362,7 +15362,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G517" t="n">
-        <v>12.5058603286743</v>
+        <v>12.505859375</v>
       </c>
       <c r="H517" t="n">
         <v>56631</v>
@@ -15391,7 +15391,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G518" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H518" t="n">
         <v>40451</v>
@@ -15420,7 +15420,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G519" t="n">
-        <v>12.5779390335083</v>
+        <v>12.5779409408569</v>
       </c>
       <c r="H519" t="n">
         <v>400862</v>
@@ -15449,7 +15449,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G520" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H520" t="n">
         <v>14770</v>
@@ -15478,7 +15478,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G521" t="n">
-        <v>12.6860599517822</v>
+        <v>12.6860589981079</v>
       </c>
       <c r="H521" t="n">
         <v>36110</v>
@@ -15507,7 +15507,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G522" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H522" t="n">
         <v>49334</v>
@@ -15594,7 +15594,7 @@
         <v>14</v>
       </c>
       <c r="G525" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139812469482</v>
       </c>
       <c r="H525" t="n">
         <v>28810</v>
@@ -15681,7 +15681,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G528" t="n">
-        <v>12.5779390335083</v>
+        <v>12.5779409408569</v>
       </c>
       <c r="H528" t="n">
         <v>17748</v>
@@ -15710,7 +15710,7 @@
         <v>14</v>
       </c>
       <c r="G529" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139812469482</v>
       </c>
       <c r="H529" t="n">
         <v>23448</v>
@@ -15739,7 +15739,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G530" t="n">
-        <v>12.5959596633911</v>
+        <v>12.5959587097168</v>
       </c>
       <c r="H530" t="n">
         <v>74663</v>
@@ -15768,7 +15768,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G531" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H531" t="n">
         <v>149774</v>
@@ -15797,7 +15797,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>12.433780670166</v>
+        <v>12.4337797164917</v>
       </c>
       <c r="H532" t="n">
         <v>36369</v>
@@ -15855,7 +15855,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G534" t="n">
-        <v>12.3076419830322</v>
+        <v>12.3076400756836</v>
       </c>
       <c r="H534" t="n">
         <v>16295</v>
@@ -15884,7 +15884,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H535" t="n">
         <v>20589</v>
@@ -15942,7 +15942,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G537" t="n">
-        <v>11.9472417831421</v>
+        <v>11.9472408294678</v>
       </c>
       <c r="H537" t="n">
         <v>63390</v>
@@ -16000,7 +16000,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G539" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H539" t="n">
         <v>19499</v>
@@ -16029,7 +16029,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G540" t="n">
-        <v>11.8391227722168</v>
+        <v>11.8391218185425</v>
       </c>
       <c r="H540" t="n">
         <v>27049</v>
@@ -16087,7 +16087,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>11.8030805587769</v>
+        <v>11.8030824661255</v>
       </c>
       <c r="H542" t="n">
         <v>17412</v>
@@ -16174,7 +16174,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G545" t="n">
-        <v>11.7670421600342</v>
+        <v>11.7670431137085</v>
       </c>
       <c r="H545" t="n">
         <v>15381</v>
@@ -16377,7 +16377,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G552" t="n">
-        <v>11.7310018539429</v>
+        <v>11.7310028076172</v>
       </c>
       <c r="H552" t="n">
         <v>582671</v>
@@ -16406,7 +16406,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>11.7670421600342</v>
+        <v>11.7670431137085</v>
       </c>
       <c r="H553" t="n">
         <v>15676</v>
@@ -16435,7 +16435,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G554" t="n">
-        <v>11.3525819778442</v>
+        <v>11.3525829315186</v>
       </c>
       <c r="H554" t="n">
         <v>54581</v>
@@ -16493,7 +16493,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G556" t="n">
-        <v>10.8480224609375</v>
+        <v>10.8480215072632</v>
       </c>
       <c r="H556" t="n">
         <v>19437</v>
@@ -16551,7 +16551,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G558" t="n">
-        <v>11.028223991394</v>
+        <v>11.0282230377197</v>
       </c>
       <c r="H558" t="n">
         <v>17257</v>
@@ -16580,7 +16580,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G559" t="n">
-        <v>11.0462436676025</v>
+        <v>11.0462427139282</v>
       </c>
       <c r="H559" t="n">
         <v>32128</v>
@@ -16638,7 +16638,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G561" t="n">
-        <v>11.2805023193359</v>
+        <v>11.2805032730103</v>
       </c>
       <c r="H561" t="n">
         <v>6288</v>
@@ -16667,7 +16667,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G562" t="n">
-        <v>11.2264432907104</v>
+        <v>11.2264423370361</v>
       </c>
       <c r="H562" t="n">
         <v>19439</v>
@@ -16754,7 +16754,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G565" t="n">
-        <v>11.7310018539429</v>
+        <v>11.7310028076172</v>
       </c>
       <c r="H565" t="n">
         <v>207603</v>
@@ -16870,7 +16870,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G569" t="n">
-        <v>12.0733804702759</v>
+        <v>12.0733814239502</v>
       </c>
       <c r="H569" t="n">
         <v>55878</v>
@@ -16899,7 +16899,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G570" t="n">
-        <v>12.2175407409668</v>
+        <v>12.2175416946411</v>
       </c>
       <c r="H570" t="n">
         <v>65134</v>
@@ -16928,7 +16928,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>12.2535820007324</v>
+        <v>12.2535810470581</v>
       </c>
       <c r="H571" t="n">
         <v>76093</v>
@@ -16986,7 +16986,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>12.4698209762573</v>
+        <v>12.469820022583</v>
       </c>
       <c r="H573" t="n">
         <v>65036</v>
@@ -17015,7 +17015,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>12.5238800048828</v>
+        <v>12.5238790512085</v>
       </c>
       <c r="H574" t="n">
         <v>51107</v>
@@ -17044,7 +17044,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G575" t="n">
-        <v>12.5779390335083</v>
+        <v>12.5779409408569</v>
       </c>
       <c r="H575" t="n">
         <v>38369</v>
@@ -17073,7 +17073,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>12.5238800048828</v>
+        <v>12.5238790512085</v>
       </c>
       <c r="H576" t="n">
         <v>71952</v>
@@ -17102,7 +17102,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>12.5238800048828</v>
+        <v>12.5238790512085</v>
       </c>
       <c r="H577" t="n">
         <v>115637</v>
@@ -17131,7 +17131,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>12.5419006347656</v>
+        <v>12.5418996810913</v>
       </c>
       <c r="H578" t="n">
         <v>46990</v>
@@ -17160,7 +17160,7 @@
         <v>14</v>
       </c>
       <c r="G579" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139812469482</v>
       </c>
       <c r="H579" t="n">
         <v>47634</v>
@@ -17189,7 +17189,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G580" t="n">
-        <v>12.5779390335083</v>
+        <v>12.5779409408569</v>
       </c>
       <c r="H580" t="n">
         <v>65852</v>
@@ -17218,7 +17218,7 @@
         <v>14</v>
       </c>
       <c r="G581" t="n">
-        <v>12.6139802932739</v>
+        <v>12.6139812469482</v>
       </c>
       <c r="H581" t="n">
         <v>46907</v>
@@ -17392,7 +17392,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>13.1185388565063</v>
+        <v>13.1185398101807</v>
       </c>
       <c r="H587" t="n">
         <v>91238</v>
@@ -17479,7 +17479,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G590" t="n">
-        <v>13.3167581558228</v>
+        <v>13.3167600631714</v>
       </c>
       <c r="H590" t="n">
         <v>126012</v>
@@ -17508,7 +17508,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G591" t="n">
-        <v>13.4969577789307</v>
+        <v>13.496958732605</v>
       </c>
       <c r="H591" t="n">
         <v>22173</v>
@@ -17537,7 +17537,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>13.154580116272</v>
+        <v>13.1545810699463</v>
       </c>
       <c r="H592" t="n">
         <v>67211</v>
@@ -17595,7 +17595,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G594" t="n">
-        <v>13.2627000808716</v>
+        <v>13.2626991271973</v>
       </c>
       <c r="H594" t="n">
         <v>103976</v>
@@ -17653,7 +17653,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G596" t="n">
-        <v>13.4428997039795</v>
+        <v>13.4428987503052</v>
       </c>
       <c r="H596" t="n">
         <v>68738</v>
@@ -17682,7 +17682,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G597" t="n">
-        <v>13.5870599746704</v>
+        <v>13.5870590209961</v>
       </c>
       <c r="H597" t="n">
         <v>60001</v>
@@ -17711,7 +17711,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G598" t="n">
-        <v>13.8213186264038</v>
+        <v>13.8213176727295</v>
       </c>
       <c r="H598" t="n">
         <v>162295</v>
@@ -17740,7 +17740,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G599" t="n">
-        <v>14.2177562713623</v>
+        <v>14.2177572250366</v>
       </c>
       <c r="H599" t="n">
         <v>167686</v>
@@ -17769,7 +17769,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G600" t="n">
-        <v>14.3979578018188</v>
+        <v>14.3979568481445</v>
       </c>
       <c r="H600" t="n">
         <v>122086</v>
@@ -17798,7 +17798,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G601" t="n">
-        <v>14.0375576019287</v>
+        <v>14.037558555603</v>
       </c>
       <c r="H601" t="n">
         <v>114031</v>
@@ -17827,7 +17827,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G602" t="n">
-        <v>14.3619165420532</v>
+        <v>14.3619174957275</v>
       </c>
       <c r="H602" t="n">
         <v>54712</v>
@@ -17856,7 +17856,7 @@
         <v>15.5</v>
       </c>
       <c r="G603" t="n">
-        <v>14.2383556365967</v>
+        <v>14.2383546829224</v>
       </c>
       <c r="H603" t="n">
         <v>176624</v>
@@ -17972,7 +17972,7 @@
         <v>15.5</v>
       </c>
       <c r="G607" t="n">
-        <v>14.2383556365967</v>
+        <v>14.2383546829224</v>
       </c>
       <c r="H607" t="n">
         <v>50628</v>
@@ -18001,7 +18001,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G608" t="n">
-        <v>14.1648664474487</v>
+        <v>14.164867401123</v>
       </c>
       <c r="H608" t="n">
         <v>34955</v>
@@ -18059,7 +18059,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G610" t="n">
-        <v>14.1832389831543</v>
+        <v>14.18323802948</v>
       </c>
       <c r="H610" t="n">
         <v>88700</v>
@@ -18117,7 +18117,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G612" t="n">
-        <v>14.2750988006592</v>
+        <v>14.2750997543335</v>
       </c>
       <c r="H612" t="n">
         <v>88428</v>
@@ -18175,7 +18175,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G614" t="n">
-        <v>13.5218448638916</v>
+        <v>13.5218439102173</v>
       </c>
       <c r="H614" t="n">
         <v>135707</v>
@@ -18204,7 +18204,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>13.7606801986694</v>
+        <v>13.7606811523438</v>
       </c>
       <c r="H615" t="n">
         <v>108828</v>
@@ -18262,7 +18262,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G617" t="n">
-        <v>14.1281223297119</v>
+        <v>14.1281232833862</v>
       </c>
       <c r="H617" t="n">
         <v>55058</v>
@@ -18291,7 +18291,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G618" t="n">
-        <v>14.0730056762695</v>
+        <v>14.0730066299438</v>
       </c>
       <c r="H618" t="n">
         <v>72156</v>
@@ -18378,7 +18378,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G621" t="n">
-        <v>13.9995183944702</v>
+        <v>13.9995174407959</v>
       </c>
       <c r="H621" t="n">
         <v>51339</v>
@@ -18523,7 +18523,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G626" t="n">
-        <v>14.311842918396</v>
+        <v>14.3118438720703</v>
       </c>
       <c r="H626" t="n">
         <v>120976</v>
@@ -18552,7 +18552,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G627" t="n">
-        <v>14.311842918396</v>
+        <v>14.3118438720703</v>
       </c>
       <c r="H627" t="n">
         <v>32076</v>
@@ -18581,7 +18581,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G628" t="n">
-        <v>14.2750988006592</v>
+        <v>14.2750997543335</v>
       </c>
       <c r="H628" t="n">
         <v>24792</v>
@@ -18639,7 +18639,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G630" t="n">
-        <v>13.9260292053223</v>
+        <v>13.9260301589966</v>
       </c>
       <c r="H630" t="n">
         <v>39144</v>
@@ -18668,7 +18668,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G631" t="n">
-        <v>13.5402164459229</v>
+        <v>13.5402154922485</v>
       </c>
       <c r="H631" t="n">
         <v>36869</v>
@@ -18697,7 +18697,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G632" t="n">
-        <v>13.3564949035645</v>
+        <v>13.3564958572388</v>
       </c>
       <c r="H632" t="n">
         <v>71465</v>
@@ -18726,7 +18726,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G633" t="n">
-        <v>13.7606801986694</v>
+        <v>13.7606811523438</v>
       </c>
       <c r="H633" t="n">
         <v>64359</v>
@@ -18755,7 +18755,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G634" t="n">
-        <v>13.3564949035645</v>
+        <v>13.3564958572388</v>
       </c>
       <c r="H634" t="n">
         <v>51629</v>
@@ -18784,7 +18784,7 @@
         <v>14.5</v>
       </c>
       <c r="G635" t="n">
-        <v>13.3197526931763</v>
+        <v>13.319751739502</v>
       </c>
       <c r="H635" t="n">
         <v>28291</v>
@@ -18813,7 +18813,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G636" t="n">
-        <v>13.3381242752075</v>
+        <v>13.3381252288818</v>
       </c>
       <c r="H636" t="n">
         <v>33851</v>
@@ -18842,7 +18842,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G637" t="n">
-        <v>13.3564949035645</v>
+        <v>13.3564958572388</v>
       </c>
       <c r="H637" t="n">
         <v>12019</v>
@@ -18871,7 +18871,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G638" t="n">
-        <v>13.3381242752075</v>
+        <v>13.3381252288818</v>
       </c>
       <c r="H638" t="n">
         <v>15391</v>
@@ -18987,7 +18987,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G642" t="n">
-        <v>13.0625419616699</v>
+        <v>13.0625429153442</v>
       </c>
       <c r="H642" t="n">
         <v>8732</v>
@@ -19016,7 +19016,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G643" t="n">
-        <v>13.0625419616699</v>
+        <v>13.0625429153442</v>
       </c>
       <c r="H643" t="n">
         <v>23236</v>
@@ -19045,7 +19045,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G644" t="n">
-        <v>13.2095193862915</v>
+        <v>13.2095184326172</v>
       </c>
       <c r="H644" t="n">
         <v>11168</v>
@@ -19103,7 +19103,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G646" t="n">
-        <v>13.1360292434692</v>
+        <v>13.1360311508179</v>
       </c>
       <c r="H646" t="n">
         <v>10395</v>
@@ -19132,7 +19132,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G647" t="n">
-        <v>13.1360292434692</v>
+        <v>13.1360311508179</v>
       </c>
       <c r="H647" t="n">
         <v>17578</v>
@@ -19161,7 +19161,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G648" t="n">
-        <v>12.970682144165</v>
+        <v>12.9706811904907</v>
       </c>
       <c r="H648" t="n">
         <v>43570</v>
@@ -19190,7 +19190,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G649" t="n">
-        <v>13.0992860794067</v>
+        <v>13.0992870330811</v>
       </c>
       <c r="H649" t="n">
         <v>17131</v>
@@ -19248,7 +19248,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G651" t="n">
-        <v>13.0992860794067</v>
+        <v>13.0992870330811</v>
       </c>
       <c r="H651" t="n">
         <v>24389</v>
@@ -19277,7 +19277,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G652" t="n">
-        <v>12.8053321838379</v>
+        <v>12.8053331375122</v>
       </c>
       <c r="H652" t="n">
         <v>25195</v>
@@ -19306,7 +19306,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G653" t="n">
-        <v>12.7502174377441</v>
+        <v>12.7502164840698</v>
       </c>
       <c r="H653" t="n">
         <v>25003</v>
@@ -19335,7 +19335,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G654" t="n">
-        <v>12.7502174377441</v>
+        <v>12.7502164840698</v>
       </c>
       <c r="H654" t="n">
         <v>48943</v>
@@ -19364,7 +19364,7 @@
         <v>14</v>
       </c>
       <c r="G655" t="n">
-        <v>12.8604497909546</v>
+        <v>12.8604507446289</v>
       </c>
       <c r="H655" t="n">
         <v>40980</v>
@@ -19422,7 +19422,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G657" t="n">
-        <v>13.2830076217651</v>
+        <v>13.2830066680908</v>
       </c>
       <c r="H657" t="n">
         <v>35610</v>
@@ -19480,7 +19480,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>13.0441694259644</v>
+        <v>13.0441703796387</v>
       </c>
       <c r="H659" t="n">
         <v>27214</v>
@@ -19538,7 +19538,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G661" t="n">
-        <v>12.8971939086914</v>
+        <v>12.8971948623657</v>
       </c>
       <c r="H661" t="n">
         <v>35218</v>
@@ -19625,7 +19625,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G664" t="n">
-        <v>12.7134733200073</v>
+        <v>12.7134742736816</v>
       </c>
       <c r="H664" t="n">
         <v>9568</v>
@@ -19654,7 +19654,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>12.4930095672607</v>
+        <v>12.4930076599121</v>
       </c>
       <c r="H665" t="n">
         <v>19345</v>
@@ -19683,7 +19683,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>12.437891960144</v>
+        <v>12.4378929138184</v>
       </c>
       <c r="H666" t="n">
         <v>29843</v>
@@ -19712,7 +19712,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>12.1255655288696</v>
+        <v>12.1255674362183</v>
       </c>
       <c r="H667" t="n">
         <v>23253</v>
@@ -19741,7 +19741,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G668" t="n">
-        <v>12.0520792007446</v>
+        <v>12.052077293396</v>
       </c>
       <c r="H668" t="n">
         <v>19347</v>
@@ -19770,7 +19770,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G669" t="n">
-        <v>11.9602184295654</v>
+        <v>11.9602193832397</v>
       </c>
       <c r="H669" t="n">
         <v>22192</v>
@@ -19799,7 +19799,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G670" t="n">
-        <v>12.0704517364502</v>
+        <v>12.0704507827759</v>
       </c>
       <c r="H670" t="n">
         <v>17409</v>
@@ -19828,7 +19828,7 @@
         <v>13</v>
       </c>
       <c r="G671" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418468475342</v>
       </c>
       <c r="H671" t="n">
         <v>11997</v>
@@ -19886,7 +19886,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G673" t="n">
-        <v>11.9602184295654</v>
+        <v>11.9602193832397</v>
       </c>
       <c r="H673" t="n">
         <v>43846</v>
@@ -19915,7 +19915,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G674" t="n">
-        <v>12.0520792007446</v>
+        <v>12.052077293396</v>
       </c>
       <c r="H674" t="n">
         <v>12157</v>
@@ -19944,7 +19944,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G675" t="n">
-        <v>11.9969625473022</v>
+        <v>11.9969635009766</v>
       </c>
       <c r="H675" t="n">
         <v>20753</v>
@@ -20031,7 +20031,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G678" t="n">
-        <v>12.8053321838379</v>
+        <v>12.8053331375122</v>
       </c>
       <c r="H678" t="n">
         <v>77708</v>
@@ -20089,7 +20089,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>12.309287071228</v>
+        <v>12.3092880249023</v>
       </c>
       <c r="H680" t="n">
         <v>34421</v>
@@ -20292,7 +20292,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G687" t="n">
-        <v>11.9969625473022</v>
+        <v>11.9969635009766</v>
       </c>
       <c r="H687" t="n">
         <v>27016</v>
@@ -20321,7 +20321,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G688" t="n">
-        <v>12.1990547180176</v>
+        <v>12.1990537643433</v>
       </c>
       <c r="H688" t="n">
         <v>23826</v>
@@ -20350,7 +20350,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G689" t="n">
-        <v>11.9969625473022</v>
+        <v>11.9969635009766</v>
       </c>
       <c r="H689" t="n">
         <v>26917</v>
@@ -20379,7 +20379,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G690" t="n">
-        <v>12.0704517364502</v>
+        <v>12.0704507827759</v>
       </c>
       <c r="H690" t="n">
         <v>22703</v>
@@ -20408,7 +20408,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>12.309287071228</v>
+        <v>12.3092880249023</v>
       </c>
       <c r="H691" t="n">
         <v>51716</v>
@@ -20524,7 +20524,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G695" t="n">
-        <v>12.1255655288696</v>
+        <v>12.1255674362183</v>
       </c>
       <c r="H695" t="n">
         <v>16112</v>
@@ -20553,7 +20553,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G696" t="n">
-        <v>12.1255655288696</v>
+        <v>12.1255674362183</v>
       </c>
       <c r="H696" t="n">
         <v>29302</v>
@@ -20582,7 +20582,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G697" t="n">
-        <v>11.9969625473022</v>
+        <v>11.9969635009766</v>
       </c>
       <c r="H697" t="n">
         <v>7540</v>
@@ -20640,7 +20640,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G699" t="n">
-        <v>12.107195854187</v>
+        <v>12.1071949005127</v>
       </c>
       <c r="H699" t="n">
         <v>23417</v>
@@ -20669,7 +20669,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G700" t="n">
-        <v>12.107195854187</v>
+        <v>12.1071949005127</v>
       </c>
       <c r="H700" t="n">
         <v>24980</v>
@@ -20727,7 +20727,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G702" t="n">
-        <v>11.7764978408813</v>
+        <v>11.7764959335327</v>
       </c>
       <c r="H702" t="n">
         <v>42526</v>
@@ -20785,7 +20785,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G704" t="n">
-        <v>11.7764978408813</v>
+        <v>11.7764959335327</v>
       </c>
       <c r="H704" t="n">
         <v>111386</v>
@@ -20843,7 +20843,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G706" t="n">
-        <v>11.7948684692383</v>
+        <v>11.7948703765869</v>
       </c>
       <c r="H706" t="n">
         <v>20608</v>
@@ -20872,7 +20872,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G707" t="n">
-        <v>11.5376615524292</v>
+        <v>11.5376605987549</v>
       </c>
       <c r="H707" t="n">
         <v>91789</v>
@@ -20901,7 +20901,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G708" t="n">
-        <v>11.2804527282715</v>
+        <v>11.2804508209229</v>
       </c>
       <c r="H708" t="n">
         <v>41975</v>
@@ -20930,7 +20930,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G709" t="n">
-        <v>11.2253351211548</v>
+        <v>11.2253360748291</v>
       </c>
       <c r="H709" t="n">
         <v>66928</v>
@@ -20959,7 +20959,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G710" t="n">
-        <v>10.9497537612915</v>
+        <v>10.9497547149658</v>
       </c>
       <c r="H710" t="n">
         <v>26047</v>
@@ -20988,7 +20988,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G711" t="n">
-        <v>11.2253351211548</v>
+        <v>11.2253360748291</v>
       </c>
       <c r="H711" t="n">
         <v>27214</v>
@@ -21017,7 +21017,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G712" t="n">
-        <v>10.9681253433228</v>
+        <v>10.9681272506714</v>
       </c>
       <c r="H712" t="n">
         <v>33615</v>
@@ -21075,7 +21075,7 @@
         <v>12</v>
       </c>
       <c r="G714" t="n">
-        <v>11.0232410430908</v>
+        <v>11.0232419967651</v>
       </c>
       <c r="H714" t="n">
         <v>44154</v>
@@ -21133,7 +21133,7 @@
         <v>11.5</v>
       </c>
       <c r="G716" t="n">
-        <v>10.5639410018921</v>
+        <v>10.5639400482178</v>
       </c>
       <c r="H716" t="n">
         <v>12973</v>
@@ -21220,7 +21220,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G719" t="n">
-        <v>10.2332439422607</v>
+        <v>10.2332429885864</v>
       </c>
       <c r="H719" t="n">
         <v>33861</v>
@@ -21249,7 +21249,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G720" t="n">
-        <v>10.2883596420288</v>
+        <v>10.2883605957031</v>
       </c>
       <c r="H720" t="n">
         <v>117037</v>
@@ -21307,7 +21307,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>10.4720811843872</v>
+        <v>10.4720802307129</v>
       </c>
       <c r="H722" t="n">
         <v>116369</v>
@@ -21336,7 +21336,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5271978378296</v>
+        <v>10.5271968841553</v>
       </c>
       <c r="H723" t="n">
         <v>141266</v>
@@ -21365,7 +21365,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G724" t="n">
-        <v>10.5455694198608</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H724" t="n">
         <v>81085</v>
@@ -21394,7 +21394,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G725" t="n">
-        <v>10.5455694198608</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H725" t="n">
         <v>11959</v>
@@ -21423,7 +21423,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G726" t="n">
-        <v>10.7844038009644</v>
+        <v>10.784405708313</v>
       </c>
       <c r="H726" t="n">
         <v>27360</v>
@@ -21481,7 +21481,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G728" t="n">
-        <v>10.5455694198608</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H728" t="n">
         <v>30621</v>
@@ -21568,7 +21568,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G731" t="n">
-        <v>10.5455694198608</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H731" t="n">
         <v>26969</v>
@@ -21597,7 +21597,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>10.1964998245239</v>
+        <v>10.1965007781982</v>
       </c>
       <c r="H732" t="n">
         <v>18842</v>
@@ -21684,7 +21684,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G735" t="n">
-        <v>10.2699880599976</v>
+        <v>10.2699871063232</v>
       </c>
       <c r="H735" t="n">
         <v>31073</v>
@@ -21742,7 +21742,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G737" t="n">
-        <v>10.2332439422607</v>
+        <v>10.2332429885864</v>
       </c>
       <c r="H737" t="n">
         <v>24316</v>
@@ -21771,7 +21771,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G738" t="n">
-        <v>10.0495223999023</v>
+        <v>10.0495233535767</v>
       </c>
       <c r="H738" t="n">
         <v>105348</v>
@@ -21887,7 +21887,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G742" t="n">
-        <v>10.2699880599976</v>
+        <v>10.2699871063232</v>
       </c>
       <c r="H742" t="n">
         <v>24494</v>
@@ -21916,7 +21916,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G743" t="n">
-        <v>10.3067321777344</v>
+        <v>10.3067312240601</v>
       </c>
       <c r="H743" t="n">
         <v>18813</v>
@@ -21945,7 +21945,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G744" t="n">
-        <v>10.1230115890503</v>
+        <v>10.123010635376</v>
       </c>
       <c r="H744" t="n">
         <v>26803</v>
@@ -21974,7 +21974,7 @@
         <v>11</v>
       </c>
       <c r="G745" t="n">
-        <v>10.104640007019</v>
+        <v>10.1046390533447</v>
       </c>
       <c r="H745" t="n">
         <v>28781</v>
@@ -22003,7 +22003,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G746" t="n">
-        <v>10.1413841247559</v>
+        <v>10.1413831710815</v>
       </c>
       <c r="H746" t="n">
         <v>4884</v>
@@ -22032,7 +22032,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>10.3434753417969</v>
+        <v>10.3434772491455</v>
       </c>
       <c r="H747" t="n">
         <v>31303</v>
@@ -22061,7 +22061,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G748" t="n">
-        <v>10.1230115890503</v>
+        <v>10.123010635376</v>
       </c>
       <c r="H748" t="n">
         <v>46409</v>
@@ -22119,7 +22119,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G750" t="n">
-        <v>9.77394104003906</v>
+        <v>9.77394199371338</v>
       </c>
       <c r="H750" t="n">
         <v>79581</v>
@@ -22148,7 +22148,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G751" t="n">
-        <v>9.66370868682861</v>
+        <v>9.66370964050293</v>
       </c>
       <c r="H751" t="n">
         <v>35542</v>
@@ -22235,7 +22235,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G754" t="n">
-        <v>10.1413841247559</v>
+        <v>10.1413831710815</v>
       </c>
       <c r="H754" t="n">
         <v>36889</v>
@@ -22264,7 +22264,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G755" t="n">
-        <v>10.2699880599976</v>
+        <v>10.2699871063232</v>
       </c>
       <c r="H755" t="n">
         <v>34506</v>
@@ -22293,7 +22293,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G756" t="n">
-        <v>10.0678958892822</v>
+        <v>10.0678949356079</v>
       </c>
       <c r="H756" t="n">
         <v>6571</v>
@@ -22322,7 +22322,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G757" t="n">
-        <v>9.97603511810303</v>
+        <v>9.97603416442871</v>
       </c>
       <c r="H757" t="n">
         <v>15326</v>
@@ -22380,7 +22380,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G759" t="n">
-        <v>10.0495223999023</v>
+        <v>10.0495233535767</v>
       </c>
       <c r="H759" t="n">
         <v>13366</v>
@@ -22409,7 +22409,7 @@
         <v>11</v>
       </c>
       <c r="G760" t="n">
-        <v>10.104640007019</v>
+        <v>10.1046390533447</v>
       </c>
       <c r="H760" t="n">
         <v>18068</v>
@@ -22467,7 +22467,7 @@
         <v>11</v>
       </c>
       <c r="G762" t="n">
-        <v>10.104640007019</v>
+        <v>10.1046390533447</v>
       </c>
       <c r="H762" t="n">
         <v>7369</v>
@@ -22496,7 +22496,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G763" t="n">
-        <v>10.2516145706177</v>
+        <v>10.251615524292</v>
       </c>
       <c r="H763" t="n">
         <v>15823</v>
@@ -22554,7 +22554,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>10.2883596420288</v>
+        <v>10.2883605957031</v>
       </c>
       <c r="H765" t="n">
         <v>18619</v>
@@ -22583,7 +22583,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G766" t="n">
-        <v>10.2883596420288</v>
+        <v>10.2883605957031</v>
       </c>
       <c r="H766" t="n">
         <v>45436</v>
@@ -22612,7 +22612,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>10.4720811843872</v>
+        <v>10.4720802307129</v>
       </c>
       <c r="H767" t="n">
         <v>57292</v>
@@ -22728,7 +22728,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G771" t="n">
-        <v>10.9681253433228</v>
+        <v>10.9681272506714</v>
       </c>
       <c r="H771" t="n">
         <v>32796</v>
@@ -22757,7 +22757,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>10.8578939437866</v>
+        <v>10.8578929901123</v>
       </c>
       <c r="H772" t="n">
         <v>54464</v>
@@ -22873,7 +22873,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G776" t="n">
-        <v>10.7292890548706</v>
+        <v>10.7292900085449</v>
       </c>
       <c r="H776" t="n">
         <v>29539</v>
@@ -22902,7 +22902,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G777" t="n">
-        <v>10.7844038009644</v>
+        <v>10.784405708313</v>
       </c>
       <c r="H777" t="n">
         <v>13471</v>
@@ -22960,7 +22960,7 @@
         <v>11.5</v>
       </c>
       <c r="G779" t="n">
-        <v>10.5639410018921</v>
+        <v>10.5639400482178</v>
       </c>
       <c r="H779" t="n">
         <v>39884</v>
@@ -22989,7 +22989,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>10.4720811843872</v>
+        <v>10.4720802307129</v>
       </c>
       <c r="H780" t="n">
         <v>10429</v>
@@ -23047,7 +23047,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G782" t="n">
-        <v>10.7109174728394</v>
+        <v>10.710916519165</v>
       </c>
       <c r="H782" t="n">
         <v>5620</v>
@@ -23163,7 +23163,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>10.4720811843872</v>
+        <v>10.4720802307129</v>
       </c>
       <c r="H786" t="n">
         <v>14719</v>
@@ -23250,7 +23250,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G789" t="n">
-        <v>10.5271978378296</v>
+        <v>10.5271968841553</v>
       </c>
       <c r="H789" t="n">
         <v>20045</v>
@@ -23279,7 +23279,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G790" t="n">
-        <v>10.3985910415649</v>
+        <v>10.3985919952393</v>
       </c>
       <c r="H790" t="n">
         <v>21217</v>
@@ -23337,7 +23337,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G792" t="n">
-        <v>10.2332439422607</v>
+        <v>10.2332429885864</v>
       </c>
       <c r="H792" t="n">
         <v>9037</v>
@@ -23366,7 +23366,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G793" t="n">
-        <v>10.3434753417969</v>
+        <v>10.3434772491455</v>
       </c>
       <c r="H793" t="n">
         <v>5226</v>
@@ -23395,7 +23395,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G794" t="n">
-        <v>10.4904527664185</v>
+        <v>10.4904537200928</v>
       </c>
       <c r="H794" t="n">
         <v>11946</v>
@@ -23424,7 +23424,7 @@
         <v>11.5</v>
       </c>
       <c r="G795" t="n">
-        <v>10.5639410018921</v>
+        <v>10.5639400482178</v>
       </c>
       <c r="H795" t="n">
         <v>12029</v>
@@ -23453,7 +23453,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G796" t="n">
-        <v>10.508825302124</v>
+        <v>10.5088243484497</v>
       </c>
       <c r="H796" t="n">
         <v>10323</v>
@@ -23569,7 +23569,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G800" t="n">
-        <v>10.5455694198608</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H800" t="n">
         <v>15103</v>
@@ -23656,7 +23656,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G803" t="n">
-        <v>10.5455694198608</v>
+        <v>10.5455675125122</v>
       </c>
       <c r="H803" t="n">
         <v>12960</v>
@@ -23685,7 +23685,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G804" t="n">
-        <v>10.5271978378296</v>
+        <v>10.5271968841553</v>
       </c>
       <c r="H804" t="n">
         <v>43296</v>
@@ -23830,7 +23830,7 @@
         <v>12</v>
       </c>
       <c r="G809" t="n">
-        <v>11.0232410430908</v>
+        <v>11.0232419967651</v>
       </c>
       <c r="H809" t="n">
         <v>33705</v>
@@ -23888,7 +23888,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G811" t="n">
-        <v>10.4904527664185</v>
+        <v>10.4904537200928</v>
       </c>
       <c r="H811" t="n">
         <v>41004</v>
@@ -23946,7 +23946,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G813" t="n">
-        <v>10.508825302124</v>
+        <v>10.5088243484497</v>
       </c>
       <c r="H813" t="n">
         <v>6949</v>
@@ -23975,7 +23975,7 @@
         <v>11.5</v>
       </c>
       <c r="G814" t="n">
-        <v>10.5639410018921</v>
+        <v>10.5639400482178</v>
       </c>
       <c r="H814" t="n">
         <v>20342</v>
@@ -24004,7 +24004,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G815" t="n">
-        <v>10.913010597229</v>
+        <v>10.9130096435547</v>
       </c>
       <c r="H815" t="n">
         <v>26494</v>
@@ -24062,7 +24062,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G817" t="n">
-        <v>11.2988252639771</v>
+        <v>11.2988224029541</v>
       </c>
       <c r="H817" t="n">
         <v>64392</v>
@@ -24120,7 +24120,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5009164810181</v>
+        <v>11.5009174346924</v>
       </c>
       <c r="H819" t="n">
         <v>30170</v>
@@ -24207,7 +24207,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G822" t="n">
-        <v>11.5376615524292</v>
+        <v>11.5376605987549</v>
       </c>
       <c r="H822" t="n">
         <v>24046</v>
@@ -24265,7 +24265,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G824" t="n">
-        <v>11.5560321807861</v>
+        <v>11.5560331344604</v>
       </c>
       <c r="H824" t="n">
         <v>17635</v>
@@ -24294,7 +24294,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G825" t="n">
-        <v>11.5192880630493</v>
+        <v>11.5192890167236</v>
       </c>
       <c r="H825" t="n">
         <v>24572</v>
@@ -24323,7 +24323,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G826" t="n">
-        <v>11.5376615524292</v>
+        <v>11.5376605987549</v>
       </c>
       <c r="H826" t="n">
         <v>15203</v>
@@ -24352,7 +24352,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G827" t="n">
-        <v>11.6478939056396</v>
+        <v>11.6478929519653</v>
       </c>
       <c r="H827" t="n">
         <v>24323</v>
@@ -24381,7 +24381,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G828" t="n">
-        <v>11.3539390563965</v>
+        <v>11.3539400100708</v>
       </c>
       <c r="H828" t="n">
         <v>54723</v>
@@ -24468,7 +24468,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>11.6478939056396</v>
+        <v>11.6478929519653</v>
       </c>
       <c r="H831" t="n">
         <v>26623</v>
@@ -24555,7 +24555,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G834" t="n">
-        <v>11.2804527282715</v>
+        <v>11.2804508209229</v>
       </c>
       <c r="H834" t="n">
         <v>21258</v>
@@ -24642,7 +24642,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G837" t="n">
-        <v>11.6846370697021</v>
+        <v>11.6846380233765</v>
       </c>
       <c r="H837" t="n">
         <v>37803</v>
@@ -24671,7 +24671,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5927753448486</v>
+        <v>11.5927762985229</v>
       </c>
       <c r="H838" t="n">
         <v>35190</v>
@@ -24787,7 +24787,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G842" t="n">
-        <v>11.5927753448486</v>
+        <v>11.5927762985229</v>
       </c>
       <c r="H842" t="n">
         <v>50833</v>
@@ -24816,7 +24816,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G843" t="n">
-        <v>11.6478939056396</v>
+        <v>11.6478929519653</v>
       </c>
       <c r="H843" t="n">
         <v>37266</v>
@@ -24845,7 +24845,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G844" t="n">
-        <v>11.5560321807861</v>
+        <v>11.5560331344604</v>
       </c>
       <c r="H844" t="n">
         <v>7150</v>
@@ -24874,7 +24874,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G845" t="n">
-        <v>11.44580078125</v>
+        <v>11.4457998275757</v>
       </c>
       <c r="H845" t="n">
         <v>311672</v>
@@ -24932,7 +24932,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G847" t="n">
-        <v>11.7764978408813</v>
+        <v>11.7764959335327</v>
       </c>
       <c r="H847" t="n">
         <v>88509</v>
@@ -24961,7 +24961,7 @@
         <v>13</v>
       </c>
       <c r="G848" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418468475342</v>
       </c>
       <c r="H848" t="n">
         <v>164023</v>
@@ -24990,7 +24990,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G849" t="n">
-        <v>12.0704517364502</v>
+        <v>12.0704507827759</v>
       </c>
       <c r="H849" t="n">
         <v>119148</v>
@@ -25019,7 +25019,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G850" t="n">
-        <v>12.1990547180176</v>
+        <v>12.1990537643433</v>
       </c>
       <c r="H850" t="n">
         <v>131994</v>
@@ -25048,7 +25048,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G851" t="n">
-        <v>12.1990547180176</v>
+        <v>12.1990537643433</v>
       </c>
       <c r="H851" t="n">
         <v>61746</v>
@@ -25077,7 +25077,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G852" t="n">
-        <v>12.2357978820801</v>
+        <v>12.2357988357544</v>
       </c>
       <c r="H852" t="n">
         <v>72949</v>
@@ -25106,7 +25106,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G853" t="n">
-        <v>12.1439390182495</v>
+        <v>12.1439399719238</v>
       </c>
       <c r="H853" t="n">
         <v>29379</v>
@@ -25135,7 +25135,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G854" t="n">
-        <v>11.6846370697021</v>
+        <v>11.6846380233765</v>
       </c>
       <c r="H854" t="n">
         <v>86975</v>
@@ -25164,7 +25164,7 @@
         <v>13</v>
       </c>
       <c r="G855" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418468475342</v>
       </c>
       <c r="H855" t="n">
         <v>50128</v>
@@ -25222,7 +25222,7 @@
         <v>13</v>
       </c>
       <c r="G857" t="n">
-        <v>11.9418458938599</v>
+        <v>11.9418468475342</v>
       </c>
       <c r="H857" t="n">
         <v>14044</v>
@@ -25367,7 +25367,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G862" t="n">
-        <v>12.0313873291016</v>
+        <v>12.0313882827759</v>
       </c>
       <c r="H862" t="n">
         <v>19814</v>
@@ -25396,7 +25396,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G863" t="n">
-        <v>12.0125007629395</v>
+        <v>12.0124998092651</v>
       </c>
       <c r="H863" t="n">
         <v>37881</v>
@@ -25454,7 +25454,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G865" t="n">
-        <v>12.1069383621216</v>
+        <v>12.1069374084473</v>
       </c>
       <c r="H865" t="n">
         <v>45791</v>
@@ -25512,7 +25512,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>12.3713636398315</v>
+        <v>12.3713645935059</v>
       </c>
       <c r="H867" t="n">
         <v>60238</v>
@@ -25541,7 +25541,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>12.3524761199951</v>
+        <v>12.3524770736694</v>
       </c>
       <c r="H868" t="n">
         <v>57547</v>
@@ -25599,7 +25599,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G870" t="n">
-        <v>12.3147010803223</v>
+        <v>12.3147029876709</v>
       </c>
       <c r="H870" t="n">
         <v>44880</v>
@@ -25715,7 +25715,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G874" t="n">
-        <v>12.8624420166016</v>
+        <v>12.8624401092529</v>
       </c>
       <c r="H874" t="n">
         <v>40450</v>
@@ -25744,7 +25744,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G875" t="n">
-        <v>13.0513172149658</v>
+        <v>13.0513162612915</v>
       </c>
       <c r="H875" t="n">
         <v>75423</v>
@@ -25831,7 +25831,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G878" t="n">
-        <v>13.2401943206787</v>
+        <v>13.2401933670044</v>
       </c>
       <c r="H878" t="n">
         <v>52129</v>
@@ -25860,7 +25860,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G879" t="n">
-        <v>13.3346309661865</v>
+        <v>13.3346300125122</v>
       </c>
       <c r="H879" t="n">
         <v>29336</v>
@@ -25889,7 +25889,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G880" t="n">
-        <v>13.4290685653687</v>
+        <v>13.4290676116943</v>
       </c>
       <c r="H880" t="n">
         <v>202506</v>
@@ -25947,7 +25947,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G882" t="n">
-        <v>13.9012584686279</v>
+        <v>13.9012575149536</v>
       </c>
       <c r="H882" t="n">
         <v>79221</v>
@@ -26092,7 +26092,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G887" t="n">
-        <v>13.6368312835693</v>
+        <v>13.6368322372437</v>
       </c>
       <c r="H887" t="n">
         <v>43603</v>
@@ -26208,7 +26208,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G891" t="n">
-        <v>13.6368312835693</v>
+        <v>13.6368322372437</v>
       </c>
       <c r="H891" t="n">
         <v>53477</v>
@@ -26266,7 +26266,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G893" t="n">
-        <v>13.4290685653687</v>
+        <v>13.4290676116943</v>
       </c>
       <c r="H893" t="n">
         <v>43307</v>
@@ -26324,7 +26324,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G895" t="n">
-        <v>13.3346309661865</v>
+        <v>13.3346300125122</v>
       </c>
       <c r="H895" t="n">
         <v>46504</v>
@@ -26353,7 +26353,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>13.50461769104</v>
+        <v>13.5046186447144</v>
       </c>
       <c r="H896" t="n">
         <v>92848</v>
@@ -26411,7 +26411,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G898" t="n">
-        <v>11.8425121307373</v>
+        <v>11.8425130844116</v>
       </c>
       <c r="H898" t="n">
         <v>542195</v>
@@ -26469,7 +26469,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>11.8991746902466</v>
+        <v>11.8991756439209</v>
       </c>
       <c r="H900" t="n">
         <v>182715</v>
@@ -26498,7 +26498,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G901" t="n">
-        <v>11.8425121307373</v>
+        <v>11.8425130844116</v>
       </c>
       <c r="H901" t="n">
         <v>104875</v>
@@ -26527,7 +26527,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G902" t="n">
-        <v>11.7480745315552</v>
+        <v>11.7480754852295</v>
       </c>
       <c r="H902" t="n">
         <v>73837</v>
@@ -26701,7 +26701,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G908" t="n">
-        <v>11.8425121307373</v>
+        <v>11.8425130844116</v>
       </c>
       <c r="H908" t="n">
         <v>44842</v>
@@ -26904,7 +26904,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G915" t="n">
-        <v>11.087007522583</v>
+        <v>11.0870094299316</v>
       </c>
       <c r="H915" t="n">
         <v>61788</v>
@@ -26933,7 +26933,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G916" t="n">
-        <v>11.3136587142944</v>
+        <v>11.3136577606201</v>
       </c>
       <c r="H916" t="n">
         <v>61548</v>
@@ -26962,7 +26962,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H917" t="n">
         <v>53671</v>
@@ -26991,7 +26991,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>11.5403108596802</v>
+        <v>11.5403099060059</v>
       </c>
       <c r="H918" t="n">
         <v>93570</v>
@@ -27020,7 +27020,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G919" t="n">
-        <v>11.3892097473145</v>
+        <v>11.3892107009888</v>
       </c>
       <c r="H919" t="n">
         <v>40951</v>
@@ -27107,7 +27107,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H922" t="n">
         <v>44712</v>
@@ -27194,7 +27194,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H925" t="n">
         <v>14606</v>
@@ -27223,7 +27223,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G926" t="n">
-        <v>11.5025367736816</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H926" t="n">
         <v>16775</v>
@@ -27252,7 +27252,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G927" t="n">
-        <v>11.426983833313</v>
+        <v>11.4269857406616</v>
       </c>
       <c r="H927" t="n">
         <v>19990</v>
@@ -27281,7 +27281,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>11.426983833313</v>
+        <v>11.4269857406616</v>
       </c>
       <c r="H928" t="n">
         <v>27198</v>
@@ -27368,7 +27368,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G931" t="n">
-        <v>11.5780868530273</v>
+        <v>11.578085899353</v>
       </c>
       <c r="H931" t="n">
         <v>35638</v>
@@ -27397,7 +27397,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G932" t="n">
-        <v>11.5025367736816</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H932" t="n">
         <v>33755</v>
@@ -27455,7 +27455,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>11.426983833313</v>
+        <v>11.4269857406616</v>
       </c>
       <c r="H934" t="n">
         <v>23909</v>
@@ -27484,7 +27484,7 @@
         <v>12</v>
       </c>
       <c r="G935" t="n">
-        <v>11.3325462341309</v>
+        <v>11.3325471878052</v>
       </c>
       <c r="H935" t="n">
         <v>57369</v>
@@ -27513,7 +27513,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G936" t="n">
-        <v>11.3136587142944</v>
+        <v>11.3136577606201</v>
       </c>
       <c r="H936" t="n">
         <v>79678</v>
@@ -27658,7 +27658,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G941" t="n">
-        <v>11.5403108596802</v>
+        <v>11.5403099060059</v>
       </c>
       <c r="H941" t="n">
         <v>131770</v>
@@ -27687,7 +27687,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G942" t="n">
-        <v>11.5403108596802</v>
+        <v>11.5403099060059</v>
       </c>
       <c r="H942" t="n">
         <v>92762</v>
@@ -27716,7 +27716,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G943" t="n">
-        <v>11.2758836746216</v>
+        <v>11.2758855819702</v>
       </c>
       <c r="H943" t="n">
         <v>68390</v>
@@ -27745,7 +27745,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G944" t="n">
-        <v>11.2758836746216</v>
+        <v>11.2758855819702</v>
       </c>
       <c r="H944" t="n">
         <v>70477</v>
@@ -27832,7 +27832,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G947" t="n">
-        <v>11.3892097473145</v>
+        <v>11.3892107009888</v>
       </c>
       <c r="H947" t="n">
         <v>98958</v>
@@ -27890,7 +27890,7 @@
         <v>12</v>
       </c>
       <c r="G949" t="n">
-        <v>11.3325462341309</v>
+        <v>11.3325471878052</v>
       </c>
       <c r="H949" t="n">
         <v>43307</v>
@@ -28006,7 +28006,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>11.2381086349487</v>
+        <v>11.238109588623</v>
       </c>
       <c r="H953" t="n">
         <v>57068</v>
@@ -28035,7 +28035,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G954" t="n">
-        <v>11.1058959960938</v>
+        <v>11.1058969497681</v>
       </c>
       <c r="H954" t="n">
         <v>34796</v>
@@ -28064,7 +28064,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G955" t="n">
-        <v>10.7470321655273</v>
+        <v>10.747031211853</v>
       </c>
       <c r="H955" t="n">
         <v>118351</v>
@@ -28093,7 +28093,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G956" t="n">
-        <v>10.7848081588745</v>
+        <v>10.7848072052002</v>
       </c>
       <c r="H956" t="n">
         <v>84552</v>
@@ -28151,7 +28151,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G958" t="n">
-        <v>11.0492334365845</v>
+        <v>11.0492343902588</v>
       </c>
       <c r="H958" t="n">
         <v>26232</v>
@@ -28209,7 +28209,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G960" t="n">
-        <v>10.9925708770752</v>
+        <v>10.9925727844238</v>
       </c>
       <c r="H960" t="n">
         <v>57906</v>
@@ -28267,7 +28267,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>11.1436719894409</v>
+        <v>11.1436729431152</v>
       </c>
       <c r="H962" t="n">
         <v>39508</v>
@@ -28296,7 +28296,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G963" t="n">
-        <v>11.1436719894409</v>
+        <v>11.1436729431152</v>
       </c>
       <c r="H963" t="n">
         <v>33441</v>
@@ -28325,7 +28325,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G964" t="n">
-        <v>11.0492334365845</v>
+        <v>11.0492343902588</v>
       </c>
       <c r="H964" t="n">
         <v>27607</v>
@@ -28354,7 +28354,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G965" t="n">
-        <v>11.1436719894409</v>
+        <v>11.1436729431152</v>
       </c>
       <c r="H965" t="n">
         <v>39503</v>
@@ -28412,7 +28412,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>11.426983833313</v>
+        <v>11.4269857406616</v>
       </c>
       <c r="H967" t="n">
         <v>156102</v>
@@ -28441,7 +28441,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G968" t="n">
-        <v>11.6347494125366</v>
+        <v>11.6347484588623</v>
       </c>
       <c r="H968" t="n">
         <v>192096</v>
@@ -28499,7 +28499,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G970" t="n">
-        <v>11.5591993331909</v>
+        <v>11.5591983795166</v>
       </c>
       <c r="H970" t="n">
         <v>71454</v>
@@ -28557,7 +28557,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G972" t="n">
-        <v>11.8425121307373</v>
+        <v>11.8425130844116</v>
       </c>
       <c r="H972" t="n">
         <v>92839</v>
@@ -28586,7 +28586,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>11.8991746902466</v>
+        <v>11.8991756439209</v>
       </c>
       <c r="H973" t="n">
         <v>78103</v>
@@ -28644,7 +28644,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G975" t="n">
-        <v>11.6347494125366</v>
+        <v>11.6347484588623</v>
       </c>
       <c r="H975" t="n">
         <v>50595</v>
@@ -28673,7 +28673,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G976" t="n">
-        <v>11.5591993331909</v>
+        <v>11.5591983795166</v>
       </c>
       <c r="H976" t="n">
         <v>51019</v>
@@ -28760,7 +28760,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G979" t="n">
-        <v>11.8425121307373</v>
+        <v>11.8425130844116</v>
       </c>
       <c r="H979" t="n">
         <v>93132</v>
@@ -28818,7 +28818,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G981" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H981" t="n">
         <v>94368</v>
@@ -28876,7 +28876,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G983" t="n">
-        <v>11.7480745315552</v>
+        <v>11.7480754852295</v>
       </c>
       <c r="H983" t="n">
         <v>81447</v>
@@ -29050,7 +29050,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G989" t="n">
-        <v>11.5591993331909</v>
+        <v>11.5591983795166</v>
       </c>
       <c r="H989" t="n">
         <v>57728</v>
@@ -29108,7 +29108,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G991" t="n">
-        <v>11.3892097473145</v>
+        <v>11.3892107009888</v>
       </c>
       <c r="H991" t="n">
         <v>38492</v>
@@ -29137,7 +29137,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>11.5025367736816</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H992" t="n">
         <v>29817</v>
@@ -29224,7 +29224,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>12.6546773910522</v>
+        <v>12.6546783447266</v>
       </c>
       <c r="H995" t="n">
         <v>364444</v>
@@ -29369,7 +29369,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>12.9002180099487</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1000" t="n">
         <v>171927</v>
@@ -29485,7 +29485,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.4101800918579</v>
+        <v>13.4101810455322</v>
       </c>
       <c r="H1004" t="n">
         <v>136741</v>
@@ -29514,7 +29514,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.1646413803101</v>
+        <v>13.1646423339844</v>
       </c>
       <c r="H1005" t="n">
         <v>174721</v>
@@ -29543,7 +29543,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.2779684066772</v>
+        <v>13.2779674530029</v>
       </c>
       <c r="H1006" t="n">
         <v>128763</v>
@@ -29572,7 +29572,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1007" t="n">
-        <v>13.4101800918579</v>
+        <v>13.4101810455322</v>
       </c>
       <c r="H1007" t="n">
         <v>116718</v>
@@ -29601,7 +29601,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>13.4101800918579</v>
+        <v>13.4101810455322</v>
       </c>
       <c r="H1008" t="n">
         <v>159287</v>
@@ -29630,7 +29630,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1009" t="n">
-        <v>13.2779684066772</v>
+        <v>13.2779674530029</v>
       </c>
       <c r="H1009" t="n">
         <v>82445</v>
@@ -29659,7 +29659,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.6746072769165</v>
+        <v>13.6746082305908</v>
       </c>
       <c r="H1010" t="n">
         <v>1286825</v>
@@ -29717,7 +29717,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.2779684066772</v>
+        <v>13.2779674530029</v>
       </c>
       <c r="H1012" t="n">
         <v>100226</v>
@@ -29775,7 +29775,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.2590808868408</v>
+        <v>13.2590818405151</v>
       </c>
       <c r="H1014" t="n">
         <v>50055</v>
@@ -29862,7 +29862,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.9946556091309</v>
+        <v>12.9946546554565</v>
       </c>
       <c r="H1017" t="n">
         <v>66115</v>
@@ -30007,7 +30007,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1022" t="n">
-        <v>13.2779684066772</v>
+        <v>13.2779674530029</v>
       </c>
       <c r="H1022" t="n">
         <v>89068</v>
@@ -30036,7 +30036,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.4101800918579</v>
+        <v>13.4101810455322</v>
       </c>
       <c r="H1023" t="n">
         <v>81380</v>
@@ -30094,7 +30094,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1025" t="n">
-        <v>13.2968559265137</v>
+        <v>13.2968549728394</v>
       </c>
       <c r="H1025" t="n">
         <v>98202</v>
@@ -30123,7 +30123,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1026" t="n">
-        <v>13.2590808868408</v>
+        <v>13.2590818405151</v>
       </c>
       <c r="H1026" t="n">
         <v>53275</v>
@@ -30268,7 +30268,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1031" t="n">
-        <v>14.6189861297607</v>
+        <v>14.6189870834351</v>
       </c>
       <c r="H1031" t="n">
         <v>170225</v>
@@ -30384,7 +30384,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.4489974975586</v>
+        <v>14.4489984512329</v>
       </c>
       <c r="H1035" t="n">
         <v>51356</v>
@@ -30471,7 +30471,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.0145835876465</v>
+        <v>14.0145845413208</v>
       </c>
       <c r="H1038" t="n">
         <v>109922</v>
@@ -30500,7 +30500,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1039" t="n">
         <v>101434</v>
@@ -30529,7 +30529,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1040" t="n">
         <v>122847</v>
@@ -30558,7 +30558,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.2223482131958</v>
+        <v>14.2223463058472</v>
       </c>
       <c r="H1041" t="n">
         <v>74947</v>
@@ -30587,7 +30587,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.0901346206665</v>
+        <v>14.0901327133179</v>
       </c>
       <c r="H1042" t="n">
         <v>80725</v>
@@ -30645,7 +30645,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.1467962265015</v>
+        <v>14.1467971801758</v>
       </c>
       <c r="H1044" t="n">
         <v>95719</v>
@@ -30703,7 +30703,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.4867744445801</v>
+        <v>14.4867734909058</v>
       </c>
       <c r="H1046" t="n">
         <v>84343</v>
@@ -30732,7 +30732,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.4867744445801</v>
+        <v>14.4867734909058</v>
       </c>
       <c r="H1047" t="n">
         <v>78283</v>
@@ -30848,7 +30848,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.2978973388672</v>
+        <v>14.2978982925415</v>
       </c>
       <c r="H1051" t="n">
         <v>58228</v>
@@ -30877,7 +30877,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.1467962265015</v>
+        <v>14.1467971801758</v>
       </c>
       <c r="H1052" t="n">
         <v>69603</v>
@@ -30906,7 +30906,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.50461769104</v>
+        <v>13.5046186447144</v>
       </c>
       <c r="H1053" t="n">
         <v>138653</v>
@@ -31022,7 +31022,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.0702047348022</v>
+        <v>13.0702056884766</v>
       </c>
       <c r="H1057" t="n">
         <v>86420</v>
@@ -31109,7 +31109,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9002180099487</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1060" t="n">
         <v>89394</v>
@@ -31138,7 +31138,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1061" t="n">
-        <v>12.598014831543</v>
+        <v>12.5980157852173</v>
       </c>
       <c r="H1061" t="n">
         <v>97412</v>
@@ -31196,7 +31196,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1063" t="n">
-        <v>11.426983833313</v>
+        <v>11.4269857406616</v>
       </c>
       <c r="H1063" t="n">
         <v>131797</v>
@@ -31225,7 +31225,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1064" t="n">
         <v>172709</v>
@@ -31254,7 +31254,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1065" t="n">
-        <v>10.9547967910767</v>
+        <v>10.954797744751</v>
       </c>
       <c r="H1065" t="n">
         <v>69290</v>
@@ -31283,7 +31283,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1066" t="n">
-        <v>9.7271032333374</v>
+        <v>9.72710418701172</v>
       </c>
       <c r="H1066" t="n">
         <v>153655</v>
@@ -31341,7 +31341,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1068" t="n">
-        <v>9.50045299530029</v>
+        <v>9.50045204162598</v>
       </c>
       <c r="H1068" t="n">
         <v>132039</v>
@@ -31370,7 +31370,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1069" t="n">
-        <v>9.74598979949951</v>
+        <v>9.74599075317383</v>
       </c>
       <c r="H1069" t="n">
         <v>94860</v>
@@ -31399,7 +31399,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.57600402832031</v>
+        <v>9.576003074646</v>
       </c>
       <c r="H1070" t="n">
         <v>43703</v>
@@ -31428,7 +31428,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1071" t="n">
-        <v>9.68932819366455</v>
+        <v>9.68932914733887</v>
       </c>
       <c r="H1071" t="n">
         <v>41718</v>
@@ -31457,7 +31457,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1072" t="n">
-        <v>10.3126192092896</v>
+        <v>10.3126182556152</v>
       </c>
       <c r="H1072" t="n">
         <v>84029</v>
@@ -31486,7 +31486,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1073" t="n">
-        <v>10.123743057251</v>
+        <v>10.1237421035767</v>
       </c>
       <c r="H1073" t="n">
         <v>107636</v>
@@ -31544,7 +31544,7 @@
         <v>10.5</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.91597938537598</v>
+        <v>9.91598033905029</v>
       </c>
       <c r="H1075" t="n">
         <v>112514</v>
@@ -31573,7 +31573,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1076" t="n">
-        <v>10.5581569671631</v>
+        <v>10.5581560134888</v>
       </c>
       <c r="H1076" t="n">
         <v>102557</v>
@@ -31660,7 +31660,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.8225841522217</v>
+        <v>10.8225831985474</v>
       </c>
       <c r="H1079" t="n">
         <v>59396</v>
@@ -31747,7 +31747,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>11.426983833313</v>
+        <v>11.4269857406616</v>
       </c>
       <c r="H1082" t="n">
         <v>139775</v>
@@ -31834,7 +31834,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.426983833313</v>
+        <v>11.4269857406616</v>
       </c>
       <c r="H1085" t="n">
         <v>40171</v>
@@ -31863,7 +31863,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1086" t="n">
-        <v>11.5969743728638</v>
+        <v>11.5969734191895</v>
       </c>
       <c r="H1086" t="n">
         <v>44872</v>
@@ -31892,7 +31892,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1087" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H1087" t="n">
         <v>51469</v>
@@ -31950,7 +31950,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1089" t="n">
-        <v>11.2192220687866</v>
+        <v>11.2192211151123</v>
       </c>
       <c r="H1089" t="n">
         <v>35118</v>
@@ -31979,7 +31979,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1090" t="n">
-        <v>11.4647617340088</v>
+        <v>11.4647607803345</v>
       </c>
       <c r="H1090" t="n">
         <v>36123</v>
@@ -32008,7 +32008,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1091" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H1091" t="n">
         <v>55988</v>
@@ -32037,7 +32037,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1092" t="n">
-        <v>11.7480745315552</v>
+        <v>11.7480754852295</v>
       </c>
       <c r="H1092" t="n">
         <v>44824</v>
@@ -32066,7 +32066,7 @@
         <v>13</v>
       </c>
       <c r="G1093" t="n">
-        <v>12.2769260406494</v>
+        <v>12.2769269943237</v>
       </c>
       <c r="H1093" t="n">
         <v>34649</v>
@@ -32124,7 +32124,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1095" t="n">
-        <v>12.6169013977051</v>
+        <v>12.6169023513794</v>
       </c>
       <c r="H1095" t="n">
         <v>35236</v>
@@ -32153,7 +32153,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.6169013977051</v>
+        <v>12.6169023513794</v>
       </c>
       <c r="H1096" t="n">
         <v>59339</v>
@@ -32269,7 +32269,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.8057794570923</v>
+        <v>12.805778503418</v>
       </c>
       <c r="H1100" t="n">
         <v>83899</v>
@@ -32298,7 +32298,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1101" t="n">
-        <v>12.7868909835815</v>
+        <v>12.7868919372559</v>
       </c>
       <c r="H1101" t="n">
         <v>100754</v>
@@ -32501,7 +32501,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1108" t="n">
-        <v>12.8057794570923</v>
+        <v>12.805778503418</v>
       </c>
       <c r="H1108" t="n">
         <v>72306</v>
@@ -32530,7 +32530,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>12.8435554504395</v>
+        <v>12.8435535430908</v>
       </c>
       <c r="H1109" t="n">
         <v>88586</v>
@@ -32588,7 +32588,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1111" t="n">
-        <v>13.3346309661865</v>
+        <v>13.3346300125122</v>
       </c>
       <c r="H1111" t="n">
         <v>87072</v>
@@ -32675,7 +32675,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>13.8823709487915</v>
+        <v>13.8823699951172</v>
       </c>
       <c r="H1114" t="n">
         <v>86472</v>
@@ -32733,7 +32733,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1116" t="n">
-        <v>14.5056610107422</v>
+        <v>14.5056600570679</v>
       </c>
       <c r="H1116" t="n">
         <v>144996</v>
@@ -32762,7 +32762,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1117" t="n">
         <v>195800</v>
@@ -32878,7 +32878,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>14.4489974975586</v>
+        <v>14.4489984512329</v>
       </c>
       <c r="H1121" t="n">
         <v>56679</v>
@@ -32965,7 +32965,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1124" t="n">
-        <v>13.9390344619751</v>
+        <v>13.9390335083008</v>
       </c>
       <c r="H1124" t="n">
         <v>138092</v>
@@ -33023,7 +33023,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1126" t="n">
-        <v>14.2223482131958</v>
+        <v>14.2223463058472</v>
       </c>
       <c r="H1126" t="n">
         <v>90069</v>
@@ -33052,7 +33052,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1127" t="n">
-        <v>14.1279096603394</v>
+        <v>14.127908706665</v>
       </c>
       <c r="H1127" t="n">
         <v>67612</v>
@@ -33168,7 +33168,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1131" t="n">
-        <v>14.7889738082886</v>
+        <v>14.7889728546143</v>
       </c>
       <c r="H1131" t="n">
         <v>197632</v>
@@ -33197,7 +33197,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>15.0534000396729</v>
+        <v>15.0534009933472</v>
       </c>
       <c r="H1132" t="n">
         <v>290925</v>
@@ -33255,7 +33255,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1134" t="n">
-        <v>14.9022989273071</v>
+        <v>14.9023008346558</v>
       </c>
       <c r="H1134" t="n">
         <v>204087</v>
@@ -33284,7 +33284,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1135" t="n">
-        <v>14.8645238876343</v>
+        <v>14.8645248413086</v>
       </c>
       <c r="H1135" t="n">
         <v>47319</v>
@@ -33313,7 +33313,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1136" t="n">
-        <v>14.9022989273071</v>
+        <v>14.9023008346558</v>
       </c>
       <c r="H1136" t="n">
         <v>70158</v>
@@ -33342,7 +33342,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1137" t="n">
-        <v>14.5056610107422</v>
+        <v>14.5056600570679</v>
       </c>
       <c r="H1137" t="n">
         <v>38856</v>
@@ -33371,7 +33371,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>14.6189861297607</v>
+        <v>14.6189870834351</v>
       </c>
       <c r="H1138" t="n">
         <v>51733</v>
@@ -33516,7 +33516,7 @@
         <v>15.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>14.6378746032715</v>
+        <v>14.6378736495972</v>
       </c>
       <c r="H1143" t="n">
         <v>54376</v>
@@ -33545,7 +33545,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1144" t="n">
-        <v>14.4867744445801</v>
+        <v>14.4867734909058</v>
       </c>
       <c r="H1144" t="n">
         <v>42484</v>
@@ -33574,7 +33574,7 @@
         <v>15.5</v>
       </c>
       <c r="G1145" t="n">
-        <v>14.6378746032715</v>
+        <v>14.6378736495972</v>
       </c>
       <c r="H1145" t="n">
         <v>37212</v>
@@ -33603,7 +33603,7 @@
         <v>15.5</v>
       </c>
       <c r="G1146" t="n">
-        <v>14.6378746032715</v>
+        <v>14.6378736495972</v>
       </c>
       <c r="H1146" t="n">
         <v>22508</v>
@@ -33661,7 +33661,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1148" t="n">
-        <v>14.2223482131958</v>
+        <v>14.2223463058472</v>
       </c>
       <c r="H1148" t="n">
         <v>54646</v>
@@ -33690,7 +33690,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1149" t="n">
-        <v>14.1467962265015</v>
+        <v>14.1467971801758</v>
       </c>
       <c r="H1149" t="n">
         <v>23325</v>
@@ -33719,7 +33719,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1150" t="n">
         <v>24139</v>
@@ -33777,7 +33777,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1152" t="n">
-        <v>14.1279096603394</v>
+        <v>14.127908706665</v>
       </c>
       <c r="H1152" t="n">
         <v>21441</v>
@@ -33806,7 +33806,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1153" t="n">
-        <v>14.0523586273193</v>
+        <v>14.0523595809937</v>
       </c>
       <c r="H1153" t="n">
         <v>21255</v>
@@ -33864,7 +33864,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1155" t="n">
-        <v>13.9012584686279</v>
+        <v>13.9012575149536</v>
       </c>
       <c r="H1155" t="n">
         <v>20658</v>
@@ -33922,7 +33922,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1157" t="n">
-        <v>13.6368312835693</v>
+        <v>13.6368322372437</v>
       </c>
       <c r="H1157" t="n">
         <v>37270</v>
@@ -33951,7 +33951,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1158" t="n">
-        <v>13.6746072769165</v>
+        <v>13.6746082305908</v>
       </c>
       <c r="H1158" t="n">
         <v>23816</v>
@@ -34009,7 +34009,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1160" t="n">
-        <v>13.1646413803101</v>
+        <v>13.1646423339844</v>
       </c>
       <c r="H1160" t="n">
         <v>22500</v>
@@ -34038,7 +34038,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1161" t="n">
-        <v>12.8624420166016</v>
+        <v>12.8624401092529</v>
       </c>
       <c r="H1161" t="n">
         <v>37279</v>
@@ -34067,7 +34067,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1162" t="n">
-        <v>13.0513172149658</v>
+        <v>13.0513162612915</v>
       </c>
       <c r="H1162" t="n">
         <v>38552</v>
@@ -34096,7 +34096,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1163" t="n">
-        <v>12.8813304901123</v>
+        <v>12.881329536438</v>
       </c>
       <c r="H1163" t="n">
         <v>48730</v>
@@ -34125,7 +34125,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1164" t="n">
-        <v>12.8624420166016</v>
+        <v>12.8624401092529</v>
       </c>
       <c r="H1164" t="n">
         <v>50167</v>
@@ -34154,7 +34154,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1165" t="n">
-        <v>13.6746072769165</v>
+        <v>13.6746082305908</v>
       </c>
       <c r="H1165" t="n">
         <v>80532</v>
@@ -34241,7 +34241,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1168" t="n">
-        <v>14.1279096603394</v>
+        <v>14.127908706665</v>
       </c>
       <c r="H1168" t="n">
         <v>66522</v>
@@ -34299,7 +34299,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1170" t="n">
-        <v>14.5056610107422</v>
+        <v>14.5056600570679</v>
       </c>
       <c r="H1170" t="n">
         <v>41250</v>
@@ -34328,7 +34328,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1171" t="n">
-        <v>14.4489974975586</v>
+        <v>14.4489984512329</v>
       </c>
       <c r="H1171" t="n">
         <v>26297</v>
@@ -34386,7 +34386,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1173" t="n">
-        <v>14.2223482131958</v>
+        <v>14.2223463058472</v>
       </c>
       <c r="H1173" t="n">
         <v>27459</v>
@@ -34415,7 +34415,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1174" t="n">
         <v>18506</v>
@@ -34444,7 +34444,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>14.0712461471558</v>
+        <v>14.0712451934814</v>
       </c>
       <c r="H1175" t="n">
         <v>25631</v>
@@ -34531,7 +34531,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1178" t="n">
-        <v>13.50461769104</v>
+        <v>13.5046186447144</v>
       </c>
       <c r="H1178" t="n">
         <v>15174</v>
@@ -34560,7 +34560,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1179" t="n">
-        <v>13.3535184860229</v>
+        <v>13.3535194396973</v>
       </c>
       <c r="H1179" t="n">
         <v>29935</v>
@@ -34647,7 +34647,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1182" t="n">
-        <v>13.6746072769165</v>
+        <v>13.6746082305908</v>
       </c>
       <c r="H1182" t="n">
         <v>41126</v>
@@ -34734,7 +34734,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1185" t="n">
-        <v>13.8257083892822</v>
+        <v>13.8257093429565</v>
       </c>
       <c r="H1185" t="n">
         <v>15549</v>
@@ -34763,7 +34763,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1186" t="n">
-        <v>13.7690448760986</v>
+        <v>13.7690458297729</v>
       </c>
       <c r="H1186" t="n">
         <v>41582</v>
@@ -34937,7 +34937,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1192" t="n">
-        <v>14.5056610107422</v>
+        <v>14.5056600570679</v>
       </c>
       <c r="H1192" t="n">
         <v>42962</v>
@@ -35024,7 +35024,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1195" t="n">
-        <v>14.467885017395</v>
+        <v>14.4678859710693</v>
       </c>
       <c r="H1195" t="n">
         <v>27592</v>
@@ -35111,7 +35111,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.4101800918579</v>
+        <v>13.4101810455322</v>
       </c>
       <c r="H1198" t="n">
         <v>69069</v>
@@ -35140,7 +35140,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1199" t="n">
-        <v>13.2590808868408</v>
+        <v>13.2590818405151</v>
       </c>
       <c r="H1199" t="n">
         <v>47019</v>
@@ -35169,7 +35169,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1200" t="n">
-        <v>12.8246660232544</v>
+        <v>12.8246650695801</v>
       </c>
       <c r="H1200" t="n">
         <v>67411</v>
@@ -35198,7 +35198,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.6546773910522</v>
+        <v>12.6546783447266</v>
       </c>
       <c r="H1201" t="n">
         <v>81412</v>
@@ -35227,7 +35227,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.9002180099487</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1202" t="n">
         <v>65638</v>
@@ -35256,7 +35256,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1203" t="n">
-        <v>12.9002180099487</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1203" t="n">
         <v>93020</v>
@@ -35285,7 +35285,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.6169013977051</v>
+        <v>12.6169023513794</v>
       </c>
       <c r="H1204" t="n">
         <v>73072</v>
@@ -35314,7 +35314,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.673565864563</v>
+        <v>12.6735649108887</v>
       </c>
       <c r="H1205" t="n">
         <v>44299</v>
@@ -35372,7 +35372,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.673565864563</v>
+        <v>12.6735649108887</v>
       </c>
       <c r="H1207" t="n">
         <v>43151</v>
@@ -35401,7 +35401,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1208" t="n">
-        <v>12.5035772323608</v>
+        <v>12.5035781860352</v>
       </c>
       <c r="H1208" t="n">
         <v>80617</v>
@@ -35430,7 +35430,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>12.6546773910522</v>
+        <v>12.6546783447266</v>
       </c>
       <c r="H1209" t="n">
         <v>67989</v>
@@ -35459,7 +35459,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.8246660232544</v>
+        <v>12.8246650695801</v>
       </c>
       <c r="H1210" t="n">
         <v>45582</v>
@@ -35488,7 +35488,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.9946556091309</v>
+        <v>12.9946546554565</v>
       </c>
       <c r="H1211" t="n">
         <v>68811</v>
@@ -35575,7 +35575,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1214" t="n">
-        <v>12.8813304901123</v>
+        <v>12.881329536438</v>
       </c>
       <c r="H1214" t="n">
         <v>18846</v>
@@ -35604,7 +35604,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.7868909835815</v>
+        <v>12.7868919372559</v>
       </c>
       <c r="H1215" t="n">
         <v>54328</v>
@@ -35720,7 +35720,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.333589553833</v>
+        <v>12.3335905075073</v>
       </c>
       <c r="H1219" t="n">
         <v>29501</v>
@@ -35749,7 +35749,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.2391510009766</v>
+        <v>12.2391500473022</v>
       </c>
       <c r="H1220" t="n">
         <v>27685</v>
@@ -35778,7 +35778,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1221" t="n">
-        <v>12.1069383621216</v>
+        <v>12.1069374084473</v>
       </c>
       <c r="H1221" t="n">
         <v>23151</v>
@@ -35807,7 +35807,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1222" t="n">
-        <v>11.8425121307373</v>
+        <v>11.8425130844116</v>
       </c>
       <c r="H1222" t="n">
         <v>58032</v>
@@ -35836,7 +35836,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1223" t="n">
-        <v>11.8991746902466</v>
+        <v>11.8991756439209</v>
       </c>
       <c r="H1223" t="n">
         <v>53407</v>
@@ -35894,7 +35894,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.3136587142944</v>
+        <v>11.3136577606201</v>
       </c>
       <c r="H1225" t="n">
         <v>79683</v>
@@ -35952,7 +35952,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1227" t="n">
-        <v>11.5403108596802</v>
+        <v>11.5403099060059</v>
       </c>
       <c r="H1227" t="n">
         <v>75434</v>
@@ -36010,7 +36010,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1229" t="n">
-        <v>11.5025367736816</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H1229" t="n">
         <v>129870</v>
@@ -36097,7 +36097,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.7480745315552</v>
+        <v>11.7480754852295</v>
       </c>
       <c r="H1232" t="n">
         <v>32850</v>
@@ -36126,7 +36126,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.6347494125366</v>
+        <v>11.6347484588623</v>
       </c>
       <c r="H1233" t="n">
         <v>115719</v>
@@ -36213,7 +36213,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1236" t="n">
-        <v>12.0313873291016</v>
+        <v>12.0313882827759</v>
       </c>
       <c r="H1236" t="n">
         <v>46924</v>
@@ -36242,7 +36242,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1237" t="n">
-        <v>12.2391510009766</v>
+        <v>12.2391500473022</v>
       </c>
       <c r="H1237" t="n">
         <v>43185</v>
@@ -36300,7 +36300,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1239" t="n">
-        <v>12.333589553833</v>
+        <v>12.3335905075073</v>
       </c>
       <c r="H1239" t="n">
         <v>39789</v>
@@ -36358,7 +36358,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1241" t="n">
-        <v>10.4070568084717</v>
+        <v>10.4070558547974</v>
       </c>
       <c r="H1241" t="n">
         <v>1787033</v>
@@ -36387,7 +36387,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1242" t="n">
-        <v>10.5581569671631</v>
+        <v>10.5581560134888</v>
       </c>
       <c r="H1242" t="n">
         <v>485582</v>
@@ -36445,7 +36445,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.8414707183838</v>
+        <v>10.8414697647095</v>
       </c>
       <c r="H1244" t="n">
         <v>308303</v>
@@ -36474,7 +36474,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1245" t="n">
-        <v>10.6148195266724</v>
+        <v>10.6148204803467</v>
       </c>
       <c r="H1245" t="n">
         <v>197691</v>
@@ -36503,7 +36503,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1246" t="n">
-        <v>10.5581569671631</v>
+        <v>10.5581560134888</v>
       </c>
       <c r="H1246" t="n">
         <v>227992</v>
@@ -36561,7 +36561,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1248" t="n">
-        <v>10.5581569671631</v>
+        <v>10.5581560134888</v>
       </c>
       <c r="H1248" t="n">
         <v>130270</v>
@@ -36648,7 +36648,7 @@
         <v>11.5</v>
       </c>
       <c r="G1251" t="n">
-        <v>10.8603582382202</v>
+        <v>10.8603572845459</v>
       </c>
       <c r="H1251" t="n">
         <v>127074</v>
@@ -36677,7 +36677,7 @@
         <v>11.5</v>
       </c>
       <c r="G1252" t="n">
-        <v>10.8603582382202</v>
+        <v>10.8603572845459</v>
       </c>
       <c r="H1252" t="n">
         <v>108669</v>
@@ -36706,7 +36706,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1253" t="n">
-        <v>10.7470321655273</v>
+        <v>10.747031211853</v>
       </c>
       <c r="H1253" t="n">
         <v>87227</v>
@@ -36735,7 +36735,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1254" t="n">
-        <v>10.6903686523438</v>
+        <v>10.6903696060181</v>
       </c>
       <c r="H1254" t="n">
         <v>134370</v>
@@ -36793,7 +36793,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1256" t="n">
-        <v>10.7848081588745</v>
+        <v>10.7848072052002</v>
       </c>
       <c r="H1256" t="n">
         <v>81826</v>
@@ -36909,7 +36909,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1260" t="n">
-        <v>10.6714820861816</v>
+        <v>10.671483039856</v>
       </c>
       <c r="H1260" t="n">
         <v>142399</v>
@@ -36967,7 +36967,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.6337060928345</v>
+        <v>10.6337070465088</v>
       </c>
       <c r="H1262" t="n">
         <v>213214</v>
@@ -36996,7 +36996,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.8414707183838</v>
+        <v>10.8414697647095</v>
       </c>
       <c r="H1263" t="n">
         <v>276933</v>
@@ -37054,7 +37054,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.6714820861816</v>
+        <v>10.671483039856</v>
       </c>
       <c r="H1265" t="n">
         <v>145457</v>
@@ -37083,7 +37083,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1266" t="n">
-        <v>10.8792457580566</v>
+        <v>10.8792448043823</v>
       </c>
       <c r="H1266" t="n">
         <v>95967</v>
@@ -37170,7 +37170,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1269" t="n">
-        <v>10.8414707183838</v>
+        <v>10.8414697647095</v>
       </c>
       <c r="H1269" t="n">
         <v>36773</v>
@@ -37228,7 +37228,7 @@
         <v>11.5</v>
       </c>
       <c r="G1271" t="n">
-        <v>10.8603582382202</v>
+        <v>10.8603572845459</v>
       </c>
       <c r="H1271" t="n">
         <v>140579</v>
@@ -37257,7 +37257,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>10.8792457580566</v>
+        <v>10.8792448043823</v>
       </c>
       <c r="H1272" t="n">
         <v>87618</v>
@@ -37315,7 +37315,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1274" t="n">
-        <v>11.2947721481323</v>
+        <v>11.2947731018066</v>
       </c>
       <c r="H1274" t="n">
         <v>205711</v>
@@ -37373,7 +37373,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>11.2381086349487</v>
+        <v>11.238109588623</v>
       </c>
       <c r="H1276" t="n">
         <v>162597</v>
@@ -37402,7 +37402,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1277" t="n">
-        <v>10.9925708770752</v>
+        <v>10.9925727844238</v>
       </c>
       <c r="H1277" t="n">
         <v>68386</v>
@@ -37431,7 +37431,7 @@
         <v>11.5</v>
       </c>
       <c r="G1278" t="n">
-        <v>10.8603582382202</v>
+        <v>10.8603572845459</v>
       </c>
       <c r="H1278" t="n">
         <v>90608</v>
@@ -37460,7 +37460,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1279" t="n">
-        <v>11.5591993331909</v>
+        <v>11.5591983795166</v>
       </c>
       <c r="H1279" t="n">
         <v>435068</v>
@@ -37489,7 +37489,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>11.426983833313</v>
+        <v>11.4269857406616</v>
       </c>
       <c r="H1280" t="n">
         <v>220294</v>
@@ -37547,7 +37547,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1282" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H1282" t="n">
         <v>144633</v>
@@ -37576,7 +37576,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1283" t="n">
-        <v>11.5969743728638</v>
+        <v>11.5969734191895</v>
       </c>
       <c r="H1283" t="n">
         <v>90591</v>
@@ -37634,7 +37634,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1285" t="n">
         <v>111072</v>
@@ -37663,7 +37663,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1286" t="n">
-        <v>11.5025367736816</v>
+        <v>11.502534866333</v>
       </c>
       <c r="H1286" t="n">
         <v>122588</v>
@@ -37692,7 +37692,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1287" t="n">
-        <v>11.5969743728638</v>
+        <v>11.5969734191895</v>
       </c>
       <c r="H1287" t="n">
         <v>76135</v>
@@ -37721,7 +37721,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1288" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1288" t="n">
         <v>85640</v>
@@ -37750,7 +37750,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1289" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1289" t="n">
         <v>115871</v>
@@ -37808,7 +37808,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1291" t="n">
-        <v>11.2192220687866</v>
+        <v>11.2192211151123</v>
       </c>
       <c r="H1291" t="n">
         <v>74002</v>
@@ -37837,7 +37837,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1292" t="n">
-        <v>11.2947721481323</v>
+        <v>11.2947731018066</v>
       </c>
       <c r="H1292" t="n">
         <v>67505</v>
@@ -37866,7 +37866,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1293" t="n">
-        <v>11.370322227478</v>
+        <v>11.3703231811523</v>
       </c>
       <c r="H1293" t="n">
         <v>58479</v>
@@ -37895,7 +37895,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1294" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H1294" t="n">
         <v>78819</v>
@@ -37924,7 +37924,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1295" t="n">
-        <v>11.5969743728638</v>
+        <v>11.5969734191895</v>
       </c>
       <c r="H1295" t="n">
         <v>129650</v>
@@ -37982,7 +37982,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>12.3713636398315</v>
+        <v>12.3713645935059</v>
       </c>
       <c r="H1297" t="n">
         <v>256188</v>
@@ -38011,7 +38011,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1298" t="n">
-        <v>12.0125007629395</v>
+        <v>12.0124998092651</v>
       </c>
       <c r="H1298" t="n">
         <v>139903</v>
@@ -38098,7 +38098,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H1301" t="n">
         <v>107532</v>
@@ -38156,7 +38156,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1303" t="n">
-        <v>11.8991746902466</v>
+        <v>11.8991756439209</v>
       </c>
       <c r="H1303" t="n">
         <v>65289</v>
@@ -38185,7 +38185,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1304" t="n">
-        <v>11.5591993331909</v>
+        <v>11.5591983795166</v>
       </c>
       <c r="H1304" t="n">
         <v>77673</v>
@@ -38214,7 +38214,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1305" t="n">
-        <v>11.9369497299194</v>
+        <v>11.9369506835938</v>
       </c>
       <c r="H1305" t="n">
         <v>84897</v>
@@ -38243,7 +38243,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1306" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H1306" t="n">
         <v>49340</v>
@@ -38330,7 +38330,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H1309" t="n">
         <v>51318</v>
@@ -38359,7 +38359,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.426983833313</v>
+        <v>11.4269857406616</v>
       </c>
       <c r="H1310" t="n">
         <v>65385</v>
@@ -38388,7 +38388,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.8802871704102</v>
+        <v>11.8802881240845</v>
       </c>
       <c r="H1311" t="n">
         <v>133633</v>
@@ -38446,7 +38446,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.8425121307373</v>
+        <v>11.8425130844116</v>
       </c>
       <c r="H1313" t="n">
         <v>98684</v>
@@ -38504,7 +38504,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1315" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H1315" t="n">
         <v>72983</v>
@@ -38533,7 +38533,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>11.8991746902466</v>
+        <v>11.8991756439209</v>
       </c>
       <c r="H1316" t="n">
         <v>54096</v>
@@ -38736,7 +38736,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1323" t="n">
-        <v>12.0313873291016</v>
+        <v>12.0313882827759</v>
       </c>
       <c r="H1323" t="n">
         <v>45985</v>
@@ -38765,7 +38765,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>11.8991746902466</v>
+        <v>11.8991756439209</v>
       </c>
       <c r="H1324" t="n">
         <v>28799</v>
@@ -38823,7 +38823,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1326" t="n">
-        <v>11.8991746902466</v>
+        <v>11.8991756439209</v>
       </c>
       <c r="H1326" t="n">
         <v>153267</v>
@@ -38852,7 +38852,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1327" t="n">
-        <v>11.8425121307373</v>
+        <v>11.8425130844116</v>
       </c>
       <c r="H1327" t="n">
         <v>37857</v>
@@ -38881,7 +38881,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1328" t="n">
-        <v>11.6347494125366</v>
+        <v>11.6347484588623</v>
       </c>
       <c r="H1328" t="n">
         <v>67972</v>
@@ -38910,7 +38910,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1329" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H1329" t="n">
         <v>85386</v>
@@ -38939,7 +38939,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>11.6158628463745</v>
+        <v>11.6158618927002</v>
       </c>
       <c r="H1330" t="n">
         <v>76432</v>
@@ -38968,7 +38968,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1331" t="n">
-        <v>11.5403108596802</v>
+        <v>11.5403099060059</v>
       </c>
       <c r="H1331" t="n">
         <v>116336</v>
@@ -39026,7 +39026,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1333" t="n">
-        <v>11.5969743728638</v>
+        <v>11.5969734191895</v>
       </c>
       <c r="H1333" t="n">
         <v>75640</v>
@@ -39084,7 +39084,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1335" t="n">
-        <v>11.9369497299194</v>
+        <v>11.9369506835938</v>
       </c>
       <c r="H1335" t="n">
         <v>90834</v>
@@ -39113,7 +39113,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1336" t="n">
-        <v>12.0125007629395</v>
+        <v>12.0124998092651</v>
       </c>
       <c r="H1336" t="n">
         <v>112912</v>
@@ -39142,7 +39142,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1337" t="n">
-        <v>14.0145835876465</v>
+        <v>14.0145845413208</v>
       </c>
       <c r="H1337" t="n">
         <v>1066070</v>
@@ -39171,7 +39171,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1338" t="n">
-        <v>14.1467962265015</v>
+        <v>14.1467971801758</v>
       </c>
       <c r="H1338" t="n">
         <v>457633</v>
@@ -39258,7 +39258,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1341" t="n">
-        <v>12.9002180099487</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1341" t="n">
         <v>192706</v>
@@ -39316,7 +39316,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1343" t="n">
-        <v>12.8624420166016</v>
+        <v>12.8624401092529</v>
       </c>
       <c r="H1343" t="n">
         <v>88422</v>
@@ -39345,7 +39345,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1344" t="n">
-        <v>12.6357898712158</v>
+        <v>12.6357908248901</v>
       </c>
       <c r="H1344" t="n">
         <v>117086</v>
@@ -39374,7 +39374,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1345" t="n">
-        <v>12.598014831543</v>
+        <v>12.5980157852173</v>
       </c>
       <c r="H1345" t="n">
         <v>134227</v>
@@ -39461,7 +39461,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1348" t="n">
-        <v>12.9002180099487</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1348" t="n">
         <v>98043</v>
@@ -39490,7 +39490,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1349" t="n">
-        <v>12.9002180099487</v>
+        <v>12.9002161026001</v>
       </c>
       <c r="H1349" t="n">
         <v>91612</v>
@@ -39519,7 +39519,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1350" t="n">
-        <v>13.0513172149658</v>
+        <v>13.0513162612915</v>
       </c>
       <c r="H1350" t="n">
         <v>78488</v>
@@ -39548,7 +39548,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0702047348022</v>
+        <v>13.0702056884766</v>
       </c>
       <c r="H1351" t="n">
         <v>153049</v>
@@ -39577,7 +39577,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1352" t="n">
-        <v>13.0513172149658</v>
+        <v>13.0513162612915</v>
       </c>
       <c r="H1352" t="n">
         <v>253856</v>
@@ -39664,7 +39664,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1355" t="n">
-        <v>13.0702047348022</v>
+        <v>13.0702056884766</v>
       </c>
       <c r="H1355" t="n">
         <v>156743</v>
@@ -39751,7 +39751,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1358" t="n">
-        <v>13.2590808868408</v>
+        <v>13.2590818405151</v>
       </c>
       <c r="H1358" t="n">
         <v>117513</v>
@@ -39867,7 +39867,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1362" t="n">
-        <v>12.5958013534546</v>
+        <v>12.5958003997803</v>
       </c>
       <c r="H1362" t="n">
         <v>209024</v>
@@ -39896,7 +39896,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1363" t="n">
-        <v>12.5573987960815</v>
+        <v>12.5573997497559</v>
       </c>
       <c r="H1363" t="n">
         <v>130670</v>
@@ -39925,7 +39925,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1364" t="n">
-        <v>12.8070106506348</v>
+        <v>12.8070116043091</v>
       </c>
       <c r="H1364" t="n">
         <v>105523</v>
@@ -39954,7 +39954,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1365" t="n">
-        <v>12.7110061645508</v>
+        <v>12.7110071182251</v>
       </c>
       <c r="H1365" t="n">
         <v>97577</v>
@@ -39983,7 +39983,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1366" t="n">
-        <v>12.5958013534546</v>
+        <v>12.5958003997803</v>
       </c>
       <c r="H1366" t="n">
         <v>71189</v>
@@ -40012,7 +40012,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1367" t="n">
-        <v>12.5189971923828</v>
+        <v>12.5189981460571</v>
       </c>
       <c r="H1367" t="n">
         <v>70377</v>
@@ -40041,7 +40041,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1368" t="n">
-        <v>12.442193031311</v>
+        <v>12.4421939849854</v>
       </c>
       <c r="H1368" t="n">
         <v>50790</v>
@@ -40070,7 +40070,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1369" t="n">
-        <v>12.5573987960815</v>
+        <v>12.5573997497559</v>
       </c>
       <c r="H1369" t="n">
         <v>38990</v>
@@ -40157,7 +40157,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1372" t="n">
-        <v>12.3461894989014</v>
+        <v>12.3461885452271</v>
       </c>
       <c r="H1372" t="n">
         <v>42496</v>
@@ -40244,7 +40244,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>12.5573987960815</v>
+        <v>12.5573997497559</v>
       </c>
       <c r="H1375" t="n">
         <v>80608</v>
@@ -40273,7 +40273,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1376" t="n">
-        <v>12.5381984710693</v>
+        <v>12.5381994247437</v>
       </c>
       <c r="H1376" t="n">
         <v>25990</v>
@@ -40302,7 +40302,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1377" t="n">
-        <v>12.5381984710693</v>
+        <v>12.5381994247437</v>
       </c>
       <c r="H1377" t="n">
         <v>66418</v>
@@ -40331,7 +40331,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1378" t="n">
-        <v>12.5573987960815</v>
+        <v>12.5573997497559</v>
       </c>
       <c r="H1378" t="n">
         <v>73905</v>
@@ -40360,7 +40360,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1379" t="n">
-        <v>12.5381984710693</v>
+        <v>12.5381994247437</v>
       </c>
       <c r="H1379" t="n">
         <v>49734</v>
@@ -40418,7 +40418,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1381" t="n">
-        <v>12.5189971923828</v>
+        <v>12.5189981460571</v>
       </c>
       <c r="H1381" t="n">
         <v>39360</v>
@@ -40476,7 +40476,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1383" t="n">
-        <v>12.6150026321411</v>
+        <v>12.6150016784668</v>
       </c>
       <c r="H1383" t="n">
         <v>152039</v>
@@ -40505,7 +40505,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.826210975647</v>
+        <v>12.8262119293213</v>
       </c>
       <c r="H1384" t="n">
         <v>135738</v>
@@ -40563,7 +40563,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1386" t="n">
-        <v>12.7878103256226</v>
+        <v>12.7878093719482</v>
       </c>
       <c r="H1386" t="n">
         <v>68715</v>
@@ -40592,7 +40592,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1387" t="n">
-        <v>12.7110061645508</v>
+        <v>12.7110071182251</v>
       </c>
       <c r="H1387" t="n">
         <v>30622</v>
@@ -40621,7 +40621,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1388" t="n">
-        <v>12.1733808517456</v>
+        <v>12.1733798980713</v>
       </c>
       <c r="H1388" t="n">
         <v>320588</v>
@@ -40650,7 +40650,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1389" t="n">
-        <v>12.5958013534546</v>
+        <v>12.5958003997803</v>
       </c>
       <c r="H1389" t="n">
         <v>126201</v>
@@ -40708,7 +40708,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1391" t="n">
-        <v>12.3077869415283</v>
+        <v>12.307785987854</v>
       </c>
       <c r="H1391" t="n">
         <v>55545</v>
@@ -40737,7 +40737,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1392" t="n">
-        <v>12.2885856628418</v>
+        <v>12.2885866165161</v>
       </c>
       <c r="H1392" t="n">
         <v>33741</v>
@@ -40824,7 +40824,7 @@
         <v>12.5</v>
       </c>
       <c r="G1395" t="n">
-        <v>12.0005722045898</v>
+        <v>12.0005731582642</v>
       </c>
       <c r="H1395" t="n">
         <v>48049</v>
@@ -40853,7 +40853,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1396" t="n">
-        <v>11.9429693222046</v>
+        <v>11.9429702758789</v>
       </c>
       <c r="H1396" t="n">
         <v>46883</v>
@@ -40940,7 +40940,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1399" t="n">
-        <v>11.9429693222046</v>
+        <v>11.9429702758789</v>
       </c>
       <c r="H1399" t="n">
         <v>42590</v>
@@ -41027,7 +41027,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1402" t="n">
-        <v>11.6357545852661</v>
+        <v>11.6357555389404</v>
       </c>
       <c r="H1402" t="n">
         <v>60322</v>
@@ -41056,7 +41056,7 @@
         <v>12.5</v>
       </c>
       <c r="G1403" t="n">
-        <v>12.0005722045898</v>
+        <v>12.0005731582642</v>
       </c>
       <c r="H1403" t="n">
         <v>57341</v>
@@ -41143,7 +41143,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1406" t="n">
-        <v>11.7125577926636</v>
+        <v>11.7125587463379</v>
       </c>
       <c r="H1406" t="n">
         <v>30508</v>
@@ -41230,7 +41230,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.2517356872559</v>
+        <v>11.2517366409302</v>
       </c>
       <c r="H1409" t="n">
         <v>97412</v>
@@ -41404,7 +41404,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.2901382446289</v>
+        <v>11.2901391983032</v>
       </c>
       <c r="H1415" t="n">
         <v>38827</v>
@@ -41433,7 +41433,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>11.4245443344116</v>
+        <v>11.4245452880859</v>
       </c>
       <c r="H1416" t="n">
         <v>44295</v>
@@ -41462,7 +41462,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1417" t="n">
-        <v>11.4245443344116</v>
+        <v>11.4245452880859</v>
       </c>
       <c r="H1417" t="n">
         <v>50545</v>
@@ -41491,7 +41491,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1418" t="n">
-        <v>11.3861436843872</v>
+        <v>11.3861427307129</v>
       </c>
       <c r="H1418" t="n">
         <v>33627</v>
@@ -41549,7 +41549,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1420" t="n">
-        <v>11.2517356872559</v>
+        <v>11.2517366409302</v>
       </c>
       <c r="H1420" t="n">
         <v>57286</v>
@@ -41636,7 +41636,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1423" t="n">
-        <v>11.3477411270142</v>
+        <v>11.3477401733398</v>
       </c>
       <c r="H1423" t="n">
         <v>109442</v>
@@ -41810,7 +41810,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1429" t="n">
-        <v>10.9253215789795</v>
+        <v>10.9253206253052</v>
       </c>
       <c r="H1429" t="n">
         <v>102974</v>
@@ -41839,7 +41839,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1430" t="n">
-        <v>10.906120300293</v>
+        <v>10.9061193466187</v>
       </c>
       <c r="H1430" t="n">
         <v>105267</v>
@@ -41926,7 +41926,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.8101148605347</v>
+        <v>10.810115814209</v>
       </c>
       <c r="H1433" t="n">
         <v>98044</v>
@@ -41955,7 +41955,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1434" t="n">
-        <v>10.9829235076904</v>
+        <v>10.9829244613647</v>
       </c>
       <c r="H1434" t="n">
         <v>135271</v>
@@ -41984,7 +41984,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1435" t="n">
-        <v>10.9829235076904</v>
+        <v>10.9829244613647</v>
       </c>
       <c r="H1435" t="n">
         <v>118624</v>
@@ -42100,7 +42100,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1439" t="n">
-        <v>11.5397520065308</v>
+        <v>11.5397510528564</v>
       </c>
       <c r="H1439" t="n">
         <v>103193</v>
@@ -42187,7 +42187,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1442" t="n">
-        <v>11.7125577926636</v>
+        <v>11.7125587463379</v>
       </c>
       <c r="H1442" t="n">
         <v>67084</v>
@@ -42216,7 +42216,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>11.4245443344116</v>
+        <v>11.4245452880859</v>
       </c>
       <c r="H1443" t="n">
         <v>105208</v>
@@ -42245,7 +42245,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1444" t="n">
-        <v>11.2517356872559</v>
+        <v>11.2517366409302</v>
       </c>
       <c r="H1444" t="n">
         <v>125746</v>
@@ -42390,7 +42390,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>10.8677177429199</v>
+        <v>10.8677186965942</v>
       </c>
       <c r="H1449" t="n">
         <v>80959</v>
@@ -42564,7 +42564,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1455" t="n">
-        <v>10.3684940338135</v>
+        <v>10.3684949874878</v>
       </c>
       <c r="H1455" t="n">
         <v>49899</v>
@@ -42622,7 +42622,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1457" t="n">
-        <v>10.6373081207275</v>
+        <v>10.6373071670532</v>
       </c>
       <c r="H1457" t="n">
         <v>74160</v>
@@ -42651,7 +42651,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>10.4837007522583</v>
+        <v>10.483699798584</v>
       </c>
       <c r="H1458" t="n">
         <v>95012</v>
@@ -42738,7 +42738,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1461" t="n">
-        <v>10.4452972412109</v>
+        <v>10.4452981948853</v>
       </c>
       <c r="H1461" t="n">
         <v>73880</v>
@@ -42767,7 +42767,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1462" t="n">
-        <v>10.4452972412109</v>
+        <v>10.4452981948853</v>
       </c>
       <c r="H1462" t="n">
         <v>63600</v>
@@ -42825,7 +42825,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1464" t="n">
-        <v>10.6373081207275</v>
+        <v>10.6373071670532</v>
       </c>
       <c r="H1464" t="n">
         <v>104012</v>
@@ -42912,7 +42912,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>11.136531829834</v>
+        <v>11.1365327835083</v>
       </c>
       <c r="H1467" t="n">
         <v>194373</v>
@@ -42941,7 +42941,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1468" t="n">
-        <v>11.1557321548462</v>
+        <v>11.1557331085205</v>
       </c>
       <c r="H1468" t="n">
         <v>131864</v>
@@ -42999,7 +42999,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1470" t="n">
-        <v>11.2517356872559</v>
+        <v>11.2517366409302</v>
       </c>
       <c r="H1470" t="n">
         <v>71816</v>
@@ -43115,7 +43115,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1474" t="n">
-        <v>11.4821472167969</v>
+        <v>11.4821481704712</v>
       </c>
       <c r="H1474" t="n">
         <v>310751</v>
@@ -43144,7 +43144,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1475" t="n">
-        <v>11.5397520065308</v>
+        <v>11.5397510528564</v>
       </c>
       <c r="H1475" t="n">
         <v>135084</v>
@@ -43173,7 +43173,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1476" t="n">
-        <v>11.7125577926636</v>
+        <v>11.7125587463379</v>
       </c>
       <c r="H1476" t="n">
         <v>120462</v>
@@ -43202,7 +43202,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1477" t="n">
-        <v>11.5781526565552</v>
+        <v>11.5781536102295</v>
       </c>
       <c r="H1477" t="n">
         <v>69164</v>
@@ -43231,7 +43231,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1478" t="n">
-        <v>11.3861436843872</v>
+        <v>11.3861427307129</v>
       </c>
       <c r="H1478" t="n">
         <v>67064</v>
@@ -43289,7 +43289,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1480" t="n">
-        <v>11.3477411270142</v>
+        <v>11.3477401733398</v>
       </c>
       <c r="H1480" t="n">
         <v>91808</v>
@@ -43318,7 +43318,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1481" t="n">
-        <v>11.1557321548462</v>
+        <v>11.1557331085205</v>
       </c>
       <c r="H1481" t="n">
         <v>89582</v>
@@ -43405,7 +43405,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1484" t="n">
-        <v>11.1557321548462</v>
+        <v>11.1557331085205</v>
       </c>
       <c r="H1484" t="n">
         <v>31229</v>
@@ -43492,7 +43492,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>11.136531829834</v>
+        <v>11.1365327835083</v>
       </c>
       <c r="H1487" t="n">
         <v>75136</v>
@@ -43724,7 +43724,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1495" t="n">
-        <v>11.2901382446289</v>
+        <v>11.2901391983032</v>
       </c>
       <c r="H1495" t="n">
         <v>53448</v>
@@ -43840,7 +43840,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1499" t="n">
-        <v>10.8485174179077</v>
+        <v>10.848518371582</v>
       </c>
       <c r="H1499" t="n">
         <v>46771</v>
@@ -43869,7 +43869,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1500" t="n">
-        <v>10.7333135604858</v>
+        <v>10.7333126068115</v>
       </c>
       <c r="H1500" t="n">
         <v>55918</v>
@@ -43985,7 +43985,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1504" t="n">
-        <v>10.6373081207275</v>
+        <v>10.6373071670532</v>
       </c>
       <c r="H1504" t="n">
         <v>50745</v>
@@ -44043,7 +44043,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1506" t="n">
-        <v>10.8485174179077</v>
+        <v>10.848518371582</v>
       </c>
       <c r="H1506" t="n">
         <v>61272</v>
@@ -44101,7 +44101,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1508" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1508" t="n">
         <v>54764</v>
@@ -44188,7 +44188,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1511" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1511" t="n">
         <v>13067</v>
@@ -44217,7 +44217,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1512" t="n">
-        <v>10.9829235076904</v>
+        <v>10.9829244613647</v>
       </c>
       <c r="H1512" t="n">
         <v>16957</v>
@@ -44246,7 +44246,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1513" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1513" t="n">
         <v>42298</v>
@@ -44391,7 +44391,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1518" t="n">
-        <v>10.8485174179077</v>
+        <v>10.848518371582</v>
       </c>
       <c r="H1518" t="n">
         <v>107258</v>
@@ -44536,7 +44536,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1523" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1523" t="n">
         <v>21178</v>
@@ -44565,7 +44565,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1524" t="n">
-        <v>11.136531829834</v>
+        <v>11.1365327835083</v>
       </c>
       <c r="H1524" t="n">
         <v>16811</v>
@@ -44594,7 +44594,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1525" t="n">
-        <v>10.9253215789795</v>
+        <v>10.9253206253052</v>
       </c>
       <c r="H1525" t="n">
         <v>38419</v>
@@ -44739,7 +44739,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1530" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1530" t="n">
         <v>147807</v>
@@ -44826,7 +44826,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1533" t="n">
-        <v>10.9253215789795</v>
+        <v>10.9253206253052</v>
       </c>
       <c r="H1533" t="n">
         <v>71087</v>
@@ -44913,7 +44913,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>11.136531829834</v>
+        <v>11.1365327835083</v>
       </c>
       <c r="H1536" t="n">
         <v>116843</v>
@@ -45029,7 +45029,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1540" t="n">
-        <v>11.2901382446289</v>
+        <v>11.2901391983032</v>
       </c>
       <c r="H1540" t="n">
         <v>240254</v>
@@ -45087,7 +45087,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>10.4837007522583</v>
+        <v>10.483699798584</v>
       </c>
       <c r="H1542" t="n">
         <v>186364</v>
@@ -45145,7 +45145,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1544" t="n">
-        <v>10.2532901763916</v>
+        <v>10.2532892227173</v>
       </c>
       <c r="H1544" t="n">
         <v>90528</v>
@@ -45203,7 +45203,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1546" t="n">
-        <v>10.1956872940063</v>
+        <v>10.195686340332</v>
       </c>
       <c r="H1546" t="n">
         <v>44577</v>
@@ -45377,7 +45377,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1552" t="n">
-        <v>10.0612802505493</v>
+        <v>10.061279296875</v>
       </c>
       <c r="H1552" t="n">
         <v>22193</v>
@@ -45406,7 +45406,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1553" t="n">
-        <v>10.0612802505493</v>
+        <v>10.061279296875</v>
       </c>
       <c r="H1553" t="n">
         <v>79841</v>
@@ -45435,7 +45435,7 @@
         <v>10.5</v>
       </c>
       <c r="G1554" t="n">
-        <v>10.0804805755615</v>
+        <v>10.0804815292358</v>
       </c>
       <c r="H1554" t="n">
         <v>58920</v>
@@ -45464,7 +45464,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1555" t="n">
-        <v>10.2148885726929</v>
+        <v>10.2148876190186</v>
       </c>
       <c r="H1555" t="n">
         <v>60815</v>
@@ -45522,7 +45522,7 @@
         <v>10.5</v>
       </c>
       <c r="G1557" t="n">
-        <v>10.0804805755615</v>
+        <v>10.0804815292358</v>
       </c>
       <c r="H1557" t="n">
         <v>129375</v>
@@ -45551,7 +45551,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1558" t="n">
-        <v>10.1188831329346</v>
+        <v>10.1188821792603</v>
       </c>
       <c r="H1558" t="n">
         <v>51017</v>
@@ -45580,7 +45580,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1559" t="n">
-        <v>10.2148885726929</v>
+        <v>10.2148876190186</v>
       </c>
       <c r="H1559" t="n">
         <v>44542</v>
@@ -45609,7 +45609,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1560" t="n">
-        <v>10.2532901763916</v>
+        <v>10.2532892227173</v>
       </c>
       <c r="H1560" t="n">
         <v>96272</v>
@@ -45638,7 +45638,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1561" t="n">
-        <v>10.1956872940063</v>
+        <v>10.195686340332</v>
       </c>
       <c r="H1561" t="n">
         <v>32083</v>
@@ -45754,7 +45754,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1565" t="n">
-        <v>10.1188831329346</v>
+        <v>10.1188821792603</v>
       </c>
       <c r="H1565" t="n">
         <v>115183</v>
@@ -45899,7 +45899,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1570" t="n">
-        <v>10.3876943588257</v>
+        <v>10.3876953125</v>
       </c>
       <c r="H1570" t="n">
         <v>53478</v>
@@ -45928,7 +45928,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1571" t="n">
-        <v>10.1956872940063</v>
+        <v>10.195686340332</v>
       </c>
       <c r="H1571" t="n">
         <v>123999</v>
@@ -45957,7 +45957,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.0996828079224</v>
+        <v>10.099681854248</v>
       </c>
       <c r="H1572" t="n">
         <v>137218</v>
@@ -46160,7 +46160,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1579" t="n">
-        <v>9.40844821929932</v>
+        <v>9.40844917297363</v>
       </c>
       <c r="H1579" t="n">
         <v>267344</v>
@@ -46189,7 +46189,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1580" t="n">
-        <v>9.18763732910156</v>
+        <v>9.18763828277588</v>
       </c>
       <c r="H1580" t="n">
         <v>96581</v>
@@ -46218,7 +46218,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1581" t="n">
-        <v>9.31244468688965</v>
+        <v>9.31244564056396</v>
       </c>
       <c r="H1581" t="n">
         <v>71124</v>
@@ -46247,7 +46247,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1582" t="n">
-        <v>9.35084629058838</v>
+        <v>9.35084533691406</v>
       </c>
       <c r="H1582" t="n">
         <v>67376</v>
@@ -46305,7 +46305,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1584" t="n">
-        <v>9.63885974884033</v>
+        <v>9.63885879516602</v>
       </c>
       <c r="H1584" t="n">
         <v>54032</v>
@@ -46334,7 +46334,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.67726230621338</v>
+        <v>9.67726135253906</v>
       </c>
       <c r="H1585" t="n">
         <v>63603</v>
@@ -46479,7 +46479,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1590" t="n">
-        <v>10.2148885726929</v>
+        <v>10.2148876190186</v>
       </c>
       <c r="H1590" t="n">
         <v>90941</v>
@@ -46566,7 +46566,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1593" t="n">
-        <v>10.0420799255371</v>
+        <v>10.0420789718628</v>
       </c>
       <c r="H1593" t="n">
         <v>97917</v>
@@ -46624,7 +46624,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1595" t="n">
-        <v>11.0597286224365</v>
+        <v>11.0597276687622</v>
       </c>
       <c r="H1595" t="n">
         <v>217040</v>
@@ -46711,7 +46711,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>11.4245443344116</v>
+        <v>11.4245452880859</v>
       </c>
       <c r="H1598" t="n">
         <v>165793</v>
@@ -46769,7 +46769,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1600" t="n">
-        <v>11.2901382446289</v>
+        <v>11.2901391983032</v>
       </c>
       <c r="H1600" t="n">
         <v>118634</v>
@@ -46798,7 +46798,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1601" t="n">
-        <v>10.8677177429199</v>
+        <v>10.8677186965942</v>
       </c>
       <c r="H1601" t="n">
         <v>43780</v>
@@ -46827,7 +46827,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1602" t="n">
-        <v>10.7333135604858</v>
+        <v>10.7333126068115</v>
       </c>
       <c r="H1602" t="n">
         <v>27587</v>
@@ -46856,7 +46856,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1603" t="n">
-        <v>10.5029010772705</v>
+        <v>10.5029001235962</v>
       </c>
       <c r="H1603" t="n">
         <v>34725</v>
@@ -46885,7 +46885,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1604" t="n">
-        <v>10.4837007522583</v>
+        <v>10.483699798584</v>
       </c>
       <c r="H1604" t="n">
         <v>35975</v>
@@ -46972,7 +46972,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1607" t="n">
-        <v>10.5029010772705</v>
+        <v>10.5029001235962</v>
       </c>
       <c r="H1607" t="n">
         <v>32660</v>
@@ -47030,7 +47030,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>10.8485174179077</v>
+        <v>10.848518371582</v>
       </c>
       <c r="H1609" t="n">
         <v>26724</v>
@@ -47059,7 +47059,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1610" t="n">
-        <v>10.8677177429199</v>
+        <v>10.8677186965942</v>
       </c>
       <c r="H1610" t="n">
         <v>33936</v>
@@ -47088,7 +47088,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1611" t="n">
-        <v>11.1557321548462</v>
+        <v>11.1557331085205</v>
       </c>
       <c r="H1611" t="n">
         <v>45935</v>
@@ -47146,7 +47146,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1613" t="n">
-        <v>10.9829235076904</v>
+        <v>10.9829244613647</v>
       </c>
       <c r="H1613" t="n">
         <v>31157</v>
@@ -47262,7 +47262,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1617" t="n">
-        <v>10.7324533462524</v>
+        <v>10.7324523925781</v>
       </c>
       <c r="H1617" t="n">
         <v>18266</v>
@@ -47813,7 +47813,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1636" t="n">
-        <v>11.35462474823</v>
+        <v>11.3546237945557</v>
       </c>
       <c r="H1636" t="n">
         <v>15276</v>
@@ -47900,7 +47900,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1639" t="n">
-        <v>10.8491106033325</v>
+        <v>10.8491096496582</v>
       </c>
       <c r="H1639" t="n">
         <v>26009</v>
@@ -48045,7 +48045,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1644" t="n">
-        <v>10.1491670608521</v>
+        <v>10.1491661071777</v>
       </c>
       <c r="H1644" t="n">
         <v>33078</v>
@@ -48074,7 +48074,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1645" t="n">
-        <v>10.1491670608521</v>
+        <v>10.1491661071777</v>
       </c>
       <c r="H1645" t="n">
         <v>13197</v>
@@ -48132,7 +48132,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1647" t="n">
-        <v>9.95473861694336</v>
+        <v>9.95473766326904</v>
       </c>
       <c r="H1647" t="n">
         <v>23059</v>
@@ -48190,7 +48190,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1649" t="n">
-        <v>10.2463817596436</v>
+        <v>10.2463808059692</v>
       </c>
       <c r="H1649" t="n">
         <v>23928</v>
@@ -48277,7 +48277,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1652" t="n">
-        <v>10.4991388320923</v>
+        <v>10.4991397857666</v>
       </c>
       <c r="H1652" t="n">
         <v>21518</v>
@@ -48451,7 +48451,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1658" t="n">
-        <v>11.0046520233154</v>
+        <v>11.0046529769897</v>
       </c>
       <c r="H1658" t="n">
         <v>57891</v>
@@ -48480,7 +48480,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1659" t="n">
-        <v>10.8685531616211</v>
+        <v>10.8685522079468</v>
       </c>
       <c r="H1659" t="n">
         <v>15199</v>
@@ -48596,7 +48596,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1663" t="n">
-        <v>10.8491106033325</v>
+        <v>10.8491096496582</v>
       </c>
       <c r="H1663" t="n">
         <v>20701</v>
@@ -48741,7 +48741,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1668" t="n">
-        <v>10.8491106033325</v>
+        <v>10.8491096496582</v>
       </c>
       <c r="H1668" t="n">
         <v>18463</v>
@@ -49089,7 +49089,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>11.7823657989502</v>
+        <v>11.7823667526245</v>
       </c>
       <c r="H1680" t="n">
         <v>55832</v>
@@ -49263,7 +49263,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1686" t="n">
-        <v>12.8517227172852</v>
+        <v>12.8517236709595</v>
       </c>
       <c r="H1686" t="n">
         <v>131047</v>
@@ -49292,7 +49292,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1687" t="n">
-        <v>12.871166229248</v>
+        <v>12.8711671829224</v>
       </c>
       <c r="H1687" t="n">
         <v>71788</v>
@@ -49350,7 +49350,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1689" t="n">
-        <v>13.0267086029053</v>
+        <v>13.0267095565796</v>
       </c>
       <c r="H1689" t="n">
         <v>152721</v>
@@ -49379,7 +49379,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1690" t="n">
-        <v>13.3961229324341</v>
+        <v>13.3961219787598</v>
       </c>
       <c r="H1690" t="n">
         <v>199874</v>
@@ -49408,7 +49408,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1691" t="n">
-        <v>13.66832447052</v>
+        <v>13.6683235168457</v>
       </c>
       <c r="H1691" t="n">
         <v>185704</v>
@@ -49611,7 +49611,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1698" t="n">
-        <v>13.2016944885254</v>
+        <v>13.2016935348511</v>
       </c>
       <c r="H1698" t="n">
         <v>52119</v>
@@ -49640,7 +49640,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1699" t="n">
-        <v>12.8322801589966</v>
+        <v>12.8322811126709</v>
       </c>
       <c r="H1699" t="n">
         <v>72591</v>
@@ -49698,7 +49698,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1701" t="n">
-        <v>12.3656511306763</v>
+        <v>12.3656520843506</v>
       </c>
       <c r="H1701" t="n">
         <v>53487</v>
@@ -49785,7 +49785,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1704" t="n">
-        <v>10.3241519927979</v>
+        <v>10.3241529464722</v>
       </c>
       <c r="H1704" t="n">
         <v>603788</v>
@@ -49901,7 +49901,7 @@
         <v>10</v>
       </c>
       <c r="G1708" t="n">
-        <v>9.7214241027832</v>
+        <v>9.72142505645752</v>
       </c>
       <c r="H1708" t="n">
         <v>200862</v>
@@ -49988,7 +49988,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1711" t="n">
-        <v>9.85752582550049</v>
+        <v>9.85752487182617</v>
       </c>
       <c r="H1711" t="n">
         <v>71749</v>
@@ -50075,7 +50075,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1714" t="n">
-        <v>8.96315288543701</v>
+        <v>8.96315383911133</v>
       </c>
       <c r="H1714" t="n">
         <v>83919</v>
@@ -50133,7 +50133,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1716" t="n">
-        <v>8.93398952484131</v>
+        <v>8.93398857116699</v>
       </c>
       <c r="H1716" t="n">
         <v>59974</v>
@@ -50162,7 +50162,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1717" t="n">
-        <v>8.87566089630127</v>
+        <v>8.87566184997559</v>
       </c>
       <c r="H1717" t="n">
         <v>50522</v>
@@ -50191,7 +50191,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1718" t="n">
-        <v>8.93398952484131</v>
+        <v>8.93398857116699</v>
       </c>
       <c r="H1718" t="n">
         <v>36638</v>
@@ -50278,7 +50278,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1721" t="n">
-        <v>9.25479602813721</v>
+        <v>9.25479698181152</v>
       </c>
       <c r="H1721" t="n">
         <v>56362</v>
@@ -50307,7 +50307,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1722" t="n">
-        <v>9.2256326675415</v>
+        <v>9.22563171386719</v>
       </c>
       <c r="H1722" t="n">
         <v>36261</v>
@@ -50365,7 +50365,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1724" t="n">
-        <v>8.89510250091553</v>
+        <v>8.89510345458984</v>
       </c>
       <c r="H1724" t="n">
         <v>33394</v>
@@ -50394,7 +50394,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1725" t="n">
-        <v>8.94371032714844</v>
+        <v>8.94371128082275</v>
       </c>
       <c r="H1725" t="n">
         <v>24396</v>
@@ -50626,7 +50626,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1733" t="n">
-        <v>10.3047103881836</v>
+        <v>10.3047113418579</v>
       </c>
       <c r="H1733" t="n">
         <v>55123</v>
@@ -50655,7 +50655,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1734" t="n">
-        <v>10.4991388320923</v>
+        <v>10.4991397857666</v>
       </c>
       <c r="H1734" t="n">
         <v>72642</v>
@@ -50771,7 +50771,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1738" t="n">
-        <v>10.7907810211182</v>
+        <v>10.7907819747925</v>
       </c>
       <c r="H1738" t="n">
         <v>42661</v>
@@ -50800,7 +50800,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>10.9852094650269</v>
+        <v>10.9852104187012</v>
       </c>
       <c r="H1739" t="n">
         <v>24687</v>
@@ -50829,7 +50829,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1740" t="n">
-        <v>10.7907810211182</v>
+        <v>10.7907819747925</v>
       </c>
       <c r="H1740" t="n">
         <v>31483</v>
@@ -50916,7 +50916,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1743" t="n">
-        <v>10.4408102035522</v>
+        <v>10.4408092498779</v>
       </c>
       <c r="H1743" t="n">
         <v>42234</v>
@@ -51032,7 +51032,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1747" t="n">
-        <v>10.3241519927979</v>
+        <v>10.3241529464722</v>
       </c>
       <c r="H1747" t="n">
         <v>53550</v>
@@ -51119,7 +51119,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1750" t="n">
-        <v>10.0908393859863</v>
+        <v>10.090838432312</v>
       </c>
       <c r="H1750" t="n">
         <v>36591</v>
@@ -51148,7 +51148,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1751" t="n">
-        <v>10.1491670608521</v>
+        <v>10.1491661071777</v>
       </c>
       <c r="H1751" t="n">
         <v>28799</v>
@@ -51177,7 +51177,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1752" t="n">
-        <v>10.0130672454834</v>
+        <v>10.0130681991577</v>
       </c>
       <c r="H1752" t="n">
         <v>20483</v>
@@ -51206,7 +51206,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1753" t="n">
-        <v>10.1491670608521</v>
+        <v>10.1491661071777</v>
       </c>
       <c r="H1753" t="n">
         <v>26172</v>
@@ -51235,7 +51235,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1754" t="n">
-        <v>10.3047103881836</v>
+        <v>10.3047113418579</v>
       </c>
       <c r="H1754" t="n">
         <v>126089</v>
@@ -51264,7 +51264,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1755" t="n">
-        <v>10.3435974121094</v>
+        <v>10.3435964584351</v>
       </c>
       <c r="H1755" t="n">
         <v>48917</v>
@@ -51293,7 +51293,7 @@
         <v>10.5</v>
       </c>
       <c r="G1756" t="n">
-        <v>10.2074956893921</v>
+        <v>10.2074966430664</v>
       </c>
       <c r="H1756" t="n">
         <v>51053</v>
@@ -51438,7 +51438,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1761" t="n">
-        <v>10.8685531616211</v>
+        <v>10.8685522079468</v>
       </c>
       <c r="H1761" t="n">
         <v>199301</v>
@@ -51496,7 +51496,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1763" t="n">
-        <v>11.082423210144</v>
+        <v>11.0824241638184</v>
       </c>
       <c r="H1763" t="n">
         <v>35180</v>
@@ -51583,7 +51583,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1766" t="n">
-        <v>10.4991388320923</v>
+        <v>10.4991397857666</v>
       </c>
       <c r="H1766" t="n">
         <v>35015</v>
@@ -51641,7 +51641,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1768" t="n">
-        <v>10.6352386474609</v>
+        <v>10.6352376937866</v>
       </c>
       <c r="H1768" t="n">
         <v>28942</v>
@@ -51728,7 +51728,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1771" t="n">
-        <v>10.6352386474609</v>
+        <v>10.6352376937866</v>
       </c>
       <c r="H1771" t="n">
         <v>19958</v>
@@ -51757,7 +51757,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1772" t="n">
-        <v>10.5185804367065</v>
+        <v>10.5185813903809</v>
       </c>
       <c r="H1772" t="n">
         <v>24007</v>
@@ -51786,7 +51786,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1773" t="n">
-        <v>10.3047103881836</v>
+        <v>10.3047113418579</v>
       </c>
       <c r="H1773" t="n">
         <v>73925</v>
@@ -51815,7 +51815,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1774" t="n">
-        <v>10.3435974121094</v>
+        <v>10.3435964584351</v>
       </c>
       <c r="H1774" t="n">
         <v>23373</v>
@@ -51873,7 +51873,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1776" t="n">
-        <v>9.3034029006958</v>
+        <v>9.30340385437012</v>
       </c>
       <c r="H1776" t="n">
         <v>521578</v>
@@ -51989,7 +51989,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1780" t="n">
-        <v>9.25479602813721</v>
+        <v>9.25479698181152</v>
       </c>
       <c r="H1780" t="n">
         <v>145725</v>
@@ -52018,7 +52018,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1781" t="n">
-        <v>9.42978191375732</v>
+        <v>9.42978286743164</v>
       </c>
       <c r="H1781" t="n">
         <v>69026</v>
@@ -52047,7 +52047,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1782" t="n">
-        <v>9.3034029006958</v>
+        <v>9.30340385437012</v>
       </c>
       <c r="H1782" t="n">
         <v>23196</v>
@@ -52192,7 +52192,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1787" t="n">
-        <v>10.3824825286865</v>
+        <v>10.3824815750122</v>
       </c>
       <c r="H1787" t="n">
         <v>85816</v>
@@ -52221,7 +52221,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1788" t="n">
-        <v>10.0908393859863</v>
+        <v>10.090838432312</v>
       </c>
       <c r="H1788" t="n">
         <v>138820</v>
@@ -52279,7 +52279,7 @@
         <v>10</v>
       </c>
       <c r="G1790" t="n">
-        <v>9.7214241027832</v>
+        <v>9.72142505645752</v>
       </c>
       <c r="H1790" t="n">
         <v>118773</v>
@@ -52308,7 +52308,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G1791" t="n">
-        <v>9.71170425415039</v>
+        <v>9.71170330047607</v>
       </c>
       <c r="H1791" t="n">
         <v>143118</v>
@@ -52337,7 +52337,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1792" t="n">
-        <v>9.74086761474609</v>
+        <v>9.74086856842041</v>
       </c>
       <c r="H1792" t="n">
         <v>80897</v>
@@ -52366,7 +52366,7 @@
         <v>10</v>
       </c>
       <c r="G1793" t="n">
-        <v>9.7214241027832</v>
+        <v>9.72142505645752</v>
       </c>
       <c r="H1793" t="n">
         <v>58089</v>
@@ -52424,7 +52424,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1795" t="n">
-        <v>9.65337467193604</v>
+        <v>9.65337562561035</v>
       </c>
       <c r="H1795" t="n">
         <v>74613</v>
@@ -52453,7 +52453,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1796" t="n">
-        <v>9.52699565887451</v>
+        <v>9.52699661254883</v>
       </c>
       <c r="H1796" t="n">
         <v>111306</v>
@@ -52540,7 +52540,7 @@
         <v>10</v>
       </c>
       <c r="G1799" t="n">
-        <v>9.7214241027832</v>
+        <v>9.72142505645752</v>
       </c>
       <c r="H1799" t="n">
         <v>69584</v>
@@ -52598,7 +52598,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1801" t="n">
-        <v>9.74086761474609</v>
+        <v>9.74086856842041</v>
       </c>
       <c r="H1801" t="n">
         <v>39572</v>
@@ -52656,7 +52656,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1803" t="n">
-        <v>9.65337467193604</v>
+        <v>9.65337562561035</v>
       </c>
       <c r="H1803" t="n">
         <v>38798</v>
@@ -52685,7 +52685,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1804" t="n">
-        <v>9.66309642791748</v>
+        <v>9.66309547424316</v>
       </c>
       <c r="H1804" t="n">
         <v>38384</v>
@@ -52772,7 +52772,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>9.74086761474609</v>
+        <v>9.74086856842041</v>
       </c>
       <c r="H1807" t="n">
         <v>29616</v>
@@ -52801,7 +52801,7 @@
         <v>10</v>
       </c>
       <c r="G1808" t="n">
-        <v>9.7214241027832</v>
+        <v>9.72142505645752</v>
       </c>
       <c r="H1808" t="n">
         <v>30385</v>
@@ -52859,7 +52859,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G1810" t="n">
-        <v>9.71170425415039</v>
+        <v>9.71170330047607</v>
       </c>
       <c r="H1810" t="n">
         <v>29942</v>
@@ -52946,7 +52946,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1813" t="n">
-        <v>9.85752582550049</v>
+        <v>9.85752487182617</v>
       </c>
       <c r="H1813" t="n">
         <v>93454</v>
@@ -52975,7 +52975,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1814" t="n">
-        <v>9.76031017303467</v>
+        <v>9.76030921936035</v>
       </c>
       <c r="H1814" t="n">
         <v>19792</v>
@@ -53091,7 +53091,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1818" t="n">
-        <v>9.85752582550049</v>
+        <v>9.85752487182617</v>
       </c>
       <c r="H1818" t="n">
         <v>29451</v>
@@ -53120,7 +53120,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1819" t="n">
-        <v>9.74086761474609</v>
+        <v>9.74086856842041</v>
       </c>
       <c r="H1819" t="n">
         <v>23091</v>
@@ -53236,7 +53236,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1823" t="n">
-        <v>10.0130672454834</v>
+        <v>10.0130681991577</v>
       </c>
       <c r="H1823" t="n">
         <v>15839</v>
@@ -53323,7 +53323,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1826" t="n">
-        <v>9.95473861694336</v>
+        <v>9.95473766326904</v>
       </c>
       <c r="H1826" t="n">
         <v>15415</v>
@@ -53352,7 +53352,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1827" t="n">
-        <v>9.85752582550049</v>
+        <v>9.85752487182617</v>
       </c>
       <c r="H1827" t="n">
         <v>17689</v>
@@ -53439,7 +53439,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1830" t="n">
-        <v>9.76031017303467</v>
+        <v>9.76030921936035</v>
       </c>
       <c r="H1830" t="n">
         <v>25818</v>
@@ -53468,7 +53468,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1831" t="n">
-        <v>9.74086761474609</v>
+        <v>9.74086856842041</v>
       </c>
       <c r="H1831" t="n">
         <v>23400</v>
@@ -53497,7 +53497,7 @@
         <v>10</v>
       </c>
       <c r="G1832" t="n">
-        <v>9.7214241027832</v>
+        <v>9.72142505645752</v>
       </c>
       <c r="H1832" t="n">
         <v>18625</v>
@@ -53526,7 +53526,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1833" t="n">
-        <v>9.56588268280029</v>
+        <v>9.56588172912598</v>
       </c>
       <c r="H1833" t="n">
         <v>56613</v>
@@ -53555,7 +53555,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1834" t="n">
-        <v>9.76031017303467</v>
+        <v>9.76030921936035</v>
       </c>
       <c r="H1834" t="n">
         <v>72061</v>
@@ -53787,7 +53787,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1842" t="n">
-        <v>8.96315288543701</v>
+        <v>8.96315383911133</v>
       </c>
       <c r="H1842" t="n">
         <v>28064</v>
@@ -53816,7 +53816,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1843" t="n">
-        <v>8.9825963973999</v>
+        <v>8.98259544372559</v>
       </c>
       <c r="H1843" t="n">
         <v>10510</v>
@@ -53845,7 +53845,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1844" t="n">
-        <v>9.07981204986572</v>
+        <v>9.07981109619141</v>
       </c>
       <c r="H1844" t="n">
         <v>13956</v>
@@ -53874,7 +53874,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1845" t="n">
-        <v>9.16730308532715</v>
+        <v>9.16730403900146</v>
       </c>
       <c r="H1845" t="n">
         <v>15500</v>
@@ -53961,7 +53961,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1848" t="n">
-        <v>9.16730308532715</v>
+        <v>9.16730403900146</v>
       </c>
       <c r="H1848" t="n">
         <v>22868</v>
@@ -54019,7 +54019,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1850" t="n">
-        <v>8.94371032714844</v>
+        <v>8.94371128082275</v>
       </c>
       <c r="H1850" t="n">
         <v>22139</v>
@@ -54135,7 +54135,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.94371032714844</v>
+        <v>8.94371128082275</v>
       </c>
       <c r="H1854" t="n">
         <v>22499</v>
@@ -54222,7 +54222,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1857" t="n">
-        <v>8.93398952484131</v>
+        <v>8.93398857116699</v>
       </c>
       <c r="H1857" t="n">
         <v>131738</v>
@@ -54454,7 +54454,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1865" t="n">
-        <v>8.93398952484131</v>
+        <v>8.93398857116699</v>
       </c>
       <c r="H1865" t="n">
         <v>14541</v>
@@ -54599,7 +54599,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1870" t="n">
-        <v>9.16730308532715</v>
+        <v>9.16730403900146</v>
       </c>
       <c r="H1870" t="n">
         <v>89308</v>
@@ -54657,7 +54657,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1872" t="n">
-        <v>9.43950366973877</v>
+        <v>9.43950271606445</v>
       </c>
       <c r="H1872" t="n">
         <v>127191</v>
@@ -54686,7 +54686,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1873" t="n">
-        <v>9.3714542388916</v>
+        <v>9.37145328521729</v>
       </c>
       <c r="H1873" t="n">
         <v>57072</v>
@@ -54744,7 +54744,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1875" t="n">
-        <v>9.43950366973877</v>
+        <v>9.43950271606445</v>
       </c>
       <c r="H1875" t="n">
         <v>19011</v>
@@ -54802,7 +54802,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G1877" t="n">
-        <v>9.71170425415039</v>
+        <v>9.71170330047607</v>
       </c>
       <c r="H1877" t="n">
         <v>58600</v>
@@ -54831,7 +54831,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1878" t="n">
-        <v>9.66309642791748</v>
+        <v>9.66309547424316</v>
       </c>
       <c r="H1878" t="n">
         <v>24758</v>
@@ -54889,7 +54889,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1880" t="n">
-        <v>9.85752582550049</v>
+        <v>9.85752487182617</v>
       </c>
       <c r="H1880" t="n">
         <v>49158</v>
@@ -54918,7 +54918,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1881" t="n">
-        <v>9.95473861694336</v>
+        <v>9.95473766326904</v>
       </c>
       <c r="H1881" t="n">
         <v>67274</v>
@@ -55005,7 +55005,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1884" t="n">
-        <v>9.56588268280029</v>
+        <v>9.56588172912598</v>
       </c>
       <c r="H1884" t="n">
         <v>105929</v>
@@ -55034,7 +55034,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1885" t="n">
-        <v>9.3714542388916</v>
+        <v>9.37145328521729</v>
       </c>
       <c r="H1885" t="n">
         <v>28452</v>
@@ -55179,7 +55179,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1890" t="n">
-        <v>9.3034029006958</v>
+        <v>9.30340385437012</v>
       </c>
       <c r="H1890" t="n">
         <v>27903</v>
@@ -55208,7 +55208,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1891" t="n">
-        <v>9.3034029006958</v>
+        <v>9.30340385437012</v>
       </c>
       <c r="H1891" t="n">
         <v>17800</v>
@@ -55266,7 +55266,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1893" t="n">
-        <v>9.3714542388916</v>
+        <v>9.37145328521729</v>
       </c>
       <c r="H1893" t="n">
         <v>25236</v>
@@ -55382,7 +55382,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1897" t="n">
-        <v>9.3034029006958</v>
+        <v>9.30340385437012</v>
       </c>
       <c r="H1897" t="n">
         <v>28121</v>
@@ -55411,7 +55411,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1898" t="n">
-        <v>9.24507522583008</v>
+        <v>9.24507427215576</v>
       </c>
       <c r="H1898" t="n">
         <v>39451</v>
@@ -55498,7 +55498,7 @@
         <v>9.5</v>
       </c>
       <c r="G1901" t="n">
-        <v>9.23535346984863</v>
+        <v>9.23535442352295</v>
       </c>
       <c r="H1901" t="n">
         <v>21277</v>
@@ -55585,7 +55585,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1904" t="n">
-        <v>9.25479602813721</v>
+        <v>9.25479698181152</v>
       </c>
       <c r="H1904" t="n">
         <v>9147</v>
@@ -55614,7 +55614,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1905" t="n">
-        <v>9.07981204986572</v>
+        <v>9.07981109619141</v>
       </c>
       <c r="H1905" t="n">
         <v>23021</v>
@@ -55672,7 +55672,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1907" t="n">
-        <v>8.87566089630127</v>
+        <v>8.87566184997559</v>
       </c>
       <c r="H1907" t="n">
         <v>26124</v>
@@ -55788,7 +55788,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1911" t="n">
-        <v>8.9825963973999</v>
+        <v>8.98259544372559</v>
       </c>
       <c r="H1911" t="n">
         <v>18727</v>
@@ -56020,7 +56020,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1919" t="n">
-        <v>8.88538265228271</v>
+        <v>8.8853816986084</v>
       </c>
       <c r="H1919" t="n">
         <v>24147</v>
@@ -56310,7 +56310,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1929" t="n">
-        <v>8.76872444152832</v>
+        <v>8.76872539520264</v>
       </c>
       <c r="H1929" t="n">
         <v>17261</v>
@@ -56658,7 +56658,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1941" t="n">
-        <v>8.88538265228271</v>
+        <v>8.8853816986084</v>
       </c>
       <c r="H1941" t="n">
         <v>32707</v>
@@ -56832,7 +56832,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1947" t="n">
-        <v>8.9825963973999</v>
+        <v>8.98259544372559</v>
       </c>
       <c r="H1947" t="n">
         <v>42580</v>
@@ -56861,7 +56861,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1948" t="n">
-        <v>8.89510250091553</v>
+        <v>8.89510345458984</v>
       </c>
       <c r="H1948" t="n">
         <v>8301</v>
@@ -56919,7 +56919,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1950" t="n">
-        <v>9.07981204986572</v>
+        <v>9.07981109619141</v>
       </c>
       <c r="H1950" t="n">
         <v>22179</v>
@@ -57064,7 +57064,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1955" t="n">
-        <v>8.58401775360107</v>
+        <v>8.58401870727539</v>
       </c>
       <c r="H1955" t="n">
         <v>38742</v>
@@ -57093,7 +57093,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1956" t="n">
-        <v>8.59374046325684</v>
+        <v>8.59373950958252</v>
       </c>
       <c r="H1956" t="n">
         <v>42934</v>
@@ -57151,7 +57151,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1958" t="n">
-        <v>8.44791793823242</v>
+        <v>8.44791698455811</v>
       </c>
       <c r="H1958" t="n">
         <v>24174</v>
@@ -57180,7 +57180,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1959" t="n">
-        <v>8.59374046325684</v>
+        <v>8.59373950958252</v>
       </c>
       <c r="H1959" t="n">
         <v>71960</v>
@@ -57238,7 +57238,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1961" t="n">
-        <v>8.94371032714844</v>
+        <v>8.94371128082275</v>
       </c>
       <c r="H1961" t="n">
         <v>42305</v>
@@ -57267,7 +57267,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1962" t="n">
-        <v>8.9534330368042</v>
+        <v>8.95343208312988</v>
       </c>
       <c r="H1962" t="n">
         <v>38971</v>
@@ -57296,7 +57296,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1963" t="n">
-        <v>8.75900459289551</v>
+        <v>8.75900363922119</v>
       </c>
       <c r="H1963" t="n">
         <v>67310</v>
@@ -57325,7 +57325,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1964" t="n">
-        <v>8.58401775360107</v>
+        <v>8.58401870727539</v>
       </c>
       <c r="H1964" t="n">
         <v>35149</v>
@@ -57354,7 +57354,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1965" t="n">
-        <v>8.59374046325684</v>
+        <v>8.59373950958252</v>
       </c>
       <c r="H1965" t="n">
         <v>27049</v>
@@ -57383,7 +57383,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1966" t="n">
-        <v>8.58401775360107</v>
+        <v>8.58401870727539</v>
       </c>
       <c r="H1966" t="n">
         <v>58634</v>
@@ -57470,7 +57470,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1969" t="n">
-        <v>7.97156763076782</v>
+        <v>7.97156858444214</v>
       </c>
       <c r="H1969" t="n">
         <v>119542</v>
@@ -57499,7 +57499,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1970" t="n">
-        <v>7.85491132736206</v>
+        <v>7.8549108505249</v>
       </c>
       <c r="H1970" t="n">
         <v>50894</v>
@@ -57528,7 +57528,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1971" t="n">
-        <v>7.78686141967773</v>
+        <v>7.78686094284058</v>
       </c>
       <c r="H1971" t="n">
         <v>43427</v>
@@ -57644,7 +57644,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G1975" t="n">
-        <v>7.61187553405762</v>
+        <v>7.61187505722046</v>
       </c>
       <c r="H1975" t="n">
         <v>56941</v>
@@ -57760,7 +57760,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1979" t="n">
-        <v>7.42716836929321</v>
+        <v>7.42716884613037</v>
       </c>
       <c r="H1979" t="n">
         <v>184321</v>
@@ -57876,7 +57876,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1983" t="n">
-        <v>7.22301864624023</v>
+        <v>7.22301816940308</v>
       </c>
       <c r="H1983" t="n">
         <v>45933</v>
@@ -57905,7 +57905,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1984" t="n">
-        <v>7.19385385513306</v>
+        <v>7.19385433197021</v>
       </c>
       <c r="H1984" t="n">
         <v>18544</v>
@@ -57963,7 +57963,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1986" t="n">
-        <v>7.10636186599731</v>
+        <v>7.10636138916016</v>
       </c>
       <c r="H1986" t="n">
         <v>55639</v>
@@ -58021,7 +58021,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1988" t="n">
-        <v>6.96054029464722</v>
+        <v>6.96053981781006</v>
       </c>
       <c r="H1988" t="n">
         <v>47460</v>
@@ -58050,7 +58050,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1989" t="n">
-        <v>6.98970460891724</v>
+        <v>6.98970413208008</v>
       </c>
       <c r="H1989" t="n">
         <v>36339</v>
@@ -58340,7 +58340,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1999" t="n">
-        <v>7.4368896484375</v>
+        <v>7.43689012527466</v>
       </c>
       <c r="H1999" t="n">
         <v>108567</v>
@@ -58369,7 +58369,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2000" t="n">
-        <v>7.32995367050171</v>
+        <v>7.32995414733887</v>
       </c>
       <c r="H2000" t="n">
         <v>162987</v>
@@ -58398,7 +58398,7 @@
         <v>7.5</v>
       </c>
       <c r="G2001" t="n">
-        <v>7.2910680770874</v>
+        <v>7.29106855392456</v>
       </c>
       <c r="H2001" t="n">
         <v>53341</v>
@@ -58427,7 +58427,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2002" t="n">
-        <v>7.30079030990601</v>
+        <v>7.30078983306885</v>
       </c>
       <c r="H2002" t="n">
         <v>42394</v>
@@ -58456,7 +58456,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2003" t="n">
-        <v>7.30079030990601</v>
+        <v>7.30078983306885</v>
       </c>
       <c r="H2003" t="n">
         <v>52481</v>
@@ -58659,7 +58659,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2010" t="n">
-        <v>7.52438259124756</v>
+        <v>7.52438306808472</v>
       </c>
       <c r="H2010" t="n">
         <v>30264</v>
@@ -58688,7 +58688,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2011" t="n">
-        <v>7.57298946380615</v>
+        <v>7.57298994064331</v>
       </c>
       <c r="H2011" t="n">
         <v>35602</v>
@@ -58891,7 +58891,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G2018" t="n">
-        <v>7.28134679794312</v>
+        <v>7.28134727478027</v>
       </c>
       <c r="H2018" t="n">
         <v>46058</v>
@@ -58920,7 +58920,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G2019" t="n">
-        <v>7.28134679794312</v>
+        <v>7.28134727478027</v>
       </c>
       <c r="H2019" t="n">
         <v>64630</v>
@@ -58978,7 +58978,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G2021" t="n">
-        <v>7.4952187538147</v>
+        <v>7.49521827697754</v>
       </c>
       <c r="H2021" t="n">
         <v>88007</v>
@@ -59065,7 +59065,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2024" t="n">
-        <v>7.46605443954468</v>
+        <v>7.46605396270752</v>
       </c>
       <c r="H2024" t="n">
         <v>74935</v>
@@ -59094,7 +59094,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G2025" t="n">
-        <v>7.4952187538147</v>
+        <v>7.49521827697754</v>
       </c>
       <c r="H2025" t="n">
         <v>85349</v>
@@ -59123,7 +59123,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2026" t="n">
-        <v>7.52438259124756</v>
+        <v>7.52438306808472</v>
       </c>
       <c r="H2026" t="n">
         <v>54279</v>
@@ -59210,7 +59210,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G2029" t="n">
-        <v>7.6702036857605</v>
+        <v>7.67020416259766</v>
       </c>
       <c r="H2029" t="n">
         <v>77224</v>
@@ -59239,7 +59239,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2030" t="n">
-        <v>7.67992544174194</v>
+        <v>7.6799259185791</v>
       </c>
       <c r="H2030" t="n">
         <v>32894</v>
@@ -59471,7 +59471,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G2038" t="n">
-        <v>8.17571830749512</v>
+        <v>8.1757173538208</v>
       </c>
       <c r="H2038" t="n">
         <v>75202</v>
@@ -59500,7 +59500,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2039" t="n">
-        <v>8.44791793823242</v>
+        <v>8.44791698455811</v>
       </c>
       <c r="H2039" t="n">
         <v>108346</v>
@@ -59645,7 +59645,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2044" t="n">
-        <v>8.45763874053955</v>
+        <v>8.45763969421387</v>
       </c>
       <c r="H2044" t="n">
         <v>166440</v>
@@ -59674,7 +59674,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G2045" t="n">
-        <v>8.46736145019531</v>
+        <v>8.467360496521</v>
       </c>
       <c r="H2045" t="n">
         <v>68088</v>
@@ -59732,7 +59732,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2047" t="n">
-        <v>8.38958930969238</v>
+        <v>8.3895902633667</v>
       </c>
       <c r="H2047" t="n">
         <v>57598</v>
@@ -59819,7 +59819,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2050" t="n">
-        <v>8.30209732055664</v>
+        <v>8.30209636688232</v>
       </c>
       <c r="H2050" t="n">
         <v>50120</v>
@@ -59964,7 +59964,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G2055" t="n">
-        <v>8.17571830749512</v>
+        <v>8.1757173538208</v>
       </c>
       <c r="H2055" t="n">
         <v>23950</v>
@@ -59993,7 +59993,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2056" t="n">
-        <v>8.02989673614502</v>
+        <v>8.02989768981934</v>
       </c>
       <c r="H2056" t="n">
         <v>41606</v>
@@ -60109,7 +60109,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2060" t="n">
-        <v>8.28265380859375</v>
+        <v>8.28265476226807</v>
       </c>
       <c r="H2060" t="n">
         <v>76613</v>
@@ -60283,7 +60283,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2066" t="n">
-        <v>8.27293300628662</v>
+        <v>8.2729320526123</v>
       </c>
       <c r="H2066" t="n">
         <v>28338</v>
@@ -60341,7 +60341,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2068" t="n">
-        <v>8.40903091430664</v>
+        <v>8.40903186798096</v>
       </c>
       <c r="H2068" t="n">
         <v>61362</v>
@@ -60399,7 +60399,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2070" t="n">
-        <v>8.58401775360107</v>
+        <v>8.58401870727539</v>
       </c>
       <c r="H2070" t="n">
         <v>75873</v>
@@ -60573,7 +60573,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2076" t="n">
-        <v>8.58401775360107</v>
+        <v>8.58401870727539</v>
       </c>
       <c r="H2076" t="n">
         <v>114056</v>
@@ -60689,7 +60689,7 @@
         <v>9.5</v>
       </c>
       <c r="G2080" t="n">
-        <v>9.23535346984863</v>
+        <v>9.23535442352295</v>
       </c>
       <c r="H2080" t="n">
         <v>212417</v>
@@ -60863,7 +60863,7 @@
         <v>9</v>
       </c>
       <c r="G2086" t="n">
-        <v>8.74928188323975</v>
+        <v>8.74928283691406</v>
       </c>
       <c r="H2086" t="n">
         <v>56700</v>
@@ -60892,7 +60892,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G2087" t="n">
-        <v>8.87566089630127</v>
+        <v>8.87566184997559</v>
       </c>
       <c r="H2087" t="n">
         <v>43995</v>
@@ -61124,7 +61124,7 @@
         <v>9.5</v>
       </c>
       <c r="G2095" t="n">
-        <v>9.23535346984863</v>
+        <v>9.23535442352295</v>
       </c>
       <c r="H2095" t="n">
         <v>75873</v>
@@ -61414,7 +61414,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2105" t="n">
-        <v>9.74086761474609</v>
+        <v>9.74086856842041</v>
       </c>
       <c r="H2105" t="n">
         <v>82235</v>
@@ -61559,7 +61559,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2110" t="n">
-        <v>10.0908393859863</v>
+        <v>10.090838432312</v>
       </c>
       <c r="H2110" t="n">
         <v>123269</v>
@@ -61617,7 +61617,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2112" t="n">
-        <v>10.9852094650269</v>
+        <v>10.9852104187012</v>
       </c>
       <c r="H2112" t="n">
         <v>426596</v>
@@ -61646,7 +61646,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2113" t="n">
-        <v>10.5185804367065</v>
+        <v>10.5185813903809</v>
       </c>
       <c r="H2113" t="n">
         <v>161514</v>
@@ -61733,7 +61733,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2116" t="n">
-        <v>10.7324533462524</v>
+        <v>10.7324523925781</v>
       </c>
       <c r="H2116" t="n">
         <v>119961</v>
@@ -61762,7 +61762,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2117" t="n">
-        <v>10.5185804367065</v>
+        <v>10.5185813903809</v>
       </c>
       <c r="H2117" t="n">
         <v>67614</v>
@@ -80052,7 +80052,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="D2748" t="n">
-        <v>30.7199993133545</v>
+        <v>30.7299995422363</v>
       </c>
       <c r="E2748" t="n">
         <v>29.5499992370605</v>
@@ -80067,6 +80067,35 @@
         <v>1017819</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>30.1000003814697</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>30.7399997711182</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>29.9699993133545</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>30.6299991607666</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>30.6299991607666</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>751094</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>
